--- a/reports/Carolinas_Job_Growth_Running_Database.xlsx
+++ b/reports/Carolinas_Job_Growth_Running_Database.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Week of 2026-09-07  ·  Window 2026-03-07 to 2026-09-07  ·  NC + SC</t>
+          <t>Week of 2026-09-14  ·  Window 2026-03-14 to 2026-09-14  ·  NC + SC</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07  (Week 8)</t>
+          <t>2026-09-14  (Week 9)</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-03-07 to 2026-09-07  (trailing 6 months)</t>
+          <t>2026-03-14 to 2026-09-14  (trailing 6 months)</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>84</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>52</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Charlotte / Uptown (Mecklenburg, NC) — SMBC Group, score 93 (unchanged, seventh consecutive quiet cycle)</t>
+          <t>Charlotte / Uptown (Mecklenburg, NC) — SMBC Group, score 93 (unchanged, eighth consecutive quiet cycle)</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>No score changes this cycle — all 11 Ranked entries repeated at unchanged scores. The most material dated developments were resolving the Scout Motors HQ (Charlotte) second-building filing date to 2026-03-28 (confirming it stays safely inside the shifted window) and reconfirming Scout Motors' Blythewood, SC EV-plant production progress (900+ robots installed, first welded body test) via the company's own June/July updates.</t>
+          <t>Scout Motors' Blythewood, SC EV assembly plant (83 -&gt; 85) on a newly announced $300M Supplier Park (~1,000 more jobs, total SC commitment now $2.3B+); JetZero (Greensboro) held flat at 81 despite a genuinely mixed cycle — construction broke ground on its NC Composite Center (NC3) building with $133.9M in new dedicated state funding, but the company confirmed a roughly one-year hiring-ramp delay (JDIG timeline-amendment request; ~0 new jobs expected in 2027 vs. 1,050 planned) tied to state-budget-funding holdups.</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>A quiet cycle for new Ranked-tier finds — all five regional research passes found zero new 500+ job / $100k+ wage qualifying announcements — but an active cycle for Watch-tier and negative/closed signals. Most significant: VinFast's Chatham County litigation reached a Sept. 2, 2026 response deadline (outcome not yet known); Six Flags Entertainment confirmed it is relocating its corporate HQ OUT of Charlotte to Arlington, TX (114 jobs, negative signal) after a $203M Q2 2026 net loss; Lowe's executed ~600 corporate layoffs (Mooresville/Charlotte) and Family Dollar closed its Matthews distribution center (373 layoffs) — both negative signals. On the Watch tier, NorthMark/Valara's Spartanburg data-center litigation remains genuinely unresolved (SELC's injunction motion still pending despite an Aug. 5 hearing) with two new public hearings scheduled (county fact-finding 9/9, state legislative session 9/14) ahead of the Sept. 21 moratorium vote; the NC Utilities Commission fast-tracked a transmission line for Vulcan Elements' Benson magnet factory citing national-security justification; AWS/Amazon's Hamlet campus held its Sept. 1 resident open house (outcome unreported); and AssetMark (Charlotte, 252 jobs, $110,518 stated wage — now fully verified) and Walmart's Gaston County fulfillment center (300+ jobs, $69,360 stated wage — now fully verified) were both confirmed to have their only dated milestone more than a year outside the current window, moving them to Excluded. Two promising 'sleeper' leads — Daimler Truck Financial Services USA (Charlotte, 276 jobs) and a Fidelity Investments Triangle-area pledge (620 jobs) — could not be fully verified this cycle and are flagged for follow-up rather than promoted.</t>
+          <t>A second consecutive quiet cycle for brand-new Ranked-tier finds (all five regional research passes found zero new 500+ job / $100k+ wage qualifying announcements), but an unusually active cycle for material updates within existing Ranked/Watch entries and for litigation/regulatory resolution. Most significant: the SC Public Service Commission ruled unanimously that NorthMark/Valara's Spartanburg data center is NOT subject to Utility Siting Act power-plant rules (a loss for SELC and other opponents), though SELC's separate Circuit Court injunction motion remains unresolved and Spartanburg County's moratorium 3rd reading (set for Sept. 21) is expected to grandfather the project regardless of outcome. VinFast met its Sept. 2 litigation deadline with an 80-page response denying breach, while Chatham County separately finalized termination of its own $400M incentive agreement with the company (July 31). Two new negative signals were identified: Thermo Fisher Scientific's phased closure of its Weaverville, NC facility (421 jobs) and Prepac Manufacturing's Whitsett, NC plant closure (~200 jobs, fully in-window). Daimler Truck Financial Services USA (Charlotte, 276 jobs, $133,940 stated wage) was fully verified but confirmed pre-window; a previously tracked Fidelity Investments 'lead' was debunked as stale 2023 data and dropped. EnerSys's Greenville, SC lithium-cell project was found to have materially restructured (defense-focused pivot, $150M DOE grant, up to $200M in incentives) and was moved from Excluded to Watch pending a disclosed headcount for the revised, smaller-scope project.</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>All five regions (Charlotte metro, NC Triangle, NC Triad/WNC/Coastal, Upstate SC, SC Midlands/Lowcountry) received a full research pass this cycle via parallel dedicated research agents, plus a targeted follow-up pass by the report compiler to resolve the Scout Motors HQ filing date, the VinFast litigation deadline, and the SELC injunction status. WebFetch (direct page retrieval) again returned blocked/EGRESS_BLOCKED for essentially every news/gov domain attempted across all agents; every finding below relies on WebSearch-result content/snippets, which do surface real, retrievable source URLs, cross-checked across multiple independent queries. Each region's WebSearch budget was exhausted before every conceivable follow-up query could be run — gaps are flagged per-item in the Watch tier and Excluded/Noise sections (e.g., the Wolfspeed WARN-notice total, the WakeMed/Atrium Sept. 8 BOC agenda, the Wake County EDGE7 pipeline-size discrepancy). No numbers were invented; 'Not disclosed' marks missing figures and 'Estimated/Inferred' marks derived ones with basis stated.</t>
+          <t>All five regions (Charlotte metro, NC Triangle, NC Triad/WNC/Coastal, Upstate SC, SC Midlands/Lowcountry) received a full research pass this cycle via parallel dedicated research agents. WebFetch (direct page retrieval) again returned blocked/EGRESS_BLOCKED for essentially every news/gov domain attempted across all agents; every finding below relies on WebSearch-result content/snippets, which do surface real, retrievable source URLs, cross-checked across multiple independent queries. Each region's WebSearch budget (200 calls) was exhausted before every conceivable follow-up query could be run this cycle — gaps are flagged per-item in the Watch tier and Excluded/Noise sections (e.g., a possible dating discrepancy on the Wolfspeed WARN notice, the AWS/Amazon Hamlet Sept. 1 open-house outcome, the Wake County EDGE7 pipeline-size discrepancy, and a not-yet-confirmed Redwood Materials startup lead). No numbers were invented; 'Not disclosed' marks missing figures and 'Estimated/Inferred' marks derived ones with basis stated.</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Trailing 6 months now runs 2026-03-07 to 2026-09-07 — the window advanced one week, moving several Watch-tier items' sole dated milestone (Ralliant Corp 2026-03-05, Environmental Air Systems 2025-11-25, Ahold Delhaize's 2026-02-16 groundbreaking) just outside the window; each is flagged 'at risk' in the Watch tier rather than dropped outright, consistent with this report's standing-item convention (as used for Google's Berkeley/Dorchester data center and Redwood Materials, now in their 6th consecutive quiet cycle).</t>
+          <t>Trailing 6 months now runs 2026-03-14 to 2026-09-14 — the window advanced one week. No currently Ranked entry's sole milestone fell out of window this cycle. In the Watch tier, Ralliant Corp. (2026-03-05) remains flagged 'at risk' as it now sits further before the window start; a new dating concern surfaced for Wolfspeed's tracked WARN notice, which multiple sources this cycle date to June 9, 2025 (not 2026) — if correct, its sole Watch-qualifying milestone is more than a year outside the window and it is now flagged 'at risk' pending a direct WARN-database check next cycle.</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>AssetMark (Charlotte, 252 jobs) and Walmart's Gaston County fulfillment center (300+ jobs) both had their wage figures fully verified this cycle ($110,518 and $69,360 respectively, both stated not inferred) but their only dated milestones (2025-07-08 and 2025-09-30) sit more than a year outside the current window — moved from unverified leads to Excluded/Noise with the reason changed from 'unverified' to 'verified but pre-window.' Scout Motors HQ's (Charlotte/Plaza Midwood) second-building filing date is now confirmed as 2026-03-28 (Hoodline), resolving last cycle's ambiguity and confirming the milestone sits safely inside the shifted window. AMAROK's (Columbia, SC) two candidate dates were reconciled: the Richland County Council incentive approval (2026-03-03) is technically pre-window, but the substantive public HQ announcement (2026-03-24) is not, so the item stays qualifying.</t>
+          <t>Daimler Truck Financial Services USA (Charlotte, 276 jobs) was fully verified this cycle ($133,940 avg wage, stated — clears the $100k bar; $7.8M capex) but its only dated milestone (2025-05-27) sits over a year outside the current window — moved from an unverified lead to Excluded/Noise as 'verified but pre-window,' consistent with the AssetMark/Walmart precedent from prior cycles. The previously tracked Fidelity Investments 'Triangle-area 620 jobs' lead was traced to a 2023 article and is not a 2026 event at all — dropped from tracking rather than carried forward as unverified. EnerSys's Greenville, SC lithium-cell project (previously an Excluded 'sleeper') announced a material scope restructuring (defense/aerospace pivot, capacity cut from ~4-5 GWh to ~1 GWh, $150M DOE grant, up to $200M in state/local incentives) on 2026-07-23; because the revised project's job count was not disclosed in any source found, it was moved to Markets to Watch rather than promoted to Ranked, and its stale ~500-job 2024 figure was not carried forward.</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>All 11 prior-ranked deals repeat this cycle at unchanged scores (0 new, 0 updated, 0 removed) — the first fully quiet Ranked cycle since the report's inception. Watch tier: 0 new items added, 0 formally removed, but AssetMark and Walmart Gaston Co. moved from unverified Excluded leads to verified-but-pre-window Excluded entries; NorthMark/Valara, WakeMed/Atrium, Vulcan Elements, AWS/Amazon Hamlet, AMAROK, and AIRSYS all received material or clarifying updates. Four new negative/closed signals were logged in Excluded/Noise this cycle: VinFast's Sept. 2 litigation deadline, Six Flags' HQ departure from Charlotte, Lowe's corporate layoffs (~600), and Family Dollar's Matthews distribution-center closure (373).</t>
+          <t>10 of 11 prior-ranked deals repeat this cycle at unchanged scores; Scout Motors' Blythewood EV plant rises 83 -&gt; 85 (Gaining Momentum) on its new $300M Supplier Park; JetZero is tagged Updated (net score unchanged at 81) reflecting its mixed groundbreaking-plus-hiring-delay cycle. 0 new Ranked-tier finds, 0 removed. Watch tier: 2 new items added (Wilmington Trade Center Expansion; EnerSys Greenville, moved from Excluded), 0 formally removed, but Wolfspeed and Environmental Air Systems are both flagged for likely removal/further at-risk status next cycle absent a fresh in-window milestone. Six new Excluded/Noise entries were logged this cycle: an updated VinFast litigation entry, Daimler Truck Financial Services USA (verified-but-pre-window), the debunked Fidelity Investments lead, two new negative signals (Thermo Fisher Weaverville, Prepac Whitsett), a new TD Bank Ballantyne unverified lead, and a Bank of America/Wells Fargo AI-headcount background note.</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S74"/>
+  <dimension ref="A1:S85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7461,6 +7461,1007 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Uptown</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group — 2nd US HQ / bank operations</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>Office / HQ banking</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>$165,316 avg (stated; vs county $90,706)</t>
+        </is>
+      </c>
+      <c r="K75" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L75" s="6" t="inlineStr">
+        <is>
+          <t>$50.5M</t>
+        </is>
+      </c>
+      <c r="M75" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $70.0M / 12 yr; $23.3M IDF-Utility Account</t>
+        </is>
+      </c>
+      <c r="N75" s="6" t="inlineStr">
+        <is>
+          <t>Lease signed / active hiring milestone (unchanged)</t>
+        </is>
+      </c>
+      <c r="O75" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="P75" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/05/04/smbc-headquarters-wells-fargo-center-uptown</t>
+        </is>
+      </c>
+      <c r="Q75" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R75" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="S75" s="6" t="inlineStr">
+        <is>
+          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill / York Co.</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>Office/HQ + biopharma mfg</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>$141,502 avg HQ / $102,752 avg mfg (both stated)</t>
+        </is>
+      </c>
+      <c r="K76" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L76" s="6" t="inlineStr">
+        <is>
+          <t>$1.5B</t>
+        </is>
+      </c>
+      <c r="M76" s="6" t="inlineStr">
+        <is>
+          <t>Fee-in-lieu-of-tax; $65M SC Coordinating Council Closing Fund grant to York Co.</t>
+        </is>
+      </c>
+      <c r="N76" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone (unchanged)</t>
+        </is>
+      </c>
+      <c r="O76" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="P76" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/york-county/news/octapharma-how-company-chose-rock-hill/article_b1518265-129d-4134-9ff9-f2d686950bd6.html</t>
+        </is>
+      </c>
+      <c r="Q76" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R76" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S76" s="6" t="inlineStr">
+        <is>
+          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C77" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Durham / RTP</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie — biopharma manufacturing campus</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="n">
+        <v>734</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / R&amp;D / lab</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>$118,041 avg (stated; vs county $102,817)</t>
+        </is>
+      </c>
+      <c r="K77" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L77" s="6" t="inlineStr">
+        <is>
+          <t>$1.4B</t>
+        </is>
+      </c>
+      <c r="M77" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $19.3M / 12 yr; $6.4M IDF-Utility; +city/county; Durham Co. performance-based award confirmed not-to-exceed $15,450,000 ("Project Glass")</t>
+        </is>
+      </c>
+      <c r="N77" s="6" t="inlineStr">
+        <is>
+          <t>Local incentive package confirmed (unchanged)</t>
+        </is>
+      </c>
+      <c r="O77" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="P77" s="6" t="inlineStr">
+        <is>
+          <t>https://www.einpresswire.com/article/926805248/board-of-county-commissioners-regular-session-highlights-from-july-13</t>
+        </is>
+      </c>
+      <c r="Q77" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R77" s="6" t="inlineStr">
+        <is>
+          <t>Suburban-urban</t>
+        </is>
+      </c>
+      <c r="S77" s="6" t="inlineStr">
+        <is>
+          <t>High-end MF + move-up for-sale around Durham/RTP; spillover Wake/Orange. Construction-phase rental near-term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Blythewood / N. Columbia</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV assembly plant + new Supplier Park</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>Auto mfg + salaried eng.</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>$30-$37.50/hr line (stated); salaried higher</t>
+        </is>
+      </c>
+      <c r="K78" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mix supports above-median HH income</t>
+        </is>
+      </c>
+      <c r="L78" s="6" t="inlineStr">
+        <is>
+          <t>$2.3B+ (site $2.0B + $25M training center + new $300M Supplier Park)</t>
+        </is>
+      </c>
+      <c r="M78" s="6" t="inlineStr">
+        <is>
+          <t>State/local package (2023); $25M readySC; Aug. 17 veto clears $150M cost-overrun payment (STILL not confirmed disbursed; SC Legislative Audit Council report due ~mid-Dec. 2026)</t>
+        </is>
+      </c>
+      <c r="N78" s="6" t="inlineStr">
+        <is>
+          <t>New $300M Supplier Park investment announced; production construction continues</t>
+        </is>
+      </c>
+      <c r="O78" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="P78" s="6" t="inlineStr">
+        <is>
+          <t>https://blog.scoutmotors.com/july-2026-scout-motors-production-center-update/</t>
+        </is>
+      </c>
+      <c r="Q78" s="6" t="inlineStr">
+        <is>
+          <t>Medium (facts); Low (headcount/timeline)</t>
+        </is>
+      </c>
+      <c r="R78" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S78" s="6" t="inlineStr">
+        <is>
+          <t>Bifurcated: salaried/professional -&gt; higher-income for-sale &amp; Class-A; hourly base + new supplier-park jobs -&gt; workforce/missing-middle rental in N. Richland/Fairfield. New Supplier Park adds ~1,000 more jobs to the local labor-demand base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C79" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs / SW Wake</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>Genentech — biomanufacturing expansion (unchanged)</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>~$119,833 avg (stated, 2025 tranche)</t>
+        </is>
+      </c>
+      <c r="K79" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L79" s="6" t="inlineStr">
+        <is>
+          <t>~$2.0B</t>
+        </is>
+      </c>
+      <c r="M79" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
+        </is>
+      </c>
+      <c r="N79" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="O79" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="P79" s="6" t="inlineStr">
+        <is>
+          <t>https://www.biospace.com/press-releases/genentech-marks-topping-out-milestone-for-new-holly-springs-north-carolina-manufacturing-facility</t>
+        </is>
+      </c>
+      <c r="Q79" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R79" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S79" s="6" t="inlineStr">
+        <is>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake; topping-out milestone continues to de-risk the 2029 hiring ramp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C80" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group — East Coast operations hub</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>Office — finance/tech</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>$194,141 avg (stated; NC Commerce JDIG figure)</t>
+        </is>
+      </c>
+      <c r="K80" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L80" s="6" t="inlineStr">
+        <is>
+          <t>$60M</t>
+        </is>
+      </c>
+      <c r="M80" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $17.2M / 12 yr; $5.7M IDF-Utility; new detail: $19.4M state grant over 12 yr + $2.2M community-college training funds + $1M combined city/county incentive</t>
+        </is>
+      </c>
+      <c r="N80" s="6" t="inlineStr">
+        <is>
+          <t>New facility / operations hub (unchanged)</t>
+        </is>
+      </c>
+      <c r="O80" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="P80" s="6" t="inlineStr">
+        <is>
+          <t>https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
+        </is>
+      </c>
+      <c r="Q80" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R80" s="6" t="inlineStr">
+        <is>
+          <t>Urban-suburban</t>
+        </is>
+      </c>
+      <c r="S80" s="6" t="inlineStr">
+        <is>
+          <t>High-skill eng/data workforce -&gt; walkable South End/Uptown &amp; inner-suburban Class-A and for-sale TH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C81" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>JetZero — aerospace plant (groundbreaking confirmed; hiring ramp delayed ~1 yr)</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace mfg + eng.</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>$89,340 avg (stated, 2025)</t>
+        </is>
+      </c>
+      <c r="K81" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated (2025)</t>
+        </is>
+      </c>
+      <c r="L81" s="6" t="inlineStr">
+        <is>
+          <t>$4.7B</t>
+        </is>
+      </c>
+      <c r="M81" s="6" t="inlineStr">
+        <is>
+          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr; new: $133.9M allocated in NC FY26-27 budget (signed 2026-07-07) for land acquisition + access-road/taxiway site prep</t>
+        </is>
+      </c>
+      <c r="N81" s="6" t="inlineStr">
+        <is>
+          <t>Construction start confirmed; JDIG hiring-schedule amendment requested</t>
+        </is>
+      </c>
+      <c r="O81" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="P81" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2026/06/15/governor-stein-celebrates-jetzero-groundbreaking-launch-greensboro-airplane-makers-14500-job-project</t>
+        </is>
+      </c>
+      <c r="Q81" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Low (current hiring-ramp timeline)</t>
+        </is>
+      </c>
+      <c r="R81" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S81" s="6" t="inlineStr">
+        <is>
+          <t>Same long-run scale, but the confirmed ~1-year hiring-ramp delay pushes the bulk of housing-demand impact further out; physical construction starting is a genuine de-risking offset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C82" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Plaza Midwood</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — Global HQ (2nd office building filed)</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>Corporate HQ / professional</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>$153,978 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K82" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L82" s="6" t="inlineStr">
+        <is>
+          <t>$206.9M</t>
+        </is>
+      </c>
+      <c r="M82" s="6" t="inlineStr">
+        <is>
+          <t>Original 2025-11-12 HQ incentive/relocation commitment</t>
+        </is>
+      </c>
+      <c r="N82" s="6" t="inlineStr">
+        <is>
+          <t>Preliminary land-development plan filed for 2nd office building (unchanged)</t>
+        </is>
+      </c>
+      <c r="O82" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="P82" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/scout-motors-hq-move-turbocharges-second-office-building-in-plaza-midwood/</t>
+        </is>
+      </c>
+      <c r="Q82" s="6" t="inlineStr">
+        <is>
+          <t>Med (facts High; milestone stage early)</t>
+        </is>
+      </c>
+      <c r="R82" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="S82" s="6" t="inlineStr">
+        <is>
+          <t>Supports Plaza Midwood/NoDa/Elizabeth close-in rental and townhome demand from a young, high-wage corporate workforce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C83" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Ballantyne</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>Citigroup — Charlotte office (grand opening)</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="n">
+        <v>510</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>Office / financial services</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>$131,832 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K83" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L83" s="6" t="inlineStr">
+        <is>
+          <t>$16.1M</t>
+        </is>
+      </c>
+      <c r="M83" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $8.9M / 10 yr</t>
+        </is>
+      </c>
+      <c r="N83" s="6" t="inlineStr">
+        <is>
+          <t>Facility grand opening</t>
+        </is>
+      </c>
+      <c r="O83" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="P83" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2026/03/16/governor-stein-celebrates-grand-opening-citi-charlotte-office</t>
+        </is>
+      </c>
+      <c r="Q83" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R83" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S83" s="6" t="inlineStr">
+        <is>
+          <t>$131,832 stated wage clears the $100k bar; supports Class-A rental and for-sale townhome demand in south Mecklenburg's Ballantyne/Blakeney/Rea Farms corridor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C84" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>Durham / Morrisville</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>Durham &amp; Wake</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>Novartis — API mfg building (unchanged)</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>$111,161 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K84" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L84" s="6" t="inlineStr">
+        <is>
+          <t>~$991M (incl. $220M API building)</t>
+        </is>
+      </c>
+      <c r="M84" s="6" t="inlineStr">
+        <is>
+          <t>Part of original $771M package incentives</t>
+        </is>
+      </c>
+      <c r="N84" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="O84" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="P84" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
+        </is>
+      </c>
+      <c r="Q84" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R84" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S84" s="6" t="inlineStr">
+        <is>
+          <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C85" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>Aspida Financial Services — HQ expansion (unchanged)</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>Office — financial services/insurance</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>$137,288 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K85" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L85" s="6" t="inlineStr">
+        <is>
+          <t>$28M+ (incl. $10M Imperial Tower renovation)</t>
+        </is>
+      </c>
+      <c r="M85" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="N85" s="6" t="inlineStr">
+        <is>
+          <t>Lease executed; building renovation still not confirmed complete</t>
+        </is>
+      </c>
+      <c r="O85" s="6" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="P85" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/imperial-tower-roars-back-as-10-million-durham-revival/</t>
+        </is>
+      </c>
+      <c r="Q85" s="6" t="inlineStr">
+        <is>
+          <t>Medium (facts High; move-in date not yet company-confirmed)</t>
+        </is>
+      </c>
+      <c r="R85" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="S85" s="6" t="inlineStr">
+        <is>
+          <t>1,000 high-wage financial-services jobs concentrated in downtown Durham support Class-A urban rental and close-in for-sale demand.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7472,7 +8473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X74"/>
+  <dimension ref="A1:X85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16091,6 +17092,1282 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Uptown</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group — 2nd US HQ / bank operations</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>Banking / financial services</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>Lease signed / active hiring milestone (unchanged)</t>
+        </is>
+      </c>
+      <c r="K75" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L75" s="6" t="inlineStr">
+        <is>
+          <t>Projected (6 yr)</t>
+        </is>
+      </c>
+      <c r="M75" s="6" t="inlineStr">
+        <is>
+          <t>$165,316 avg (stated; vs county $90,706)</t>
+        </is>
+      </c>
+      <c r="N75" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O75" s="6" t="inlineStr">
+        <is>
+          <t>$50.5M</t>
+        </is>
+      </c>
+      <c r="P75" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $70.0M / 12 yr; $23.3M IDF-Utility Account</t>
+        </is>
+      </c>
+      <c r="Q75" s="6" t="inlineStr">
+        <is>
+          <t>Leased former One Wells Fargo Center (301 South College St); move-in "as early as this fall" 2026 per Business NC</t>
+        </is>
+      </c>
+      <c r="R75" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="S75" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/05/04/smbc-headquarters-wells-fargo-center-uptown</t>
+        </is>
+      </c>
+      <c r="T75" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U75" s="6" t="inlineStr">
+        <is>
+          <t>Office / HQ banking</t>
+        </is>
+      </c>
+      <c r="V75" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="W75" s="6" t="inlineStr">
+        <is>
+          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth.</t>
+        </is>
+      </c>
+      <c r="X75" s="6" t="inlineStr">
+        <is>
+          <t>Eighth consecutive quiet cycle for a new milestone; lease and fall-2026 move-in timing reconfirmed via Business NC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill / York Co.</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>Biopharmaceutical (plasma fractionation)</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone (unchanged)</t>
+        </is>
+      </c>
+      <c r="K76" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L76" s="6" t="inlineStr">
+        <is>
+          <t>Projected (1,200 new + 300 relocated)</t>
+        </is>
+      </c>
+      <c r="M76" s="6" t="inlineStr">
+        <is>
+          <t>$141,502 avg HQ / $102,752 avg mfg (both stated)</t>
+        </is>
+      </c>
+      <c r="N76" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O76" s="6" t="inlineStr">
+        <is>
+          <t>$1.5B</t>
+        </is>
+      </c>
+      <c r="P76" s="6" t="inlineStr">
+        <is>
+          <t>Fee-in-lieu-of-tax; $65M SC Coordinating Council Closing Fund grant to York Co.</t>
+        </is>
+      </c>
+      <c r="Q76" s="6" t="inlineStr">
+        <is>
+          <t>50 acres purchased at Palmetto Research Park; construction slated to begin late 2026; production mid-2030s</t>
+        </is>
+      </c>
+      <c r="R76" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="S76" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/york-county/news/octapharma-how-company-chose-rock-hill/article_b1518265-129d-4134-9ff9-f2d686950bd6.html</t>
+        </is>
+      </c>
+      <c r="T76" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U76" s="6" t="inlineStr">
+        <is>
+          <t>Office/HQ + biopharma mfg</t>
+        </is>
+      </c>
+      <c r="V76" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W76" s="6" t="inlineStr">
+        <is>
+          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH.</t>
+        </is>
+      </c>
+      <c r="X76" s="6" t="inlineStr">
+        <is>
+          <t>No new dated milestone found this cycle; COO remarks and site-selection detail from the Aug. 19 SC I-77 Alliance summit reconfirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D77" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>Durham / RTP</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie — biopharma manufacturing campus</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>Biopharma / life sciences mfg</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>Local incentive package confirmed (unchanged)</t>
+        </is>
+      </c>
+      <c r="K77" s="6" t="n">
+        <v>734</v>
+      </c>
+      <c r="L77" s="6" t="inlineStr">
+        <is>
+          <t>Projected (+2,000 construction)</t>
+        </is>
+      </c>
+      <c r="M77" s="6" t="inlineStr">
+        <is>
+          <t>$118,041 avg (stated; vs county $102,817)</t>
+        </is>
+      </c>
+      <c r="N77" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O77" s="6" t="inlineStr">
+        <is>
+          <t>$1.4B</t>
+        </is>
+      </c>
+      <c r="P77" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $19.3M / 12 yr; $6.4M IDF-Utility; +city/county; Durham Co. performance-based award confirmed not-to-exceed $15,450,000 ("Project Glass")</t>
+        </is>
+      </c>
+      <c r="Q77" s="6" t="inlineStr">
+        <is>
+          <t>Construction 2026; complete ~end-2028; hiring through ~2031</t>
+        </is>
+      </c>
+      <c r="R77" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="S77" s="6" t="inlineStr">
+        <is>
+          <t>https://www.einpresswire.com/article/926805248/board-of-county-commissioners-regular-session-highlights-from-july-13</t>
+        </is>
+      </c>
+      <c r="T77" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U77" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / R&amp;D / lab</t>
+        </is>
+      </c>
+      <c r="V77" s="6" t="inlineStr">
+        <is>
+          <t>Suburban-urban</t>
+        </is>
+      </c>
+      <c r="W77" s="6" t="inlineStr">
+        <is>
+          <t>High-end MF + move-up for-sale around Durham/RTP; spillover Wake/Orange. Construction-phase rental near-term.</t>
+        </is>
+      </c>
+      <c r="X77" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found this cycle; incentive stack and 730-734 job figure (state vs. company sourcing variance) reconfirmed via WRAL/NC Governor coverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Gaining Momentum</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D78" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>Blythewood / N. Columbia</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV assembly plant + new Supplier Park</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>Automotive / EV manufacturing</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>New $300M Supplier Park investment announced; production construction continues</t>
+        </is>
+      </c>
+      <c r="K78" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L78" s="6" t="inlineStr">
+        <is>
+          <t>Projected (4,000-5,000 assembly + ~1,000 supplier-park; 600+ hired as of Apr 2026)</t>
+        </is>
+      </c>
+      <c r="M78" s="6" t="inlineStr">
+        <is>
+          <t>$30-$37.50/hr line (stated); salaried higher</t>
+        </is>
+      </c>
+      <c r="N78" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mix supports above-median HH income</t>
+        </is>
+      </c>
+      <c r="O78" s="6" t="inlineStr">
+        <is>
+          <t>$2.3B+ (site $2.0B + $25M training center + new $300M Supplier Park)</t>
+        </is>
+      </c>
+      <c r="P78" s="6" t="inlineStr">
+        <is>
+          <t>State/local package (2023); $25M readySC; Aug. 17 veto clears $150M cost-overrun payment (STILL not confirmed disbursed; SC Legislative Audit Council report due ~mid-Dec. 2026)</t>
+        </is>
+      </c>
+      <c r="Q78" s="6" t="inlineStr">
+        <is>
+          <t>Body Shop/Paint Shop/Supplier Park construction ongoing per July 2026 company blog update (published Aug. 6); first test vehicles still targeted off the line by end of 2026, customer shipments 2027</t>
+        </is>
+      </c>
+      <c r="R78" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="S78" s="6" t="inlineStr">
+        <is>
+          <t>https://blog.scoutmotors.com/july-2026-scout-motors-production-center-update/</t>
+        </is>
+      </c>
+      <c r="T78" s="6" t="inlineStr">
+        <is>
+          <t>Medium (facts); Low (headcount/timeline)</t>
+        </is>
+      </c>
+      <c r="U78" s="6" t="inlineStr">
+        <is>
+          <t>Auto mfg + salaried eng.</t>
+        </is>
+      </c>
+      <c r="V78" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W78" s="6" t="inlineStr">
+        <is>
+          <t>Bifurcated: salaried/professional -&gt; higher-income for-sale &amp; Class-A; hourly base + new supplier-park jobs -&gt; workforce/missing-middle rental in N. Richland/Fairfield. New Supplier Park adds ~1,000 more jobs to the local labor-demand base.</t>
+        </is>
+      </c>
+      <c r="X78" s="6" t="inlineStr">
+        <is>
+          <t>Material update: Scout announced an additional $300M Supplier Park investment (~1,000 more supplier jobs), pushing total SC commitment past $2.3B. The $150M state cost-overrun payment remains undisbursed pending either a legislative veto override or the Legislative Audit Council's report (due ~120 days after the FY26-27 budget was signed, i.e. ~mid-December 2026); ~$47.5M of the $150M has reportedly already been invoiced to contractors. The Shives family lawsuit (blasting/septic/stormwater damage claims, filed Aug. 7) remains pending with no ruling or new filing found. Score raised 83-&gt;85 to reflect the job-count and capital-investment increase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D79" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs / SW Wake</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>Genentech — biomanufacturing expansion (unchanged)</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="K79" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="L79" s="6" t="inlineStr">
+        <is>
+          <t>Projected (site total)</t>
+        </is>
+      </c>
+      <c r="M79" s="6" t="inlineStr">
+        <is>
+          <t>~$119,833 avg (stated, 2025 tranche)</t>
+        </is>
+      </c>
+      <c r="N79" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O79" s="6" t="inlineStr">
+        <is>
+          <t>~$2.0B</t>
+        </is>
+      </c>
+      <c r="P79" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
+        </is>
+      </c>
+      <c r="Q79" s="6" t="inlineStr">
+        <is>
+          <t>Topping-out ceremony held Aug. 2026; operational target 2029 unchanged</t>
+        </is>
+      </c>
+      <c r="R79" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="S79" s="6" t="inlineStr">
+        <is>
+          <t>https://www.biospace.com/press-releases/genentech-marks-topping-out-milestone-for-new-holly-springs-north-carolina-manufacturing-facility</t>
+        </is>
+      </c>
+      <c r="T79" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U79" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="V79" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W79" s="6" t="inlineStr">
+        <is>
+          <t>Strong higher-income for-sale + Class-A rental in fast-growing SW Wake; topping-out milestone continues to de-risk the 2029 hiring ramp.</t>
+        </is>
+      </c>
+      <c r="X79" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone found this cycle; topping-out detail and $2.0B total investment reconfirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D80" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group — East Coast operations hub</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>Investment mgmt / finance + tech</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>New facility / operations hub (unchanged)</t>
+        </is>
+      </c>
+      <c r="K80" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="L80" s="6" t="inlineStr">
+        <is>
+          <t>Projected</t>
+        </is>
+      </c>
+      <c r="M80" s="6" t="inlineStr">
+        <is>
+          <t>$194,141 avg (stated; NC Commerce JDIG figure)</t>
+        </is>
+      </c>
+      <c r="N80" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O80" s="6" t="inlineStr">
+        <is>
+          <t>$60M</t>
+        </is>
+      </c>
+      <c r="P80" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $17.2M / 12 yr; $5.7M IDF-Utility; new detail: $19.4M state grant over 12 yr + $2.2M community-college training funds + $1M combined city/county incentive</t>
+        </is>
+      </c>
+      <c r="Q80" s="6" t="inlineStr">
+        <is>
+          <t>16-yr lease (196,940 sf, One Independence Center); lease term began 2026-05-22, memorandum filed with Mecklenburg Co. 2026-05-26</t>
+        </is>
+      </c>
+      <c r="R80" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="S80" s="6" t="inlineStr">
+        <is>
+          <t>https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
+        </is>
+      </c>
+      <c r="T80" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U80" s="6" t="inlineStr">
+        <is>
+          <t>Office — finance/tech</t>
+        </is>
+      </c>
+      <c r="V80" s="6" t="inlineStr">
+        <is>
+          <t>Urban-suburban</t>
+        </is>
+      </c>
+      <c r="W80" s="6" t="inlineStr">
+        <is>
+          <t>High-skill eng/data workforce -&gt; walkable South End/Uptown &amp; inner-suburban Class-A and for-sale TH.</t>
+        </is>
+      </c>
+      <c r="X80" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found this cycle; lease term and a fuller incentive breakdown ($19.4M state + $2.2M workforce-training + $1M local) reconfirmed via CRE Direct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D81" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>JetZero — aerospace plant (groundbreaking confirmed; hiring ramp delayed ~1 yr)</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace / advanced manufacturing</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>Construction start confirmed; JDIG hiring-schedule amendment requested</t>
+        </is>
+      </c>
+      <c r="K81" s="6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="L81" s="6" t="inlineStr">
+        <is>
+          <t>Projected</t>
+        </is>
+      </c>
+      <c r="M81" s="6" t="inlineStr">
+        <is>
+          <t>$89,340 avg (stated, 2025)</t>
+        </is>
+      </c>
+      <c r="N81" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated (2025)</t>
+        </is>
+      </c>
+      <c r="O81" s="6" t="inlineStr">
+        <is>
+          <t>$4.7B</t>
+        </is>
+      </c>
+      <c r="P81" s="6" t="inlineStr">
+        <is>
+          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr; new: $133.9M allocated in NC FY26-27 budget (signed 2026-07-07) for land acquisition + access-road/taxiway site prep</t>
+        </is>
+      </c>
+      <c r="Q81" s="6" t="inlineStr">
+        <is>
+          <t>Groundbreaking held 2026-06-15 for the NC Composite Center (NC3), a 150,000 sf build-to-suit R&amp;D/mfg lab (HITT Contracting, GC); company requested a JDIG hiring-schedule amendment citing state-budget-funding delays — now expects ~0 new jobs in 2027 (vs. ~1,050 originally planned), with ramp resuming 2028-2029</t>
+        </is>
+      </c>
+      <c r="R81" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="S81" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2026/06/15/governor-stein-celebrates-jetzero-groundbreaking-launch-greensboro-airplane-makers-14500-job-project</t>
+        </is>
+      </c>
+      <c r="T81" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Low (current hiring-ramp timeline)</t>
+        </is>
+      </c>
+      <c r="U81" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace mfg + eng.</t>
+        </is>
+      </c>
+      <c r="V81" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W81" s="6" t="inlineStr">
+        <is>
+          <t>Same long-run scale, but the confirmed ~1-year hiring-ramp delay pushes the bulk of housing-demand impact further out; physical construction starting is a genuine de-risking offset.</t>
+        </is>
+      </c>
+      <c r="X81" s="6" t="inlineStr">
+        <is>
+          <t>Material, mixed-signal update: physical construction has now started (NC3 building groundbreaking, GC engaged, $133.9M in dedicated state funding flowing) — a real de-risking event — but JetZero itself confirmed a roughly one-year hiring-ramp delay tied to state-budget-funding holdups, formalized via a JDIG timeline-amendment request. Net effect on score judged a wash; tagged Updated rather than Repeated given the substantive new facts on both sides.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D82" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Plaza Midwood</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — Global HQ (2nd office building filed)</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>Automotive (EV) — corporate HQ</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>Preliminary land-development plan filed for 2nd office building (unchanged)</t>
+        </is>
+      </c>
+      <c r="K82" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L82" s="6" t="inlineStr">
+        <is>
+          <t>Projected (365 relocating + 835 new local hires)</t>
+        </is>
+      </c>
+      <c r="M82" s="6" t="inlineStr">
+        <is>
+          <t>$153,978 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N82" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O82" s="6" t="inlineStr">
+        <is>
+          <t>$206.9M</t>
+        </is>
+      </c>
+      <c r="P82" s="6" t="inlineStr">
+        <is>
+          <t>Original 2025-11-12 HQ incentive/relocation commitment</t>
+        </is>
+      </c>
+      <c r="Q82" s="6" t="inlineStr">
+        <is>
+          <t>1st ~150,000 sf building move-in ~mid-2026; 2nd building's land-development plan filed 2026-03-28; construction start still targeted H1 2027</t>
+        </is>
+      </c>
+      <c r="R82" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="S82" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/scout-motors-hq-move-turbocharges-second-office-building-in-plaza-midwood/</t>
+        </is>
+      </c>
+      <c r="T82" s="6" t="inlineStr">
+        <is>
+          <t>Med (facts High; milestone stage early)</t>
+        </is>
+      </c>
+      <c r="U82" s="6" t="inlineStr">
+        <is>
+          <t>Corporate HQ / professional</t>
+        </is>
+      </c>
+      <c r="V82" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="W82" s="6" t="inlineStr">
+        <is>
+          <t>Supports Plaza Midwood/NoDa/Elizabeth close-in rental and townhome demand from a young, high-wage corporate workforce.</t>
+        </is>
+      </c>
+      <c r="X82" s="6" t="inlineStr">
+        <is>
+          <t>No fresher permit/construction-progress milestone found this cycle. New risk-factor context (not scored): Scout Motors is defending franchise-dealer lawsuits in five states (CA, FL, CO, NY, CT) over its direct-to-consumer sales model; reporting is explicit that the company is 'pushing ahead' with the Charlotte HQ regardless.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D83" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Ballantyne</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>Citigroup — Charlotte office (grand opening)</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>Banking / financial services</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>Facility grand opening</t>
+        </is>
+      </c>
+      <c r="K83" s="6" t="n">
+        <v>510</v>
+      </c>
+      <c r="L83" s="6" t="inlineStr">
+        <is>
+          <t>Confirmed (stated)</t>
+        </is>
+      </c>
+      <c r="M83" s="6" t="inlineStr">
+        <is>
+          <t>$131,832 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N83" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O83" s="6" t="inlineStr">
+        <is>
+          <t>$16.1M</t>
+        </is>
+      </c>
+      <c r="P83" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $8.9M / 10 yr</t>
+        </is>
+      </c>
+      <c r="Q83" s="6" t="inlineStr">
+        <is>
+          <t>Grand opening held 2026-03-16 at 11225 North Community House Road (Gragg Building); facility total capacity 785 employees incl. 275 relocating from existing Charlotte offices</t>
+        </is>
+      </c>
+      <c r="R83" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="S83" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2026/03/16/governor-stein-celebrates-grand-opening-citi-charlotte-office</t>
+        </is>
+      </c>
+      <c r="T83" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U83" s="6" t="inlineStr">
+        <is>
+          <t>Office / financial services</t>
+        </is>
+      </c>
+      <c r="V83" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W83" s="6" t="inlineStr">
+        <is>
+          <t>$131,832 stated wage clears the $100k bar; supports Class-A rental and for-sale townhome demand in south Mecklenburg's Ballantyne/Blakeney/Rea Farms corridor.</t>
+        </is>
+      </c>
+      <c r="X83" s="6" t="inlineStr">
+        <is>
+          <t>No fresher milestone found this cycle despite a dedicated recheck; jobs, wage, and date reconfirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D84" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>Durham / Morrisville</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>Durham &amp; Wake</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>Novartis — API mfg building (unchanged)</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="K84" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="L84" s="6" t="inlineStr">
+        <is>
+          <t>Projected (part of pre-window deal)</t>
+        </is>
+      </c>
+      <c r="M84" s="6" t="inlineStr">
+        <is>
+          <t>$111,161 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N84" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O84" s="6" t="inlineStr">
+        <is>
+          <t>~$991M (incl. $220M API building)</t>
+        </is>
+      </c>
+      <c r="P84" s="6" t="inlineStr">
+        <is>
+          <t>Part of original $771M package incentives</t>
+        </is>
+      </c>
+      <c r="Q84" s="6" t="inlineStr">
+        <is>
+          <t>Facility opening targeted 2027-2028</t>
+        </is>
+      </c>
+      <c r="R84" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="S84" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
+        </is>
+      </c>
+      <c r="T84" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U84" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="V84" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W84" s="6" t="inlineStr">
+        <is>
+          <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
+        </is>
+      </c>
+      <c r="X84" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found this cycle; underlying $771M (Nov. 2025) + $220M Morrisville API building figures reconciled to the tracked ~$991M total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D85" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>Aspida Financial Services — HQ expansion (unchanged)</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>Financial services / insurance HQ</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>Lease executed; building renovation still not confirmed complete</t>
+        </is>
+      </c>
+      <c r="K85" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L85" s="6" t="inlineStr">
+        <is>
+          <t>Projected</t>
+        </is>
+      </c>
+      <c r="M85" s="6" t="inlineStr">
+        <is>
+          <t>$137,288 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N85" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O85" s="6" t="inlineStr">
+        <is>
+          <t>$28M+ (incl. $10M Imperial Tower renovation)</t>
+        </is>
+      </c>
+      <c r="P85" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="Q85" s="6" t="inlineStr">
+        <is>
+          <t>89,770 sf lease (top 3 floors, Imperial Tower, 4820 Emperor Blvd); Drawbridge Realty's $10M renovation still described only in future/in-progress tense ('slated to wrap by summer 2026') with no dated confirmation of completion found; move-in still stated as targeted Q4 2026</t>
+        </is>
+      </c>
+      <c r="R85" s="6" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="S85" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/imperial-tower-roars-back-as-10-million-durham-revival/</t>
+        </is>
+      </c>
+      <c r="T85" s="6" t="inlineStr">
+        <is>
+          <t>Medium (facts High; move-in date not yet company-confirmed)</t>
+        </is>
+      </c>
+      <c r="U85" s="6" t="inlineStr">
+        <is>
+          <t>Office — financial services/insurance</t>
+        </is>
+      </c>
+      <c r="V85" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="W85" s="6" t="inlineStr">
+        <is>
+          <t>1,000 high-wage financial-services jobs concentrated in downtown Durham support Class-A urban rental and close-in for-sale demand.</t>
+        </is>
+      </c>
+      <c r="X85" s="6" t="inlineStr">
+        <is>
+          <t>Second consecutive cycle with no dated confirmation that the Imperial Tower renovation (originally targeted for 'summer 2026' completion) has actually finished; every source retrieved still uses future/in-progress language. Flagged as a persistent risk item pending hard confirmation. Move-in still stated as targeted Q4 2026.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16102,7 +18379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L334"/>
+  <dimension ref="A1:L386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -36827,6 +39104,3230 @@
         </is>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B335" s="6" t="inlineStr">
+        <is>
+          <t>North Charleston</t>
+        </is>
+      </c>
+      <c r="C335" s="6" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="D335" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E335" s="6" t="inlineStr">
+        <is>
+          <t>SC Ports Authority — Leatherman Terminal (pause remains in effect)</t>
+        </is>
+      </c>
+      <c r="F335" s="6" t="inlineStr">
+        <is>
+          <t>400 direct + ~1,200 indirect</t>
+        </is>
+      </c>
+      <c r="G335" s="6" t="inlineStr">
+        <is>
+          <t>$1.2B</t>
+        </is>
+      </c>
+      <c r="H335" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I335" s="6" t="inlineStr">
+        <is>
+          <t>No reopening date found this cycle despite a dedicated recheck; the Aug. 1, 2026 pause remains in effect with no timeline set (SC Ports says timing depends on future cargo demand). CAUTION: several search hits referencing a Leatherman 'reopening' with weekly Asia/ZIM service trace to Sept. 2024, following an unrelated 2023 ILA labor-dispute closure — not to be conflated with the current 2026 pause.</t>
+        </is>
+      </c>
+      <c r="J335" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked; no change)</t>
+        </is>
+      </c>
+      <c r="K335" s="6" t="inlineStr">
+        <is>
+          <t>https://www.live5news.com/2026/06/25/sc-ports-pause-leatherman-terminal-operations-aug-1-consolidate-container-work/</t>
+        </is>
+      </c>
+      <c r="L335" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B336" s="6" t="inlineStr">
+        <is>
+          <t>Cherokee Co. / Blacksburg</t>
+        </is>
+      </c>
+      <c r="C336" s="6" t="inlineStr">
+        <is>
+          <t>Cherokee</t>
+        </is>
+      </c>
+      <c r="D336" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E336" s="6" t="inlineStr">
+        <is>
+          <t>USA Rare Earth — rare-earth magnet plant</t>
+        </is>
+      </c>
+      <c r="F336" s="6" t="inlineStr">
+        <is>
+          <t>~490</t>
+        </is>
+      </c>
+      <c r="G336" s="6" t="inlineStr">
+        <is>
+          <t>$1.2B</t>
+        </is>
+      </c>
+      <c r="H336" s="6" t="inlineStr">
+        <is>
+          <t>$24.50-$63/hr (stated; unchanged)</t>
+        </is>
+      </c>
+      <c r="I336" s="6" t="inlineStr">
+        <is>
+          <t>No headcount increase found this cycle; still 490 jobs (just under the 500 threshold), $1.2B capex, Bailey Park site. New detail: operational target now specifically stated as April 2028. Backed by up to $1.6B in CHIPS Act funding.</t>
+        </is>
+      </c>
+      <c r="J336" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked)</t>
+        </is>
+      </c>
+      <c r="K336" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/spartanburg/business/usa-rare-earth-blacksburg-sc-facility/article_2681ca76-7e5f-4a73-8a80-13231e38917f.html</t>
+        </is>
+      </c>
+      <c r="L336" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B337" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg (former Kohler plant)</t>
+        </is>
+      </c>
+      <c r="C337" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D337" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E337" s="6" t="inlineStr">
+        <is>
+          <t>NorthMark/Valara "Project Moc-1" — AI/HPC data center (MAJOR regulatory developments this cycle)</t>
+        </is>
+      </c>
+      <c r="F337" s="6" t="inlineStr">
+        <is>
+          <t>27 FT confirmed on incentive filings (company's own ~150-at-full-operation claim not independently corroborated)</t>
+        </is>
+      </c>
+      <c r="G337" s="6" t="inlineStr">
+        <is>
+          <t>$2.8B</t>
+        </is>
+      </c>
+      <c r="H337" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I337" s="6" t="inlineStr">
+        <is>
+          <t>Significant movement on multiple fronts: (1) the SC Public Service Commission unanimously ruled (~Sept. 4) the data center is NOT subject to Utility Siting Act power-plant rules and that only SC's Office of Regulatory Staff — not private plaintiffs — can bring such enforcement actions, a loss for opponents; (2) SELC's separate Circuit Court preliminary-injunction motion (filed Aug. 20) remains UNRESOLVED with no ruling or hearing date found; (3) the county's moratorium 3rd/final reading is confirmed scheduled for Sept. 21, but the draft ordinance exempts already-approved projects, and council members have said they are 'not inclined' to add NorthMark to it regardless of the vote's outcome; (4) the Public Safety Committee's fact-finding hearing was held Sept. 9 (no vote; a contentious follow-on council session Sept. 10 saw clashes between council, attorneys, developers, and residents); (5) the state legislative event (Sen. Kimbrell, Rep. Moore, re: SC Senate bill S.867 on statewide data-center siting) was held today, Sept. 14 — outcome not yet reportable. (6) SCDES air permit (11 additional gas turbines) remains under review; NorthMark says it still hopes for approval by year-end. Net: opponents lost the state-regulatory argument, but the circuit-court injunction is the one live wildcard, and NorthMark appears likely to be grandfathered out of the moratorium regardless.</t>
+        </is>
+      </c>
+      <c r="J337" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (multiple hearings this cycle)</t>
+        </is>
+      </c>
+      <c r="K337" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/2026/08/27/spartanburg-data-center-not-subject-to-public-power-plant-rules-sc-regulators-rule/</t>
+        </is>
+      </c>
+      <c r="L337" s="6" t="inlineStr">
+        <is>
+          <t>Med-High (state-level regulatory risk resolved in developer's favor; county litigation/injunction still open)</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B338" s="6" t="inlineStr">
+        <is>
+          <t>Wake County (statewide)</t>
+        </is>
+      </c>
+      <c r="C338" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D338" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E338" s="6" t="inlineStr">
+        <is>
+          <t>WakeMed / Atrium Health — proposed merger</t>
+        </is>
+      </c>
+      <c r="F338" s="6" t="inlineStr">
+        <is>
+          <t>3,300 (statewide, 5 yr)</t>
+        </is>
+      </c>
+      <c r="G338" s="6" t="inlineStr">
+        <is>
+          <t>$2.0B (Wake Co. portion)</t>
+        </is>
+      </c>
+      <c r="H338" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I338" s="6" t="inlineStr">
+        <is>
+          <t>No vote outcome found for the Sept. 8, 2026 Wake Co. BOC agenda despite dedicated searching. New complication: a September WRAL headline reports WakeMed 'loses two top executives as proposed merger with Atrium looms,' and NC Health News (Aug. 31) still frames the deal via '10 key questions' with no resolution. Treat the merger as still pending; county says it lacks authority to approve/block it (a federal regulatory matter).</t>
+        </is>
+      </c>
+      <c r="J338" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (still pending; vote outcome unconfirmed)</t>
+        </is>
+      </c>
+      <c r="K338" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/wakemed-atrium-health-possible-deal-public-meeting-monday-august-17-2026/</t>
+        </is>
+      </c>
+      <c r="L338" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B339" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="C339" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="D339" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E339" s="6" t="inlineStr">
+        <is>
+          <t>Boom Supersonic — Overture assembly (AT RISK)</t>
+        </is>
+      </c>
+      <c r="F339" s="6" t="inlineStr">
+        <is>
+          <t>&lt;=500 currently; must hit 500 by 12/31/26 or lease may terminate</t>
+        </is>
+      </c>
+      <c r="G339" s="6" t="inlineStr">
+        <is>
+          <t>~$50M (hangar)</t>
+        </is>
+      </c>
+      <c r="H339" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I339" s="6" t="inlineStr">
+        <is>
+          <t>No positive headcount movement found this cycle; as of March 2026 reporting the 179,000 sq ft hangar remained largely idle since its June 2024 ribbon-cutting, with company saying only it 'looks forward to beginning Overture test production as soon as possible.' The Dec. 31, 2026 lease trigger (500+ employees or termination risk) stands unaddressed in any dated source found.</t>
+        </is>
+      </c>
+      <c r="J339" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked; no change)</t>
+        </is>
+      </c>
+      <c r="K339" s="6" t="inlineStr">
+        <is>
+          <t>https://www.prismnews.com/local/guilford-nc/boom-supersonics-greensboro-factory-sits-idle-as-state</t>
+        </is>
+      </c>
+      <c r="L339" s="6" t="inlineStr">
+        <is>
+          <t>Med-High (risk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B340" s="6" t="inlineStr">
+        <is>
+          <t>Rowan County</t>
+        </is>
+      </c>
+      <c r="C340" s="6" t="inlineStr">
+        <is>
+          <t>Rowan</t>
+        </is>
+      </c>
+      <c r="D340" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E340" s="6" t="inlineStr">
+        <is>
+          <t>American Eagle Outfitters</t>
+        </is>
+      </c>
+      <c r="F340" s="6" t="inlineStr">
+        <is>
+          <t>200+ (state figure; county vote cited 258)</t>
+        </is>
+      </c>
+      <c r="G340" s="6" t="inlineStr">
+        <is>
+          <t>$41M</t>
+        </is>
+      </c>
+      <c r="H340" s="6" t="inlineStr">
+        <is>
+          <t>$57,351 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I340" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; Q1 2027 ops start still targeted.</t>
+        </is>
+      </c>
+      <c r="J340" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked; no change)</t>
+        </is>
+      </c>
+      <c r="K340" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2026/07/17/governor-stein-announces-american-eagle-outfitters-inc-selects-rowan-county-41-million-southeast</t>
+        </is>
+      </c>
+      <c r="L340" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B341" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte (CLT airport)</t>
+        </is>
+      </c>
+      <c r="C341" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D341" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E341" s="6" t="inlineStr">
+        <is>
+          <t>Averitt — logistics campus</t>
+        </is>
+      </c>
+      <c r="F341" s="6" t="inlineStr">
+        <is>
+          <t>211 (confirmed)</t>
+        </is>
+      </c>
+      <c r="G341" s="6" t="inlineStr">
+        <is>
+          <t>$200M</t>
+        </is>
+      </c>
+      <c r="H341" s="6" t="inlineStr">
+        <is>
+          <t>$81,769 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I341" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; construction reconfirmed as 'set to begin immediately' per May 2026 reporting, completion still targeted 2028.</t>
+        </is>
+      </c>
+      <c r="J341" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked; no change)</t>
+        </is>
+      </c>
+      <c r="K341" s="6" t="inlineStr">
+        <is>
+          <t>https://www.charlottenc.gov/City-News/Averitt-Announces-New-Commitment-to-Charlotte</t>
+        </is>
+      </c>
+      <c r="L341" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B342" s="6" t="inlineStr">
+        <is>
+          <t>York Co.</t>
+        </is>
+      </c>
+      <c r="C342" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="D342" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E342" s="6" t="inlineStr">
+        <is>
+          <t>QTS "Project Cobra" — data-center campus</t>
+        </is>
+      </c>
+      <c r="F342" s="6" t="inlineStr">
+        <is>
+          <t>~200 FTE (+~1,000 constr.)</t>
+        </is>
+      </c>
+      <c r="G342" s="6" t="inlineStr">
+        <is>
+          <t>up to $8B</t>
+        </is>
+      </c>
+      <c r="H342" s="6" t="inlineStr">
+        <is>
+          <t>~$80k median (stated)</t>
+        </is>
+      </c>
+      <c r="I342" s="6" t="inlineStr">
+        <is>
+          <t>Most recent dated activity found: a community Q&amp;A panel held 2026-05-12 at Oakridge Elementary (Clover), with construction confirmed ongoing as of that date. No newer (Aug./Sept.) update surfaced this cycle.</t>
+        </is>
+      </c>
+      <c r="J342" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-12 (most recent confirmed activity)</t>
+        </is>
+      </c>
+      <c r="K342" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/york-county/news/data-center-york-chester-qts-construction/article_1f68a2a7-8190-49df-b518-23aa5babd587.html</t>
+        </is>
+      </c>
+      <c r="L342" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B343" s="6" t="inlineStr">
+        <is>
+          <t>Burlington / Alamance-Guilford line</t>
+        </is>
+      </c>
+      <c r="C343" s="6" t="inlineStr">
+        <is>
+          <t>Alamance</t>
+        </is>
+      </c>
+      <c r="D343" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E343" s="6" t="inlineStr">
+        <is>
+          <t>Ahold Delhaize USA (Food Lion parent) — distribution center</t>
+        </is>
+      </c>
+      <c r="F343" s="6" t="inlineStr">
+        <is>
+          <t>500-505</t>
+        </is>
+      </c>
+      <c r="G343" s="6" t="inlineStr">
+        <is>
+          <t>$860M</t>
+        </is>
+      </c>
+      <c r="H343" s="6" t="inlineStr">
+        <is>
+          <t>~$60k-$67k avg (Estimated/Inferred, sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I343" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle beyond the Feb. 16, 2026 groundbreaking already tracked (now further outside the shifted window); new detail: opening is now specifically targeted for 2029. Construction reported underway. Flagged further 'at risk' absent a fresh 2026-03-14-or-later milestone.</t>
+        </is>
+      </c>
+      <c r="J343" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-16 (pre-window; at risk)</t>
+        </is>
+      </c>
+      <c r="K343" s="6" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/02/16/3238762/0/en/Ahold-Delhaize-USA-Breaks-Ground-on-New-860-Million-Distribution-Center-in-Burlington-N-C.html</t>
+        </is>
+      </c>
+      <c r="L343" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B344" s="6" t="inlineStr">
+        <is>
+          <t>Pender / New Hanover</t>
+        </is>
+      </c>
+      <c r="C344" s="6" t="inlineStr">
+        <is>
+          <t>Pender (+New Hanover)</t>
+        </is>
+      </c>
+      <c r="D344" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E344" s="6" t="inlineStr">
+        <is>
+          <t>Amazon — robotics fulfillment center</t>
+        </is>
+      </c>
+      <c r="F344" s="6" t="inlineStr">
+        <is>
+          <t>1,000+</t>
+        </is>
+      </c>
+      <c r="G344" s="6" t="inlineStr">
+        <is>
+          <t>$350M</t>
+        </is>
+      </c>
+      <c r="H344" s="6" t="inlineStr">
+        <is>
+          <t>~$22/hr avg (Estimated/Inferred ~$45,760/yr, sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I344" s="6" t="inlineStr">
+        <is>
+          <t>CONFIRMED ON TRACK: as of Dec. 2025 the building shell was complete and robotics were being installed; company 'remains on track for Fall 2026 launch' and is actively hiring 1,000+ warehouse-associate roles ahead of opening.</t>
+        </is>
+      </c>
+      <c r="J344" s="6" t="inlineStr">
+        <is>
+          <t>2026-08 (reconfirmed on track)</t>
+        </is>
+      </c>
+      <c r="K344" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wilmingtonbiz.com/more_news/2026/08/10/amazon_begins_hiring_as_local_facilities_near_completion/27737</t>
+        </is>
+      </c>
+      <c r="L344" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B345" s="6" t="inlineStr">
+        <is>
+          <t>Wake Co. (aggregate)</t>
+        </is>
+      </c>
+      <c r="C345" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D345" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E345" s="6" t="inlineStr">
+        <is>
+          <t>County jobs pipeline (EDGE 7, 52 projects)</t>
+        </is>
+      </c>
+      <c r="F345" s="6" t="inlineStr">
+        <is>
+          <t>~11,000 (pipeline)</t>
+        </is>
+      </c>
+      <c r="G345" s="6" t="inlineStr">
+        <is>
+          <t>$11B</t>
+        </is>
+      </c>
+      <c r="H345" s="6" t="inlineStr">
+        <is>
+          <t>Mixed (office-skewed)</t>
+        </is>
+      </c>
+      <c r="I345" s="6" t="inlineStr">
+        <is>
+          <t>Discrepancy partially resolved: confirmed the ~$11B/11,000-job/52-project figure remains WCED's current active full-pipeline headline. Located WCED's own 'New and Expanding' report (covering Oct. 1, 2025-May 31, 2026), which plausibly is the source of the smaller ~$5.6B/8,000-job LinkedIn figure — likely a landed/realized-projects subset rather than the full unlanded pipeline. Could not open the PDF (fetch blocked) to confirm exact totals this cycle — recommend a direct pull next cycle.</t>
+        </is>
+      </c>
+      <c r="J345" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (partially resolved)</t>
+        </is>
+      </c>
+      <c r="K345" s="6" t="inlineStr">
+        <is>
+          <t>https://nchospitalityalliance.com/wake-county-pursues-11-billion-jobs-pipeline/</t>
+        </is>
+      </c>
+      <c r="L345" s="6" t="inlineStr">
+        <is>
+          <t>Low (figure discrepancy unresolved)</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B346" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / SouthPark</t>
+        </is>
+      </c>
+      <c r="C346" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D346" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E346" s="6" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase — SouthPark consolidated office</t>
+        </is>
+      </c>
+      <c r="F346" s="6" t="inlineStr">
+        <is>
+          <t>400 new + ~600 relocated = 1,000 total</t>
+        </is>
+      </c>
+      <c r="G346" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H346" s="6" t="inlineStr">
+        <is>
+          <t>~$105k Estimated/Inferred — basis not independently confirmed this cycle</t>
+        </is>
+      </c>
+      <c r="I346" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; One Piedmont Town Center lease (145,000 sf/5 floors, ~1,000 total employees: 400 new + ~600 relocated) reconfirmed. Move-in timing sourcing remains inconsistent across outlets ('later in 2026' vs. 'early 2028'); wage still not disclosed/confirmed in any source found.</t>
+        </is>
+      </c>
+      <c r="J346" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked; no change)</t>
+        </is>
+      </c>
+      <c r="K346" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wbtv.com/2026/04/21/jpmorgan-chase-open-1000-employee-charlotte-office-add-400-jobs/</t>
+        </is>
+      </c>
+      <c r="L346" s="6" t="inlineStr">
+        <is>
+          <t>High (jobs/lease); Low (wage basis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B347" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh / North Hills</t>
+        </is>
+      </c>
+      <c r="C347" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D347" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E347" s="6" t="inlineStr">
+        <is>
+          <t>Ralliant Corp. — global HQ launch</t>
+        </is>
+      </c>
+      <c r="F347" s="6" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G347" s="6" t="inlineStr">
+        <is>
+          <t>$2.1M</t>
+        </is>
+      </c>
+      <c r="H347" s="6" t="inlineStr">
+        <is>
+          <t>$170k-$189k avg (stated)</t>
+        </is>
+      </c>
+      <c r="I347" s="6" t="inlineStr">
+        <is>
+          <t>No fresher milestone found this cycle; the grand-opening date (2026-03-05) sits further before the window start (now 2026-03-14) under the shifted window — flagged at risk of falling out absent a fresh 2026 update.</t>
+        </is>
+      </c>
+      <c r="J347" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-05 (pre-window; at risk)</t>
+        </is>
+      </c>
+      <c r="K347" s="6" t="inlineStr">
+        <is>
+          <t>https://investors.ralliant.com/news-events/press-releases/detail/121/ralliant-opens-global-headquarters-in-raleigh-north-carolina</t>
+        </is>
+      </c>
+      <c r="L347" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B348" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh / North Hills</t>
+        </is>
+      </c>
+      <c r="C348" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D348" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E348" s="6" t="inlineStr">
+        <is>
+          <t>Jewelers Mutual Group</t>
+        </is>
+      </c>
+      <c r="F348" s="6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G348" s="6" t="inlineStr">
+        <is>
+          <t>$5.85M</t>
+        </is>
+      </c>
+      <c r="H348" s="6" t="inlineStr">
+        <is>
+          <t>$169,592 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I348" s="6" t="inlineStr">
+        <is>
+          <t>Not actively re-searched this cycle (research budget prioritized elsewhere); no new evidence surfaced incidentally. Recommend a direct re-check next cycle.</t>
+        </is>
+      </c>
+      <c r="J348" s="6" t="inlineStr">
+        <is>
+          <t>2025-10 (pre-window; legacy entry; not rechecked this cycle)</t>
+        </is>
+      </c>
+      <c r="K348" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/jewelers-mutual-coming-to-raleigh-with-200-jobs-averaging-169k/</t>
+        </is>
+      </c>
+      <c r="L348" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B349" s="6" t="inlineStr">
+        <is>
+          <t>Garner</t>
+        </is>
+      </c>
+      <c r="C349" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D349" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E349" s="6" t="inlineStr">
+        <is>
+          <t>Gregory Poole Equipment Co. — HQ relocation</t>
+        </is>
+      </c>
+      <c r="F349" s="6" t="inlineStr">
+        <is>
+          <t>500+ (5 yr)</t>
+        </is>
+      </c>
+      <c r="G349" s="6" t="inlineStr">
+        <is>
+          <t>$347M</t>
+        </is>
+      </c>
+      <c r="H349" s="6" t="inlineStr">
+        <is>
+          <t>~$75,381 companywide avg (Estimated/Inferred, sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I349" s="6" t="inlineStr">
+        <is>
+          <t>No groundbreaking confirmed this cycle; project still described at the announcement stage ('construction expected within 24 months' as of Oct. 2025).</t>
+        </is>
+      </c>
+      <c r="J349" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked; no change)</t>
+        </is>
+      </c>
+      <c r="K349" s="6" t="inlineStr">
+        <is>
+          <t>https://www.garnernc.gov/Home/Components/News/News/2344/17</t>
+        </is>
+      </c>
+      <c r="L349" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B350" s="6" t="inlineStr">
+        <is>
+          <t>Siler City</t>
+        </is>
+      </c>
+      <c r="C350" s="6" t="inlineStr">
+        <is>
+          <t>Chatham</t>
+        </is>
+      </c>
+      <c r="D350" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E350" s="6" t="inlineStr">
+        <is>
+          <t>Wolfspeed — silicon-carbide fab (dating discrepancy: sole WARN milestone may be PRE-WINDOW)</t>
+        </is>
+      </c>
+      <c r="F350" s="6" t="inlineStr">
+        <is>
+          <t>1,800 (proj.)</t>
+        </is>
+      </c>
+      <c r="G350" s="6" t="inlineStr">
+        <is>
+          <t>$5.0B</t>
+        </is>
+      </c>
+      <c r="H350" s="6" t="inlineStr">
+        <is>
+          <t>$77,753 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I350" s="6" t="inlineStr">
+        <is>
+          <t>IMPORTANT finding: multiple sources this cycle consistently date the tracked '73-worker WARN notice' to June 9, 2025 (effective Aug. 8, 2025) — NOT 2026 as previously carried. If correct, this milestone is now more than a year outside the 6-month window, and no second/larger 2026 WARN notice (the previously flagged 'possibly separate 300-worker' filing) could be confirmed or ruled out this cycle (the commerce.nc.gov WARN listing could not be directly fetched). Flagging this item 'at risk' — its sole dated Watch-qualifying milestone may not actually be in-window. Recommend a direct WARN-database pull next cycle to resolve definitively.</t>
+        </is>
+      </c>
+      <c r="J350" s="6" t="inlineStr">
+        <is>
+          <t>2025-06-09 (dating discrepancy — likely pre-window; at risk)</t>
+        </is>
+      </c>
+      <c r="K350" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/story/wolfspeed-to-layoff-73-siler-city-employees-to-adjust-for-soft-demand/22046474/</t>
+        </is>
+      </c>
+      <c r="L350" s="6" t="inlineStr">
+        <is>
+          <t>Low-Medium (dating discrepancy unresolved — may not qualify as in-window)</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B351" s="6" t="inlineStr">
+        <is>
+          <t>Benson</t>
+        </is>
+      </c>
+      <c r="C351" s="6" t="inlineStr">
+        <is>
+          <t>Johnston</t>
+        </is>
+      </c>
+      <c r="D351" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E351" s="6" t="inlineStr">
+        <is>
+          <t>Vulcan Elements — magnet factory</t>
+        </is>
+      </c>
+      <c r="F351" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (proj.)</t>
+        </is>
+      </c>
+      <c r="G351" s="6" t="inlineStr">
+        <is>
+          <t>$918.4M</t>
+        </is>
+      </c>
+      <c r="H351" s="6" t="inlineStr">
+        <is>
+          <t>$81,932 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I351" s="6" t="inlineStr">
+        <is>
+          <t>NC Utilities Commission's fast-tracked 230kV transmission line remains under construction, targeted for completion around March 2027. No factory-groundbreaking event found this cycle; company's own March 2026 comments target starting operations Q1 2027 after doubling the planned facility to 1M+ sq ft.</t>
+        </is>
+      </c>
+      <c r="J351" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked; no change)</t>
+        </is>
+      </c>
+      <c r="K351" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2025/11/18/governor-stein-announces-vulcan-elements-selects-johnston-county-1000-job-magnet-factory-investing</t>
+        </is>
+      </c>
+      <c r="L351" s="6" t="inlineStr">
+        <is>
+          <t>Medium-High (infrastructure clearance confirmed; factory groundbreaking date still unconfirmed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B352" s="6" t="inlineStr">
+        <is>
+          <t>Multi-site NC incl. Wilmington</t>
+        </is>
+      </c>
+      <c r="C352" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover +</t>
+        </is>
+      </c>
+      <c r="D352" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E352" s="6" t="inlineStr">
+        <is>
+          <t>Amazon-Corning — fiber-optics partnership</t>
+        </is>
+      </c>
+      <c r="F352" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (multi-site, unallocated)</t>
+        </is>
+      </c>
+      <c r="G352" s="6" t="inlineStr">
+        <is>
+          <t>Multi-billion (undisclosed)</t>
+        </is>
+      </c>
+      <c r="H352" s="6" t="inlineStr">
+        <is>
+          <t>Avg salary &gt;$65,000 (sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I352" s="6" t="inlineStr">
+        <is>
+          <t>Reconfirmed as an in-window deal (announced 2026-06-08): multibillion-dollar Amazon/Corning fiber-optics partnership, ~1,000 NC manufacturing jobs plus hundreds of construction jobs, new Fiber Optic Technician Training Program with Catawba Valley CC. Wilmington is one of Corning's two NC fiber plants (with Concord). Wage still not disclosed/sub-$100k assumption unchanged; per-site Wilmington allocation still not broken out.</t>
+        </is>
+      </c>
+      <c r="J352" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-08 (reconfirmed in-window)</t>
+        </is>
+      </c>
+      <c r="K352" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wilmingtonbiz.com/technology/2026/06/08/amazon_corning_strike_multibillion_dollar_deal_to_add_1000_nc_jobs/27560</t>
+        </is>
+      </c>
+      <c r="L352" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B353" s="6" t="inlineStr">
+        <is>
+          <t>Arden</t>
+        </is>
+      </c>
+      <c r="C353" s="6" t="inlineStr">
+        <is>
+          <t>Buncombe</t>
+        </is>
+      </c>
+      <c r="D353" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E353" s="6" t="inlineStr">
+        <is>
+          <t>Pratt &amp; Whitney (RTX) — casting foundry expansion</t>
+        </is>
+      </c>
+      <c r="F353" s="6" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="G353" s="6" t="inlineStr">
+        <is>
+          <t>$285M</t>
+        </is>
+      </c>
+      <c r="H353" s="6" t="inlineStr">
+        <is>
+          <t>$62,413 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I353" s="6" t="inlineStr">
+        <is>
+          <t>UPDATE, positive: company now employs 1,000 (vs. an 800-by-2027 commitment) and expects 1,200 by 2027 — running ahead of schedule. First casting-foundry equipment arrivals expected end of 2026 (a future in-window milestone to watch next cycle).</t>
+        </is>
+      </c>
+      <c r="J353" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (updated; ahead of schedule)</t>
+        </is>
+      </c>
+      <c r="K353" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ashevillechamber.org/news-events/press-releases/pratt-whitney-expands-in-asheville/</t>
+        </is>
+      </c>
+      <c r="L353" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B354" s="6" t="inlineStr">
+        <is>
+          <t>Asheville / Arden</t>
+        </is>
+      </c>
+      <c r="C354" s="6" t="inlineStr">
+        <is>
+          <t>Buncombe</t>
+        </is>
+      </c>
+      <c r="D354" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E354" s="6" t="inlineStr">
+        <is>
+          <t>Eaton — Low Voltage Assembly expansion</t>
+        </is>
+      </c>
+      <c r="F354" s="6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G354" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H354" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Estimated mid-$60k-$80k)</t>
+        </is>
+      </c>
+      <c r="I354" s="6" t="inlineStr">
+        <is>
+          <t>Reconfirmed: announced April 7-8, 2026 (in-window), 300 jobs over 12 months, described as the seventh major Buncombe manufacturing expansion since Hurricane Helene. No new dated milestone this cycle.</t>
+        </is>
+      </c>
+      <c r="J354" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked)</t>
+        </is>
+      </c>
+      <c r="K354" s="6" t="inlineStr">
+        <is>
+          <t>https://wlos.com/news/local/eaton-buncombe-county-300-jobs-asheville-advanced-manufacturing-expansion-arden-avery-creek-power-management-company</t>
+        </is>
+      </c>
+      <c r="L354" s="6" t="inlineStr">
+        <is>
+          <t>High (jobs); Low (wage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B355" s="6" t="inlineStr">
+        <is>
+          <t>Hendersonville</t>
+        </is>
+      </c>
+      <c r="C355" s="6" t="inlineStr">
+        <is>
+          <t>Henderson</t>
+        </is>
+      </c>
+      <c r="D355" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E355" s="6" t="inlineStr">
+        <is>
+          <t>BorgWarner — vertical-integration expansion</t>
+        </is>
+      </c>
+      <c r="F355" s="6" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="G355" s="6" t="inlineStr">
+        <is>
+          <t>$100M</t>
+        </is>
+      </c>
+      <c r="H355" s="6" t="inlineStr">
+        <is>
+          <t>$67,047 avg (stated; below $100k)</t>
+        </is>
+      </c>
+      <c r="I355" s="6" t="inlineStr">
+        <is>
+          <t>Reconfirmed: announced May 26-27, 2026 (in-window), $100M/378 jobs, ~$67k wage, backed by a $3.6M JDIG (new detail). No new dated milestone this cycle.</t>
+        </is>
+      </c>
+      <c r="J355" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked)</t>
+        </is>
+      </c>
+      <c r="K355" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2026/05/26/governor-stein-announces-100-million-expansion-borgwarner-hendersonville</t>
+        </is>
+      </c>
+      <c r="L355" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B356" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro</t>
+        </is>
+      </c>
+      <c r="C356" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="D356" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E356" s="6" t="inlineStr">
+        <is>
+          <t>Lumentum — AI/data-center optics</t>
+        </is>
+      </c>
+      <c r="F356" s="6" t="inlineStr">
+        <is>
+          <t>~400</t>
+        </is>
+      </c>
+      <c r="G356" s="6" t="inlineStr">
+        <is>
+          <t>Hundreds of millions</t>
+        </is>
+      </c>
+      <c r="H356" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I356" s="6" t="inlineStr">
+        <is>
+          <t>Ribbon-cutting reconfirmed complete April 29, 2026 (in-window); Nvidia confirmed as a customer relationship; production ramp still targeted mid-2028. No new dated milestone this cycle.</t>
+        </is>
+      </c>
+      <c r="J356" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked)</t>
+        </is>
+      </c>
+      <c r="K356" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/red-hot-lumentum-plans-400-worker-greensboro-plant/</t>
+        </is>
+      </c>
+      <c r="L356" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B357" s="6" t="inlineStr">
+        <is>
+          <t>Kernersville</t>
+        </is>
+      </c>
+      <c r="C357" s="6" t="inlineStr">
+        <is>
+          <t>Forsyth</t>
+        </is>
+      </c>
+      <c r="D357" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E357" s="6" t="inlineStr">
+        <is>
+          <t>John Deere — excavator plant (relocating from Japan)</t>
+        </is>
+      </c>
+      <c r="F357" s="6" t="inlineStr">
+        <is>
+          <t>150+</t>
+        </is>
+      </c>
+      <c r="G357" s="6" t="inlineStr">
+        <is>
+          <t>$70M</t>
+        </is>
+      </c>
+      <c r="H357" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Inferred skilled-mfg)</t>
+        </is>
+      </c>
+      <c r="I357" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; construction still slated to begin 'later this year' (2026); opening still targeted 'sometime in 2027.'</t>
+        </is>
+      </c>
+      <c r="J357" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked; no change)</t>
+        </is>
+      </c>
+      <c r="K357" s="6" t="inlineStr">
+        <is>
+          <t>https://businessfacilities.com/john-deere-builds-new-facilities-in-north-carolina-indiana/</t>
+        </is>
+      </c>
+      <c r="L357" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B358" s="6" t="inlineStr">
+        <is>
+          <t>Asheboro</t>
+        </is>
+      </c>
+      <c r="C358" s="6" t="inlineStr">
+        <is>
+          <t>Randolph</t>
+        </is>
+      </c>
+      <c r="D358" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E358" s="6" t="inlineStr">
+        <is>
+          <t>Environmental Air Systems (FLAGGED FOR LIKELY DROP NEXT CYCLE)</t>
+        </is>
+      </c>
+      <c r="F358" s="6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G358" s="6" t="inlineStr">
+        <is>
+          <t>$20M</t>
+        </is>
+      </c>
+      <c r="H358" s="6" t="inlineStr">
+        <is>
+          <t>$55,133 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I358" s="6" t="inlineStr">
+        <is>
+          <t>No 2026-dated update found despite a dedicated search for a third-plus consecutive cycle; the only confirmed fact remains the leased former Klaussner Furniture site. The original Nov. 25, 2025 announcement is now 9+ months stale. Recommend removing from active tracking next cycle absent a fresh hiring/construction milestone.</t>
+        </is>
+      </c>
+      <c r="J358" s="6" t="inlineStr">
+        <is>
+          <t>2025-11-25 (orig.; at risk of removal next cycle)</t>
+        </is>
+      </c>
+      <c r="K358" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/randolph-county-wins-20-million-hvac-project-300-jobs/</t>
+        </is>
+      </c>
+      <c r="L358" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B359" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington</t>
+        </is>
+      </c>
+      <c r="C359" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover</t>
+        </is>
+      </c>
+      <c r="D359" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E359" s="6" t="inlineStr">
+        <is>
+          <t>GE Hitachi / Global Nuclear Fuel — GNF4 fuel line</t>
+        </is>
+      </c>
+      <c r="F359" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G359" s="6" t="inlineStr">
+        <is>
+          <t>Not itemized</t>
+        </is>
+      </c>
+      <c r="H359" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I359" s="6" t="inlineStr">
+        <is>
+          <t>New detail: company confirmed $50M+ in facility-enhancement investment this year and next, plus new engineering/supply-chain/manufacturing hires (count still not disclosed). GNF4 fuel-line fabrication start is now effectively in-window (early 2026).</t>
+        </is>
+      </c>
+      <c r="J359" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (updated)</t>
+        </is>
+      </c>
+      <c r="K359" s="6" t="inlineStr">
+        <is>
+          <t>https://www.gevernova.com/news/press-releases/global-nuclear-fuel-introduces-next-generation-fuel-product</t>
+        </is>
+      </c>
+      <c r="L359" s="6" t="inlineStr">
+        <is>
+          <t>Low (indirect job-board proxy only, no dated milestone)</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B360" s="6" t="inlineStr">
+        <is>
+          <t>Liberty</t>
+        </is>
+      </c>
+      <c r="C360" s="6" t="inlineStr">
+        <is>
+          <t>Randolph</t>
+        </is>
+      </c>
+      <c r="D360" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E360" s="6" t="inlineStr">
+        <is>
+          <t>Toyota Battery Manufacturing NC (TBMNC)</t>
+        </is>
+      </c>
+      <c r="F360" s="6" t="inlineStr">
+        <is>
+          <t>5,100 (proj. total); 3,000+ employed</t>
+        </is>
+      </c>
+      <c r="G360" s="6" t="inlineStr">
+        <is>
+          <t>$13.9B</t>
+        </is>
+      </c>
+      <c r="H360" s="6" t="inlineStr">
+        <is>
+          <t>$62,234 avg (stated; below $100k)</t>
+        </is>
+      </c>
+      <c r="I360" s="6" t="inlineStr">
+        <is>
+          <t>No new 2026 investment/hiring milestone found this cycle; reconfirmed unchanged (4 hybrid lines already operating, capacity for 600k vehicles/yr worth of batteries as of Nov. 2025 background).</t>
+        </is>
+      </c>
+      <c r="J360" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked; no change)</t>
+        </is>
+      </c>
+      <c r="K360" s="6" t="inlineStr">
+        <is>
+          <t>https://rebusinessonline.com/toyota-begins-production-at-13-9b-battery-plant-in-north-carolina-pledges-additional-10b-investment-over-next-five-years/</t>
+        </is>
+      </c>
+      <c r="L360" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B361" s="6" t="inlineStr">
+        <is>
+          <t>Rowan / Kannapolis</t>
+        </is>
+      </c>
+      <c r="C361" s="6" t="inlineStr">
+        <is>
+          <t>Rowan</t>
+        </is>
+      </c>
+      <c r="D361" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E361" s="6" t="inlineStr">
+        <is>
+          <t>Google — 730k sq ft warehouse lease (3rd-party logistics operator)</t>
+        </is>
+      </c>
+      <c r="F361" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G361" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H361" s="6" t="inlineStr">
+        <is>
+          <t>$55k-$150k range (job-board postings)</t>
+        </is>
+      </c>
+      <c r="I361" s="6" t="inlineStr">
+        <is>
+          <t>Not covered by any regional research pass this cycle; carried forward unchanged from the prior report. Jobs/wage still undisclosed.</t>
+        </is>
+      </c>
+      <c r="J361" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-07 (not rechecked this cycle)</t>
+        </is>
+      </c>
+      <c r="K361" s="6" t="inlineStr">
+        <is>
+          <t>https://www.qcnews.com/news/u-s/north-carolina/kannapolis/google-signs-multi-year-lease-to-move-into-730000-square-foot-warehouse-in-kannapolis/</t>
+        </is>
+      </c>
+      <c r="L361" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B362" s="6" t="inlineStr">
+        <is>
+          <t>RTP</t>
+        </is>
+      </c>
+      <c r="C362" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D362" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E362" s="6" t="inlineStr">
+        <is>
+          <t>Apple — RTP campus extension</t>
+        </is>
+      </c>
+      <c r="F362" s="6" t="inlineStr">
+        <is>
+          <t>3,000 originally projected; only ~600-990 added to date</t>
+        </is>
+      </c>
+      <c r="G362" s="6" t="inlineStr">
+        <is>
+          <t>$552M-$1B+ (paused)</t>
+        </is>
+      </c>
+      <c r="H362" s="6" t="inlineStr">
+        <is>
+          <t>$187k avg (stated, original 2021 award)</t>
+        </is>
+      </c>
+      <c r="I362" s="6" t="inlineStr">
+        <is>
+          <t>Material update: the RTP 3.0 park-wide redevelopment framework was unanimously approved by RTP companies/landowners in July 2026; Apple is an active member of the RTP Owners and Tenants Association. Apple's own building construction timeline remains unannounced; $845.8M in state incentives remain at stake. No Apple-specific hiring update found.</t>
+        </is>
+      </c>
+      <c r="J362" s="6" t="inlineStr">
+        <is>
+          <t>2026-07 (RTP 3.0 approval)</t>
+        </is>
+      </c>
+      <c r="K362" s="6" t="inlineStr">
+        <is>
+          <t>https://www.rtp.org/2026/06/research-triangle-park-approves-3-0/</t>
+        </is>
+      </c>
+      <c r="L362" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B363" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Raleigh / Rural Hall</t>
+        </is>
+      </c>
+      <c r="C363" s="6" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="D363" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E363" s="6" t="inlineStr">
+        <is>
+          <t>Siemens Energy — $421M NC expansion</t>
+        </is>
+      </c>
+      <c r="F363" s="6" t="inlineStr">
+        <is>
+          <t>500 (statewide)</t>
+        </is>
+      </c>
+      <c r="G363" s="6" t="inlineStr">
+        <is>
+          <t>$421M</t>
+        </is>
+      </c>
+      <c r="H363" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Inferred ~$87k from prior tranche; sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I363" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte-specific detail newly confirmed: the expansion is centered on Siemens Energy's existing Westinghouse Blvd facility (101 Siemens Ave.), restarting large gas-turbine production (idle since 2020) alongside expanded power-transformer manufacturing; the Charlotte-specific share of the 500 statewide jobs is still not broken out (Raleigh also receives a share). Original announcement remains pre-window (2026-02-03/05); no in-window groundbreaking/hiring-start milestone found despite searching.</t>
+        </is>
+      </c>
+      <c r="J363" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-03 (pre-window; Charlotte-site detail newly confirmed)</t>
+        </is>
+      </c>
+      <c r="K363" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/siemens-energys-421-million-n-c-expansion-adding-500-jobs/</t>
+        </is>
+      </c>
+      <c r="L363" s="6" t="inlineStr">
+        <is>
+          <t>Med (totals uncertain)</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B364" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh / Wendell / Knightdale</t>
+        </is>
+      </c>
+      <c r="C364" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D364" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E364" s="6" t="inlineStr">
+        <is>
+          <t>Siemens AG — power devices for AI/data centers</t>
+        </is>
+      </c>
+      <c r="F364" s="6" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="G364" s="6" t="inlineStr">
+        <is>
+          <t>part of $165M</t>
+        </is>
+      </c>
+      <c r="H364" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I364" s="6" t="inlineStr">
+        <is>
+          <t>Reconfirmed unchanged; breakdown reconfirmed (Raleigh 100 jobs at a new 131,000 sf facility; Wendell +200 jobs by 2028 at the existing site plus +50 jobs at a new 101,000 sf facility; Knightdale 100 positions targeted by end of 2026). No new dated milestone this cycle.</t>
+        </is>
+      </c>
+      <c r="J364" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked)</t>
+        </is>
+      </c>
+      <c r="K364" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/business/siemens-350-jobs-nc-sc-165m-investment-ai-data-centers-raleigh-wendell-march-2026/</t>
+        </is>
+      </c>
+      <c r="L364" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B365" s="6" t="inlineStr">
+        <is>
+          <t>Hamlet</t>
+        </is>
+      </c>
+      <c r="C365" s="6" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="D365" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E365" s="6" t="inlineStr">
+        <is>
+          <t>AWS/Amazon — AI/cloud campus "Project Blue Marlin" (open house held; no recap; secrecy controversy surfaced)</t>
+        </is>
+      </c>
+      <c r="F365" s="6" t="inlineStr">
+        <is>
+          <t>500 permanent (confirmed)</t>
+        </is>
+      </c>
+      <c r="G365" s="6" t="inlineStr">
+        <is>
+          <t>$10B</t>
+        </is>
+      </c>
+      <c r="H365" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I365" s="6" t="inlineStr">
+        <is>
+          <t>The Sept. 1, 2026 resident open house at Cole Auditorium is confirmed to have been held (drop-in format), but for a second consecutive cycle no post-event recap, attendance count, or resident-reaction coverage was found despite dedicated searching. New context (Aug. 2026 investigative reporting): the 'Project Blue Marlin' code name was kept secret from the public even during commission votes — only the County Manager and a handful of officials reportedly knew Amazon was the company — and an earlier public hearing drew unanimous opposition from roughly 36 speakers; several pieces link resident distrust to Hamlet's 1991 Imperial Foods fire (25 deaths). This is a community-relations risk factor; the project itself continues to proceed (final air-quality permits already confirmed issued Aug. 28, 2026).</t>
+        </is>
+      </c>
+      <c r="J365" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01 (open house held; recap still not found)</t>
+        </is>
+      </c>
+      <c r="K365" s="6" t="inlineStr">
+        <is>
+          <t>https://www.deq.nc.gov/news/press-releases/2026/08/28/ncdeqs-division-air-quality-requires-additional-monitoring-testing-final-air-quality-permits-amazon</t>
+        </is>
+      </c>
+      <c r="L365" s="6" t="inlineStr">
+        <is>
+          <t>High (permits/scheduling confirmed); Low (post-event outcome; rising community-relations risk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B366" s="6" t="inlineStr">
+        <is>
+          <t>Orangeburg / I-26</t>
+        </is>
+      </c>
+      <c r="C366" s="6" t="inlineStr">
+        <is>
+          <t>Orangeburg</t>
+        </is>
+      </c>
+      <c r="D366" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E366" s="6" t="inlineStr">
+        <is>
+          <t>Ferrara Candy</t>
+        </is>
+      </c>
+      <c r="F366" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (10 yr)</t>
+        </is>
+      </c>
+      <c r="G366" s="6" t="inlineStr">
+        <is>
+          <t>$675M</t>
+        </is>
+      </c>
+      <c r="H366" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; confectionery = workforce-tier</t>
+        </is>
+      </c>
+      <c r="I366" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle beyond the May 19-20, 2026 groundbreaking already on record; new detail: production is specifically targeted for Q1 2029, and up to $85M in state GO bond funding has been approved for the project.</t>
+        </is>
+      </c>
+      <c r="J366" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked; new detail)</t>
+        </is>
+      </c>
+      <c r="K366" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wistv.com/2026/04/22/ferrara-candy-company-build-675m-orangeburg-county-plant-create-1000-jobs-officials-say/</t>
+        </is>
+      </c>
+      <c r="L366" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B367" s="6" t="inlineStr">
+        <is>
+          <t>Columbia / BullStreet</t>
+        </is>
+      </c>
+      <c r="C367" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="D367" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E367" s="6" t="inlineStr">
+        <is>
+          <t>AMAROK — new HQ (perimeter security)</t>
+        </is>
+      </c>
+      <c r="F367" s="6" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="G367" s="6" t="inlineStr">
+        <is>
+          <t>$69M</t>
+        </is>
+      </c>
+      <c r="H367" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; HQ/professional (portion likely $100k+)</t>
+        </is>
+      </c>
+      <c r="I367" s="6" t="inlineStr">
+        <is>
+          <t>No dated groundbreaking/construction-start milestone found beyond the original March 24, 2026 announcement (construction 'expected to begin in 2026,' completion 2028). No update since.</t>
+        </is>
+      </c>
+      <c r="J367" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked; no change)</t>
+        </is>
+      </c>
+      <c r="K367" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.sc.gov/news/2026-03/amarok-expands-richland-county-operations-new-headquarters</t>
+        </is>
+      </c>
+      <c r="L367" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B368" s="6" t="inlineStr">
+        <is>
+          <t>North Charleston</t>
+        </is>
+      </c>
+      <c r="C368" s="6" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="D368" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E368" s="6" t="inlineStr">
+        <is>
+          <t>Boeing 787 — production-rate ramp (NEW: apprenticeship expansion + reconciled headcount)</t>
+        </is>
+      </c>
+      <c r="F368" s="6" t="inlineStr">
+        <is>
+          <t>1,000+ new jobs over 5 yrs (unchanged); campus total now 9,059 (was 8,200+)</t>
+        </is>
+      </c>
+      <c r="G368" s="6" t="inlineStr">
+        <is>
+          <t>$1B+ (existing)</t>
+        </is>
+      </c>
+      <c r="H368" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mixed (production ~$70-85k; eng. above $100k)</t>
+        </is>
+      </c>
+      <c r="I368" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle beyond the Aug. 27-28, 2026 apprenticeship-doubling announcement already on record; ~98 active job postings observed as of Sept. 2026 is a thin, non-discrete signal only.</t>
+        </is>
+      </c>
+      <c r="J368" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked; no change)</t>
+        </is>
+      </c>
+      <c r="K368" s="6" t="inlineStr">
+        <is>
+          <t>https://www.live5news.com/2026/08/27/boeing-double-apprenticeship-program-north-charleston-plant/</t>
+        </is>
+      </c>
+      <c r="L368" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B369" s="6" t="inlineStr">
+        <is>
+          <t>Goose Creek</t>
+        </is>
+      </c>
+      <c r="C369" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley</t>
+        </is>
+      </c>
+      <c r="D369" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E369" s="6" t="inlineStr">
+        <is>
+          <t>HII (Newport News Shipbuilding) — no new momentum this cycle</t>
+        </is>
+      </c>
+      <c r="F369" s="6" t="inlineStr">
+        <is>
+          <t>~475 employees (unchanged)</t>
+        </is>
+      </c>
+      <c r="G369" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H369" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I369" s="6" t="inlineStr">
+        <is>
+          <t>July 27, 2026 visit by Australia's Defence Minister reaffirmed AUKUS submarine-supplier qualification (13 Australian suppliers qualified via AUSSQ to date); HII states production at the site is up &gt;50% since its Jan. 2025 acquisition and that it 'intends to generate hundreds of additional jobs,' but no specific new job count, dollar figure, or dated milestone for a Goose Creek-specific expansion was found this cycle — remains too vague to move the needle.</t>
+        </is>
+      </c>
+      <c r="J369" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked; still inconclusive)</t>
+        </is>
+      </c>
+      <c r="K369" s="6" t="inlineStr">
+        <is>
+          <t>https://www.hii.com/news/hii-closes-on-asset-acquisition-to-expand-shipbuilding-capacity</t>
+        </is>
+      </c>
+      <c r="L369" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B370" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley / Dorchester</t>
+        </is>
+      </c>
+      <c r="C370" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley &amp; Dorchester</t>
+        </is>
+      </c>
+      <c r="D370" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E370" s="6" t="inlineStr">
+        <is>
+          <t>Google — data-center expansion</t>
+        </is>
+      </c>
+      <c r="F370" s="6" t="inlineStr">
+        <is>
+          <t>~160 apprentices (FTE n/d)</t>
+        </is>
+      </c>
+      <c r="G370" s="6" t="inlineStr">
+        <is>
+          <t>$9B</t>
+        </is>
+      </c>
+      <c r="H370" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I370" s="6" t="inlineStr">
+        <is>
+          <t>Standing gap continues for a 7th consecutive cycle — no verifiable dated 2026 project-specific milestone found despite repeated dedicated searches; all retrievable content still traces to the original Sept. 26, 2024 announcement.</t>
+        </is>
+      </c>
+      <c r="J370" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked; standing gap)</t>
+        </is>
+      </c>
+      <c r="K370" s="6" t="inlineStr">
+        <is>
+          <t>https://blog.google/company-news/inside-google/company-announcements/google-american-innovation-south-carolina/</t>
+        </is>
+      </c>
+      <c r="L370" s="6" t="inlineStr">
+        <is>
+          <t>Low-Med (persistent quiet, growing stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B371" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="C371" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D371" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E371" s="6" t="inlineStr">
+        <is>
+          <t>Siemens Smart Infrastructure</t>
+        </is>
+      </c>
+      <c r="F371" s="6" t="inlineStr">
+        <is>
+          <t>~150</t>
+        </is>
+      </c>
+      <c r="G371" s="6" t="inlineStr">
+        <is>
+          <t>$165M</t>
+        </is>
+      </c>
+      <c r="H371" s="6" t="inlineStr">
+        <is>
+          <t>Avg $78,811/yr ($37.89/hr); 90th pct ~$100k (Estimated/Inferred)</t>
+        </is>
+      </c>
+      <c r="I371" s="6" t="inlineStr">
+        <is>
+          <t>Reconfirmed unchanged; no new dated milestone this cycle.</t>
+        </is>
+      </c>
+      <c r="J371" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked)</t>
+        </is>
+      </c>
+      <c r="K371" s="6" t="inlineStr">
+        <is>
+          <t>https://www.foxcarolina.com/2026/03/18/tech-manufacturer-building-expanding-upstate-facilities-creating-150-new-jobs/</t>
+        </is>
+      </c>
+      <c r="L371" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B372" s="6" t="inlineStr">
+        <is>
+          <t>Woodruff / Spartanburg Co.</t>
+        </is>
+      </c>
+      <c r="C372" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D372" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E372" s="6" t="inlineStr">
+        <is>
+          <t>AIRSYS Cooling Technologies — global HQ</t>
+        </is>
+      </c>
+      <c r="F372" s="6" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G372" s="6" t="inlineStr">
+        <is>
+          <t>$40-60M</t>
+        </is>
+      </c>
+      <c r="H372" s="6" t="inlineStr">
+        <is>
+          <t>Eng. roles $69-93k; assembly $34-46k (Estimated/Inferred)</t>
+        </is>
+      </c>
+      <c r="I372" s="6" t="inlineStr">
+        <is>
+          <t>No dated confirmation found this cycle that manufacturing/3D-printing operations have begun; the Q1 2027 target remains unchanged from last cycle's clarification.</t>
+        </is>
+      </c>
+      <c r="J372" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked; no change)</t>
+        </is>
+      </c>
+      <c r="K372" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/spartanburg/business/airsys-data-center-water-woodruff-sc/article_86465e32-7d21-4bba-9a9b-3e6ea0e2d691.html</t>
+        </is>
+      </c>
+      <c r="L372" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B373" s="6" t="inlineStr">
+        <is>
+          <t>Gray Court</t>
+        </is>
+      </c>
+      <c r="C373" s="6" t="inlineStr">
+        <is>
+          <t>Laurens</t>
+        </is>
+      </c>
+      <c r="D373" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E373" s="6" t="inlineStr">
+        <is>
+          <t>Aptiv Services US — Connexial Center</t>
+        </is>
+      </c>
+      <c r="F373" s="6" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="G373" s="6" t="inlineStr">
+        <is>
+          <t>$120.8M</t>
+        </is>
+      </c>
+      <c r="H373" s="6" t="inlineStr">
+        <is>
+          <t>~$49-76k technician range (Estimated/Inferred)</t>
+        </is>
+      </c>
+      <c r="I373" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; 'Project Oracle' details reconfirmed unchanged.</t>
+        </is>
+      </c>
+      <c r="J373" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked; no change)</t>
+        </is>
+      </c>
+      <c r="K373" s="6" t="inlineStr">
+        <is>
+          <t>https://growlaurenscounty.com/news/article/momentum-continues-at-the-connexial-center-with-aptivs-investment</t>
+        </is>
+      </c>
+      <c r="L373" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B374" s="6" t="inlineStr">
+        <is>
+          <t>Easley (Anderson/Pickens border)</t>
+        </is>
+      </c>
+      <c r="C374" s="6" t="inlineStr">
+        <is>
+          <t>Anderson</t>
+        </is>
+      </c>
+      <c r="D374" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E374" s="6" t="inlineStr">
+        <is>
+          <t>Signature Foods USA</t>
+        </is>
+      </c>
+      <c r="F374" s="6" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="G374" s="6" t="inlineStr">
+        <is>
+          <t>$11.5M</t>
+        </is>
+      </c>
+      <c r="H374" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred sub-$50k (food mfg.)</t>
+        </is>
+      </c>
+      <c r="I374" s="6" t="inlineStr">
+        <is>
+          <t>Confirmed operations are already online; 202 jobs, no headcount change found this cycle.</t>
+        </is>
+      </c>
+      <c r="J374" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked)</t>
+        </is>
+      </c>
+      <c r="K374" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/greenville/business/easley-anderson-county-signature-foods-investment/article_1d618a58-af96-435a-a05c-7cc6f9253a83.html</t>
+        </is>
+      </c>
+      <c r="L374" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B375" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="C375" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D375" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E375" s="6" t="inlineStr">
+        <is>
+          <t>GNQ Insilico — AI/quantum techbio HQ</t>
+        </is>
+      </c>
+      <c r="F375" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G375" s="6" t="inlineStr">
+        <is>
+          <t>$500M (valuation, not capex)</t>
+        </is>
+      </c>
+      <c r="H375" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I375" s="6" t="inlineStr">
+        <is>
+          <t>SPAC business-combination deadline (extended to Sept. 28, 2026) confirmed still upcoming — falls just after this report's date; deal still described as 'expected to close Q3 2026.' Jobs remain undisclosed. Flag for direct confirmation next cycle.</t>
+        </is>
+      </c>
+      <c r="J375" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (deadline approaching)</t>
+        </is>
+      </c>
+      <c r="K375" s="6" t="inlineStr">
+        <is>
+          <t>https://www.greenvillebusinessmag.com/stories/techbio-innovator-gnq-moves-north-american-headquarters-labs-to-greenville,43132</t>
+        </is>
+      </c>
+      <c r="L375" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B376" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="C376" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D376" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E376" s="6" t="inlineStr">
+        <is>
+          <t>GE Vernova — gas turbine mfg (momentum flat this cycle)</t>
+        </is>
+      </c>
+      <c r="F376" s="6" t="inlineStr">
+        <is>
+          <t>650 total planned; ~200 hired past yr</t>
+        </is>
+      </c>
+      <c r="G376" s="6" t="inlineStr">
+        <is>
+          <t>$160M (Greenville)</t>
+        </is>
+      </c>
+      <c r="H376" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mixed (bulk likely sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I376" s="6" t="inlineStr">
+        <is>
+          <t>No material change found this cycle; new detail: the plant reportedly produced 62 turbines in 2026 to date, consistent with a continuing (flat-to-modest) ramp.</t>
+        </is>
+      </c>
+      <c r="J376" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked)</t>
+        </is>
+      </c>
+      <c r="K376" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/greenville/business/ge-vernova-greenville-sc-manufacturing-new-jobs/article_7ef2b156-de75-11ef-b98b-b7f96e0e5f82.html</t>
+        </is>
+      </c>
+      <c r="L376" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B377" s="6" t="inlineStr">
+        <is>
+          <t>Laurens Co. (Laurens)</t>
+        </is>
+      </c>
+      <c r="C377" s="6" t="inlineStr">
+        <is>
+          <t>Laurens</t>
+        </is>
+      </c>
+      <c r="D377" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E377" s="6" t="inlineStr">
+        <is>
+          <t>Suniva Inc. — solar-cell manufacturing plant</t>
+        </is>
+      </c>
+      <c r="F377" s="6" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="G377" s="6" t="inlineStr">
+        <is>
+          <t>$350M</t>
+        </is>
+      </c>
+      <c r="H377" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred sub-$100k blended</t>
+        </is>
+      </c>
+      <c r="I377" s="6" t="inlineStr">
+        <is>
+          <t>No change to the 564-job/$350M project scope; new financing milestone: the company closed an $835M capital raise in July 2026 to help fund the plant — a de-risking development, not a jobs change.</t>
+        </is>
+      </c>
+      <c r="J377" s="6" t="inlineStr">
+        <is>
+          <t>2026-07 (capital raise)</t>
+        </is>
+      </c>
+      <c r="K377" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/greenville/business/suniva-solar-cell-plant-laurens-sc/article_986c2fc2-2335-48cb-bd3c-92e89604c49c.html</t>
+        </is>
+      </c>
+      <c r="L377" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B378" s="6" t="inlineStr">
+        <is>
+          <t>Piedmont</t>
+        </is>
+      </c>
+      <c r="C378" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D378" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E378" s="6" t="inlineStr">
+        <is>
+          <t>Isuzu North America — truck assembly plant</t>
+        </is>
+      </c>
+      <c r="F378" s="6" t="inlineStr">
+        <is>
+          <t>700+</t>
+        </is>
+      </c>
+      <c r="G378" s="6" t="inlineStr">
+        <is>
+          <t>$280M</t>
+        </is>
+      </c>
+      <c r="H378" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred: assembly $35-56k, engineers $79-108k — blended sub-$100k</t>
+        </is>
+      </c>
+      <c r="I378" s="6" t="inlineStr">
+        <is>
+          <t>Confirmed active hiring continuing: a July 8, 2026 direct-hire event recruited for 150+ positions (assembly, quality, maintenance, warehouse, logistics) via a Greenville Tech partnership; 700-total-job plan and $280M capex unchanged, 2027 launch still targeted.</t>
+        </is>
+      </c>
+      <c r="J378" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-08 (hiring event)</t>
+        </is>
+      </c>
+      <c r="K378" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ccjdigital.com/business/article/15767928/isuzu-building-280m-truck-plant-in-south-carolina-creating-700-jobs</t>
+        </is>
+      </c>
+      <c r="L378" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B379" s="6" t="inlineStr">
+        <is>
+          <t>Ridgeville / Camp Hall</t>
+        </is>
+      </c>
+      <c r="C379" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley</t>
+        </is>
+      </c>
+      <c r="D379" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E379" s="6" t="inlineStr">
+        <is>
+          <t>Redwood Materials — battery-materials recycling campus</t>
+        </is>
+      </c>
+      <c r="F379" s="6" t="inlineStr">
+        <is>
+          <t>1,500 (over coming years)</t>
+        </is>
+      </c>
+      <c r="G379" s="6" t="inlineStr">
+        <is>
+          <t>$3.5B</t>
+        </is>
+      </c>
+      <c r="H379" s="6" t="inlineStr">
+        <is>
+          <t>$27-75/hr stated (~$56k-156k) — upper tier clears $100k</t>
+        </is>
+      </c>
+      <c r="I379" s="6" t="inlineStr">
+        <is>
+          <t>Standing gap continues for a 7th consecutive cycle for a fully confirmed, dated 2026 milestone — BUT a promising lead surfaced this cycle: company/trade-press items titled around 'Redwood begins critical materials recovery in South Carolina' describe first-facility startup on the 600-acre Berkeley Co. campus. The exact publish date and any updated job/production figures could not be confirmed this cycle (WebFetch blocked to both redwoodmaterials.com and recyclingtoday.com) — recommend a direct fetch attempt next cycle, as this could finally close the standing gap.</t>
+        </is>
+      </c>
+      <c r="J379" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (lead found, unconfirmed)</t>
+        </is>
+      </c>
+      <c r="K379" s="6" t="inlineStr">
+        <is>
+          <t>https://www.redwoodmaterials.com/news/redwood-begins-critical-materials-recovery-in-south-carolina/</t>
+        </is>
+      </c>
+      <c r="L379" s="6" t="inlineStr">
+        <is>
+          <t>Med (confirmed no fully-verified in-window update, not merely unfound; a strong unconfirmed lead exists)</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B380" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="C380" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D380" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E380" s="6" t="inlineStr">
+        <is>
+          <t>PSA Airlines — Charlotte headquarters</t>
+        </is>
+      </c>
+      <c r="F380" s="6" t="inlineStr">
+        <is>
+          <t>~400 (450+ total team members at HQ)</t>
+        </is>
+      </c>
+      <c r="G380" s="6" t="inlineStr">
+        <is>
+          <t>Not itemized</t>
+        </is>
+      </c>
+      <c r="H380" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Estimated/Inferred mixed corporate/admin/ops, likely sub-$100k blended)</t>
+        </is>
+      </c>
+      <c r="I380" s="6" t="inlineStr">
+        <is>
+          <t>Reconfirmed grand-opening coverage dated 2026-03-19 (some outlets say '3/25' for related coverage, same week) across multiple outlets; 400 jobs relocated from Dayton, OH, ~450+ on-site as of Jan. 2026; wage still undisclosed. No update since.</t>
+        </is>
+      </c>
+      <c r="J380" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-19 (reconfirmed)</t>
+        </is>
+      </c>
+      <c r="K380" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2026/03/19/governor-stein-celebrates-psa-airlines-headquarters-grand-opening-charlotte-highlights-only</t>
+        </is>
+      </c>
+      <c r="L380" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B381" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Steele Creek</t>
+        </is>
+      </c>
+      <c r="C381" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D381" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E381" s="6" t="inlineStr">
+        <is>
+          <t>Maersk — North American HQ (NEW to Watch)</t>
+        </is>
+      </c>
+      <c r="F381" s="6" t="inlineStr">
+        <is>
+          <t>520 (confirmed, stated)</t>
+        </is>
+      </c>
+      <c r="G381" s="6" t="inlineStr">
+        <is>
+          <t>$16M</t>
+        </is>
+      </c>
+      <c r="H381" s="6" t="inlineStr">
+        <is>
+          <t>$100,962 avg (stated) — clears $100k bar</t>
+        </is>
+      </c>
+      <c r="I381" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found despite a dedicated recheck; the only dated milestone remains the 2026-02-24 hiring-ramp delay approval, which stays pre-window under the further-shifted boundary too.</t>
+        </is>
+      </c>
+      <c r="J381" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked; still pre-window)</t>
+        </is>
+      </c>
+      <c r="K381" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/maersk-delays-charlotte-headquarters-plan-hiring-520-workers-by-1-year/</t>
+        </is>
+      </c>
+      <c r="L381" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); milestone timing at window edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B382" s="6" t="inlineStr">
+        <is>
+          <t>Salisbury / Granite Industrial Park</t>
+        </is>
+      </c>
+      <c r="C382" s="6" t="inlineStr">
+        <is>
+          <t>Rowan</t>
+        </is>
+      </c>
+      <c r="D382" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E382" s="6" t="inlineStr">
+        <is>
+          <t>Jabil Inc. — advanced manufacturing (AI/data-center hardware) (NEW to Watch)</t>
+        </is>
+      </c>
+      <c r="F382" s="6" t="inlineStr">
+        <is>
+          <t>1,181 (stated, over 5 yr)</t>
+        </is>
+      </c>
+      <c r="G382" s="6" t="inlineStr">
+        <is>
+          <t>~$264M near-term / ~$500M multi-year</t>
+        </is>
+      </c>
+      <c r="H382" s="6" t="inlineStr">
+        <is>
+          <t>$62,034 avg (stated) — sub-$100k</t>
+        </is>
+      </c>
+      <c r="I382" s="6" t="inlineStr">
+        <is>
+          <t>No dated 2026 confirmation was found that operations have actually begun at the 'mid-calendar-year 2026' target; open postings (Operations Development Manager, Facilities Manager, Sr. Engineering Manager) suggest active ramp-up but no press-confirmed operational-start date.</t>
+        </is>
+      </c>
+      <c r="J382" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked)</t>
+        </is>
+      </c>
+      <c r="K382" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/fortune-500-company-eyes-rowan-county-for-264-million-investment-creating-1181-jobs/</t>
+        </is>
+      </c>
+      <c r="L382" s="6" t="inlineStr">
+        <is>
+          <t>Medium (facts High; in-window operational milestone unconfirmed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B383" s="6" t="inlineStr">
+        <is>
+          <t>Morrisville / RTP-adjacent</t>
+        </is>
+      </c>
+      <c r="C383" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D383" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E383" s="6" t="inlineStr">
+        <is>
+          <t>Forge Nano — battery-manufacturing expansion ("America's Battery Gigafactory") (NEW to Watch)</t>
+        </is>
+      </c>
+      <c r="F383" s="6" t="inlineStr">
+        <is>
+          <t>250+ (projected, incremental to an existing 200-job 2023 commitment)</t>
+        </is>
+      </c>
+      <c r="G383" s="6" t="inlineStr">
+        <is>
+          <t>~$300M (incl. $100M DOE non-dilutive funding)</t>
+        </is>
+      </c>
+      <c r="H383" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed for the 2026 expansion (a 2023 filing implied ~$80k for the original 200 jobs, but that predates this expansion and is not carried forward as current)</t>
+        </is>
+      </c>
+      <c r="I383" s="6" t="inlineStr">
+        <is>
+          <t>Reconfirmed groundbreaking (2026-08-19); detail: expanding from 100,000 sf to ~315,000 sf, up to $100M DOE backing, ~3 GWh annual capacity at full production, production start targeted 2028.</t>
+        </is>
+      </c>
+      <c r="J383" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (rechecked)</t>
+        </is>
+      </c>
+      <c r="K383" s="6" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/08/19/3347836/0/en/forge-nano-breaks-ground-on-america-s-battery-gigafactory-to-strengthen-u-s-defense-supply-chains.html</t>
+        </is>
+      </c>
+      <c r="L383" s="6" t="inlineStr">
+        <is>
+          <t>High (jobs/date/DOE funding multiply corroborated); Low (wage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B384" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington / US-421 corridor</t>
+        </is>
+      </c>
+      <c r="C384" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover</t>
+        </is>
+      </c>
+      <c r="D384" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E384" s="6" t="inlineStr">
+        <is>
+          <t>Protocase / 45Drives / ProtoSpace Mfg — precision manufacturing campus (NEW to Watch)</t>
+        </is>
+      </c>
+      <c r="F384" s="6" t="inlineStr">
+        <is>
+          <t>~100 confirmed; company target 500+ total</t>
+        </is>
+      </c>
+      <c r="G384" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H384" s="6" t="inlineStr">
+        <is>
+          <t>$34,840-$41,409 stated for production/assembly roles (sub-$100k); wage for planned corporate/engineering roles not disclosed</t>
+        </is>
+      </c>
+      <c r="I384" s="6" t="inlineStr">
+        <is>
+          <t>Positive update, upgraded confidence: production is now confirmed by multiple sources to have actually launched in early 2026, ~3 years ahead of schedule (previously a single-source, Low-confidence claim); company held an April 30, 2026 career fair. Still 500+ current/planned jobs at $34,840-$41,409 for production roles (sub-$100k); wage for planned corporate/engineering roles still not disclosed.</t>
+        </is>
+      </c>
+      <c r="J384" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (upgraded confidence)</t>
+        </is>
+      </c>
+      <c r="K384" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wilmingtonbiz.com/technology/2026/08/12/protocase_firm_focus_growth_here/27730</t>
+        </is>
+      </c>
+      <c r="L384" s="6" t="inlineStr">
+        <is>
+          <t>Medium-High (production launch now multiply corroborated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B385" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington / US-421 corridor (Wilmington Trade Center)</t>
+        </is>
+      </c>
+      <c r="C385" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover</t>
+        </is>
+      </c>
+      <c r="D385" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E385" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington Trade Center — multi-tenant industrial park expansion (NEW to Watch)</t>
+        </is>
+      </c>
+      <c r="F385" s="6" t="inlineStr">
+        <is>
+          <t>1,500+ (aggregate, long-run park build-out; not a single employer's committed headcount)</t>
+        </is>
+      </c>
+      <c r="G385" s="6" t="inlineStr">
+        <is>
+          <t>$300-400M added tax base (park build-out); ~$3.3M county incentive</t>
+        </is>
+      </c>
+      <c r="H385" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I385" s="6" t="inlineStr">
+        <is>
+          <t>New candidate found this cycle: a New Hanover Co. incentive agreement (~$3.3M) supports expanding the park by up to 10 new buildings (13 total, 3.2M+ sq ft), projected at 1,500+ jobs and $300-400M in added tax base over a 2024-2031 build period. Does not qualify for Ranked or a standard Watch company-entry: it is a multi-tenant park build-out (not a single named employer/HQ), the jobs figure is an aggregate long-run park estimate rather than one company's committed headcount, and wages are undisclosed. Flagged given the scale.</t>
+        </is>
+      </c>
+      <c r="J385" s="6" t="inlineStr">
+        <is>
+          <t>2024-04 (incentive agreement; park build-out ongoing through 2031)</t>
+        </is>
+      </c>
+      <c r="K385" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wilmingtonbiz.com/government/2024/04/15/new_hanover_industrial_park_to_get_33m_in_incentives_for_expansion_new_jobs/25498</t>
+        </is>
+      </c>
+      <c r="L385" s="6" t="inlineStr">
+        <is>
+          <t>Medium (aggregate park estimate, not a single-employer commitment)</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B386" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="C386" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D386" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E386" s="6" t="inlineStr">
+        <is>
+          <t>EnerSys — lithium-cell manufacturing facility (MATERIAL RESTRUCTURING; moved from Excluded to Watch)</t>
+        </is>
+      </c>
+      <c r="F386" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed for the revised project (2024's ~500-job figure is now stale given the scope cut and should not be carried forward)</t>
+        </is>
+      </c>
+      <c r="G386" s="6" t="inlineStr">
+        <is>
+          <t>~$500M total net investment (restructured); $150M DOE grant + up to $200M state/local incentives confirmed</t>
+        </is>
+      </c>
+      <c r="H386" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I386" s="6" t="inlineStr">
+        <is>
+          <t>Material in-window update (announced 2026-07-23): EnerSys 'refined' its Greenville lithium-cell plant, pivoting from general-purpose EV/grid battery cells to a defense/aerospace-focused facility, cutting planned capacity from ~4-5 GWh to ~1 GWh, and confirming a $150M DOE grant plus up to $200M in state/local incentives. Construction now targeted for 1H FY2028 (later than the original 2025 construction start). No jobs figure for the revised, smaller-scope project was found in any source — moved here from Excluded/Noise (where it sat as a stale 'sleeper') given the concrete new financing/scope details, but held at Watch rather than Ranked pending a disclosed headcount.</t>
+        </is>
+      </c>
+      <c r="J386" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K386" s="6" t="inlineStr">
+        <is>
+          <t>https://investor.enersys.com/news/news-details/2026/EnerSys-Refines-Plans-for-DefenseFocused-Lithium-Cell-Manufacturing-Facility-with-DOE-Support/default.aspx</t>
+        </is>
+      </c>
+      <c r="L386" s="6" t="inlineStr">
+        <is>
+          <t>Medium (restructuring/financing facts corroborated; jobs figure undisclosed)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36838,7 +42339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -43193,6 +48694,300 @@
         </is>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t>VinFast — EV/battery megafactory (litigation ongoing; response filed)</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>Moncure (Chatham)</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>0 (deal terminated; a 1,400-job revised plan floated 3/18/26 remains superseded by litigation)</t>
+        </is>
+      </c>
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-02 (response filed)</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>VinFast met the Sept. 2, 2026 deadline by filing an 80-page response denying it breached the site agreement, calling the state's suit 'premature,' and asserting it has until Dec. 31, 2026 to hit 1,750 jobs/$500M invested (~$229M invested to date per the company). Separately, Chatham County formally terminated its own $400M incentive agreement with VinFast (voted late July, finalized 2026-07-31) for missed performance obligations; no incentive dollars were ever disbursed. Chatham commissioners set a closed-session special meeting for 2026-09-15 covering an unspecified economic-development/incentives matter alongside the county's data-center-moratorium lawsuit — outcome unknown as of this report. Still an unresolved, negative/closed signal, not a qualifying announcement.</t>
+        </is>
+      </c>
+      <c r="H152" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/nccapitol/vinfast-fights-nc-effort-to-boot-it-from-chatham-megasite-new-legal-filing-september-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>Daimler Truck Financial Services USA — HQ relocation (now fully verified)</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E153" s="6" t="inlineStr">
+        <is>
+          <t>276 (verified: 193 new + 83 relocated from MI/TX; $133,940 avg wage stated, clears $100k bar)</t>
+        </is>
+      </c>
+      <c r="F153" s="6" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="G153" s="6" t="inlineStr">
+        <is>
+          <t>Wage, jobs, and capex ($7.8M) now fully confirmed (NC Commerce, Business NC, Axios Charlotte) — new HQ at the Boyle Building, 13034 Ballantyne Corporate Place. However, the announcement date (2025-05-27) sits over a year outside the current 6-month window, and no in-window milestone (office opening, lease finalization, occupancy) was found despite dedicated searching. Re-flag if a 2026 occupancy/opening milestone surfaces.</t>
+        </is>
+      </c>
+      <c r="H153" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2025/05/27/governor-stein-announces-new-headquarters-operations-daimler-truck-financial-services-usa-charlotte</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t>Fidelity Investments — Triangle-area jobs pledge (DEBUNKED — dropped from tracking)</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>Triangle area</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E154" s="6" t="inlineStr">
+        <is>
+          <t>620 (per a 2023 headline only)</t>
+        </is>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
+        <is>
+          <t>2023 (stale)</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="inlineStr">
+        <is>
+          <t>Resolved this cycle: the '620 jobs' figure traces to a 2023 article about Fidelity's plan to hire 4,000 people companywide in H1 2023, of which 620 were in NC — not a 2026 announcement. No evidence found of any fresh 2026 Fidelity Triangle hiring announcement. Dropped as an active lead rather than continuing to carry it as 'unverified.'</t>
+        </is>
+      </c>
+      <c r="H154" s="6" t="inlineStr">
+        <is>
+          <t>https://www.aol.com/fidelity-pledges-620-jobs-nc-161500733.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B155" s="6" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific — Weaverville facility phase-out/closure (NEW negative signal)</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>Weaverville (Buncombe)</t>
+        </is>
+      </c>
+      <c r="D155" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>421 (layoffs; peak employment was 550)</t>
+        </is>
+      </c>
+      <c r="F155" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-08 (WARN filed; pre-window)</t>
+        </is>
+      </c>
+      <c r="G155" s="6" t="inlineStr">
+        <is>
+          <t>Negative signal, newly identified this cycle: WARN filed Jan. 8, 2026 for the phased closure of the 330,000 sq ft Aiken Road facility as product lines shift to other US Thermo Fisher sites; first separations targeted Dec. 31, 2026, continuing through Dec. 31, 2027. WARN filing date is pre-window, but the phase-out is an ongoing, materially relevant counterweight to Buncombe Co.'s recent run of manufacturing-expansion wins (Eaton, Pratt &amp; Whitney, BorgWarner). Not a qualifying growth announcement regardless.</t>
+        </is>
+      </c>
+      <c r="H155" s="6" t="inlineStr">
+        <is>
+          <t>https://wlos.com/news/local/thermo-fisher-scientific-phase-out-weaverville-operations-2026-customer-demands-jobs-employees-company-site-product-facility-mass-layoffs-closures</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t>Prepac Manufacturing — plant closure (NEW negative signal)</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>Whitsett (Guilford)</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
+          <t>~200 (layoffs)</t>
+        </is>
+      </c>
+      <c r="F156" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-03 (WARN filed); effective 2026-05-02</t>
+        </is>
+      </c>
+      <c r="G156" s="6" t="inlineStr">
+        <is>
+          <t>Negative signal, newly identified this cycle and fully in-window: the Canadian furniture maker is shuttering its Hendren Road plant, citing high domestic costs and Chinese import competition. Low-wage furniture manufacturing; not a qualifying growth announcement.</t>
+        </is>
+      </c>
+      <c r="H156" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/prepac-laying-off-200-furniture-workers-in-guilford-county/</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="inlineStr">
+        <is>
+          <t>TD Bank — Ballantyne office expansion (unverified lead)</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Ballantyne</t>
+        </is>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="G157" s="6" t="inlineStr">
+        <is>
+          <t>A td.com corporate story referencing TD Bank 'enhancing its corporate presence in Charlotte with new office space in Ballantyne' surfaced this cycle but could not be opened/verified for job count, wage, or date before the research session's search budget was exhausted. Flagged as a lead for next-cycle verification rather than promoted on an unconfirmed basis.</t>
+        </is>
+      </c>
+      <c r="H157" s="6" t="inlineStr">
+        <is>
+          <t>https://stories.td.com/us/en/article/td-bank-enhances-corporate-presence-in-charlotte-with-new-office-space-in-ballantyne</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>Bank of America / Wells Fargo — AI-driven headcount pressure (background context, not a discrete event)</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (no specific facility/date)</t>
+        </is>
+      </c>
+      <c r="F158" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-16 (pre-window)</t>
+        </is>
+      </c>
+      <c r="G158" s="6" t="inlineStr">
+        <is>
+          <t>Background/negative context only, not a discrete qualifying or dated event: reporting from Jan. 16, 2026 describes both banks signaling flat-to-declining Charlotte-area headcount in 2026 due to AI adoption (BofA crediting AI with eliminating the need for ~2,000 coding-related roles companywide; Wells Fargo, with 27,000 Charlotte employees — its largest single-location workforce — 'signaling more job cuts' through 2026). Logged for awareness given Wells Fargo's and BofA's outsized Charlotte footprint, but excluded as non-specific and pre-window.</t>
+        </is>
+      </c>
+      <c r="H158" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/01/16/bank-america-wells-fargo-ai-job-cuts</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -43204,7 +48999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -45455,6 +51250,438 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>Business North Carolina — SMBC move-in</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg Co. NC</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group fall-2026 move-in timing at former One Wells Fargo Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>WRAL — JetZero groundbreaking / hiring delay</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>Guilford Co. NC</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>JetZero NC3 groundbreaking (June 15, 2026); JDIG hiring-schedule amendment / state-budget-funding delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Carolina Journal — JetZero budget funding</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>https://www.carolinajournal.com/</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>Guilford Co. NC</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>NC FY26-27 budget's $133.9M JetZero allocation; hiring-timeline delay confirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>HITT Contracting — JetZero groundbreaking</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>trade_journal</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>https://www.hitt.com/</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>Guilford Co. NC</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>JetZero NC Composite Center (NC3) construction-start detail, general contractor</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>WLTX — Scout Motors Supplier Park / veto</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wltx.com/</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>Richland Co. SC</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors $300M Supplier Park announcement; McMaster veto on $150M cost-overrun payment</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>Post and Courier — Scout Motors cost-overrun controversy</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/columbia/</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>Richland Co. SC</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors $150M payment status; Legislative Audit Council review timeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>WIS-TV — Scout Motors Shives lawsuit</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wistv.com/</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>Richland Co. SC</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>Shives family lawsuit against Scout Motors/Richland County; environmental-fine repayment</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>SC Daily Gazette / WSPA / Fox Carolina — Spartanburg moratorium</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wspa.com/</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg Co. SC</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>County moratorium 3rd-reading scheduling and grandfathering of NorthMark/Valara; Sept. 9 fact-finding hearing; Sept. 10 council session</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>WLOS — Thermo Fisher Weaverville closure</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>https://wlos.com/</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>Buncombe Co. NC</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific Weaverville facility phase-out WARN notice (421 jobs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>Business North Carolina — Prepac Manufacturing closure</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>Guilford Co. NC</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>Prepac Manufacturing Whitsett plant closure WARN notice (~200 jobs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>TD Bank corporate stories</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>company_primary</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>https://stories.td.com/</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg Co. NC</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>TD Bank Ballantyne office expansion (unverified lead)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>Axios Charlotte — bank AI headcount</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg Co. NC</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>Bank of America / Wells Fargo AI-driven headcount pressure, Jan. 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>EnerSys investor relations</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>company_primary</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>https://investor.enersys.com/</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>Greenville Co. SC</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>EnerSys Greenville lithium-cell facility defense-focused restructuring, DOE grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>WilmingtonBiz — Wilmington Trade Center expansion</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wilmingtonbiz.com/</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover Co. NC</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington Trade Center multi-tenant industrial park expansion incentive agreement</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>WRAL — VinFast September response filing</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/nccapitol/</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>Chatham Co. NC</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>VinFast's Sept. 2, 2026 response to NC's amended complaint</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>Chatham Journal — VinFast / Chatham Co. termination</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>https://chathamjournal.com/</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>Chatham Co. NC</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>Chatham County's termination of its $400M VinFast incentive agreement; Sept. 15 special meeting</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -45466,7 +51693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -47082,6 +53309,226 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; eighth consecutive quiet cycle, no new milestone found; lease/move-in timing reconfirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma (Rock Hill)</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new dated milestone found this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie (Durham)</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; incentive stack and job-count sourcing variance (730 vs 734) reconfirmed, no fresher dated development.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV plant (Blythewood)</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>Raised from 83; new $300M Supplier Park investment adds ~1,000 jobs and pushes total capital commitment past $2.3B, improving both the job-count and capital-investment-certainty factors. $150M state payment remains undisbursed and the Shives lawsuit remains unresolved, so the increase is modest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>Genentech (Holly Springs)</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle; fuller incentive breakdown reconfirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>JetZero (Greensboro)</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>Held flat; groundbreaking/construction-start on the NC3 building and $133.9M in dedicated state funding are a genuine de-risking event, offset by a confirmed ~1-year hiring-ramp delay (JDIG timeline-amendment request, ~0 new 2027 jobs vs. 1,050 planned). Net judged a wash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — Global HQ (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no fresher permit/construction news found. Franchise-dealer litigation in five states noted as a risk factor but not scored, since the company states it is proceeding with the HQ regardless.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>Citigroup (Charlotte / Ballantyne)</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no fresher milestone found despite a dedicated recheck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Novartis (Durham/Morrisville)</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>Aspida Financial Services (Durham)</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; second consecutive cycle with no dated confirmation that the Imperial Tower renovation has completed past its 'summer 2026' target — flagged as a persistent risk item.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/Carolinas_Job_Growth_Running_Database.xlsx
+++ b/reports/Carolinas_Job_Growth_Running_Database.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Week of 2026-09-14  ·  Window 2026-03-14 to 2026-09-14  ·  NC + SC</t>
+          <t>Week of 2026-09-21  ·  Window 2026-03-21 to 2026-09-21  ·  NC + SC</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14  (Week 9)</t>
+          <t>2026-09-21  (Week 10)</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 to 2026-09-14  (trailing 6 months)</t>
+          <t>2026-03-21 to 2026-09-21  (trailing 6 months)</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>94</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>46</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Charlotte / Uptown (Mecklenburg, NC) — SMBC Group, score 93 (unchanged, eighth consecutive quiet cycle)</t>
+          <t>Charlotte / Uptown (Mecklenburg, NC) — SMBC Group, score 94 (raised from 93 on a firmer October move-in date and active campus recruiting)</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Scout Motors' Blythewood, SC EV assembly plant (83 -&gt; 85) on a newly announced $300M Supplier Park (~1,000 more jobs, total SC commitment now $2.3B+); JetZero (Greensboro) held flat at 81 despite a genuinely mixed cycle — construction broke ground on its NC Composite Center (NC3) building with $133.9M in new dedicated state funding, but the company confirmed a roughly one-year hiring-ramp delay (JDIG timeline-amendment request; ~0 new jobs expected in 2027 vs. 1,050 planned) tied to state-budget-funding holdups.</t>
+          <t>AbbVie (Durham/RTP) rose 85 -&gt; 87 after Durham City Council added a companion incentive layer (~$24.8M combined city+county) on top of the county's July approval; JetZero (Greensboro) rose 81 -&gt; 82 as its previously-pending JDIG hiring-delay amendment was formally finalized while $133.9M in state funding was released and NC3 construction visibly proceeds. Aspida Financial Services (Durham, score 74) was REMOVED from Ranked — its only two confirmed milestones (Nov./Dec. 2025) are now conclusively pre-window with no fresher 2026 update found for a third consecutive cycle.</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>A second consecutive quiet cycle for brand-new Ranked-tier finds (all five regional research passes found zero new 500+ job / $100k+ wage qualifying announcements), but an unusually active cycle for material updates within existing Ranked/Watch entries and for litigation/regulatory resolution. Most significant: the SC Public Service Commission ruled unanimously that NorthMark/Valara's Spartanburg data center is NOT subject to Utility Siting Act power-plant rules (a loss for SELC and other opponents), though SELC's separate Circuit Court injunction motion remains unresolved and Spartanburg County's moratorium 3rd reading (set for Sept. 21) is expected to grandfather the project regardless of outcome. VinFast met its Sept. 2 litigation deadline with an 80-page response denying breach, while Chatham County separately finalized termination of its own $400M incentive agreement with the company (July 31). Two new negative signals were identified: Thermo Fisher Scientific's phased closure of its Weaverville, NC facility (421 jobs) and Prepac Manufacturing's Whitsett, NC plant closure (~200 jobs, fully in-window). Daimler Truck Financial Services USA (Charlotte, 276 jobs, $133,940 stated wage) was fully verified but confirmed pre-window; a previously tracked Fidelity Investments 'lead' was debunked as stale 2023 data and dropped. EnerSys's Greenville, SC lithium-cell project was found to have materially restructured (defense-focused pivot, $150M DOE grant, up to $200M in incentives) and was moved from Excluded to Watch pending a disclosed headcount for the revised, smaller-scope project.</t>
+          <t>No new 500+ job / $100k+ wage qualifying announcement was found in any of the five regions this cycle — the third consecutive quiet cycle for brand-new Ranked-tier finds — but the trailing-6-month window's weekly advance forced a genuine reckoning with several long-tracked entries whose only dated milestones have now aged out of window: Aspida Financial Services was removed from Ranked, and Ralliant Corp., Jewelers Mutual Group, Wolfspeed, and Environmental Air Systems were removed from Markets to Watch (Wolfspeed's WARN-notice dating ambiguity, flagged for two cycles, was conclusively resolved this cycle as a mid-2025 event). Citigroup (Charlotte/Ballantyne) narrowly avoided the same fate: a dedicated recheck found a genuinely dated, in-window hiring-progress update (2026-04-23) that keeps it Ranked. The single biggest open story is the Spartanburg NorthMark/Valara data-center fight: a Sept. 17 Circuit Court hearing on SELC's injunction ended with no ruling (judge took it under advisement), and the county council's moratorium 3rd/final-reading vote was scheduled for the evening of this report's compilation (Sept. 21) with the outcome not yet known. The Wake County Board of Commissioners' vote on the WakeMed/Atrium Health merger was also scheduled for today with the outcome unknown. A new Watch entry (TD Bank, Ballantyne) was promoted from an unverified lead after a confirmed in-window office-occupancy milestone, and Google's Berkeley/Dorchester, SC data-center entry was downgraded to stale background after 8 consecutive cycles with no dated 2026 update.</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>All five regions (Charlotte metro, NC Triangle, NC Triad/WNC/Coastal, Upstate SC, SC Midlands/Lowcountry) received a full research pass this cycle via parallel dedicated research agents. WebFetch (direct page retrieval) again returned blocked/EGRESS_BLOCKED for essentially every news/gov domain attempted across all agents; every finding below relies on WebSearch-result content/snippets, which do surface real, retrievable source URLs, cross-checked across multiple independent queries. Each region's WebSearch budget (200 calls) was exhausted before every conceivable follow-up query could be run this cycle — gaps are flagged per-item in the Watch tier and Excluded/Noise sections (e.g., a possible dating discrepancy on the Wolfspeed WARN notice, the AWS/Amazon Hamlet Sept. 1 open-house outcome, the Wake County EDGE7 pipeline-size discrepancy, and a not-yet-confirmed Redwood Materials startup lead). No numbers were invented; 'Not disclosed' marks missing figures and 'Estimated/Inferred' marks derived ones with basis stated.</t>
+          <t>All five regions (Charlotte metro, NC Triangle, NC Triad/WNC/Coastal, Upstate SC, SC Midlands/Lowcountry) received a full research pass this cycle via parallel dedicated research agents. WebFetch (direct page retrieval) again returned blocked/egress-restricted for the large majority of news/gov/company domains attempted across all agents; nearly every finding below relies on WebSearch-result content/snippets, which do surface real, retrievable source URLs, cross-checked across multiple independent queries per claim. No numbers were invented; 'Not disclosed' marks missing figures and 'Estimated/Inferred' marks derived ones with basis stated.</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Trailing 6 months now runs 2026-03-14 to 2026-09-14 — the window advanced one week. No currently Ranked entry's sole milestone fell out of window this cycle. In the Watch tier, Ralliant Corp. (2026-03-05) remains flagged 'at risk' as it now sits further before the window start; a new dating concern surfaced for Wolfspeed's tracked WARN notice, which multiple sources this cycle date to June 9, 2025 (not 2026) — if correct, its sole Watch-qualifying milestone is more than a year outside the window and it is now flagged 'at risk' pending a direct WARN-database check next cycle.</t>
+          <t>Trailing 6 months now runs 2026-03-21 to 2026-09-21 — the window advanced one week. This shift pushed several long-tracked entries' sole dated milestones out of window: Aspida Financial Services (Ranked, removed), and Ralliant Corp., Jewelers Mutual Group, and Wolfspeed (Watch, all removed). Citigroup (Ranked) was at the same risk but was kept after a fresh in-window milestone was located (2026-04-23). Scout Motors HQ's 2nd-building filing (2026-03-28) remains just inside window; watch it closely next cycle.</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Daimler Truck Financial Services USA (Charlotte, 276 jobs) was fully verified this cycle ($133,940 avg wage, stated — clears the $100k bar; $7.8M capex) but its only dated milestone (2025-05-27) sits over a year outside the current window — moved from an unverified lead to Excluded/Noise as 'verified but pre-window,' consistent with the AssetMark/Walmart precedent from prior cycles. The previously tracked Fidelity Investments 'Triangle-area 620 jobs' lead was traced to a 2023 article and is not a 2026 event at all — dropped from tracking rather than carried forward as unverified. EnerSys's Greenville, SC lithium-cell project (previously an Excluded 'sleeper') announced a material scope restructuring (defense/aerospace pivot, capacity cut from ~4-5 GWh to ~1 GWh, $150M DOE grant, up to $200M in state/local incentives) on 2026-07-23; because the revised project's job count was not disclosed in any source found, it was moved to Markets to Watch rather than promoted to Ranked, and its stale ~500-job 2024 figure was not carried forward.</t>
+          <t>Wolfspeed's WARN-notice dating ambiguity — flagged as unresolved for two consecutive prior cycles — was conclusively resolved this cycle via indexed WARN data: notification 6/24/2025, effective 11/14/2025, entirely a 2025 event over a year outside the current window; the entry was removed from Watch. Redwood Materials' 7-cycle 'standing gap' was also resolved: multiple independent outlets confirm its Camp Hall, SC critical-materials-recovery operations actually began in November 2025 (pre-window), explaining the lack of further in-window movement. EnerSys's Greenville, SC lithium-cell project (restructured 2026-07-23) still has no disclosed jobs figure for the revised, smaller-scope project as of this cycle — the pre-restructuring ~500-job 2024 figure must not be carried forward. TD Bank's Ballantyne office expansion was promoted from an unverified Excluded lead to active Watch after a confirmed dated in-window occupancy milestone (though it still discloses no jobs/wage figure).</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>10 of 11 prior-ranked deals repeat this cycle at unchanged scores; Scout Motors' Blythewood EV plant rises 83 -&gt; 85 (Gaining Momentum) on its new $300M Supplier Park; JetZero is tagged Updated (net score unchanged at 81) reflecting its mixed groundbreaking-plus-hiring-delay cycle. 0 new Ranked-tier finds, 0 removed. Watch tier: 2 new items added (Wilmington Trade Center Expansion; EnerSys Greenville, moved from Excluded), 0 formally removed, but Wolfspeed and Environmental Air Systems are both flagged for likely removal/further at-risk status next cycle absent a fresh in-window milestone. Six new Excluded/Noise entries were logged this cycle: an updated VinFast litigation entry, Daimler Truck Financial Services USA (verified-but-pre-window), the debunked Fidelity Investments lead, two new negative signals (Thermo Fisher Weaverville, Prepac Whitsett), a new TD Bank Ballantyne unverified lead, and a Bank of America/Wells Fargo AI-headcount background note.</t>
+          <t>9 of 10 remaining prior-ranked deals repeat or update this cycle; SMBC (93-&gt;94), AbbVie (85-&gt;87), and JetZero (81-&gt;82) each rose modestly on new capital-certainty/momentum facts. Aspida Financial Services (score 74) was REMOVED from Ranked (milestones now pre-window, no fresh 2026 update found). 0 new Ranked-tier finds this cycle. Watch tier: 1 new item added (TD Bank, Ballantyne — promoted from an unverified lead), 4 items removed (Ralliant Corp., Jewelers Mutual Group, Wolfspeed, Environmental Air Systems — all confirmed pre-window with no fresh update), and 1 item downgraded to stale background (Google Berkeley/Dorchester, SC — 8 consecutive quiet cycles). New Excluded/Noise entries include the Aspida/Ralliant/Jewelers Mutual/Wolfspeed/Environmental Air Systems removals themselves, an updated VinFast entry (Sept. 15/16 closed-session meeting held, outcome undisclosed), a new Walmart corporate-office layoff signal (267 jobs, Charlotte), and several sub-threshold items.</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S85"/>
+  <dimension ref="A1:S95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8462,6 +8462,916 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Uptown</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group — 2nd US HQ / bank operations</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>Office / HQ banking</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>$165,316 avg (stated; vs county $90,706)</t>
+        </is>
+      </c>
+      <c r="K86" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L86" s="6" t="inlineStr">
+        <is>
+          <t>$50.5M</t>
+        </is>
+      </c>
+      <c r="M86" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $70.0M / 12 yr; $23.3M IDF-Utility Account</t>
+        </is>
+      </c>
+      <c r="N86" s="6" t="inlineStr">
+        <is>
+          <t>Active recruiting + firmer October move-in date</t>
+        </is>
+      </c>
+      <c r="O86" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P86" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bankingdive.com/news/smbc-revs-up-recruiting-charlotte-banking-talent-tech-cyber-data-jobs/830268/</t>
+        </is>
+      </c>
+      <c r="Q86" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R86" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="S86" s="6" t="inlineStr">
+        <is>
+          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C87" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill / York Co.</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>Office/HQ + biopharma mfg</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>$141,502 avg HQ / $102,752 avg mfg (both stated)</t>
+        </is>
+      </c>
+      <c r="K87" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L87" s="6" t="inlineStr">
+        <is>
+          <t>$1.5B</t>
+        </is>
+      </c>
+      <c r="M87" s="6" t="inlineStr">
+        <is>
+          <t>Fee-in-lieu-of-tax; $65M SC Coordinating Council Closing Fund grant to York Co.</t>
+        </is>
+      </c>
+      <c r="N87" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone (unchanged)</t>
+        </is>
+      </c>
+      <c r="O87" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="P87" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/york-county/news/octapharma-how-company-chose-rock-hill/article_b1518265-129d-4134-9ff9-f2d686950bd6.html</t>
+        </is>
+      </c>
+      <c r="Q87" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R87" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S87" s="6" t="inlineStr">
+        <is>
+          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C88" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>Durham / RTP</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie — biopharma manufacturing campus</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="n">
+        <v>734</v>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / R&amp;D / lab</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>$118,041 avg (stated; vs county $102,817)</t>
+        </is>
+      </c>
+      <c r="K88" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L88" s="6" t="inlineStr">
+        <is>
+          <t>$1.4B</t>
+        </is>
+      </c>
+      <c r="M88" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $19.3M / 12 yr; $6.4M IDF-Utility; Durham Co. performance-based award not-to-exceed $15,450,000 ("Project Glass," approved 2026-07-13); a Durham City Council incentive item for the same project appeared on its 2026-09-17 agenda, bringing the combined city+county local incentive to ~$24.8M</t>
+        </is>
+      </c>
+      <c r="N88" s="6" t="inlineStr">
+        <is>
+          <t>Durham City Council incentive layer added on top of county approval</t>
+        </is>
+      </c>
+      <c r="O88" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="P88" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/abbvie-pledges-1-3-billion-investment-734-jobs-in-durham/</t>
+        </is>
+      </c>
+      <c r="Q88" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R88" s="6" t="inlineStr">
+        <is>
+          <t>Suburban-urban</t>
+        </is>
+      </c>
+      <c r="S88" s="6" t="inlineStr">
+        <is>
+          <t>High-end MF + move-up for-sale around Durham/RTP; spillover Wake/Orange. Construction-phase rental near-term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C89" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>Blythewood / N. Columbia</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV assembly plant + new Supplier Park</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>Auto mfg + salaried eng.</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>$30-$37.50/hr line (stated); salaried higher</t>
+        </is>
+      </c>
+      <c r="K89" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mix supports above-median HH income</t>
+        </is>
+      </c>
+      <c r="L89" s="6" t="inlineStr">
+        <is>
+          <t>$2.3B+ (site $2.0B + $25M training center + $300M Supplier Park)</t>
+        </is>
+      </c>
+      <c r="M89" s="6" t="inlineStr">
+        <is>
+          <t>State/local package (2023); $25M readySC; the Aug. 17 veto took effect immediately, allowing the $150M state cost-overrun payment to be made without waiting for the Legislative Audit Council review (due ~mid-Dec. 2026)</t>
+        </is>
+      </c>
+      <c r="N89" s="6" t="inlineStr">
+        <is>
+          <t>Cost-overrun payment procedurally cleared; lawsuit and headcount unresolved</t>
+        </is>
+      </c>
+      <c r="O89" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="P89" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/2026/08/17/sc-governor-vetoes-delay-on-paying-agency-overruns-at-scout-motors-site/</t>
+        </is>
+      </c>
+      <c r="Q89" s="6" t="inlineStr">
+        <is>
+          <t>Medium (facts); Low (headcount/timeline)</t>
+        </is>
+      </c>
+      <c r="R89" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S89" s="6" t="inlineStr">
+        <is>
+          <t>Bifurcated: salaried/professional -&gt; higher-income for-sale &amp; Class-A; hourly base + supplier-park jobs -&gt; workforce/missing-middle rental in N. Richland/Fairfield.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C90" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs / SW Wake</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>Genentech — biomanufacturing expansion (unchanged)</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>~$119,833 avg (stated, 2025 tranche)</t>
+        </is>
+      </c>
+      <c r="K90" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L90" s="6" t="inlineStr">
+        <is>
+          <t>~$2.0B</t>
+        </is>
+      </c>
+      <c r="M90" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
+        </is>
+      </c>
+      <c r="N90" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="O90" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="P90" s="6" t="inlineStr">
+        <is>
+          <t>https://www.biospace.com/press-releases/genentech-marks-topping-out-milestone-for-new-holly-springs-north-carolina-manufacturing-facility</t>
+        </is>
+      </c>
+      <c r="Q90" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R90" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S90" s="6" t="inlineStr">
+        <is>
+          <t>Strong higher-income for-sale + Class-A rental demand in fast-growing SW Wake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C91" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>JetZero — aerospace plant (hiring-delay amendment finalized; construction + funding progressing)</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace mfg + eng.</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>$89,340 avg (stated, 2025)</t>
+        </is>
+      </c>
+      <c r="K91" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated (2025)</t>
+        </is>
+      </c>
+      <c r="L91" s="6" t="inlineStr">
+        <is>
+          <t>$4.7B</t>
+        </is>
+      </c>
+      <c r="M91" s="6" t="inlineStr">
+        <is>
+          <t>Transformative JDIG up to $1.018B-$1.57B / 37 yr; Guilford grant $75.9M / 20 yr; $133.9M NC FY26-27 budget funding formally released upon Gov. Stein's 2026-07-07 signature (on top of $118.1M already allotted)</t>
+        </is>
+      </c>
+      <c r="N91" s="6" t="inlineStr">
+        <is>
+          <t>JDIG hiring-schedule amendment formally approved; state funding released; NC3 construction ongoing</t>
+        </is>
+      </c>
+      <c r="O91" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="P91" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/budget-upholds-jetzero-incentives-payout-plan/</t>
+        </is>
+      </c>
+      <c r="Q91" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Medium (hiring-ramp timeline now formally fixed but still delayed)</t>
+        </is>
+      </c>
+      <c r="R91" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S91" s="6" t="inlineStr">
+        <is>
+          <t>Same long-run scale; the hiring-ramp delay is now formally locked into the JDIG (removing ambiguity) while funding release and visible NC3 construction are genuine de-risking offsets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C92" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group — East Coast ops hub (unchanged)</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>Office — finance/tech</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>$194,141 avg (stated; NC Commerce JDIG figure)</t>
+        </is>
+      </c>
+      <c r="K92" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L92" s="6" t="inlineStr">
+        <is>
+          <t>$60M</t>
+        </is>
+      </c>
+      <c r="M92" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $17.2M / 12 yr; $5.7M IDF-Utility; $19.4M state grant/12yr + $2.2M training funds + $1M local</t>
+        </is>
+      </c>
+      <c r="N92" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="O92" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="P92" s="6" t="inlineStr">
+        <is>
+          <t>https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
+        </is>
+      </c>
+      <c r="Q92" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R92" s="6" t="inlineStr">
+        <is>
+          <t>Urban-suburban</t>
+        </is>
+      </c>
+      <c r="S92" s="6" t="inlineStr">
+        <is>
+          <t>High-skill eng/data workforce -&gt; walkable South End/Uptown &amp; inner-suburban Class-A and for-sale TH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C93" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Plaza Midwood</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — Global HQ (litigation risk growing)</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>Corporate HQ / professional</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>$153,978 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K93" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L93" s="6" t="inlineStr">
+        <is>
+          <t>$206.9M</t>
+        </is>
+      </c>
+      <c r="M93" s="6" t="inlineStr">
+        <is>
+          <t>Original 2025-11-12 HQ incentive/relocation commitment</t>
+        </is>
+      </c>
+      <c r="N93" s="6" t="inlineStr">
+        <is>
+          <t>No permit/construction progress found; franchise-dealer litigation footprint widened</t>
+        </is>
+      </c>
+      <c r="O93" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="P93" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/scout-motors-hq-move-turbocharges-second-office-building-in-plaza-midwood/</t>
+        </is>
+      </c>
+      <c r="Q93" s="6" t="inlineStr">
+        <is>
+          <t>Med (facts High; milestone stage early)</t>
+        </is>
+      </c>
+      <c r="R93" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="S93" s="6" t="inlineStr">
+        <is>
+          <t>Supports Plaza Midwood/NoDa/Elizabeth close-in rental and townhome demand from a young, high-wage corporate workforce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C94" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Ballantyne</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>Citigroup — Charlotte office (hiring ramp confirmed proceeding)</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="n">
+        <v>510</v>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>Office / financial services</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="inlineStr">
+        <is>
+          <t>$131,832 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K94" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L94" s="6" t="inlineStr">
+        <is>
+          <t>$16.1M</t>
+        </is>
+      </c>
+      <c r="M94" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $8.9M / 10 yr</t>
+        </is>
+      </c>
+      <c r="N94" s="6" t="inlineStr">
+        <is>
+          <t>In-window hiring-progress milestone confirmed (resolves window-boundary risk)</t>
+        </is>
+      </c>
+      <c r="O94" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="P94" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wfae.org/business/2026-04-23/charlottes-banking-jobs-hot-streak-continues</t>
+        </is>
+      </c>
+      <c r="Q94" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R94" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S94" s="6" t="inlineStr">
+        <is>
+          <t>$131,832 stated wage clears the $100k bar; supports Class-A rental and for-sale townhome demand in south Mecklenburg's Ballantyne/Blakeney/Rea Farms corridor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C95" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>Durham / Morrisville</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>Durham &amp; Wake</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>Novartis — API mfg building (unchanged)</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="J95" s="6" t="inlineStr">
+        <is>
+          <t>$111,161 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K95" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L95" s="6" t="inlineStr">
+        <is>
+          <t>~$991M (incl. $220M API building)</t>
+        </is>
+      </c>
+      <c r="M95" s="6" t="inlineStr">
+        <is>
+          <t>Part of original $771M package incentives</t>
+        </is>
+      </c>
+      <c r="N95" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="O95" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="P95" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
+        </is>
+      </c>
+      <c r="Q95" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R95" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S95" s="6" t="inlineStr">
+        <is>
+          <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8473,7 +9383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X85"/>
+  <dimension ref="A1:X95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18368,6 +19278,1166 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>Gaining Momentum</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Uptown</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group — 2nd US HQ / bank operations</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>Banking / financial services</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>Active recruiting + firmer October move-in date</t>
+        </is>
+      </c>
+      <c r="K86" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L86" s="6" t="inlineStr">
+        <is>
+          <t>Projected (6 yr)</t>
+        </is>
+      </c>
+      <c r="M86" s="6" t="inlineStr">
+        <is>
+          <t>$165,316 avg (stated; vs county $90,706)</t>
+        </is>
+      </c>
+      <c r="N86" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O86" s="6" t="inlineStr">
+        <is>
+          <t>$50.5M</t>
+        </is>
+      </c>
+      <c r="P86" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $70.0M / 12 yr; $23.3M IDF-Utility Account</t>
+        </is>
+      </c>
+      <c r="Q86" s="6" t="inlineStr">
+        <is>
+          <t>Currently ~300 employees operating from 500 E. Morehead St.; move into former One Wells Fargo Center (301 S. College St.) now specifically targeted for October 2026 (firmer than the prior 'fall 2026' language); actively recruiting on college campuses for summer-2027 analyst/intern classes</t>
+        </is>
+      </c>
+      <c r="R86" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="S86" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bankingdive.com/news/smbc-revs-up-recruiting-charlotte-banking-talent-tech-cyber-data-jobs/830268/</t>
+        </is>
+      </c>
+      <c r="T86" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U86" s="6" t="inlineStr">
+        <is>
+          <t>Office / HQ banking</t>
+        </is>
+      </c>
+      <c r="V86" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="W86" s="6" t="inlineStr">
+        <is>
+          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth.</t>
+        </is>
+      </c>
+      <c r="X86" s="6" t="inlineStr">
+        <is>
+          <t>Ninth consecutive cycle without a new milestone on the lease itself, but active campus recruiting and a firmer October move-in date (vs. general 'fall 2026') modestly raise momentum/certainty; the bank has not yet physically moved in as of 2026-09-21.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D87" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill / York Co.</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>Biopharmaceutical (plasma fractionation)</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone (unchanged)</t>
+        </is>
+      </c>
+      <c r="K87" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L87" s="6" t="inlineStr">
+        <is>
+          <t>Projected (1,200 new + 300 relocated)</t>
+        </is>
+      </c>
+      <c r="M87" s="6" t="inlineStr">
+        <is>
+          <t>$141,502 avg HQ / $102,752 avg mfg (both stated)</t>
+        </is>
+      </c>
+      <c r="N87" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O87" s="6" t="inlineStr">
+        <is>
+          <t>$1.5B</t>
+        </is>
+      </c>
+      <c r="P87" s="6" t="inlineStr">
+        <is>
+          <t>Fee-in-lieu-of-tax; $65M SC Coordinating Council Closing Fund grant to York Co.</t>
+        </is>
+      </c>
+      <c r="Q87" s="6" t="inlineStr">
+        <is>
+          <t>50 acres purchased at Palmetto Research Park; construction slated to begin late 2026; full operations still projected for the 2030s</t>
+        </is>
+      </c>
+      <c r="R87" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="S87" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/york-county/news/octapharma-how-company-chose-rock-hill/article_b1518265-129d-4134-9ff9-f2d686950bd6.html</t>
+        </is>
+      </c>
+      <c r="T87" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U87" s="6" t="inlineStr">
+        <is>
+          <t>Office/HQ + biopharma mfg</t>
+        </is>
+      </c>
+      <c r="V87" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W87" s="6" t="inlineStr">
+        <is>
+          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH.</t>
+        </is>
+      </c>
+      <c r="X87" s="6" t="inlineStr">
+        <is>
+          <t>No new dated milestone found this cycle despite a dedicated recheck; the full timeline of city/county/state approvals (Rock Hill Council 7-0 on 2026-07-23; SC Commerce formal announcement 2026-07-29) was reconfirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D88" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>Durham / RTP</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie — biopharma manufacturing campus</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>Biopharma / life sciences mfg</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>Durham City Council incentive layer added on top of county approval</t>
+        </is>
+      </c>
+      <c r="K88" s="6" t="n">
+        <v>734</v>
+      </c>
+      <c r="L88" s="6" t="inlineStr">
+        <is>
+          <t>Projected (+2,000 construction)</t>
+        </is>
+      </c>
+      <c r="M88" s="6" t="inlineStr">
+        <is>
+          <t>$118,041 avg (stated; vs county $102,817)</t>
+        </is>
+      </c>
+      <c r="N88" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O88" s="6" t="inlineStr">
+        <is>
+          <t>$1.4B</t>
+        </is>
+      </c>
+      <c r="P88" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $19.3M / 12 yr; $6.4M IDF-Utility; Durham Co. performance-based award not-to-exceed $15,450,000 ("Project Glass," approved 2026-07-13); a Durham City Council incentive item for the same project appeared on its 2026-09-17 agenda, bringing the combined city+county local incentive to ~$24.8M</t>
+        </is>
+      </c>
+      <c r="Q88" s="6" t="inlineStr">
+        <is>
+          <t>Construction 2026; complete ~end-2028; hiring through ~2031</t>
+        </is>
+      </c>
+      <c r="R88" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="S88" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/abbvie-pledges-1-3-billion-investment-734-jobs-in-durham/</t>
+        </is>
+      </c>
+      <c r="T88" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U88" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / R&amp;D / lab</t>
+        </is>
+      </c>
+      <c r="V88" s="6" t="inlineStr">
+        <is>
+          <t>Suburban-urban</t>
+        </is>
+      </c>
+      <c r="W88" s="6" t="inlineStr">
+        <is>
+          <t>High-end MF + move-up for-sale around Durham/RTP; spillover Wake/Orange. Construction-phase rental near-term.</t>
+        </is>
+      </c>
+      <c r="X88" s="6" t="inlineStr">
+        <is>
+          <t>Durham City Council took up a companion economic-incentive item for the same AbbVie campus at its Sept. 17, 2026 meeting, layering a city-level incentive on top of the county's July 13 award — the first time both local-government tiers have committed. No physical-groundbreaking news found yet; AbbVie's own release still targets construction 'in 2026.' Score raised 85-&gt;87 for improved capital-investment certainty and repeat momentum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D89" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>Blythewood / N. Columbia</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV assembly plant + new Supplier Park</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>Automotive / EV manufacturing</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>Cost-overrun payment procedurally cleared; lawsuit and headcount unresolved</t>
+        </is>
+      </c>
+      <c r="K89" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L89" s="6" t="inlineStr">
+        <is>
+          <t>Projected (4,000-5,000 assembly + ~1,000 supplier-park; 600+ hired as of Apr 2026, no fresher figure disclosed)</t>
+        </is>
+      </c>
+      <c r="M89" s="6" t="inlineStr">
+        <is>
+          <t>$30-$37.50/hr line (stated); salaried higher</t>
+        </is>
+      </c>
+      <c r="N89" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mix supports above-median HH income</t>
+        </is>
+      </c>
+      <c r="O89" s="6" t="inlineStr">
+        <is>
+          <t>$2.3B+ (site $2.0B + $25M training center + $300M Supplier Park)</t>
+        </is>
+      </c>
+      <c r="P89" s="6" t="inlineStr">
+        <is>
+          <t>State/local package (2023); $25M readySC; the Aug. 17 veto took effect immediately, allowing the $150M state cost-overrun payment to be made without waiting for the Legislative Audit Council review (due ~mid-Dec. 2026)</t>
+        </is>
+      </c>
+      <c r="Q89" s="6" t="inlineStr">
+        <is>
+          <t>Body Shop/Paint Shop/Supplier Park construction ongoing per company blog; Scout's own current guidance is initial production 2027 / customer deliveries 2028 (a more conservative framing than earlier 'customer shipments 2027' language)</t>
+        </is>
+      </c>
+      <c r="R89" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S89" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/2026/08/17/sc-governor-vetoes-delay-on-paying-agency-overruns-at-scout-motors-site/</t>
+        </is>
+      </c>
+      <c r="T89" s="6" t="inlineStr">
+        <is>
+          <t>Medium (facts); Low (headcount/timeline)</t>
+        </is>
+      </c>
+      <c r="U89" s="6" t="inlineStr">
+        <is>
+          <t>Auto mfg + salaried eng.</t>
+        </is>
+      </c>
+      <c r="V89" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W89" s="6" t="inlineStr">
+        <is>
+          <t>Bifurcated: salaried/professional -&gt; higher-income for-sale &amp; Class-A; hourly base + supplier-park jobs -&gt; workforce/missing-middle rental in N. Richland/Fairfield.</t>
+        </is>
+      </c>
+      <c r="X89" s="6" t="inlineStr">
+        <is>
+          <t>No new headcount figure found since April 2026 (unofficial third-party estimates of 995-1,313 employees are not corroborated by Scout/state sources). Gov. McMaster's Aug. 17 line-item veto took effect immediately, clearing the $150M cost-overrun payment procedurally (still not confirmed disbursed beyond the ~$47.5M already invoiced); the Legislative Audit Council's independent review continues, due ~mid-December 2026. The Shives family blasting/nuisance lawsuit remains pending with no hearing date found. Scout's own current official language sets customer deliveries at 2028 (not 2027), more conservative than previously carried. Score held flat at 85 — capital-investment certainty modestly improved by the veto, offset by continued headcount/timeline uncertainty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D90" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs / SW Wake</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>Genentech — biomanufacturing expansion (unchanged)</t>
+        </is>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="K90" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="L90" s="6" t="inlineStr">
+        <is>
+          <t>Projected (site total)</t>
+        </is>
+      </c>
+      <c r="M90" s="6" t="inlineStr">
+        <is>
+          <t>~$119,833 avg (stated, 2025 tranche)</t>
+        </is>
+      </c>
+      <c r="N90" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O90" s="6" t="inlineStr">
+        <is>
+          <t>~$2.0B</t>
+        </is>
+      </c>
+      <c r="P90" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
+        </is>
+      </c>
+      <c r="Q90" s="6" t="inlineStr">
+        <is>
+          <t>Topping-out ceremony held Aug. 18, 2026; operational target 2029 unchanged</t>
+        </is>
+      </c>
+      <c r="R90" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="S90" s="6" t="inlineStr">
+        <is>
+          <t>https://www.biospace.com/press-releases/genentech-marks-topping-out-milestone-for-new-holly-springs-north-carolina-manufacturing-facility</t>
+        </is>
+      </c>
+      <c r="T90" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U90" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="V90" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W90" s="6" t="inlineStr">
+        <is>
+          <t>Strong higher-income for-sale + Class-A rental demand in fast-growing SW Wake.</t>
+        </is>
+      </c>
+      <c r="X90" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone found this cycle beyond the already-tracked Aug. 18 topping-out ceremony.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D91" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>JetZero — aerospace plant (hiring-delay amendment finalized; construction + funding progressing)</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace / advanced manufacturing</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>JDIG hiring-schedule amendment formally approved; state funding released; NC3 construction ongoing</t>
+        </is>
+      </c>
+      <c r="K91" s="6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="L91" s="6" t="inlineStr">
+        <is>
+          <t>Projected</t>
+        </is>
+      </c>
+      <c r="M91" s="6" t="inlineStr">
+        <is>
+          <t>$89,340 avg (stated, 2025)</t>
+        </is>
+      </c>
+      <c r="N91" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated (2025)</t>
+        </is>
+      </c>
+      <c r="O91" s="6" t="inlineStr">
+        <is>
+          <t>$4.7B</t>
+        </is>
+      </c>
+      <c r="P91" s="6" t="inlineStr">
+        <is>
+          <t>Transformative JDIG up to $1.018B-$1.57B / 37 yr; Guilford grant $75.9M / 20 yr; $133.9M NC FY26-27 budget funding formally released upon Gov. Stein's 2026-07-07 signature (on top of $118.1M already allotted)</t>
+        </is>
+      </c>
+      <c r="Q91" s="6" t="inlineStr">
+        <is>
+          <t>NC's Economic Investment Committee unanimously approved shifting the JDIG base period by one year (now Jan 2028-Dec 2037); NC3 (150,000 sf composite-manufacturing building) construction confirmed ongoing under HITT Contracting; JetZero signed an EXIM Bank Letter of Interest (up to $3B financing) in July 2026</t>
+        </is>
+      </c>
+      <c r="R91" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="S91" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/budget-upholds-jetzero-incentives-payout-plan/</t>
+        </is>
+      </c>
+      <c r="T91" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Medium (hiring-ramp timeline now formally fixed but still delayed)</t>
+        </is>
+      </c>
+      <c r="U91" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace mfg + eng.</t>
+        </is>
+      </c>
+      <c r="V91" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W91" s="6" t="inlineStr">
+        <is>
+          <t>Same long-run scale; the hiring-ramp delay is now formally locked into the JDIG (removing ambiguity) while funding release and visible NC3 construction are genuine de-risking offsets.</t>
+        </is>
+      </c>
+      <c r="X91" s="6" t="inlineStr">
+        <is>
+          <t>The previously-reported ~1-year hiring delay is now a finalized JDIG amendment rather than a pending request — a formalization, not a new setback. Simultaneously, the state-budget standoff that caused the delay was resolved via the July 7 budget signing, releasing $133.9M and enabling visible NC3 construction progress; a $3B EXIM Bank financing LOI was also signed. Net effect judged mildly positive; score raised 81-&gt;82 for improved capital-investment certainty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D92" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group — East Coast ops hub (unchanged)</t>
+        </is>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>Investment mgmt / finance + tech</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="K92" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="L92" s="6" t="inlineStr">
+        <is>
+          <t>Projected</t>
+        </is>
+      </c>
+      <c r="M92" s="6" t="inlineStr">
+        <is>
+          <t>$194,141 avg (stated; NC Commerce JDIG figure)</t>
+        </is>
+      </c>
+      <c r="N92" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O92" s="6" t="inlineStr">
+        <is>
+          <t>$60M</t>
+        </is>
+      </c>
+      <c r="P92" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $17.2M / 12 yr; $5.7M IDF-Utility; $19.4M state grant/12yr + $2.2M training funds + $1M local</t>
+        </is>
+      </c>
+      <c r="Q92" s="6" t="inlineStr">
+        <is>
+          <t>16-yr lease (196,940 sf, One Independence Center) began 2026-05-22</t>
+        </is>
+      </c>
+      <c r="R92" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="S92" s="6" t="inlineStr">
+        <is>
+          <t>https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
+        </is>
+      </c>
+      <c r="T92" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U92" s="6" t="inlineStr">
+        <is>
+          <t>Office — finance/tech</t>
+        </is>
+      </c>
+      <c r="V92" s="6" t="inlineStr">
+        <is>
+          <t>Urban-suburban</t>
+        </is>
+      </c>
+      <c r="W92" s="6" t="inlineStr">
+        <is>
+          <t>High-skill eng/data workforce -&gt; walkable South End/Uptown &amp; inner-suburban Class-A and for-sale TH.</t>
+        </is>
+      </c>
+      <c r="X92" s="6" t="inlineStr">
+        <is>
+          <t>No hiring or occupancy update found dated after the 2026-05-22 lease start through 2026-09-21 despite a dedicated recheck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D93" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Plaza Midwood</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — Global HQ (litigation risk growing)</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>Automotive (EV) — corporate HQ</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>No permit/construction progress found; franchise-dealer litigation footprint widened</t>
+        </is>
+      </c>
+      <c r="K93" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L93" s="6" t="inlineStr">
+        <is>
+          <t>Projected (365 relocating + 835 new local hires)</t>
+        </is>
+      </c>
+      <c r="M93" s="6" t="inlineStr">
+        <is>
+          <t>$153,978 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N93" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O93" s="6" t="inlineStr">
+        <is>
+          <t>$206.9M</t>
+        </is>
+      </c>
+      <c r="P93" s="6" t="inlineStr">
+        <is>
+          <t>Original 2025-11-12 HQ incentive/relocation commitment</t>
+        </is>
+      </c>
+      <c r="Q93" s="6" t="inlineStr">
+        <is>
+          <t>2nd office building preliminary land-development plan (filed 2026-03-28) still awaiting staff review/approvals; construction start still targeted H1 2027</t>
+        </is>
+      </c>
+      <c r="R93" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="S93" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/scout-motors-hq-move-turbocharges-second-office-building-in-plaza-midwood/</t>
+        </is>
+      </c>
+      <c r="T93" s="6" t="inlineStr">
+        <is>
+          <t>Med (facts High; milestone stage early)</t>
+        </is>
+      </c>
+      <c r="U93" s="6" t="inlineStr">
+        <is>
+          <t>Corporate HQ / professional</t>
+        </is>
+      </c>
+      <c r="V93" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="W93" s="6" t="inlineStr">
+        <is>
+          <t>Supports Plaza Midwood/NoDa/Elizabeth close-in rental and townhome demand from a young, high-wage corporate workforce.</t>
+        </is>
+      </c>
+      <c r="X93" s="6" t="inlineStr">
+        <is>
+          <t>No fresher permit/construction milestone found this cycle. Risk factor context (not scored): franchise-dealer lawsuits over Scout's direct-to-consumer sales model have now spread to a 6th state (WA, per a July 2026 filing, up from 5 previously), with a federal judge having denied a motion to dismiss the California suit in March 2026; the company continues stating it is proceeding with the Charlotte HQ regardless.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D94" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Ballantyne</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>Citigroup — Charlotte office (hiring ramp confirmed proceeding)</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>Banking / financial services</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="inlineStr">
+        <is>
+          <t>In-window hiring-progress milestone confirmed (resolves window-boundary risk)</t>
+        </is>
+      </c>
+      <c r="K94" s="6" t="n">
+        <v>510</v>
+      </c>
+      <c r="L94" s="6" t="inlineStr">
+        <is>
+          <t>Confirmed (stated); facility ultimately to house 785 employees incl. ~275 relocated</t>
+        </is>
+      </c>
+      <c r="M94" s="6" t="inlineStr">
+        <is>
+          <t>$131,832 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N94" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O94" s="6" t="inlineStr">
+        <is>
+          <t>$16.1M</t>
+        </is>
+      </c>
+      <c r="P94" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $8.9M / 10 yr</t>
+        </is>
+      </c>
+      <c r="Q94" s="6" t="inlineStr">
+        <is>
+          <t>Grand opening held 2026-03-16 (now pre-window); a dated 2026-04-23 update confirms the hiring buildout is actively proceeding toward the 785-employee target</t>
+        </is>
+      </c>
+      <c r="R94" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="S94" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wfae.org/business/2026-04-23/charlottes-banking-jobs-hot-streak-continues</t>
+        </is>
+      </c>
+      <c r="T94" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U94" s="6" t="inlineStr">
+        <is>
+          <t>Office / financial services</t>
+        </is>
+      </c>
+      <c r="V94" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W94" s="6" t="inlineStr">
+        <is>
+          <t>$131,832 stated wage clears the $100k bar; supports Class-A rental and for-sale townhome demand in south Mecklenburg's Ballantyne/Blakeney/Rea Farms corridor.</t>
+        </is>
+      </c>
+      <c r="X94" s="6" t="inlineStr">
+        <is>
+          <t>This entry's only previously-tracked milestone (2026-03-16 grand opening) fell before this cycle's window start (2026-03-21), putting it at risk of removal. A dedicated recheck found a genuinely dated, in-window hiring-progress article (WFAE, 2026-04-23) confirming the buildout toward 785 total employees is actively proceeding — sufficient to keep this entry Ranked. No news found dated after April 2026; recommend using 2026-04-23 as the new anchor milestone going forward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D95" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>Durham / Morrisville</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>Durham &amp; Wake</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>Novartis — API mfg building (unchanged)</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="J95" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="K95" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="L95" s="6" t="inlineStr">
+        <is>
+          <t>Projected (part of pre-window deal)</t>
+        </is>
+      </c>
+      <c r="M95" s="6" t="inlineStr">
+        <is>
+          <t>$111,161 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N95" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O95" s="6" t="inlineStr">
+        <is>
+          <t>~$991M (incl. $220M API building)</t>
+        </is>
+      </c>
+      <c r="P95" s="6" t="inlineStr">
+        <is>
+          <t>Part of original $771M package incentives</t>
+        </is>
+      </c>
+      <c r="Q95" s="6" t="inlineStr">
+        <is>
+          <t>Facility opening targeted 2027-2028</t>
+        </is>
+      </c>
+      <c r="R95" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="S95" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
+        </is>
+      </c>
+      <c r="T95" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U95" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="V95" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W95" s="6" t="inlineStr">
+        <is>
+          <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
+        </is>
+      </c>
+      <c r="X95" s="6" t="inlineStr">
+        <is>
+          <t>No new construction/hiring milestone found since the April 30, 2026 $220M API-building announcement despite a dedicated recheck this cycle.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18379,7 +20449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L386"/>
+  <dimension ref="A1:L432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -42328,6 +44398,2858 @@
         </is>
       </c>
     </row>
+    <row r="387">
+      <c r="A387" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B387" s="6" t="inlineStr">
+        <is>
+          <t>North Charleston</t>
+        </is>
+      </c>
+      <c r="C387" s="6" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="D387" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E387" s="6" t="inlineStr">
+        <is>
+          <t>SC Ports Authority — Leatherman Terminal (pause remains in effect)</t>
+        </is>
+      </c>
+      <c r="F387" s="6" t="inlineStr">
+        <is>
+          <t>400 direct + ~1,200 indirect</t>
+        </is>
+      </c>
+      <c r="G387" s="6" t="inlineStr">
+        <is>
+          <t>$1.2B</t>
+        </is>
+      </c>
+      <c r="H387" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I387" s="6" t="inlineStr">
+        <is>
+          <t>No confirmed reopening date found this cycle. A headline suggesting a possible September 'reopening with major weekly Asia service' surfaced but could not be accessed or dated with confidence — given SCSPA's URL structure it may be recycled Sept. 2024 reopening coverage (following the unrelated 2023 ILA labor closure), not a new 2026 development. Not reporting a reopening as confirmed; flagged for a different access route next cycle.</t>
+        </is>
+      </c>
+      <c r="J387" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (rechecked; unresolved)</t>
+        </is>
+      </c>
+      <c r="K387" s="6" t="inlineStr">
+        <is>
+          <t>https://www.live5news.com/2026/06/25/sc-ports-pause-leatherman-terminal-operations-aug-1-consolidate-container-work/</t>
+        </is>
+      </c>
+      <c r="L387" s="6" t="inlineStr">
+        <is>
+          <t>Med (ambiguous headline unresolved)</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B388" s="6" t="inlineStr">
+        <is>
+          <t>Cherokee Co. / Blacksburg</t>
+        </is>
+      </c>
+      <c r="C388" s="6" t="inlineStr">
+        <is>
+          <t>Cherokee</t>
+        </is>
+      </c>
+      <c r="D388" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E388" s="6" t="inlineStr">
+        <is>
+          <t>USA Rare Earth — rare-earth magnet plant</t>
+        </is>
+      </c>
+      <c r="F388" s="6" t="inlineStr">
+        <is>
+          <t>~490</t>
+        </is>
+      </c>
+      <c r="G388" s="6" t="inlineStr">
+        <is>
+          <t>$1.2B</t>
+        </is>
+      </c>
+      <c r="H388" s="6" t="inlineStr">
+        <is>
+          <t>$24.50-$63/hr (stated; unchanged)</t>
+        </is>
+      </c>
+      <c r="I388" s="6" t="inlineStr">
+        <is>
+          <t>Groundbreaking held Sept. 9, 2026 at Bailey Industrial Park (124-acre site, ~800,000 sf facility); operational target confirmed April 2028. Headcount still just under the 500 threshold — no increase found. New detail: a $250,000 company contribution to Spartanburg Community College for a new "SPARK Center" workforce-training facility in Cherokee County.</t>
+        </is>
+      </c>
+      <c r="J388" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-09 (groundbreaking)</t>
+        </is>
+      </c>
+      <c r="K388" s="6" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/09/09/3358813/0/en/usa-rare-earth-breaks-ground-on-advanced-rare-earth-metal-and-magnet-manufacturing-facility-in-blacksburg-south-carolina.html</t>
+        </is>
+      </c>
+      <c r="L388" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B389" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg (former Kohler plant)</t>
+        </is>
+      </c>
+      <c r="C389" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D389" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E389" s="6" t="inlineStr">
+        <is>
+          <t>NorthMark/Valara "Project Moc-1" — AI/HPC data center (litigation timeline advances; vote outcome unknown)</t>
+        </is>
+      </c>
+      <c r="F389" s="6" t="inlineStr">
+        <is>
+          <t>27 FT confirmed on incentive filings (company's own ~150-at-full-operation claim not independently corroborated)</t>
+        </is>
+      </c>
+      <c r="G389" s="6" t="inlineStr">
+        <is>
+          <t>$2.8-3.0B</t>
+        </is>
+      </c>
+      <c r="H389" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I389" s="6" t="inlineStr">
+        <is>
+          <t>Active multi-front cycle: (1) the county's moratorium 3rd/final reading, previously delayed from Aug. 17 to today, was on tonight's (Sept. 21) council agenda — outcome not yet published as of this report's compilation. (2) A Sept. 17 Circuit Court hearing (Judge J. Derham Cole Jr.) on SELC's motion to dismiss/injunction (major-vs-minor development classification) ended with NO ruling from the bench; the judge took the matter under advisement, a written order possible in 'days or weeks' — construction continues in the meantime. (3) The draft moratorium ordinance exempts already-approved projects, so Valara/NorthMark is expected to be grandfathered regardless of the vote's outcome. (4) SC Senate bill S.867 (statewide data-center siting) remains pending on the Senate floor after an April 28, 2026 committee-favorable report; no full floor vote found. A Sept. 14 constituent town hall (Sen. Kimbrell, Inman City Hall) was informational only.</t>
+        </is>
+      </c>
+      <c r="J389" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (vote outcome pending; multiple open threads)</t>
+        </is>
+      </c>
+      <c r="K389" s="6" t="inlineStr">
+        <is>
+          <t>https://www.foxcarolina.com/2026/09/17/judge-consider-halting-spartanburg-data-center-construction-thursday/</t>
+        </is>
+      </c>
+      <c r="L389" s="6" t="inlineStr">
+        <is>
+          <t>Med-High (state-level regulatory risk resolved in developer's favor; county litigation/injunction ruling and tonight's vote both still open)</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B390" s="6" t="inlineStr">
+        <is>
+          <t>Wake County (statewide)</t>
+        </is>
+      </c>
+      <c r="C390" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D390" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E390" s="6" t="inlineStr">
+        <is>
+          <t>WakeMed / Atrium Health — proposed merger (vote scheduled today)</t>
+        </is>
+      </c>
+      <c r="F390" s="6" t="inlineStr">
+        <is>
+          <t>3,300 (statewide, 5 yr)</t>
+        </is>
+      </c>
+      <c r="G390" s="6" t="inlineStr">
+        <is>
+          <t>$2.0B (Wake Co. portion)</t>
+        </is>
+      </c>
+      <c r="H390" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I390" s="6" t="inlineStr">
+        <is>
+          <t>Wake County Board of Commissioners vote was scheduled for TODAY, Sept. 21, 2026, 2pm, at the Wake County Justice Center. The renegotiated deal reportedly includes $150M cash to the county, expanded county governance/board-appointment rights (8 of 14 WakeMed board seats), and expanded indigent-care commitments. Commissioner Vickie Adamson (District 7) has publicly stated intent to vote no; Gov. Stein has said he will not oppose the merger. NO VOTE OUTCOME available as of this report's compilation — top priority to confirm next cycle.</t>
+        </is>
+      </c>
+      <c r="J390" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (vote today; outcome unknown)</t>
+        </is>
+      </c>
+      <c r="K390" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/wake-commissioners-schedule-vote-pave-way-wakemed-atrium-merger-september-2026/</t>
+        </is>
+      </c>
+      <c r="L390" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); outcome pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B391" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="C391" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="D391" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E391" s="6" t="inlineStr">
+        <is>
+          <t>Boom Supersonic — Overture assembly (AT RISK — deadline now ~3 months out)</t>
+        </is>
+      </c>
+      <c r="F391" s="6" t="inlineStr">
+        <is>
+          <t>&lt;=500 currently; must hit 500 by 12/31/26 or lease may terminate</t>
+        </is>
+      </c>
+      <c r="G391" s="6" t="inlineStr">
+        <is>
+          <t>~$50M (hangar)</t>
+        </is>
+      </c>
+      <c r="H391" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I391" s="6" t="inlineStr">
+        <is>
+          <t>No dated Sept. 2026 headcount/hiring figures were located despite extensive searching. The CEO was quoted in May 2026 'floating' a possible full NC HQ move (commentary, not a hiring commitment). No evidence found of a meaningful hiring ramp toward the Dec. 31, 2026 500-employee lease-termination trigger, which is now roughly 3 months away. Escalating urgency flag — recommend a dedicated follow-up next cycle.</t>
+        </is>
+      </c>
+      <c r="J391" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (rechecked; no headcount evidence found)</t>
+        </is>
+      </c>
+      <c r="K391" s="6" t="inlineStr">
+        <is>
+          <t>https://www.prismnews.com/local/guilford-nc/boom-supersonics-greensboro-factory-sits-idle-as-state</t>
+        </is>
+      </c>
+      <c r="L391" s="6" t="inlineStr">
+        <is>
+          <t>Med-High (risk escalating)</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B392" s="6" t="inlineStr">
+        <is>
+          <t>Rowan County</t>
+        </is>
+      </c>
+      <c r="C392" s="6" t="inlineStr">
+        <is>
+          <t>Rowan</t>
+        </is>
+      </c>
+      <c r="D392" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E392" s="6" t="inlineStr">
+        <is>
+          <t>American Eagle Outfitters</t>
+        </is>
+      </c>
+      <c r="F392" s="6" t="inlineStr">
+        <is>
+          <t>200+ (state figure; county vote cited 258)</t>
+        </is>
+      </c>
+      <c r="G392" s="6" t="inlineStr">
+        <is>
+          <t>$41M</t>
+        </is>
+      </c>
+      <c r="H392" s="6" t="inlineStr">
+        <is>
+          <t>$57,351 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I392" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; Q1 2027 ops start still targeted.</t>
+        </is>
+      </c>
+      <c r="J392" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (rechecked; no change)</t>
+        </is>
+      </c>
+      <c r="K392" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2026/07/17/governor-stein-announces-american-eagle-outfitters-inc-selects-rowan-county-41-million-southeast</t>
+        </is>
+      </c>
+      <c r="L392" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B393" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte (CLT airport)</t>
+        </is>
+      </c>
+      <c r="C393" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D393" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E393" s="6" t="inlineStr">
+        <is>
+          <t>Averitt — logistics campus (zoning still pending; infrastructure headwind)</t>
+        </is>
+      </c>
+      <c r="F393" s="6" t="inlineStr">
+        <is>
+          <t>211 (confirmed)</t>
+        </is>
+      </c>
+      <c r="G393" s="6" t="inlineStr">
+        <is>
+          <t>$200M</t>
+        </is>
+      </c>
+      <c r="H393" s="6" t="inlineStr">
+        <is>
+          <t>$81,769 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I393" s="6" t="inlineStr">
+        <is>
+          <t>City of Charlotte's zoning process (public hearing 2026-03-23, Zoning Committee work session 2026-04-07) is confirmed still working through Council as of the most recent reporting found; no vertical-construction start confirmed. New headwind: NCDOT will close the nearby Shopton Road bridge for replacement through summer 2027, a real access/build-out complication for the site.</t>
+        </is>
+      </c>
+      <c r="J393" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-29 (most recent dated update)</t>
+        </is>
+      </c>
+      <c r="K393" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/04/29/averitt-charlotte-douglas-airport-campus-jobs</t>
+        </is>
+      </c>
+      <c r="L393" s="6" t="inlineStr">
+        <is>
+          <t>High (jobs/wage); Med (construction timing given bridge closure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B394" s="6" t="inlineStr">
+        <is>
+          <t>Wake Co. (aggregate)</t>
+        </is>
+      </c>
+      <c r="C394" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D394" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E394" s="6" t="inlineStr">
+        <is>
+          <t>County jobs pipeline (EDGE 7, 52 projects)</t>
+        </is>
+      </c>
+      <c r="F394" s="6" t="inlineStr">
+        <is>
+          <t>~11,000 (pipeline)</t>
+        </is>
+      </c>
+      <c r="G394" s="6" t="inlineStr">
+        <is>
+          <t>$11B</t>
+        </is>
+      </c>
+      <c r="H394" s="6" t="inlineStr">
+        <is>
+          <t>Mixed (office-skewed)</t>
+        </is>
+      </c>
+      <c r="I394" s="6" t="inlineStr">
+        <is>
+          <t>Located Wake County Economic Development's own "New and Expanding" report (covering Oct. 1, 2025-May 31, 2026, published June 9, 2026) at e1.nmcdn.io, but the domain was fetch-blocked so the exact ~$5.6B/8,000-job figure could not be line-item reconciled this cycle. Working inference (not confirmed): "New and Expanding" appears to cover realized/announced deals in a fixed trailing window, while the EDGE7 figure is the full forward-looking active sales pipeline (including unannounced prospects) — a scope difference, not a contradiction. Recommend another access attempt next cycle.</t>
+        </is>
+      </c>
+      <c r="J394" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-09 (report publish date)</t>
+        </is>
+      </c>
+      <c r="K394" s="6" t="inlineStr">
+        <is>
+          <t>https://nchospitalityalliance.com/wake-county-pursues-11-billion-jobs-pipeline/</t>
+        </is>
+      </c>
+      <c r="L394" s="6" t="inlineStr">
+        <is>
+          <t>Low-Med (discrepancy explanation is inferential, not confirmed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B395" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / SouthPark</t>
+        </is>
+      </c>
+      <c r="C395" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D395" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E395" s="6" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase — SouthPark consolidated office (move-in timing clarified)</t>
+        </is>
+      </c>
+      <c r="F395" s="6" t="inlineStr">
+        <is>
+          <t>400 new + ~600 relocated = 1,000 total</t>
+        </is>
+      </c>
+      <c r="G395" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H395" s="6" t="inlineStr">
+        <is>
+          <t>~$105k Estimated/Inferred — basis not independently confirmed</t>
+        </is>
+      </c>
+      <c r="I395" s="6" t="inlineStr">
+        <is>
+          <t>Move-in timing resolved as a prior inconsistency: WFAE and Axios (both 2026-04-21) confirm move-in is targeted for early 2028 (not "later in 2026," which appears to have been an earlier rumor/error). Current nearby headcount ~600, consolidating with 400 new hires to ~1,000 total at One Piedmont Town Center (145,000 sf, 5 floors). Wage still not disclosed by the company.</t>
+        </is>
+      </c>
+      <c r="J395" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="K395" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wfae.org/business/2026-04-21/jpmorgan-chase-adding-400-jobs-consolidate-in-southpark-offices</t>
+        </is>
+      </c>
+      <c r="L395" s="6" t="inlineStr">
+        <is>
+          <t>High (jobs/lease/timing); Low (wage basis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B396" s="6" t="inlineStr">
+        <is>
+          <t>Garner</t>
+        </is>
+      </c>
+      <c r="C396" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D396" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E396" s="6" t="inlineStr">
+        <is>
+          <t>Gregory Poole Equipment Co. — HQ relocation</t>
+        </is>
+      </c>
+      <c r="F396" s="6" t="inlineStr">
+        <is>
+          <t>500+ (5 yr)</t>
+        </is>
+      </c>
+      <c r="G396" s="6" t="inlineStr">
+        <is>
+          <t>$347M</t>
+        </is>
+      </c>
+      <c r="H396" s="6" t="inlineStr">
+        <is>
+          <t>~$75,381 companywide avg (Estimated/Inferred, sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I396" s="6" t="inlineStr">
+        <is>
+          <t>No groundbreaking confirmed this cycle; project remains at "construction expected within 24 months" per Oct. 2025 reporting on the 130-acre site purchased Feb. 2025.</t>
+        </is>
+      </c>
+      <c r="J396" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (rechecked; no change)</t>
+        </is>
+      </c>
+      <c r="K396" s="6" t="inlineStr">
+        <is>
+          <t>https://www.garnernc.gov/Home/Components/News/News/2344/17</t>
+        </is>
+      </c>
+      <c r="L396" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B397" s="6" t="inlineStr">
+        <is>
+          <t>Benson</t>
+        </is>
+      </c>
+      <c r="C397" s="6" t="inlineStr">
+        <is>
+          <t>Johnston</t>
+        </is>
+      </c>
+      <c r="D397" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E397" s="6" t="inlineStr">
+        <is>
+          <t>Vulcan Elements — magnet factory (transmission line fast-tracked)</t>
+        </is>
+      </c>
+      <c r="F397" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (proj.)</t>
+        </is>
+      </c>
+      <c r="G397" s="6" t="inlineStr">
+        <is>
+          <t>$918.4M</t>
+        </is>
+      </c>
+      <c r="H397" s="6" t="inlineStr">
+        <is>
+          <t>$81,932 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I397" s="6" t="inlineStr">
+        <is>
+          <t>NC Utilities Commission fast-tracked (citing national-security grounds, skipping normal hearing steps) approval of the 1.31-mile, 230kV transmission line needed to serve the site, reported late Aug. 2026. No factory-groundbreaking event found this cycle; company's own guidance still targets starting operations Q1 2027 after doubling the planned facility to 1M+ sq ft.</t>
+        </is>
+      </c>
+      <c r="J397" s="6" t="inlineStr">
+        <is>
+          <t>2026-08 (transmission-line fast-track approval)</t>
+        </is>
+      </c>
+      <c r="K397" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/nccapitol/north-carolina-fast-tracks-power-line-for-rare-earth-magnet-factory-august-2026/</t>
+        </is>
+      </c>
+      <c r="L397" s="6" t="inlineStr">
+        <is>
+          <t>Medium-High (infrastructure clearance confirmed; factory groundbreaking date still unconfirmed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B398" s="6" t="inlineStr">
+        <is>
+          <t>Multi-site NC incl. Wilmington</t>
+        </is>
+      </c>
+      <c r="C398" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover +</t>
+        </is>
+      </c>
+      <c r="D398" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E398" s="6" t="inlineStr">
+        <is>
+          <t>Amazon-Corning — fiber-optics partnership</t>
+        </is>
+      </c>
+      <c r="F398" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (multi-site, unallocated)</t>
+        </is>
+      </c>
+      <c r="G398" s="6" t="inlineStr">
+        <is>
+          <t>Multi-billion (undisclosed)</t>
+        </is>
+      </c>
+      <c r="H398" s="6" t="inlineStr">
+        <is>
+          <t>Avg salary &gt;$65,000 (sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I398" s="6" t="inlineStr">
+        <is>
+          <t>Reconfirmed as an in-window deal (announced 2026-06-08). Wilmington-specific job allocation remains undisclosed — company officials reportedly did not respond to requests for a Wilmington/Concord split. No update found this cycle resolving the site-specific breakdown.</t>
+        </is>
+      </c>
+      <c r="J398" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-08 (reconfirmed; allocation still undisclosed)</t>
+        </is>
+      </c>
+      <c r="K398" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wilmingtonbiz.com/technology/2026/06/08/amazon_corning_strike_multibillion_dollar_deal_to_add_1000_nc_jobs/27560</t>
+        </is>
+      </c>
+      <c r="L398" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B399" s="6" t="inlineStr">
+        <is>
+          <t>Arden</t>
+        </is>
+      </c>
+      <c r="C399" s="6" t="inlineStr">
+        <is>
+          <t>Buncombe</t>
+        </is>
+      </c>
+      <c r="D399" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E399" s="6" t="inlineStr">
+        <is>
+          <t>Pratt &amp; Whitney (RTX) — casting foundry expansion</t>
+        </is>
+      </c>
+      <c r="F399" s="6" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="G399" s="6" t="inlineStr">
+        <is>
+          <t>$285M</t>
+        </is>
+      </c>
+      <c r="H399" s="6" t="inlineStr">
+        <is>
+          <t>$62,413 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I399" s="6" t="inlineStr">
+        <is>
+          <t>On track, not yet achieved: first casting-foundry equipment arrivals still expected end of 2026 (first parts production targeted mid-2027), but no dated Sept. 2026 confirmation was found that equipment has actually arrived. The previously-reported ~1,000-employed/ahead-of-schedule figure was not re-confirmed with a fresh date this cycle.</t>
+        </is>
+      </c>
+      <c r="J399" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (rechecked; on track, unconfirmed)</t>
+        </is>
+      </c>
+      <c r="K399" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/pratt-whitney-announces-285-million-expansion-325-more-jobs-for-buncombe-county/pratt-whitney-asheville/</t>
+        </is>
+      </c>
+      <c r="L399" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B400" s="6" t="inlineStr">
+        <is>
+          <t>Asheville / Arden</t>
+        </is>
+      </c>
+      <c r="C400" s="6" t="inlineStr">
+        <is>
+          <t>Buncombe</t>
+        </is>
+      </c>
+      <c r="D400" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E400" s="6" t="inlineStr">
+        <is>
+          <t>Eaton — Low Voltage Assembly expansion</t>
+        </is>
+      </c>
+      <c r="F400" s="6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G400" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H400" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Estimated mid-$60k-$80k)</t>
+        </is>
+      </c>
+      <c r="I400" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle beyond the original April 7-8, 2026 announcement (seventh Helene-recovery manufacturing expansion since Hurricane Helene); jobs to be filled within 12 months of the announcement.</t>
+        </is>
+      </c>
+      <c r="J400" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (rechecked; no change)</t>
+        </is>
+      </c>
+      <c r="K400" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ashevillechamber.org/news-events/press-releases/eaton-invests-in-workforce-growth-in-buncombe-county/</t>
+        </is>
+      </c>
+      <c r="L400" s="6" t="inlineStr">
+        <is>
+          <t>High (jobs); Low (wage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B401" s="6" t="inlineStr">
+        <is>
+          <t>Hendersonville</t>
+        </is>
+      </c>
+      <c r="C401" s="6" t="inlineStr">
+        <is>
+          <t>Henderson</t>
+        </is>
+      </c>
+      <c r="D401" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E401" s="6" t="inlineStr">
+        <is>
+          <t>BorgWarner — vertical-integration expansion</t>
+        </is>
+      </c>
+      <c r="F401" s="6" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="G401" s="6" t="inlineStr">
+        <is>
+          <t>$100M</t>
+        </is>
+      </c>
+      <c r="H401" s="6" t="inlineStr">
+        <is>
+          <t>$67,047 avg (stated; below $100k)</t>
+        </is>
+      </c>
+      <c r="I401" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle beyond the original May 26, 2026 announcement ($3.6M JDIG, 140,000 sf addition, current headcount ~149 growing to ~571 by 2029).</t>
+        </is>
+      </c>
+      <c r="J401" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (rechecked; no change)</t>
+        </is>
+      </c>
+      <c r="K401" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2026/05/26/governor-stein-announces-100-million-expansion-borgwarner-hendersonville</t>
+        </is>
+      </c>
+      <c r="L401" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B402" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro</t>
+        </is>
+      </c>
+      <c r="C402" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="D402" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E402" s="6" t="inlineStr">
+        <is>
+          <t>Lumentum — AI/data-center optics (opening confirmed)</t>
+        </is>
+      </c>
+      <c r="F402" s="6" t="inlineStr">
+        <is>
+          <t>~400</t>
+        </is>
+      </c>
+      <c r="G402" s="6" t="inlineStr">
+        <is>
+          <t>Hundreds of millions</t>
+        </is>
+      </c>
+      <c r="H402" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I402" s="6" t="inlineStr">
+        <is>
+          <t>Confirmed the facility (acquired from Qorvo) is now open/operational, being retrofitted to manufacture InP-based CW/UHP lasers for AI data centers; ~400 jobs preserved/created; production ramp still targeted mid-2028. This confirms, rather than newly changes, the previously-noted April 29, 2026 ribbon-cutting.</t>
+        </is>
+      </c>
+      <c r="J402" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-29 (opening reconfirmed)</t>
+        </is>
+      </c>
+      <c r="K402" s="6" t="inlineStr">
+        <is>
+          <t>https://myfox8.com/news/north-carolina/greensboro/lumentum-holdings-opens-new-manufacturing-facility-in-greensboro/amp/</t>
+        </is>
+      </c>
+      <c r="L402" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B403" s="6" t="inlineStr">
+        <is>
+          <t>Kernersville</t>
+        </is>
+      </c>
+      <c r="C403" s="6" t="inlineStr">
+        <is>
+          <t>Forsyth</t>
+        </is>
+      </c>
+      <c r="D403" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E403" s="6" t="inlineStr">
+        <is>
+          <t>John Deere — excavator plant (relocating from Japan)</t>
+        </is>
+      </c>
+      <c r="F403" s="6" t="inlineStr">
+        <is>
+          <t>150+</t>
+        </is>
+      </c>
+      <c r="G403" s="6" t="inlineStr">
+        <is>
+          <t>$70M</t>
+        </is>
+      </c>
+      <c r="H403" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Inferred skilled-mfg)</t>
+        </is>
+      </c>
+      <c r="I403" s="6" t="inlineStr">
+        <is>
+          <t>Construction confirmed underway on the west campus (designated for small-excavator assembly) — a firmer confirmation than "later this year" language used previously. Plant remains targeted to open 2027, production shifting from Japan.</t>
+        </is>
+      </c>
+      <c r="J403" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (construction confirmed underway)</t>
+        </is>
+      </c>
+      <c r="K403" s="6" t="inlineStr">
+        <is>
+          <t>https://www.deere.com/en-us/our-company/locations/factories/kernersville</t>
+        </is>
+      </c>
+      <c r="L403" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B404" s="6" t="inlineStr">
+        <is>
+          <t>Rowan / Kannapolis</t>
+        </is>
+      </c>
+      <c r="C404" s="6" t="inlineStr">
+        <is>
+          <t>Rowan</t>
+        </is>
+      </c>
+      <c r="D404" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E404" s="6" t="inlineStr">
+        <is>
+          <t>Google — 730k sq ft warehouse lease (3rd-party logistics operator)</t>
+        </is>
+      </c>
+      <c r="F404" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G404" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H404" s="6" t="inlineStr">
+        <is>
+          <t>$55k-$150k range (job-board postings)</t>
+        </is>
+      </c>
+      <c r="I404" s="6" t="inlineStr">
+        <is>
+          <t>Not covered by any regional research pass this cycle; carried forward unchanged from the prior report. Jobs/wage still undisclosed.</t>
+        </is>
+      </c>
+      <c r="J404" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-07 (not rechecked this cycle)</t>
+        </is>
+      </c>
+      <c r="K404" s="6" t="inlineStr">
+        <is>
+          <t>https://www.qcnews.com/news/u-s/north-carolina/kannapolis/google-signs-multi-year-lease-to-move-into-730000-square-foot-warehouse-in-kannapolis/</t>
+        </is>
+      </c>
+      <c r="L404" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B405" s="6" t="inlineStr">
+        <is>
+          <t>RTP</t>
+        </is>
+      </c>
+      <c r="C405" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D405" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E405" s="6" t="inlineStr">
+        <is>
+          <t>Apple — RTP campus extension</t>
+        </is>
+      </c>
+      <c r="F405" s="6" t="inlineStr">
+        <is>
+          <t>3,000 originally projected; only ~600-990 added to date</t>
+        </is>
+      </c>
+      <c r="G405" s="6" t="inlineStr">
+        <is>
+          <t>$552M-$1B+ (paused)</t>
+        </is>
+      </c>
+      <c r="H405" s="6" t="inlineStr">
+        <is>
+          <t>$187k avg (stated, original 2021 award)</t>
+        </is>
+      </c>
+      <c r="I405" s="6" t="inlineStr">
+        <is>
+          <t>No new Apple-specific building or hiring milestone found dated after the July 2026 RTP 3.0 framework approval already on record. Apple's own building construction timeline remains unannounced; ~$845.8M in state incentives remain at stake.</t>
+        </is>
+      </c>
+      <c r="J405" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (rechecked; no change)</t>
+        </is>
+      </c>
+      <c r="K405" s="6" t="inlineStr">
+        <is>
+          <t>https://www.rtp.org/2026/06/research-triangle-park-approves-3-0/</t>
+        </is>
+      </c>
+      <c r="L405" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B406" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Raleigh / Rural Hall</t>
+        </is>
+      </c>
+      <c r="C406" s="6" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="D406" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E406" s="6" t="inlineStr">
+        <is>
+          <t>Siemens Energy — $421M NC expansion (Charlotte-specific wage now confirmed)</t>
+        </is>
+      </c>
+      <c r="F406" s="6" t="inlineStr">
+        <is>
+          <t>500 (statewide)</t>
+        </is>
+      </c>
+      <c r="G406" s="6" t="inlineStr">
+        <is>
+          <t>$421M</t>
+        </is>
+      </c>
+      <c r="H406" s="6" t="inlineStr">
+        <is>
+          <t>$82,052 avg for the Charlotte-specific share (newly confirmed, sub-$100k; largely mechanic/assembly/logistics roles)</t>
+        </is>
+      </c>
+      <c r="I406" s="6" t="inlineStr">
+        <is>
+          <t>New detail: the Charlotte-specific average wage for this expansion (centered on the Westinghouse Blvd facility, restarting gas-turbine production alongside transformer manufacturing) is confirmed at $82,052 — below the $100k bar, consistent with this entry's continued Watch (not Ranked) status. Original announcement remains pre-window (2026-02-03/05); no in-window groundbreaking/hiring-start milestone found.</t>
+        </is>
+      </c>
+      <c r="J406" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (Charlotte-specific wage confirmed)</t>
+        </is>
+      </c>
+      <c r="K406" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/02/siemens-energy-announces-421-million-expansion-in-charlotte-boosting-local-economy-with-500-new-jobs/</t>
+        </is>
+      </c>
+      <c r="L406" s="6" t="inlineStr">
+        <is>
+          <t>Med (totals uncertain; Charlotte wage now confirmed sub-$100k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B407" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh / Wendell / Knightdale</t>
+        </is>
+      </c>
+      <c r="C407" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D407" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E407" s="6" t="inlineStr">
+        <is>
+          <t>Siemens AG — power devices for AI/data centers</t>
+        </is>
+      </c>
+      <c r="F407" s="6" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="G407" s="6" t="inlineStr">
+        <is>
+          <t>part of $165M</t>
+        </is>
+      </c>
+      <c r="H407" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I407" s="6" t="inlineStr">
+        <is>
+          <t>Not covered by any regional research pass this cycle; carried forward unchanged from the prior report.</t>
+        </is>
+      </c>
+      <c r="J407" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (not rechecked this cycle)</t>
+        </is>
+      </c>
+      <c r="K407" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/business/siemens-350-jobs-nc-sc-165m-investment-ai-data-centers-raleigh-wendell-march-2026/</t>
+        </is>
+      </c>
+      <c r="L407" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B408" s="6" t="inlineStr">
+        <is>
+          <t>Hamlet</t>
+        </is>
+      </c>
+      <c r="C408" s="6" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="D408" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E408" s="6" t="inlineStr">
+        <is>
+          <t>AWS/Amazon — AI/cloud campus "Project Blue Marlin"</t>
+        </is>
+      </c>
+      <c r="F408" s="6" t="inlineStr">
+        <is>
+          <t>500 permanent (confirmed)</t>
+        </is>
+      </c>
+      <c r="G408" s="6" t="inlineStr">
+        <is>
+          <t>$10B</t>
+        </is>
+      </c>
+      <c r="H408" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I408" s="6" t="inlineStr">
+        <is>
+          <t>Not covered by any regional research pass this cycle (Richmond Co. falls outside all five assigned regions); carried forward unchanged from the prior report.</t>
+        </is>
+      </c>
+      <c r="J408" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (not rechecked this cycle)</t>
+        </is>
+      </c>
+      <c r="K408" s="6" t="inlineStr">
+        <is>
+          <t>https://www.deq.nc.gov/news/press-releases/2026/08/28/ncdeqs-division-air-quality-requires-additional-monitoring-testing-final-air-quality-permits-amazon</t>
+        </is>
+      </c>
+      <c r="L408" s="6" t="inlineStr">
+        <is>
+          <t>High (permits/scheduling confirmed); Low (post-event outcome)</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B409" s="6" t="inlineStr">
+        <is>
+          <t>Orangeburg / I-26</t>
+        </is>
+      </c>
+      <c r="C409" s="6" t="inlineStr">
+        <is>
+          <t>Orangeburg</t>
+        </is>
+      </c>
+      <c r="D409" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E409" s="6" t="inlineStr">
+        <is>
+          <t>Ferrara Candy — new mfg + corporate site</t>
+        </is>
+      </c>
+      <c r="F409" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (10 yr)</t>
+        </is>
+      </c>
+      <c r="G409" s="6" t="inlineStr">
+        <is>
+          <t>$675M</t>
+        </is>
+      </c>
+      <c r="H409" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; confectionery = workforce-tier</t>
+        </is>
+      </c>
+      <c r="I409" s="6" t="inlineStr">
+        <is>
+          <t>Not covered by any regional research pass this cycle (Orangeburg Co. falls outside all five assigned regions); carried forward unchanged from the prior report.</t>
+        </is>
+      </c>
+      <c r="J409" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 (not rechecked this cycle)</t>
+        </is>
+      </c>
+      <c r="K409" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wistv.com/2026/04/22/ferrara-candy-company-build-675m-orangeburg-county-plant-create-1000-jobs-officials-say/</t>
+        </is>
+      </c>
+      <c r="L409" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B410" s="6" t="inlineStr">
+        <is>
+          <t>Columbia / BullStreet</t>
+        </is>
+      </c>
+      <c r="C410" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="D410" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E410" s="6" t="inlineStr">
+        <is>
+          <t>AMAROK — new HQ (perimeter security)</t>
+        </is>
+      </c>
+      <c r="F410" s="6" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="G410" s="6" t="inlineStr">
+        <is>
+          <t>$69M</t>
+        </is>
+      </c>
+      <c r="H410" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; HQ/professional (portion likely $100k+)</t>
+        </is>
+      </c>
+      <c r="I410" s="6" t="inlineStr">
+        <is>
+          <t>No groundbreaking confirmation found this cycle; coverage remains anchored to the original March 24, 2026 announcement ("construction expected to begin in 2026," online by end of 2028).</t>
+        </is>
+      </c>
+      <c r="J410" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (rechecked; no change)</t>
+        </is>
+      </c>
+      <c r="K410" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.sc.gov/news/2026-03/amarok-expands-richland-county-operations-new-headquarters</t>
+        </is>
+      </c>
+      <c r="L410" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B411" s="6" t="inlineStr">
+        <is>
+          <t>North Charleston</t>
+        </is>
+      </c>
+      <c r="C411" s="6" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="D411" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E411" s="6" t="inlineStr">
+        <is>
+          <t>Boeing 787 — production-rate ramp (apprenticeship doubling reconfirmed)</t>
+        </is>
+      </c>
+      <c r="F411" s="6" t="inlineStr">
+        <is>
+          <t>1,000+ new jobs over 5 yrs (unchanged); campus total ~9,059</t>
+        </is>
+      </c>
+      <c r="G411" s="6" t="inlineStr">
+        <is>
+          <t>$1B+ (existing)</t>
+        </is>
+      </c>
+      <c r="H411" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mixed (production ~$70-85k; eng. above $100k)</t>
+        </is>
+      </c>
+      <c r="I411" s="6" t="inlineStr">
+        <is>
+          <t>Reconfirmed the Aug. 27, 2026 announcement to more than double the registered apprenticeship program (from ~500 to 1,000+ apprentices over two years), tied to the ~$1B North Charleston investment; the announcement was made jointly with Acting US Labor Secretary Keith Sonderling, who signed an MOU with DOL on-site. No newer production-rate or headcount figure found this cycle.</t>
+        </is>
+      </c>
+      <c r="J411" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-27 (reconfirmed)</t>
+        </is>
+      </c>
+      <c r="K411" s="6" t="inlineStr">
+        <is>
+          <t>https://www.live5news.com/2026/08/27/boeing-double-apprenticeship-program-north-charleston-plant/</t>
+        </is>
+      </c>
+      <c r="L411" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B412" s="6" t="inlineStr">
+        <is>
+          <t>Goose Creek</t>
+        </is>
+      </c>
+      <c r="C412" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley</t>
+        </is>
+      </c>
+      <c r="D412" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E412" s="6" t="inlineStr">
+        <is>
+          <t>HII (Newport News Shipbuilding) — no site-specific new figure</t>
+        </is>
+      </c>
+      <c r="F412" s="6" t="inlineStr">
+        <is>
+          <t>~475 employees (unchanged)</t>
+        </is>
+      </c>
+      <c r="G412" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H412" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I412" s="6" t="inlineStr">
+        <is>
+          <t>No Goose Creek-specific new expansion figure found this cycle. HII's company-wide 2026 plan to outsource 2.5M+ shipbuilding labor hours (a 30% YoY increase across 25 locations in 11 states, "equivalent to more than 1,000 additional jobs") is a multi-state aggregate, not a Goose Creek-specific commitment, so it does not qualify as a new dedicated announcement for this site. Active hiring (pipefitters, mechanical techs) continues per job postings.</t>
+        </is>
+      </c>
+      <c r="J412" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (rechecked; still inconclusive)</t>
+        </is>
+      </c>
+      <c r="K412" s="6" t="inlineStr">
+        <is>
+          <t>https://www.hii.com/news/hii-closes-on-asset-acquisition-to-expand-shipbuilding-capacity</t>
+        </is>
+      </c>
+      <c r="L412" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B413" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="C413" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D413" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E413" s="6" t="inlineStr">
+        <is>
+          <t>Siemens Smart Infrastructure</t>
+        </is>
+      </c>
+      <c r="F413" s="6" t="inlineStr">
+        <is>
+          <t>~150</t>
+        </is>
+      </c>
+      <c r="G413" s="6" t="inlineStr">
+        <is>
+          <t>$165M</t>
+        </is>
+      </c>
+      <c r="H413" s="6" t="inlineStr">
+        <is>
+          <t>Avg $78,811/yr ($37.89/hr); 90th pct ~$100k (Estimated/Inferred)</t>
+        </is>
+      </c>
+      <c r="I413" s="6" t="inlineStr">
+        <is>
+          <t>No material update found this cycle beyond the March 2026 announcement (&gt;$165M Carolinas-wide investment in electrical products for data centers); active job postings continue.</t>
+        </is>
+      </c>
+      <c r="J413" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (rechecked)</t>
+        </is>
+      </c>
+      <c r="K413" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wspa.com/news/local-news/siemens-to-expand-production-in-spartanburg-co-add-150-jobs/</t>
+        </is>
+      </c>
+      <c r="L413" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B414" s="6" t="inlineStr">
+        <is>
+          <t>Woodruff / Spartanburg Co.</t>
+        </is>
+      </c>
+      <c r="C414" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D414" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E414" s="6" t="inlineStr">
+        <is>
+          <t>AIRSYS Cooling Technologies — global HQ</t>
+        </is>
+      </c>
+      <c r="F414" s="6" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G414" s="6" t="inlineStr">
+        <is>
+          <t>$40M</t>
+        </is>
+      </c>
+      <c r="H414" s="6" t="inlineStr">
+        <is>
+          <t>Eng. roles $69-93k; assembly $34-46k (Estimated/Inferred)</t>
+        </is>
+      </c>
+      <c r="I414" s="6" t="inlineStr">
+        <is>
+          <t>Corporate/HQ teams confirmed now operating on-site at the new Woodruff campus; manufacturing/3D-printing production start remains targeted for Q1 2027 (unchanged from prior guidance).</t>
+        </is>
+      </c>
+      <c r="J414" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (partial update)</t>
+        </is>
+      </c>
+      <c r="K414" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/spartanburg/business/airsys-data-center-water-woodruff-sc/article_86465e32-7d21-4bba-9a9b-3e6ea0e2d691.html</t>
+        </is>
+      </c>
+      <c r="L414" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B415" s="6" t="inlineStr">
+        <is>
+          <t>Gray Court</t>
+        </is>
+      </c>
+      <c r="C415" s="6" t="inlineStr">
+        <is>
+          <t>Laurens</t>
+        </is>
+      </c>
+      <c r="D415" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E415" s="6" t="inlineStr">
+        <is>
+          <t>Aptiv Services US — Connexial Center</t>
+        </is>
+      </c>
+      <c r="F415" s="6" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="G415" s="6" t="inlineStr">
+        <is>
+          <t>$120.8M</t>
+        </is>
+      </c>
+      <c r="H415" s="6" t="inlineStr">
+        <is>
+          <t>~$49-76k technician range (Estimated/Inferred)</t>
+        </is>
+      </c>
+      <c r="I415" s="6" t="inlineStr">
+        <is>
+          <t>No Aptiv-specific update found this cycle ("Project Oracle" details reconfirmed unchanged). Adjacent signal: the same Connexial Center industrial park separately landed a Shamrock Technologies (specialty additives) corporate HQ relocation from New Jersey — a different company, jobs/wage undisclosed, noted only as a park-level momentum signal.</t>
+        </is>
+      </c>
+      <c r="J415" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (rechecked; no change)</t>
+        </is>
+      </c>
+      <c r="K415" s="6" t="inlineStr">
+        <is>
+          <t>https://growlaurenscounty.com/news/article/momentum-continues-at-the-connexial-center-with-aptivs-investment</t>
+        </is>
+      </c>
+      <c r="L415" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B416" s="6" t="inlineStr">
+        <is>
+          <t>Easley (Anderson/Pickens border)</t>
+        </is>
+      </c>
+      <c r="C416" s="6" t="inlineStr">
+        <is>
+          <t>Anderson</t>
+        </is>
+      </c>
+      <c r="D416" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E416" s="6" t="inlineStr">
+        <is>
+          <t>Signature Foods USA</t>
+        </is>
+      </c>
+      <c r="F416" s="6" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="G416" s="6" t="inlineStr">
+        <is>
+          <t>$11.5M</t>
+        </is>
+      </c>
+      <c r="H416" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred sub-$50k (food mfg.)</t>
+        </is>
+      </c>
+      <c r="I416" s="6" t="inlineStr">
+        <is>
+          <t>Operations confirmed already online; no headcount change found this cycle.</t>
+        </is>
+      </c>
+      <c r="J416" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (rechecked)</t>
+        </is>
+      </c>
+      <c r="K416" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/greenville/business/easley-anderson-county-signature-foods-investment/article_1d618a58-af96-435a-a05c-7cc6f9253a83.html</t>
+        </is>
+      </c>
+      <c r="L416" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B417" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="C417" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D417" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E417" s="6" t="inlineStr">
+        <is>
+          <t>GNQ Insilico — AI/quantum techbio HQ (SPAC deadline imminent)</t>
+        </is>
+      </c>
+      <c r="F417" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G417" s="6" t="inlineStr">
+        <is>
+          <t>$500M (valuation, not capex)</t>
+        </is>
+      </c>
+      <c r="H417" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I417" s="6" t="inlineStr">
+        <is>
+          <t>IB Acquisition Corp. (NASDAQ: IBAC) stockholders already approved extending the SPAC business-combination deadline to Sept. 28, 2026 — 7 days from this report. Deal still described as "expected to close in Q3 2026," but no confirmation the combination has actually closed was found. Jobs remain undisclosed. Urgent recheck warranted next cycle given the imminent deadline.</t>
+        </is>
+      </c>
+      <c r="J417" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (deadline 7 days out; deal not yet confirmed closed)</t>
+        </is>
+      </c>
+      <c r="K417" s="6" t="inlineStr">
+        <is>
+          <t>https://www.investing.com/news/sec-filings/ib-acquisition-stockholders-approve-extension-of-business-combination-deadline-93CH-4582632</t>
+        </is>
+      </c>
+      <c r="L417" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B418" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="C418" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D418" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E418" s="6" t="inlineStr">
+        <is>
+          <t>GE Vernova — gas turbine mfg (strong company-wide demand; no new local jobs figure)</t>
+        </is>
+      </c>
+      <c r="F418" s="6" t="inlineStr">
+        <is>
+          <t>650 total planned; ~200 hired past yr</t>
+        </is>
+      </c>
+      <c r="G418" s="6" t="inlineStr">
+        <is>
+          <t>$160M (Greenville)</t>
+        </is>
+      </c>
+      <c r="H418" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mixed (bulk likely sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I418" s="6" t="inlineStr">
+        <is>
+          <t>Company-wide gas-turbine order backlog grew to 116 GW at end of Q2 2026 (up from 100 GW in Q1), with guidance toward 125 GW under contract by year-end 2026 — a strong demand signal for continued Greenville hiring, but no new Greenville-specific headcount figure was found this cycle beyond the existing 650-job plan.</t>
+        </is>
+      </c>
+      <c r="J418" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (backlog update; no new local jobs figure)</t>
+        </is>
+      </c>
+      <c r="K418" s="6" t="inlineStr">
+        <is>
+          <t>https://www.utilitydive.com/news/ge-vernova-gas-turbine-backlog-climbs-to-116-gw/826039/</t>
+        </is>
+      </c>
+      <c r="L418" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B419" s="6" t="inlineStr">
+        <is>
+          <t>Laurens Co. (Laurens)</t>
+        </is>
+      </c>
+      <c r="C419" s="6" t="inlineStr">
+        <is>
+          <t>Laurens</t>
+        </is>
+      </c>
+      <c r="D419" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E419" s="6" t="inlineStr">
+        <is>
+          <t>Suniva Inc. — solar-cell manufacturing plant (figures need reconciliation)</t>
+        </is>
+      </c>
+      <c r="F419" s="6" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="G419" s="6" t="inlineStr">
+        <is>
+          <t>$350M (per governor.sc.gov) — a Sept. 2026 report cites $600M+ total including the capital raise</t>
+        </is>
+      </c>
+      <c r="H419" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred sub-$100k blended</t>
+        </is>
+      </c>
+      <c r="I419" s="6" t="inlineStr">
+        <is>
+          <t>pv-magazine (Sept. 9, 2026) reports Suniva has raised $835M to fund 4.5 GW of new domestic solar-cell capacity at the 620,000 sf facility, describing the project as "fully funded"; building shell reported complete, opening targeted late 2027. Note: this capital-raise closing date and total-investment figure differ from what was carried in prior cycles (previously dated to July 2026 at $350M) — flagged for reconciliation against the original SC Governor's office release next cycle.</t>
+        </is>
+      </c>
+      <c r="J419" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-09 (capital raise reported)</t>
+        </is>
+      </c>
+      <c r="K419" s="6" t="inlineStr">
+        <is>
+          <t>https://pv-magazine-usa.com/2026/09/09/suniva-raises-835-million-to-drive-4-5-gw-in-new-domestic-cell-capacity/</t>
+        </is>
+      </c>
+      <c r="L419" s="6" t="inlineStr">
+        <is>
+          <t>High (raise); Med (figure reconciliation needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B420" s="6" t="inlineStr">
+        <is>
+          <t>Piedmont</t>
+        </is>
+      </c>
+      <c r="C420" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D420" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E420" s="6" t="inlineStr">
+        <is>
+          <t>Isuzu North America — truck assembly plant</t>
+        </is>
+      </c>
+      <c r="F420" s="6" t="inlineStr">
+        <is>
+          <t>700+</t>
+        </is>
+      </c>
+      <c r="G420" s="6" t="inlineStr">
+        <is>
+          <t>$280M</t>
+        </is>
+      </c>
+      <c r="H420" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred: assembly $35-56k, engineers $79-108k — blended sub-$100k</t>
+        </is>
+      </c>
+      <c r="I420" s="6" t="inlineStr">
+        <is>
+          <t>No new hiring event found beyond the already-tracked July 8, 2026 direct-hire event; company's stated goal remains 150 employees by end of 2026, with hiring continuing through 2027 "and beyond." 700-total-job plan and $280M capex unchanged, 2027 launch still targeted.</t>
+        </is>
+      </c>
+      <c r="J420" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (rechecked; no new event)</t>
+        </is>
+      </c>
+      <c r="K420" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ccjdigital.com/business/article/15767928/isuzu-building-280m-truck-plant-in-south-carolina-creating-700-jobs</t>
+        </is>
+      </c>
+      <c r="L420" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B421" s="6" t="inlineStr">
+        <is>
+          <t>Ridgeville / Camp Hall</t>
+        </is>
+      </c>
+      <c r="C421" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley</t>
+        </is>
+      </c>
+      <c r="D421" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E421" s="6" t="inlineStr">
+        <is>
+          <t>Redwood Materials — battery-materials recycling campus (standing gap resolved)</t>
+        </is>
+      </c>
+      <c r="F421" s="6" t="inlineStr">
+        <is>
+          <t>1,500 (over the next decade — a longer horizon than previously carried)</t>
+        </is>
+      </c>
+      <c r="G421" s="6" t="inlineStr">
+        <is>
+          <t>$3.5B</t>
+        </is>
+      </c>
+      <c r="H421" s="6" t="inlineStr">
+        <is>
+          <t>$27-75/hr stated (~$56k-156k) — upper tier clears $100k</t>
+        </is>
+      </c>
+      <c r="I421" s="6" t="inlineStr">
+        <is>
+          <t>The 7-cycle standing gap is resolved: multiple independent outlets (electrive.com, Charged EVs, Recycling Today, batteriesnews.com) confirm critical-materials-recovery operations at the 600-acre Camp Hall campus actually began in November 2025 (initial phase ~20,000 metric tonnes/yr of recovered lithium, nickel, cobalt, copper), building toward the previously stated 100 GWh/yr target. This milestone predates the current window (2026-03-21 to 2026-09-21), which explains the lack of further movement — the project has moved into an ordinary ramp/hiring phase with no new dated 2026 PR found. Keep on Watch pending a genuinely new 2026 milestone.</t>
+        </is>
+      </c>
+      <c r="J421" s="6" t="inlineStr">
+        <is>
+          <t>2025-11 (startup date now confirmed; pre-window)</t>
+        </is>
+      </c>
+      <c r="K421" s="6" t="inlineStr">
+        <is>
+          <t>https://www.redwoodmaterials.com/news/redwood-begins-critical-materials-recovery-in-south-carolina/</t>
+        </is>
+      </c>
+      <c r="L421" s="6" t="inlineStr">
+        <is>
+          <t>Med-High (startup date now corroborated; no new in-window movement)</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B422" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="C422" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D422" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E422" s="6" t="inlineStr">
+        <is>
+          <t>PSA Airlines — Charlotte headquarters</t>
+        </is>
+      </c>
+      <c r="F422" s="6" t="inlineStr">
+        <is>
+          <t>~400 (450+ total team members at HQ)</t>
+        </is>
+      </c>
+      <c r="G422" s="6" t="inlineStr">
+        <is>
+          <t>Not itemized</t>
+        </is>
+      </c>
+      <c r="H422" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Estimated/Inferred mixed corporate/admin/ops, likely sub-$100k blended)</t>
+        </is>
+      </c>
+      <c r="I422" s="6" t="inlineStr">
+        <is>
+          <t>HQ relocation confirmed completed 2026-01-12; of the ~250 net-new positions, the company states over 80% have been filled but is "still seeking 170 more employees" — these two figures are internally inconsistent in the sourcing itself (flagged rather than reconciled). No wage disclosure found.</t>
+        </is>
+      </c>
+      <c r="J422" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (hiring-progress detail found; dates cluster Jan-Mar 2026)</t>
+        </is>
+      </c>
+      <c r="K422" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2026/03/19/governor-stein-celebrates-psa-airlines-headquarters-grand-opening-charlotte-highlights-only</t>
+        </is>
+      </c>
+      <c r="L422" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B423" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Steele Creek</t>
+        </is>
+      </c>
+      <c r="C423" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D423" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E423" s="6" t="inlineStr">
+        <is>
+          <t>Maersk — North American HQ</t>
+        </is>
+      </c>
+      <c r="F423" s="6" t="inlineStr">
+        <is>
+          <t>520 (confirmed, stated)</t>
+        </is>
+      </c>
+      <c r="G423" s="6" t="inlineStr">
+        <is>
+          <t>$16M</t>
+        </is>
+      </c>
+      <c r="H423" s="6" t="inlineStr">
+        <is>
+          <t>$100,962 avg (stated) — clears $100k bar</t>
+        </is>
+      </c>
+      <c r="I423" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; searched specifically for 2026 news beyond the 2026-02-24 hiring-delay approval, nothing newer surfaced.</t>
+        </is>
+      </c>
+      <c r="J423" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (rechecked; no change)</t>
+        </is>
+      </c>
+      <c r="K423" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/maersk-delays-charlotte-headquarters-plan-hiring-520-workers-by-1-year/</t>
+        </is>
+      </c>
+      <c r="L423" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); milestone timing at window edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B424" s="6" t="inlineStr">
+        <is>
+          <t>Salisbury / Granite Industrial Park</t>
+        </is>
+      </c>
+      <c r="C424" s="6" t="inlineStr">
+        <is>
+          <t>Rowan</t>
+        </is>
+      </c>
+      <c r="D424" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E424" s="6" t="inlineStr">
+        <is>
+          <t>Jabil Inc. — advanced manufacturing (AI/data-center hardware)</t>
+        </is>
+      </c>
+      <c r="F424" s="6" t="inlineStr">
+        <is>
+          <t>1,181 (stated, over 5 yr)</t>
+        </is>
+      </c>
+      <c r="G424" s="6" t="inlineStr">
+        <is>
+          <t>~$264M near-term / ~$500M multi-year</t>
+        </is>
+      </c>
+      <c r="H424" s="6" t="inlineStr">
+        <is>
+          <t>$62,034 avg (stated) — sub-$100k</t>
+        </is>
+      </c>
+      <c r="I424" s="6" t="inlineStr">
+        <is>
+          <t>No confirmation found that operations have actually started; all sources (Rowan EDC, Salisbury Post, Area Development) still describe a forward-looking "mid-2026" operational target with no dated confirmation of an actual opening/ramp-up.</t>
+        </is>
+      </c>
+      <c r="J424" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (rechecked; still unconfirmed)</t>
+        </is>
+      </c>
+      <c r="K424" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/fortune-500-company-eyes-rowan-county-for-264-million-investment-creating-1181-jobs/</t>
+        </is>
+      </c>
+      <c r="L424" s="6" t="inlineStr">
+        <is>
+          <t>Medium (facts High; in-window operational milestone unconfirmed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B425" s="6" t="inlineStr">
+        <is>
+          <t>Morrisville / RTP-adjacent</t>
+        </is>
+      </c>
+      <c r="C425" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D425" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E425" s="6" t="inlineStr">
+        <is>
+          <t>Forge Nano — battery-manufacturing expansion ("America's Battery Gigafactory")</t>
+        </is>
+      </c>
+      <c r="F425" s="6" t="inlineStr">
+        <is>
+          <t>250+ (projected, incremental to an existing 200-job 2023 commitment)</t>
+        </is>
+      </c>
+      <c r="G425" s="6" t="inlineStr">
+        <is>
+          <t>~$300M (incl. $100M DOE non-dilutive funding)</t>
+        </is>
+      </c>
+      <c r="H425" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed for the 2026 expansion</t>
+        </is>
+      </c>
+      <c r="I425" s="6" t="inlineStr">
+        <is>
+          <t>New Sept. 17, 2026 announcement of an expanded partnership with Voltaiq (AI battery-software company) tied to the gigafactory build, alongside a previously noted Samsung SDI construction-assistance partnership; the Aug. 19, 2026 groundbreaking stands. Production still targeted 2028.</t>
+        </is>
+      </c>
+      <c r="J425" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17 (Voltaiq partnership)</t>
+        </is>
+      </c>
+      <c r="K425" s="6" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/09/17/3363983/</t>
+        </is>
+      </c>
+      <c r="L425" s="6" t="inlineStr">
+        <is>
+          <t>High (partnership/date corroborated); Low (wage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B426" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington / US-421 corridor</t>
+        </is>
+      </c>
+      <c r="C426" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover</t>
+        </is>
+      </c>
+      <c r="D426" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E426" s="6" t="inlineStr">
+        <is>
+          <t>Protocase / 45Drives / ProtoSpace Mfg — precision manufacturing campus</t>
+        </is>
+      </c>
+      <c r="F426" s="6" t="inlineStr">
+        <is>
+          <t>~100 confirmed; company target 500+ total</t>
+        </is>
+      </c>
+      <c r="G426" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H426" s="6" t="inlineStr">
+        <is>
+          <t>$34,840-$41,409 stated for production/assembly roles (sub-$100k); corporate/engineering wage not disclosed</t>
+        </is>
+      </c>
+      <c r="I426" s="6" t="inlineStr">
+        <is>
+          <t>Continued hiring momentum confirmed: an April 30, 2026 career fair at the Maritime North Business Park had all three "Proto Companies" brands hiring simultaneously; the group (branded "The Proto Companies," now including "Protomentum") is targeting $1 billion in annual revenue within five years, with much of that growth slated for Wilmington. Could not obtain an updated precise headcount toward the 500+ target this cycle (a secondary source claiming a "500-job update" was blocked/unverifiable — treat as unconfirmed).</t>
+        </is>
+      </c>
+      <c r="J426" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (momentum confirmed; headcount not updated)</t>
+        </is>
+      </c>
+      <c r="K426" s="6" t="inlineStr">
+        <is>
+          <t>https://www.newmediawire.com/news/the-protocase-companies-and-advanced-glazings-announce-wilmington-nc-career-fair-to-support-rapid-u-s-expansion-7086465</t>
+        </is>
+      </c>
+      <c r="L426" s="6" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B427" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington / US-421 corridor (Wilmington Trade Center)</t>
+        </is>
+      </c>
+      <c r="C427" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover</t>
+        </is>
+      </c>
+      <c r="D427" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E427" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington Trade Center — multi-tenant industrial park expansion</t>
+        </is>
+      </c>
+      <c r="F427" s="6" t="inlineStr">
+        <is>
+          <t>1,500+ (aggregate, long-run park build-out; not a single employer's committed headcount)</t>
+        </is>
+      </c>
+      <c r="G427" s="6" t="inlineStr">
+        <is>
+          <t>$300-400M added tax base (park build-out); ~$3.3M county incentive</t>
+        </is>
+      </c>
+      <c r="H427" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I427" s="6" t="inlineStr">
+        <is>
+          <t>Construction progressing: Building 4 (~153,000 sf) nearing completion with new leases signed (Glass Warehouse ~55,500 sf in Building 3; American Tire Distributors ~110,000 sf in Building 4). Phase 2 (kicked off March 2026) covers ~125 acres of clearing/grading for future Buildings 4-8 and 11-13, plus utility infrastructure, toward the full 13-building, 3.2M sf plan.</t>
+        </is>
+      </c>
+      <c r="J427" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-29 (most recent dated leasing update found)</t>
+        </is>
+      </c>
+      <c r="K427" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wilmingtonbiz.com/real_estate_-_commercial/2026/01/29/wilmington_trade_center_inks_new_leases_as_park_build-out_continues/27187</t>
+        </is>
+      </c>
+      <c r="L427" s="6" t="inlineStr">
+        <is>
+          <t>Medium (aggregate park estimate, not a single-employer commitment)</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B428" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="C428" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D428" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E428" s="6" t="inlineStr">
+        <is>
+          <t>EnerSys — lithium-cell manufacturing facility (jobs still undisclosed for revised project)</t>
+        </is>
+      </c>
+      <c r="F428" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed for the revised project (the pre-restructuring ~500-job 2024 figure must NOT be carried forward)</t>
+        </is>
+      </c>
+      <c r="G428" s="6" t="inlineStr">
+        <is>
+          <t>~$500M total net investment (restructured); $150M DOE grant + up to $200M state/local incentives</t>
+        </is>
+      </c>
+      <c r="H428" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I428" s="6" t="inlineStr">
+        <is>
+          <t>On Sept. 11, 2026, EnerSys management discussed the restructured (defense/aerospace-focused, ~1 GWh capacity) project again at the Jefferies Renewables/Clean Energy/E&amp;C conference, describing it as a "strategic response to defense supply-chain risk" that "could be expanded further" — but no primary-source confirmation of a new jobs figure was found. Multiple secondary aggregators keep resurfacing the original Feb. 2024 "500 new jobs" figure, which predates the July 23, 2026 restructuring and should not be treated as current. Construction still targeted to begin H1 of the company's fiscal 2028. This remains the single most important open item for this entry — a primary-source (SEC/investor-site) pull is needed to resolve it.</t>
+        </is>
+      </c>
+      <c r="J428" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-11 (conference remarks; no new jobs figure disclosed)</t>
+        </is>
+      </c>
+      <c r="K428" s="6" t="inlineStr">
+        <is>
+          <t>https://www.tipranks.com/news/company-announcements/enersys-refines-u-s-defense-focused-lithium-ion-plant-plan</t>
+        </is>
+      </c>
+      <c r="L428" s="6" t="inlineStr">
+        <is>
+          <t>Medium (restructuring/financing facts corroborated; jobs figure still undisclosed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B429" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington</t>
+        </is>
+      </c>
+      <c r="C429" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover</t>
+        </is>
+      </c>
+      <c r="D429" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E429" s="6" t="inlineStr">
+        <is>
+          <t>GE Hitachi / Global Nuclear Fuel — GNF4 fuel line</t>
+        </is>
+      </c>
+      <c r="F429" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G429" s="6" t="inlineStr">
+        <is>
+          <t>Not itemized</t>
+        </is>
+      </c>
+      <c r="H429" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I429" s="6" t="inlineStr">
+        <is>
+          <t>Confirmed the company plans to invest more than $50 million in 2026-2027 to support the GNF4 next-gen fuel product at the Castle Hayne Road facility, requiring "several new positions" in engineering, supply chain, and manufacturing — but a specific job-count figure for GNF4 itself remains Not Disclosed. (A separate, earlier-vintage ~500-job/~$131k-wage expansion at the same campus, originally reported 2022, is not part of this in-window item.)</t>
+        </is>
+      </c>
+      <c r="J429" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (investment confirmed; jobs still undisclosed)</t>
+        </is>
+      </c>
+      <c r="K429" s="6" t="inlineStr">
+        <is>
+          <t>https://www.gevernova.com/news/press-releases/global-nuclear-fuel-introduces-next-generation-fuel-product</t>
+        </is>
+      </c>
+      <c r="L429" s="6" t="inlineStr">
+        <is>
+          <t>Low-Med (indirect signal only, no discrete jobs figure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B430" s="6" t="inlineStr">
+        <is>
+          <t>Burlington / Alamance-Guilford line</t>
+        </is>
+      </c>
+      <c r="C430" s="6" t="inlineStr">
+        <is>
+          <t>Alamance</t>
+        </is>
+      </c>
+      <c r="D430" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E430" s="6" t="inlineStr">
+        <is>
+          <t>Ahold Delhaize USA (Food Lion parent) — distribution center</t>
+        </is>
+      </c>
+      <c r="F430" s="6" t="inlineStr">
+        <is>
+          <t>500-505</t>
+        </is>
+      </c>
+      <c r="G430" s="6" t="inlineStr">
+        <is>
+          <t>$860M</t>
+        </is>
+      </c>
+      <c r="H430" s="6" t="inlineStr">
+        <is>
+          <t>~$60k-$67k avg (Estimated/Inferred, sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I430" s="6" t="inlineStr">
+        <is>
+          <t>Construction confirmed underway on the $860M, 1M+ sf distribution center (per Feb. 16, 2026 groundbreaking, now pre-window); facility "will eventually employ more than 500 people," opening still targeted 2029. No fresher construction milestone beyond general 'underway' status found this cycle.</t>
+        </is>
+      </c>
+      <c r="J430" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21 (rechecked; construction underway confirmed)</t>
+        </is>
+      </c>
+      <c r="K430" s="6" t="inlineStr">
+        <is>
+          <t>https://alamancenews.com/officials-on-hand-for-food-lion-distribution-center-groundbreaking/</t>
+        </is>
+      </c>
+      <c r="L430" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B431" s="6" t="inlineStr">
+        <is>
+          <t>Pender / New Hanover</t>
+        </is>
+      </c>
+      <c r="C431" s="6" t="inlineStr">
+        <is>
+          <t>Pender (+New Hanover)</t>
+        </is>
+      </c>
+      <c r="D431" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E431" s="6" t="inlineStr">
+        <is>
+          <t>Amazon — robotics fulfillment center (occupancy imminent, not yet confirmed open)</t>
+        </is>
+      </c>
+      <c r="F431" s="6" t="inlineStr">
+        <is>
+          <t>1,000+</t>
+        </is>
+      </c>
+      <c r="G431" s="6" t="inlineStr">
+        <is>
+          <t>$350M</t>
+        </is>
+      </c>
+      <c r="H431" s="6" t="inlineStr">
+        <is>
+          <t>~$22/hr avg (Estimated/Inferred ~$45,760/yr, sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I431" s="6" t="inlineStr">
+        <is>
+          <t>As of an Aug. 10, 2026 report, Amazon had begun hiring for the fulfillment center and was preparing to hire for the adjacent delivery station; building occupancy was expected mid-to-late September 2026, with both facilities on track to open for the holiday season and a grand-opening ceremony planned for fall 2026. Could not confirm as of 2026-09-21 that the facility has formally opened — status is "hiring underway, occupancy imminent," not a confirmed opening. Recheck next cycle for the formal opening.</t>
+        </is>
+      </c>
+      <c r="J431" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10 (most recent dated update)</t>
+        </is>
+      </c>
+      <c r="K431" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wilmingtonbiz.com/more_news/2026/08/10/amazon_begins_hiring_as_local_facilities_near_completion/27737</t>
+        </is>
+      </c>
+      <c r="L431" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B432" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Ballantyne</t>
+        </is>
+      </c>
+      <c r="C432" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D432" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E432" s="6" t="inlineStr">
+        <is>
+          <t>TD Bank — Ballantyne office expansion (NEW to Watch — moved from unverified lead)</t>
+        </is>
+      </c>
+      <c r="F432" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (an Estimated/Inferred ~430 net-new-seat capacity figure can be calculated from 540 capacity minus ~111 prior seats, but this is capacity headroom, not a confirmed hiring commitment)</t>
+        </is>
+      </c>
+      <c r="G432" s="6" t="inlineStr">
+        <is>
+          <t>Not itemized</t>
+        </is>
+      </c>
+      <c r="H432" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I432" s="6" t="inlineStr">
+        <is>
+          <t>A real, dated, in-window occupancy milestone was confirmed this cycle: TD signed a 10-year lease (announced 2025-09-30, pre-window) for 91,464 sf across 3 floors plus a ground-floor suite in the Harris Building, 13024 Ballantyne Corporate Place — capacity for up to ~540 colleagues, more than tripling capacity from its prior 111-seat Irby Building office. First employees moved in June 2026; a ribbon-cutting/grand-opening was covered Sept. 2 and Sept. 8, 2026. TD has never disclosed a specific new-jobs figure or wage tied to this expansion — only office capacity — so it cannot qualify for Ranked, but the confirmed in-window occupancy milestone merits promotion from an unverified Excluded lead to active Watch tracking.</t>
+        </is>
+      </c>
+      <c r="J432" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-08 (grand-opening coverage)</t>
+        </is>
+      </c>
+      <c r="K432" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wbtv.com/2026/09/08/this-bank-wants-be-one-charlottes-banking-giants/</t>
+        </is>
+      </c>
+      <c r="L432" s="6" t="inlineStr">
+        <is>
+          <t>Medium (occupancy/capacity confirmed; jobs/wage undisclosed)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -42339,7 +47261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H158"/>
+  <dimension ref="A1:H173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48988,6 +53910,636 @@
         </is>
       </c>
     </row>
+    <row r="159">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>Aspida Financial Services — HQ expansion (REMOVED from Ranked — window risk resolved negatively)</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E159" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (was Ranked, score 74)</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
+        <is>
+          <t>2025-11-19 (announcement); 2025-12 (Imperial Tower lease signing)</t>
+        </is>
+      </c>
+      <c r="G159" s="6" t="inlineStr">
+        <is>
+          <t>Definitively resolved this cycle: the only two confirmed dates for this project — the Nov. 19, 2025 HQ-expansion announcement and the Dec. 2025 Imperial Tower lease signing — both fall before the 2026-03-21 window start. A dedicated search (the third consecutive cycle) found no fresher 2026 milestone; the $10M Imperial Tower renovation is still only described as 'slated to wrap by summer 2026' in the most recent coverage found, with no confirmation of actual completion, and Q4 2026 move-in remains an unconfirmed forward-looking target rather than a dated milestone. Removed from Ranked per the report's window rule; re-flag if a 2026-dated renovation-completion or move-in milestone surfaces.</t>
+        </is>
+      </c>
+      <c r="H159" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/raleigh/2025/11/19/aspida-financial-services-firm-plots-1000-job-expansion-in-durham</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="inlineStr">
+        <is>
+          <t>Ralliant Corp. — global HQ launch (REMOVED from Watch)</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh / North Hills (Wake)</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>Third consecutive cycle flagged "at risk." The only dated milestone remains the March 5, 2026 grand opening/ribbon-cutting, which sits before the 2026-03-21 window start; no fresher 2026 hiring/expansion milestone was found despite a dedicated search. Removed from active Watch tracking.</t>
+        </is>
+      </c>
+      <c r="H160" s="6" t="inlineStr">
+        <is>
+          <t>https://wral.com/business/technology/ralliant-launches-raleigh-global-hq-north-hills-march-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t>Jewelers Mutual Group (REMOVED from Watch)</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh / North Hills (Wake)</t>
+        </is>
+      </c>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>2025-10-01 (grand opening)</t>
+        </is>
+      </c>
+      <c r="G161" s="6" t="inlineStr">
+        <is>
+          <t>Grand opening now confirmed dated Oct. 1, 2025 — before the 2026-03-21 window start. No 2026-dated milestone found. Also sub-threshold regardless (200 jobs, wage undisclosed/likely sub-$100k). Removed from active Watch tracking.</t>
+        </is>
+      </c>
+      <c r="H161" s="6" t="inlineStr">
+        <is>
+          <t>https://www.jewelersmutual.com/newsroom/jewelers-mutual-expands-raleigh</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t>Wolfspeed — silicon-carbide fab (REMOVED from Watch — WARN dating conclusively resolved)</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>Siler City (Chatham)</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>1,800 (proj.); 73 (WARN layoffs)</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>2025-06-24 (WARN notification); 2025-11-14 (effective)</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>The multi-cycle dating ambiguity is now conclusively resolved via indexed WARN data: notification 6/24/2025, received by NC 6/26/2025, effective 11/14/2025 for 73 employees at 1000 Carolina Core Parkway — entirely a 2025 event, more than a year before the current window start. No 2026-dated WARN notice or other in-window milestone (positive or negative) was found. The company has also cut its 2026 capex guidance amid broader financial distress. Removed from active Watch tracking absent a genuinely 2026-dated development.</t>
+        </is>
+      </c>
+      <c r="H162" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
+        <is>
+          <t>Environmental Air Systems (REMOVED from Watch)</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>Asheboro (Randolph)</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="G163" s="6" t="inlineStr">
+        <is>
+          <t>Fourth consecutive cycle with no 2026-dated update found despite a dedicated final search; the original Nov. 25, 2025 announcement is now 10 months stale. Removed from active Watch tracking per the standing multi-cycle flag.</t>
+        </is>
+      </c>
+      <c r="H163" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/randolph-county-wins-20-million-hvac-project-300-jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B164" s="6" t="inlineStr">
+        <is>
+          <t>Google — data-center expansion (DOWNGRADED from Watch — stale)</t>
+        </is>
+      </c>
+      <c r="C164" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley &amp; Dorchester</t>
+        </is>
+      </c>
+      <c r="D164" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E164" s="6" t="inlineStr">
+        <is>
+          <t>~160 apprentices (FTE n/d)</t>
+        </is>
+      </c>
+      <c r="F164" s="6" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="G164" s="6" t="inlineStr">
+        <is>
+          <t>Eighth consecutive cycle with no verifiable dated 2026 project-specific milestone found beyond the original Sept. 26, 2024 announcement and its various syndicated recaps. No longer meets the bar for an active, dated Watch entry; downgraded to stale background context. Re-promote if a genuinely new 2026 milestone surfaces.</t>
+        </is>
+      </c>
+      <c r="H164" s="6" t="inlineStr">
+        <is>
+          <t>https://blog.google/company-news/inside-google/company-announcements/google-american-innovation-south-carolina/</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B165" s="6" t="inlineStr">
+        <is>
+          <t>VinFast — EV/battery megasite (litigation ongoing; closed-session meeting held, outcome undisclosed)</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>Moncure (Chatham)</t>
+        </is>
+      </c>
+      <c r="D165" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E165" s="6" t="inlineStr">
+        <is>
+          <t>0 (deal terminated)</t>
+        </is>
+      </c>
+      <c r="F165" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15/16 (special meeting)</t>
+        </is>
+      </c>
+      <c r="G165" s="6" t="inlineStr">
+        <is>
+          <t>Chatham County commissioners' Sept. 15/16, 2026 closed-session special meeting (reported as roughly four hours) covering incentive-related matters alongside a separate data-center-moratorium lawsuit did occur, but closed sessions are not required to disclose substantive outcomes immediately and none was found. VinFast's Sept. 2 response to the state's suit remains pending; VinFast has until Dec. 31, 2026 to hit 1,750 jobs/$500M invested (claims ~$229M invested to date) or lose the site outright. Still an unresolved negative/closed signal, not a qualifying announcement.</t>
+        </is>
+      </c>
+      <c r="H165" s="6" t="inlineStr">
+        <is>
+          <t>https://chathamjournal.com/2026/09/13/</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B166" s="6" t="inlineStr">
+        <is>
+          <t>Walmart corporate office — consolidation layoffs (NEW negative signal)</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte (Water Ridge Pkwy)</t>
+        </is>
+      </c>
+      <c r="D166" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E166" s="6" t="inlineStr">
+        <is>
+          <t>267 (layoffs, effective 2026-06-13; 422 total office jobs lost at this location since mid-2025 incl. an earlier 155-cut round)</t>
+        </is>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-13 (effective)</t>
+        </is>
+      </c>
+      <c r="G166" s="6" t="inlineStr">
+        <is>
+          <t>Negative signal, in-window: Walmart is consolidating this Charlotte corporate office function to Bentonville, AR and Sunnyvale, CA.</t>
+        </is>
+      </c>
+      <c r="H166" s="6" t="inlineStr">
+        <is>
+          <t>https://www.aol.com/retail-giant-closing-charlotte-corporate-205922962.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B167" s="6" t="inlineStr">
+        <is>
+          <t>Shemar Electric USA — new plant/HQ</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte (north Mecklenburg)</t>
+        </is>
+      </c>
+      <c r="D167" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E167" s="6" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F167" s="6" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="G167" s="6" t="inlineStr">
+        <is>
+          <t>Below the 500-job Ranked threshold and the 200-job Watch floor; Chinese power-grid-equipment maker's first US facility.</t>
+        </is>
+      </c>
+      <c r="H167" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/09/chinese-power-grid-maker-shemar-electric-picks-charlotte-plans-80-new-jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B168" s="6" t="inlineStr">
+        <is>
+          <t>Duff-Norton facility closure</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte (Mecklenburg)</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E168" s="6" t="inlineStr">
+        <is>
+          <t>73 (layoffs)</t>
+        </is>
+      </c>
+      <c r="F168" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-29 (closing)</t>
+        </is>
+      </c>
+      <c r="G168" s="6" t="inlineStr">
+        <is>
+          <t>Negative signal, below the 200-job floor regardless; noted for completeness given the in-window closing date.</t>
+        </is>
+      </c>
+      <c r="H168" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B169" s="6" t="inlineStr">
+        <is>
+          <t>Avelo Airlines — base closure</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington (New Hanover)</t>
+        </is>
+      </c>
+      <c r="D169" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E169" s="6" t="inlineStr">
+        <is>
+          <t>82 (layoffs)</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-07 (WARN); effective 2026-03-06</t>
+        </is>
+      </c>
+      <c r="G169" s="6" t="inlineStr">
+        <is>
+          <t>Negative signal, both below the 200-job floor and pre-window; permanent closure of Wilmington base operations.</t>
+        </is>
+      </c>
+      <c r="H169" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B170" s="6" t="inlineStr">
+        <is>
+          <t>Heron Therapeutics — HQ relocation to Cary (unverified lead)</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>Cary (Wake)</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E170" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
+        <is>
+          <t>2025-01-01 (effective, pre-window)</t>
+        </is>
+      </c>
+      <c r="G170" s="6" t="inlineStr">
+        <is>
+          <t>Relocation from San Diego effective Jan. 1, 2025; job count and wage not found in this pass — evidence suggests a smaller corporate-HQ move, not clearly 500+/high-wage. Flagged for a closer look next cycle rather than promoted on insufficient qualifying detail.</t>
+        </is>
+      </c>
+      <c r="H170" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B171" s="6" t="inlineStr">
+        <is>
+          <t>Sub-200-job / below-Watch-floor items (Charlotte-metro SC counties)</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>York / Lancaster / Chester</t>
+        </is>
+      </c>
+      <c r="D171" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E171" s="6" t="inlineStr">
+        <is>
+          <t>Each &lt;160</t>
+        </is>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
+        <is>
+          <t>Various 2026</t>
+        </is>
+      </c>
+      <c r="G171" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch-tier floor: Riverstone Logistics (York Co., 159, repeat exclusion), SCHNEEBERGER (York Co., 101), Pratt Industries (York Co., 116).</t>
+        </is>
+      </c>
+      <c r="H171" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B172" s="6" t="inlineStr">
+        <is>
+          <t>Sub-200-job / below-Watch-floor items (SC Midlands/Lowcountry)</t>
+        </is>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
+        <is>
+          <t>Richland / Lexington / Charleston / Berkeley / Dorchester</t>
+        </is>
+      </c>
+      <c r="D172" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E172" s="6" t="inlineStr">
+        <is>
+          <t>Each &lt;80</t>
+        </is>
+      </c>
+      <c r="F172" s="6" t="inlineStr">
+        <is>
+          <t>Various 2026</t>
+        </is>
+      </c>
+      <c r="G172" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch-tier floor: Stöbich (Dorchester, ~20), Carolina Heavy Steel LLC (Dorchester, jobs n/d), IEB Americas (Charleston, 30), Prysmian (Lexington, 30), Modus21 LLC (Charleston, 80), Cantey Tech Consulting (Charleston, jobs n/d).</t>
+        </is>
+      </c>
+      <c r="H172" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B173" s="6" t="inlineStr">
+        <is>
+          <t>Negative signals below the 500-job threshold (NC Triangle)</t>
+        </is>
+      </c>
+      <c r="C173" s="6" t="inlineStr">
+        <is>
+          <t>Wake / Durham</t>
+        </is>
+      </c>
+      <c r="D173" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E173" s="6" t="inlineStr">
+        <is>
+          <t>Each &lt;350 (layoffs)</t>
+        </is>
+      </c>
+      <c r="F173" s="6" t="inlineStr">
+        <is>
+          <t>Various 2026</t>
+        </is>
+      </c>
+      <c r="G173" s="6" t="inlineStr">
+        <is>
+          <t>Below the "major layoff" bar for a dedicated flag, noted for cumulative context: Wells Fargo (~112 Raleigh corporate-office layoffs, effective 2026-04-04), FedEx (~340 combined Raleigh/Durham shipping-center jobs cut, Feb. 2026 effective), Pendo (~30 Raleigh cuts as part of a ~90-person company-wide restructuring).</t>
+        </is>
+      </c>
+      <c r="H173" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -48999,7 +54551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -51682,6 +57234,465 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>Banking Dive — SMBC recruiting</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>trade_journal</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bankingdive.com/</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg Co. NC</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group active campus recruiting, October 2026 move-in date</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>WFAE — Citi / JPMorgan hiring ramp</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wfae.org/</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg Co. NC</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>Citigroup Ballantyne hiring-progress update (Apr. 2026); JPMorgan Chase SouthPark move-in timing</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>Business North Carolina — AbbVie / JetZero</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>Durham &amp; Guilford Co. NC</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie Durham City Council incentive item; JetZero state-budget funding release</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>ENR / HITT Contracting — JetZero NC3</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>trade_journal</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>https://www.enr.com/</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>Guilford Co. NC</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>JetZero NC Composite Center construction-progress confirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>SC Daily Gazette / Post and Courier — Scout Motors veto</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>Richland Co. SC</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>Gov. McMaster's Aug. 17 veto clearing the $150M Scout Motors cost-overrun payment</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>WIS-TV — Shives family lawsuit</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wistv.com/</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>Richland Co. SC</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>Shives family lawsuit against Scout Motors/Richland County status</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>Fox Carolina / WBTV — Spartanburg data-center litigation</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>https://www.foxcarolina.com/</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg Co. SC</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>Sept. 17 Circuit Court hearing on SELC injunction/major-vs-minor classification; Sept. 21 moratorium vote</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>GlobeNewswire — USA Rare Earth / Forge Nano</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>company_primary</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>Cherokee &amp; Wake Co.</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>USA Rare Earth Blacksburg groundbreaking; Forge Nano Voltaiq partnership</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>pv magazine USA — Suniva capital raise</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>trade_journal</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>https://pv-magazine-usa.com/</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>Laurens Co. SC</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>Suniva $835M capital raise for 4.5 GW solar-cell capacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>TipRanks / Investing.com — EnerSys / GNQ Insilico</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>trade_journal</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>https://www.tipranks.com/</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>Greenville Co. SC</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>EnerSys Jefferies conference remarks; IB Acquisition Corp./GNQ Insilico SPAC deadline extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>Utility Dive — GE Vernova backlog</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>trade_journal</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>https://www.utilitydive.com/</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>Greenville Co. SC</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>GE Vernova company-wide gas-turbine order backlog growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>Axios Charlotte / WBTV — TD Bank Ballantyne</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg Co. NC</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>TD Bank Ballantyne office expansion grand opening</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>Hoodline — Shemar Electric / Scout litigation</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg Co. NC</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>Shemar Electric USA new Charlotte plant; Scout Motors franchise-dealer litigation expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>WilmingtonBiz — Wilmington Trade Center / Protocase</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wilmingtonbiz.com/</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover Co. NC</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington Trade Center leasing update; Protocase/45Drives career fair and revenue target</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>Deere.com / ForConstructionPros — John Deere Kernersville</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>company_primary</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>https://www.deere.com/</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>Forsyth Co. NC</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>John Deere Kernersville excavator plant construction-start confirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>WRAL — Vulcan Elements transmission line</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>Johnston Co. NC</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>NC Utilities Commission fast-tracked 230kV transmission-line approval for Vulcan Elements</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>Live5News — Boeing apprenticeship program</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>https://www.live5news.com/</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>Charleston Co. SC</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>Boeing North Charleston apprenticeship program doubling, DOL MOU signing</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -51693,7 +57704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -53529,6 +59540,206 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>Raised from 93; fundamentals unchanged but active campus recruiting and a firmer October move-in date (vs. general "fall 2026") modestly improve the repeat-momentum/certainty read after nine consecutive quiet cycles on the underlying lease.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma (Rock Hill)</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new dated milestone found this cycle despite a dedicated recheck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie (Durham)</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>Raised from 85; Durham City Council added a companion incentive layer on top of the county's July approval (combined ~$24.8M local incentive), improving capital-investment certainty and repeat momentum. No new job/wage facts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV plant (Blythewood)</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>Held flat; Gov. McMaster's veto procedurally cleared the $150M cost-overrun payment (modest capital-certainty improvement), offset by no new headcount figure since April, a still-pending Shives lawsuit, and Scout's own more conservative production timeline (customer deliveries now 2028, not 2027).</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>Genentech (Holly Springs)</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>JetZero (Greensboro)</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>Raised from 81; the previously-pending JDIG hiring-schedule amendment is now formally approved (a finalization, not a new setback), state funding ($133.9M) was released via the July 7 budget signing, NC3 construction is visibly underway, and a $3B EXIM Bank financing LOI was signed — net positive on capital-investment certainty despite the confirmed hiring-ramp delay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no hiring or occupancy update found this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — Global HQ (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no fresher permit/construction news found. Franchise-dealer litigation footprint has grown to a 6th state, noted as a risk factor but not scored, since the company states it is proceeding with the HQ regardless.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>Citigroup (Charlotte / Ballantyne)</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; this entry's only previously-tracked milestone fell out of window this cycle, but a dedicated recheck found a genuinely dated, in-window hiring-progress update (2026-04-23) confirming the buildout toward 785 total employees is proceeding — sufficient to keep it Ranked at the same score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>Novartis (Durham/Morrisville)</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/Carolinas_Job_Growth_Running_Database.xlsx
+++ b/reports/Carolinas_Job_Growth_Running_Database.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Week of 2026-09-21  ·  Window 2026-03-21 to 2026-09-21  ·  NC + SC</t>
+          <t>Week of 2026-09-28  ·  Window 2026-03-28 to 2026-09-28  ·  NC + SC</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21  (Week 10)</t>
+          <t>2026-09-28  (Week 11)</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-03-21 to 2026-09-21  (trailing 6 months)</t>
+          <t>2026-03-28 to 2026-09-28  (trailing 6 months)</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>104</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Charlotte / Uptown (Mecklenburg, NC) — SMBC Group, score 94 (raised from 93 on a firmer October move-in date and active campus recruiting)</t>
+          <t>Charlotte / Uptown (Mecklenburg, NC) — SMBC Group, score 94 (unchanged) — tenth consecutive cycle without a new lease milestone; October 2026 move-in target reconfirmed but not yet realized.</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>AbbVie (Durham/RTP) rose 85 -&gt; 87 after Durham City Council added a companion incentive layer (~$24.8M combined city+county) on top of the county's July approval; JetZero (Greensboro) rose 81 -&gt; 82 as its previously-pending JDIG hiring-delay amendment was formally finalized while $133.9M in state funding was released and NC3 construction visibly proceeds. Aspida Financial Services (Durham, score 74) was REMOVED from Ranked — its only two confirmed milestones (Nov./Dec. 2025) are now conclusively pre-window with no fresher 2026 update found for a third consecutive cycle.</t>
+          <t>No Ranked-tier score changed this cycle — the first cycle with zero Ranked-tier score movement since early in the report's run. Scout Motors (Blythewood) and Scout Motors HQ (Charlotte) both picked up new risk-factor detail (a fuller account of the Shives-family blasting-damage lawsuit plus an unconfirmed report of a longer Terra-pickup delay; a franchise-dealer lawsuit footprint now spanning ~7 states) without changing their scores. The most consequential news of the cycle was procedural/regulatory rather than score-moving: the WakeMed/Atrium Health merger was approved 5-2 by Wake County commissioners (moving to FTC/DOJ review) and the Spartanburg data-center moratorium passed 5-1 while explicitly grandfathering the NorthMark/Valara project, alongside a second developer-favorable SC PSC ruling.</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>No new 500+ job / $100k+ wage qualifying announcement was found in any of the five regions this cycle — the third consecutive quiet cycle for brand-new Ranked-tier finds — but the trailing-6-month window's weekly advance forced a genuine reckoning with several long-tracked entries whose only dated milestones have now aged out of window: Aspida Financial Services was removed from Ranked, and Ralliant Corp., Jewelers Mutual Group, Wolfspeed, and Environmental Air Systems were removed from Markets to Watch (Wolfspeed's WARN-notice dating ambiguity, flagged for two cycles, was conclusively resolved this cycle as a mid-2025 event). Citigroup (Charlotte/Ballantyne) narrowly avoided the same fate: a dedicated recheck found a genuinely dated, in-window hiring-progress update (2026-04-23) that keeps it Ranked. The single biggest open story is the Spartanburg NorthMark/Valara data-center fight: a Sept. 17 Circuit Court hearing on SELC's injunction ended with no ruling (judge took it under advisement), and the county council's moratorium 3rd/final-reading vote was scheduled for the evening of this report's compilation (Sept. 21) with the outcome not yet known. The Wake County Board of Commissioners' vote on the WakeMed/Atrium Health merger was also scheduled for today with the outcome unknown. A new Watch entry (TD Bank, Ballantyne) was promoted from an unverified lead after a confirmed in-window office-occupancy milestone, and Google's Berkeley/Dorchester, SC data-center entry was downgraded to stale background after 8 consecutive cycles with no dated 2026 update.</t>
+          <t>A fourth consecutive quiet cycle for brand-new Ranked-tier finds and, for the first time in the report's run, zero Ranked-tier score changes — but an unusually consequential cycle for Watch-tier resolution. Two of the report's longest-running open threads resolved this cycle, both favorably for the tracked projects: the Wake County Board of Commissioners approved the WakeMed/Atrium Health merger 5-2 (now moving to FTC/DOJ review), and Spartanburg County Council passed its data-center moratorium 5-1 while explicitly grandfathering the NorthMark/Valara 'Project Moc-1' data center — compounded by a second developer-favorable ruling (the SC Public Service Commission's Aug. 27 finding that Valara's on-site gas plant is not subject to utility-siting review). Elsewhere, GNQ Insilico's SPAC deal did NOT close by its Sept. 28 deadline as previously flagged — IB Acquisition Corp. is seeking a second extension to March 2027, confirming the Greenville deal remains unresolved. Boom Supersonic (Greensboro) remains the region's most urgent unresolved risk: no headcount evidence was found despite a second dedicated search, with its Dec. 31, 2026 500-employee lease-termination deadline now roughly 3 months out. Amazon's Pender/New Hanover fulfillment center still has not been confirmed open despite a completed building shell. Ferrara Candy (Orangeburg, SC) broke ground in-window (May 2026) and AWS/Amazon's Hamlet, NC data center cleared a key air-quality-permit hurdle (Aug. 29, 2026) — both incremental de-risking events for carryover Watch items outside the five core regions.</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>All five regions (Charlotte metro, NC Triangle, NC Triad/WNC/Coastal, Upstate SC, SC Midlands/Lowcountry) received a full research pass this cycle via parallel dedicated research agents. WebFetch (direct page retrieval) again returned blocked/egress-restricted for the large majority of news/gov/company domains attempted across all agents; nearly every finding below relies on WebSearch-result content/snippets, which do surface real, retrievable source URLs, cross-checked across multiple independent queries per claim. No numbers were invented; 'Not disclosed' marks missing figures and 'Estimated/Inferred' marks derived ones with basis stated.</t>
+          <t>All five regions (Charlotte metro, NC Triangle, NC Triad/WNC/Coastal, Upstate SC, SC Midlands/Lowcountry) received a full research pass this cycle via parallel dedicated research agents. WebFetch (direct page retrieval) again returned blocked/egress-restricted for the large majority of news/gov/company/SEC domains attempted across all agents; nearly every finding below relies on WebSearch-result content/snippets, which do surface real, retrievable source URLs, cross-checked across multiple independent queries per claim. No numbers were invented; 'Not disclosed' marks missing figures and 'Estimated/Inferred' marks derived ones with basis stated.</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Trailing 6 months now runs 2026-03-21 to 2026-09-21 — the window advanced one week. This shift pushed several long-tracked entries' sole dated milestones out of window: Aspida Financial Services (Ranked, removed), and Ralliant Corp., Jewelers Mutual Group, and Wolfspeed (Watch, all removed). Citigroup (Ranked) was at the same risk but was kept after a fresh in-window milestone was located (2026-04-23). Scout Motors HQ's 2nd-building filing (2026-03-28) remains just inside window; watch it closely next cycle.</t>
+          <t>Trailing 6 months now runs 2026-03-28 to 2026-09-28 — the window advanced one week. Citigroup's April 23, 2026 anchor milestone and Scout Motors HQ's March 28, 2026 filing date both remain comfortably inside the new window; no Ranked entry's sole milestone aged out this cycle.</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Wolfspeed's WARN-notice dating ambiguity — flagged as unresolved for two consecutive prior cycles — was conclusively resolved this cycle via indexed WARN data: notification 6/24/2025, effective 11/14/2025, entirely a 2025 event over a year outside the current window; the entry was removed from Watch. Redwood Materials' 7-cycle 'standing gap' was also resolved: multiple independent outlets confirm its Camp Hall, SC critical-materials-recovery operations actually began in November 2025 (pre-window), explaining the lack of further in-window movement. EnerSys's Greenville, SC lithium-cell project (restructured 2026-07-23) still has no disclosed jobs figure for the revised, smaller-scope project as of this cycle — the pre-restructuring ~500-job 2024 figure must not be carried forward. TD Bank's Ballantyne office expansion was promoted from an unverified Excluded lead to active Watch after a confirmed dated in-window occupancy milestone (though it still discloses no jobs/wage figure).</t>
+          <t>Two long-flagged data gaps were resolved this cycle: the Wake County EDGE6-vs-EDGE7 pipeline-figure discrepancy (EDGE7's current pipeline remains 52 projects/$11B+/~11,000 jobs; the ~$5.6B/~10,800-job figure belongs to the completed prior cycle) and Suniva's capex discrepancy (facility-specific investment reconciled to ~$600M via SEC/pv-magazine coverage, distinct from the separate $835M corporate capital raise). EnerSys's restructured Greenville project scope was also confirmed via a primary SEC 8-K (rescoped to up to 1 GWh, ~$650M gross/~$500M net) though its jobs figure remains undisclosed. AIRSYS's capex now shows a new discrepancy ($40M originally tracked vs. $60M in several 2026 secondary sources) flagged for reconciliation next cycle.</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>9 of 10 remaining prior-ranked deals repeat or update this cycle; SMBC (93-&gt;94), AbbVie (85-&gt;87), and JetZero (81-&gt;82) each rose modestly on new capital-certainty/momentum facts. Aspida Financial Services (score 74) was REMOVED from Ranked (milestones now pre-window, no fresh 2026 update found). 0 new Ranked-tier finds this cycle. Watch tier: 1 new item added (TD Bank, Ballantyne — promoted from an unverified lead), 4 items removed (Ralliant Corp., Jewelers Mutual Group, Wolfspeed, Environmental Air Systems — all confirmed pre-window with no fresh update), and 1 item downgraded to stale background (Google Berkeley/Dorchester, SC — 8 consecutive quiet cycles). New Excluded/Noise entries include the Aspida/Ralliant/Jewelers Mutual/Wolfspeed/Environmental Air Systems removals themselves, an updated VinFast entry (Sept. 15/16 closed-session meeting held, outcome undisclosed), a new Walmart corporate-office layoff signal (267 jobs, Charlotte), and several sub-threshold items.</t>
+          <t>All 10 Ranked entries repeated this cycle with no score changes — a fourth consecutive quiet cycle for brand-new Ranked-tier finds and the first cycle with zero Ranked-tier score movement. Aspida Financial Services was rechecked and remains excluded/removed (still no dated confirmation of its expected Q4 2026 move-in). Watch tier: 1 new item added (Pacific Life Insurance, Charlotte/South End — high wage but pre-window base announcement), 0 items removed, all 46 carried-forward items rechecked with updates ranging from major (WakeMed/Atrium merger approved; Spartanburg moratorium resolved in the developer's favor) to minor (source/detail corrections). New Excluded/Noise entries include two new negative signals (Wells Fargo Winston-Salem office closure, 194 jobs; FedEx Greensboro facility closure, 164 jobs) and roughly two dozen sub-threshold or recycled items.</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S95"/>
+  <dimension ref="A1:S105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9372,6 +9372,916 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Uptown</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group — 2nd US HQ / bank operations</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>Office / HQ banking</t>
+        </is>
+      </c>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>$165,316 avg (stated; vs county $90,706)</t>
+        </is>
+      </c>
+      <c r="K96" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L96" s="6" t="inlineStr">
+        <is>
+          <t>$50.5M</t>
+        </is>
+      </c>
+      <c r="M96" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $70.0M / 12 yr; $23.3M IDF-Utility Account</t>
+        </is>
+      </c>
+      <c r="N96" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle; move-in still pending</t>
+        </is>
+      </c>
+      <c r="O96" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P96" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bankingdive.com/news/smbc-revs-up-recruiting-charlotte-banking-talent-tech-cyber-data-jobs/830268/</t>
+        </is>
+      </c>
+      <c r="Q96" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R96" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="S96" s="6" t="inlineStr">
+        <is>
+          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C97" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill / York Co.</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>Office/HQ + biopharma mfg</t>
+        </is>
+      </c>
+      <c r="J97" s="6" t="inlineStr">
+        <is>
+          <t>$141,502 avg HQ / $102,752 avg mfg (both stated)</t>
+        </is>
+      </c>
+      <c r="K97" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L97" s="6" t="inlineStr">
+        <is>
+          <t>$1.5B</t>
+        </is>
+      </c>
+      <c r="M97" s="6" t="inlineStr">
+        <is>
+          <t>Fee-in-lieu-of-tax; $65M SC Coordinating Council Closing Fund grant to York Co.</t>
+        </is>
+      </c>
+      <c r="N97" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone (unchanged)</t>
+        </is>
+      </c>
+      <c r="O97" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="P97" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/york-county/news/octapharma-how-company-chose-rock-hill/article_b1518265-129d-4134-9ff9-f2d686950bd6.html</t>
+        </is>
+      </c>
+      <c r="Q97" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R97" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S97" s="6" t="inlineStr">
+        <is>
+          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C98" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>Durham / RTP</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie — biopharma manufacturing campus</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="n">
+        <v>734</v>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / R&amp;D / lab</t>
+        </is>
+      </c>
+      <c r="J98" s="6" t="inlineStr">
+        <is>
+          <t>$118,041 avg (stated; vs county $102,817)</t>
+        </is>
+      </c>
+      <c r="K98" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L98" s="6" t="inlineStr">
+        <is>
+          <t>$1.4B</t>
+        </is>
+      </c>
+      <c r="M98" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $19.3M / 12 yr; $6.4M IDF-Utility; Durham Co. performance-based award not-to-exceed $15,450,000 ("Project Glass"); Durham City Council companion incentive item (Sept. 17, 2026) brings combined city+county local incentive to ~$24.8M</t>
+        </is>
+      </c>
+      <c r="N98" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="O98" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="P98" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/abbvie-pledges-1-3-billion-investment-734-jobs-in-durham/</t>
+        </is>
+      </c>
+      <c r="Q98" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R98" s="6" t="inlineStr">
+        <is>
+          <t>Suburban-urban</t>
+        </is>
+      </c>
+      <c r="S98" s="6" t="inlineStr">
+        <is>
+          <t>High-end MF + move-up for-sale around Durham/RTP; spillover Wake/Orange. Construction-phase rental near-term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C99" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>Blythewood / N. Columbia</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV assembly plant + new Supplier Park</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>Auto mfg + salaried eng.</t>
+        </is>
+      </c>
+      <c r="J99" s="6" t="inlineStr">
+        <is>
+          <t>$30-$37.50/hr line (stated); salaried higher</t>
+        </is>
+      </c>
+      <c r="K99" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mix supports above-median HH income</t>
+        </is>
+      </c>
+      <c r="L99" s="6" t="inlineStr">
+        <is>
+          <t>$2.3B+ (site $2.0B + $25M training center + $300M Supplier Park)</t>
+        </is>
+      </c>
+      <c r="M99" s="6" t="inlineStr">
+        <is>
+          <t>State/local package (2023); $25M readySC; $150M cost-overrun payment cleared by Aug. 17 veto; Legislative Audit Council/Inspector General joint review of the overrun and SC Commerce due diligence remains on track for ~mid-Dec. 2026</t>
+        </is>
+      </c>
+      <c r="N99" s="6" t="inlineStr">
+        <is>
+          <t>Elderly-couple blasting-damage lawsuit gains detail; unconfirmed report of a longer Terra pickup delay</t>
+        </is>
+      </c>
+      <c r="O99" s="6" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="P99" s="6" t="inlineStr">
+        <is>
+          <t>https://blog.scoutmotors.com/september-2026-scout-motors-production-center-update/</t>
+        </is>
+      </c>
+      <c r="Q99" s="6" t="inlineStr">
+        <is>
+          <t>Medium (facts); Low (headcount/timeline)</t>
+        </is>
+      </c>
+      <c r="R99" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S99" s="6" t="inlineStr">
+        <is>
+          <t>Bifurcated: salaried/professional -&gt; higher-income for-sale &amp; Class-A; hourly base + supplier-park jobs -&gt; workforce/missing-middle rental in N. Richland/Fairfield.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C100" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs / SW Wake</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>Genentech — biomanufacturing expansion (unchanged)</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="J100" s="6" t="inlineStr">
+        <is>
+          <t>~$119,833 avg (stated, 2025 tranche)</t>
+        </is>
+      </c>
+      <c r="K100" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L100" s="6" t="inlineStr">
+        <is>
+          <t>~$2.0B</t>
+        </is>
+      </c>
+      <c r="M100" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
+        </is>
+      </c>
+      <c r="N100" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="O100" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="P100" s="6" t="inlineStr">
+        <is>
+          <t>https://www.biospace.com/press-releases/genentech-marks-topping-out-milestone-for-new-holly-springs-north-carolina-manufacturing-facility</t>
+        </is>
+      </c>
+      <c r="Q100" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R100" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S100" s="6" t="inlineStr">
+        <is>
+          <t>Strong higher-income for-sale + Class-A rental demand in fast-growing SW Wake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C101" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>JetZero — aerospace plant (unchanged)</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace mfg + eng.</t>
+        </is>
+      </c>
+      <c r="J101" s="6" t="inlineStr">
+        <is>
+          <t>$89,340 avg (stated, 2025)</t>
+        </is>
+      </c>
+      <c r="K101" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated (2025)</t>
+        </is>
+      </c>
+      <c r="L101" s="6" t="inlineStr">
+        <is>
+          <t>$4.7B</t>
+        </is>
+      </c>
+      <c r="M101" s="6" t="inlineStr">
+        <is>
+          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr; $133.9M NC FY26-27 budget funding</t>
+        </is>
+      </c>
+      <c r="N101" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="O101" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="P101" s="6" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/jetzero-and-exim-sign-letter-of-interest-to-explore-up-to-3b-in-financing-for-new-aerospace-manufacturing-campus-in-greensboro-north-carolina-302829244.html</t>
+        </is>
+      </c>
+      <c r="Q101" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Medium (hiring-ramp timeline)</t>
+        </is>
+      </c>
+      <c r="R101" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S101" s="6" t="inlineStr">
+        <is>
+          <t>Same long-run scale; mass hiring is confirmed pushed to 2028, not yet underway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C102" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group — East Coast ops hub (unchanged)</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>Office — finance/tech</t>
+        </is>
+      </c>
+      <c r="J102" s="6" t="inlineStr">
+        <is>
+          <t>$194,141 avg (stated; NC Commerce JDIG figure)</t>
+        </is>
+      </c>
+      <c r="K102" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L102" s="6" t="inlineStr">
+        <is>
+          <t>$60M</t>
+        </is>
+      </c>
+      <c r="M102" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $17.2M / 12 yr; $5.7M IDF-Utility; $19.4M state grant/12yr + $2.2M training funds + $1M local</t>
+        </is>
+      </c>
+      <c r="N102" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="O102" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="P102" s="6" t="inlineStr">
+        <is>
+          <t>https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
+        </is>
+      </c>
+      <c r="Q102" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R102" s="6" t="inlineStr">
+        <is>
+          <t>Urban-suburban</t>
+        </is>
+      </c>
+      <c r="S102" s="6" t="inlineStr">
+        <is>
+          <t>High-skill eng/data workforce -&gt; walkable South End/Uptown &amp; inner-suburban Class-A and for-sale TH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C103" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Plaza Midwood</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — Global HQ (litigation footprint widens further)</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>Corporate HQ / professional</t>
+        </is>
+      </c>
+      <c r="J103" s="6" t="inlineStr">
+        <is>
+          <t>$153,978 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K103" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L103" s="6" t="inlineStr">
+        <is>
+          <t>$206.9M</t>
+        </is>
+      </c>
+      <c r="M103" s="6" t="inlineStr">
+        <is>
+          <t>Original 2025-11-12 HQ incentive/relocation commitment</t>
+        </is>
+      </c>
+      <c r="N103" s="6" t="inlineStr">
+        <is>
+          <t>No permit/construction progress found; franchise-dealer litigation now spans ~7 states</t>
+        </is>
+      </c>
+      <c r="O103" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="P103" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/scout-motors-hq-move-turbocharges-second-office-building-in-plaza-midwood/</t>
+        </is>
+      </c>
+      <c r="Q103" s="6" t="inlineStr">
+        <is>
+          <t>Med (facts High; milestone stage early)</t>
+        </is>
+      </c>
+      <c r="R103" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="S103" s="6" t="inlineStr">
+        <is>
+          <t>Supports Plaza Midwood/NoDa/Elizabeth close-in rental and townhome demand from a young, high-wage corporate workforce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C104" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Ballantyne</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>Citigroup — Charlotte office (hiring ramp proceeding)</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="n">
+        <v>510</v>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>Office / financial services</t>
+        </is>
+      </c>
+      <c r="J104" s="6" t="inlineStr">
+        <is>
+          <t>$131,832 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K104" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L104" s="6" t="inlineStr">
+        <is>
+          <t>$16.1M</t>
+        </is>
+      </c>
+      <c r="M104" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $8.9M / 10 yr</t>
+        </is>
+      </c>
+      <c r="N104" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="O104" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="P104" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wfae.org/business/2026-04-23/charlottes-banking-jobs-hot-streak-continues</t>
+        </is>
+      </c>
+      <c r="Q104" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R104" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S104" s="6" t="inlineStr">
+        <is>
+          <t>$131,832 stated wage clears the $100k bar; supports Class-A rental and for-sale townhome demand in south Mecklenburg's Ballantyne/Blakeney/Rea Farms corridor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C105" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>Durham / Morrisville</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>Durham &amp; Wake</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>Novartis — API mfg building (unchanged)</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="J105" s="6" t="inlineStr">
+        <is>
+          <t>$111,161 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K105" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L105" s="6" t="inlineStr">
+        <is>
+          <t>~$991M (incl. $220M API building)</t>
+        </is>
+      </c>
+      <c r="M105" s="6" t="inlineStr">
+        <is>
+          <t>Part of original $771M package incentives</t>
+        </is>
+      </c>
+      <c r="N105" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="O105" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="P105" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
+        </is>
+      </c>
+      <c r="Q105" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R105" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S105" s="6" t="inlineStr">
+        <is>
+          <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9383,7 +10293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X95"/>
+  <dimension ref="A1:X105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20438,6 +21348,1166 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Uptown</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group — 2nd US HQ / bank operations</t>
+        </is>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>Banking / financial services</t>
+        </is>
+      </c>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle; move-in still pending</t>
+        </is>
+      </c>
+      <c r="K96" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L96" s="6" t="inlineStr">
+        <is>
+          <t>Projected (6 yr)</t>
+        </is>
+      </c>
+      <c r="M96" s="6" t="inlineStr">
+        <is>
+          <t>$165,316 avg (stated; vs county $90,706)</t>
+        </is>
+      </c>
+      <c r="N96" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O96" s="6" t="inlineStr">
+        <is>
+          <t>$50.5M</t>
+        </is>
+      </c>
+      <c r="P96" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $70.0M / 12 yr; $23.3M IDF-Utility Account</t>
+        </is>
+      </c>
+      <c r="Q96" s="6" t="inlineStr">
+        <is>
+          <t>October 2026 move-in target into former One Wells Fargo Center (301 S. College St.) reconfirmed; bank has not yet physically relocated as of 2026-09-28; active campus recruiting for summer-2027 analyst/intern classes continues (~150 summer interns hosted, some converted to FT offers)</t>
+        </is>
+      </c>
+      <c r="R96" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="S96" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bankingdive.com/news/smbc-revs-up-recruiting-charlotte-banking-talent-tech-cyber-data-jobs/830268/</t>
+        </is>
+      </c>
+      <c r="T96" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U96" s="6" t="inlineStr">
+        <is>
+          <t>Office / HQ banking</t>
+        </is>
+      </c>
+      <c r="V96" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="W96" s="6" t="inlineStr">
+        <is>
+          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth.</t>
+        </is>
+      </c>
+      <c r="X96" s="6" t="inlineStr">
+        <is>
+          <t>Tenth consecutive cycle without a new lease/occupancy milestone; October move-in target reconfirmed but not yet realized. Score held flat at 94.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D97" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill / York Co.</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus</t>
+        </is>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>Biopharmaceutical (plasma fractionation)</t>
+        </is>
+      </c>
+      <c r="J97" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone (unchanged)</t>
+        </is>
+      </c>
+      <c r="K97" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L97" s="6" t="inlineStr">
+        <is>
+          <t>Projected (1,200 new + 300 relocated)</t>
+        </is>
+      </c>
+      <c r="M97" s="6" t="inlineStr">
+        <is>
+          <t>$141,502 avg HQ / $102,752 avg mfg (both stated)</t>
+        </is>
+      </c>
+      <c r="N97" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O97" s="6" t="inlineStr">
+        <is>
+          <t>$1.5B</t>
+        </is>
+      </c>
+      <c r="P97" s="6" t="inlineStr">
+        <is>
+          <t>Fee-in-lieu-of-tax; $65M SC Coordinating Council Closing Fund grant to York Co.</t>
+        </is>
+      </c>
+      <c r="Q97" s="6" t="inlineStr">
+        <is>
+          <t>50 acres purchased at Palmetto Research Park; construction slated to begin late 2026; full operations still projected for the 2030s</t>
+        </is>
+      </c>
+      <c r="R97" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="S97" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/york-county/news/octapharma-how-company-chose-rock-hill/article_b1518265-129d-4134-9ff9-f2d686950bd6.html</t>
+        </is>
+      </c>
+      <c r="T97" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U97" s="6" t="inlineStr">
+        <is>
+          <t>Office/HQ + biopharma mfg</t>
+        </is>
+      </c>
+      <c r="V97" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W97" s="6" t="inlineStr">
+        <is>
+          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH.</t>
+        </is>
+      </c>
+      <c r="X97" s="6" t="inlineStr">
+        <is>
+          <t>Fourth consecutive cycle with no fresher dated milestone found despite a dedicated recheck; full approval/finalization timeline reconfirmed. Score held flat at 91.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D98" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>Durham / RTP</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie — biopharma manufacturing campus</t>
+        </is>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>Biopharma / life sciences mfg</t>
+        </is>
+      </c>
+      <c r="J98" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="K98" s="6" t="n">
+        <v>734</v>
+      </c>
+      <c r="L98" s="6" t="inlineStr">
+        <is>
+          <t>Projected (+2,000 construction)</t>
+        </is>
+      </c>
+      <c r="M98" s="6" t="inlineStr">
+        <is>
+          <t>$118,041 avg (stated; vs county $102,817)</t>
+        </is>
+      </c>
+      <c r="N98" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O98" s="6" t="inlineStr">
+        <is>
+          <t>$1.4B</t>
+        </is>
+      </c>
+      <c r="P98" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $19.3M / 12 yr; $6.4M IDF-Utility; Durham Co. performance-based award not-to-exceed $15,450,000 ("Project Glass"); Durham City Council companion incentive item (Sept. 17, 2026) brings combined city+county local incentive to ~$24.8M</t>
+        </is>
+      </c>
+      <c r="Q98" s="6" t="inlineStr">
+        <is>
+          <t>Construction 2026; complete ~end-2028; hiring through ~2031</t>
+        </is>
+      </c>
+      <c r="R98" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="S98" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/abbvie-pledges-1-3-billion-investment-734-jobs-in-durham/</t>
+        </is>
+      </c>
+      <c r="T98" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U98" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / R&amp;D / lab</t>
+        </is>
+      </c>
+      <c r="V98" s="6" t="inlineStr">
+        <is>
+          <t>Suburban-urban</t>
+        </is>
+      </c>
+      <c r="W98" s="6" t="inlineStr">
+        <is>
+          <t>High-end MF + move-up for-sale around Durham/RTP; spillover Wake/Orange. Construction-phase rental near-term.</t>
+        </is>
+      </c>
+      <c r="X98" s="6" t="inlineStr">
+        <is>
+          <t>No new physical-groundbreaking or hiring milestone found this cycle beyond the already-tracked Sept. 17 city incentive item; company still targets construction "in 2026." Score held flat at 87.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D99" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>Blythewood / N. Columbia</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV assembly plant + new Supplier Park</t>
+        </is>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>Automotive / EV manufacturing</t>
+        </is>
+      </c>
+      <c r="J99" s="6" t="inlineStr">
+        <is>
+          <t>Elderly-couple blasting-damage lawsuit gains detail; unconfirmed report of a longer Terra pickup delay</t>
+        </is>
+      </c>
+      <c r="K99" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L99" s="6" t="inlineStr">
+        <is>
+          <t>Projected (4,000-5,000 assembly + ~1,000 supplier-park; 600+ hired as of Apr 2026, no fresher figure disclosed)</t>
+        </is>
+      </c>
+      <c r="M99" s="6" t="inlineStr">
+        <is>
+          <t>$30-$37.50/hr line (stated); salaried higher</t>
+        </is>
+      </c>
+      <c r="N99" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mix supports above-median HH income</t>
+        </is>
+      </c>
+      <c r="O99" s="6" t="inlineStr">
+        <is>
+          <t>$2.3B+ (site $2.0B + $25M training center + $300M Supplier Park)</t>
+        </is>
+      </c>
+      <c r="P99" s="6" t="inlineStr">
+        <is>
+          <t>State/local package (2023); $25M readySC; $150M cost-overrun payment cleared by Aug. 17 veto; Legislative Audit Council/Inspector General joint review of the overrun and SC Commerce due diligence remains on track for ~mid-Dec. 2026</t>
+        </is>
+      </c>
+      <c r="Q99" s="6" t="inlineStr">
+        <is>
+          <t>Body Shop equipment training, robotics testing, and active test builds confirmed ongoing per a September 2026 company update; initial production still targeted 2027, customer deliveries 2028 per Scout's own guidance</t>
+        </is>
+      </c>
+      <c r="R99" s="6" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="S99" s="6" t="inlineStr">
+        <is>
+          <t>https://blog.scoutmotors.com/september-2026-scout-motors-production-center-update/</t>
+        </is>
+      </c>
+      <c r="T99" s="6" t="inlineStr">
+        <is>
+          <t>Medium (facts); Low (headcount/timeline)</t>
+        </is>
+      </c>
+      <c r="U99" s="6" t="inlineStr">
+        <is>
+          <t>Auto mfg + salaried eng.</t>
+        </is>
+      </c>
+      <c r="V99" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W99" s="6" t="inlineStr">
+        <is>
+          <t>Bifurcated: salaried/professional -&gt; higher-income for-sale &amp; Class-A; hourly base + supplier-park jobs -&gt; workforce/missing-middle rental in N. Richland/Fairfield.</t>
+        </is>
+      </c>
+      <c r="X99" s="6" t="inlineStr">
+        <is>
+          <t>The Shives family lawsuit (filed Aug. 7, 2026; elderly Richland Co. couple alleging blasting damage, a 2025 guest eye injury, and septic-system disruption) remains pending with new reporting detail (WIS-TV, Aug. 12 &amp; Aug. 25) but no ruling. AutoForecast Solutions (April 2026) reported the Terra pickup slipping to March 2030 and Traveler SUV to September 2028 — a longer delay than previously carried — but Scout Motors publicly disputes any change, reiterating 2027/2028 guidance; flagged as unconfirmed for next cycle. No new headcount figure. Score held flat at 85.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D100" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs / SW Wake</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>Genentech — biomanufacturing expansion (unchanged)</t>
+        </is>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="J100" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="K100" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="L100" s="6" t="inlineStr">
+        <is>
+          <t>Projected (site total)</t>
+        </is>
+      </c>
+      <c r="M100" s="6" t="inlineStr">
+        <is>
+          <t>~$119,833 avg (stated, 2025 tranche)</t>
+        </is>
+      </c>
+      <c r="N100" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O100" s="6" t="inlineStr">
+        <is>
+          <t>~$2.0B</t>
+        </is>
+      </c>
+      <c r="P100" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
+        </is>
+      </c>
+      <c r="Q100" s="6" t="inlineStr">
+        <is>
+          <t>Topping-out ceremony held Aug. 18, 2026; operational target 2029 unchanged</t>
+        </is>
+      </c>
+      <c r="R100" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="S100" s="6" t="inlineStr">
+        <is>
+          <t>https://www.biospace.com/press-releases/genentech-marks-topping-out-milestone-for-new-holly-springs-north-carolina-manufacturing-facility</t>
+        </is>
+      </c>
+      <c r="T100" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U100" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="V100" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W100" s="6" t="inlineStr">
+        <is>
+          <t>Strong higher-income for-sale + Class-A rental demand in fast-growing SW Wake.</t>
+        </is>
+      </c>
+      <c r="X100" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone found this cycle beyond the already-tracked Aug. 18 topping-out ceremony despite a dedicated recheck. Score held flat at 82.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D101" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>JetZero — aerospace plant (unchanged)</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace / advanced manufacturing</t>
+        </is>
+      </c>
+      <c r="J101" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="K101" s="6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="L101" s="6" t="inlineStr">
+        <is>
+          <t>Projected</t>
+        </is>
+      </c>
+      <c r="M101" s="6" t="inlineStr">
+        <is>
+          <t>$89,340 avg (stated, 2025)</t>
+        </is>
+      </c>
+      <c r="N101" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated (2025)</t>
+        </is>
+      </c>
+      <c r="O101" s="6" t="inlineStr">
+        <is>
+          <t>$4.7B</t>
+        </is>
+      </c>
+      <c r="P101" s="6" t="inlineStr">
+        <is>
+          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr; $133.9M NC FY26-27 budget funding</t>
+        </is>
+      </c>
+      <c r="Q101" s="6" t="inlineStr">
+        <is>
+          <t>NC3 (150,000 sf composite-mfg building) construction confirmed ongoing under HITT Contracting; JDIG hiring-schedule amendment (JetZero will create ~0 JDIG-countable jobs in 2027, ramping 2028-2029) and the $3B EXIM Bank financing LOI (signed July 21, 2026) remain the latest confirmed facts; active job postings (Aug/Sep 2026) are early build-out/engineering roles, not yet the bulk hiring ramp</t>
+        </is>
+      </c>
+      <c r="R101" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="S101" s="6" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/jetzero-and-exim-sign-letter-of-interest-to-explore-up-to-3b-in-financing-for-new-aerospace-manufacturing-campus-in-greensboro-north-carolina-302829244.html</t>
+        </is>
+      </c>
+      <c r="T101" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Medium (hiring-ramp timeline)</t>
+        </is>
+      </c>
+      <c r="U101" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace mfg + eng.</t>
+        </is>
+      </c>
+      <c r="V101" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W101" s="6" t="inlineStr">
+        <is>
+          <t>Same long-run scale; mass hiring is confirmed pushed to 2028, not yet underway.</t>
+        </is>
+      </c>
+      <c r="X101" s="6" t="inlineStr">
+        <is>
+          <t>No new dated construction/hiring progress confirmed this cycle beyond the already-tracked NC3 groundbreaking, JDIG amendment, and EXIM LOI; current job postings confirm hiring has not yet reached bulk-ramp scale. Score held flat at 82.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D102" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group — East Coast ops hub (unchanged)</t>
+        </is>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>Investment mgmt / finance + tech</t>
+        </is>
+      </c>
+      <c r="J102" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="K102" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="L102" s="6" t="inlineStr">
+        <is>
+          <t>Projected</t>
+        </is>
+      </c>
+      <c r="M102" s="6" t="inlineStr">
+        <is>
+          <t>$194,141 avg (stated; NC Commerce JDIG figure)</t>
+        </is>
+      </c>
+      <c r="N102" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O102" s="6" t="inlineStr">
+        <is>
+          <t>$60M</t>
+        </is>
+      </c>
+      <c r="P102" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $17.2M / 12 yr; $5.7M IDF-Utility; $19.4M state grant/12yr + $2.2M training funds + $1M local</t>
+        </is>
+      </c>
+      <c r="Q102" s="6" t="inlineStr">
+        <is>
+          <t>16-yr lease (196,940 sf, One Independence Center) began 2026-05-22; ~21 active Charlotte job postings (Platform Engineer, Tax Manager, Operations Associate, etc.) confirm hiring is underway, though development is proceeding "in phases" with no headcount/occupancy milestone disclosed</t>
+        </is>
+      </c>
+      <c r="R102" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="S102" s="6" t="inlineStr">
+        <is>
+          <t>https://crenews.com/2026/05/28/capital-group-leases-200000-sf-at-charlottes-one-independence-center-office/</t>
+        </is>
+      </c>
+      <c r="T102" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U102" s="6" t="inlineStr">
+        <is>
+          <t>Office — finance/tech</t>
+        </is>
+      </c>
+      <c r="V102" s="6" t="inlineStr">
+        <is>
+          <t>Urban-suburban</t>
+        </is>
+      </c>
+      <c r="W102" s="6" t="inlineStr">
+        <is>
+          <t>High-skill eng/data workforce -&gt; walkable South End/Uptown &amp; inner-suburban Class-A and for-sale TH.</t>
+        </is>
+      </c>
+      <c r="X102" s="6" t="inlineStr">
+        <is>
+          <t>No hiring or occupancy update found dated after the 2026-05-22 lease start despite a dedicated recheck; active job postings confirm ongoing hiring but no discrete milestone. Score held flat at 81.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D103" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Plaza Midwood</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — Global HQ (litigation footprint widens further)</t>
+        </is>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>Automotive (EV) — corporate HQ</t>
+        </is>
+      </c>
+      <c r="J103" s="6" t="inlineStr">
+        <is>
+          <t>No permit/construction progress found; franchise-dealer litigation now spans ~7 states</t>
+        </is>
+      </c>
+      <c r="K103" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L103" s="6" t="inlineStr">
+        <is>
+          <t>Projected (365 relocating + 835 new local hires)</t>
+        </is>
+      </c>
+      <c r="M103" s="6" t="inlineStr">
+        <is>
+          <t>$153,978 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N103" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O103" s="6" t="inlineStr">
+        <is>
+          <t>$206.9M</t>
+        </is>
+      </c>
+      <c r="P103" s="6" t="inlineStr">
+        <is>
+          <t>Original 2025-11-12 HQ incentive/relocation commitment</t>
+        </is>
+      </c>
+      <c r="Q103" s="6" t="inlineStr">
+        <is>
+          <t>2nd office building preliminary land-development plan (filed 2026-03-28) still awaiting staff review/approvals; construction start still targeted H1 2027</t>
+        </is>
+      </c>
+      <c r="R103" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="S103" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/scout-motors-hq-move-turbocharges-second-office-building-in-plaza-midwood/</t>
+        </is>
+      </c>
+      <c r="T103" s="6" t="inlineStr">
+        <is>
+          <t>Med (facts High; milestone stage early)</t>
+        </is>
+      </c>
+      <c r="U103" s="6" t="inlineStr">
+        <is>
+          <t>Corporate HQ / professional</t>
+        </is>
+      </c>
+      <c r="V103" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="W103" s="6" t="inlineStr">
+        <is>
+          <t>Supports Plaza Midwood/NoDa/Elizabeth close-in rental and townhome demand from a young, high-wage corporate workforce.</t>
+        </is>
+      </c>
+      <c r="X103" s="6" t="inlineStr">
+        <is>
+          <t>No fresher permit/construction milestone found this cycle. Risk-factor context (not scored): franchise-dealer/DTC-sales-model litigation against Scout/VW now spans at least 7 states (adding a Washington state class action to the previously tracked CA, FL, CO, NY, CT, WA list); company continues stating it is proceeding with the Charlotte HQ regardless. Score held flat at 79.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D104" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Ballantyne</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>Citigroup — Charlotte office (hiring ramp proceeding)</t>
+        </is>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>Banking / financial services</t>
+        </is>
+      </c>
+      <c r="J104" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="K104" s="6" t="n">
+        <v>510</v>
+      </c>
+      <c r="L104" s="6" t="inlineStr">
+        <is>
+          <t>Confirmed (stated); facility ultimately to house 785 employees incl. ~275 relocated</t>
+        </is>
+      </c>
+      <c r="M104" s="6" t="inlineStr">
+        <is>
+          <t>$131,832 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N104" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O104" s="6" t="inlineStr">
+        <is>
+          <t>$16.1M</t>
+        </is>
+      </c>
+      <c r="P104" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $8.9M / 10 yr</t>
+        </is>
+      </c>
+      <c r="Q104" s="6" t="inlineStr">
+        <is>
+          <t>No headcount-progress update found dated after the 2026-04-23 hiring-progress article despite a dedicated recheck</t>
+        </is>
+      </c>
+      <c r="R104" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="S104" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wfae.org/business/2026-04-23/charlottes-banking-jobs-hot-streak-continues</t>
+        </is>
+      </c>
+      <c r="T104" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U104" s="6" t="inlineStr">
+        <is>
+          <t>Office / financial services</t>
+        </is>
+      </c>
+      <c r="V104" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W104" s="6" t="inlineStr">
+        <is>
+          <t>$131,832 stated wage clears the $100k bar; supports Class-A rental and for-sale townhome demand in south Mecklenburg's Ballantyne/Blakeney/Rea Farms corridor.</t>
+        </is>
+      </c>
+      <c r="X104" s="6" t="inlineStr">
+        <is>
+          <t>No fresher milestone found this cycle. Score held flat at 78.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D105" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>Durham / Morrisville</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>Durham &amp; Wake</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>Novartis — API mfg building (unchanged)</t>
+        </is>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="J105" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="K105" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="L105" s="6" t="inlineStr">
+        <is>
+          <t>Projected (part of pre-window deal)</t>
+        </is>
+      </c>
+      <c r="M105" s="6" t="inlineStr">
+        <is>
+          <t>$111,161 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N105" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O105" s="6" t="inlineStr">
+        <is>
+          <t>~$991M (incl. $220M API building)</t>
+        </is>
+      </c>
+      <c r="P105" s="6" t="inlineStr">
+        <is>
+          <t>Part of original $771M package incentives</t>
+        </is>
+      </c>
+      <c r="Q105" s="6" t="inlineStr">
+        <is>
+          <t>Facility opening targeted 2027-2028</t>
+        </is>
+      </c>
+      <c r="R105" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="S105" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
+        </is>
+      </c>
+      <c r="T105" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U105" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="V105" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W105" s="6" t="inlineStr">
+        <is>
+          <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
+        </is>
+      </c>
+      <c r="X105" s="6" t="inlineStr">
+        <is>
+          <t>No new construction/hiring milestone found since the April 30, 2026 announcement despite a dedicated recheck. Score held flat at 77.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20449,7 +22519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L432"/>
+  <dimension ref="A1:L479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -47250,6 +49320,2920 @@
         </is>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B433" s="6" t="inlineStr">
+        <is>
+          <t>North Charleston</t>
+        </is>
+      </c>
+      <c r="C433" s="6" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="D433" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E433" s="6" t="inlineStr">
+        <is>
+          <t>SC Ports Authority — Leatherman Terminal (pause remains in effect)</t>
+        </is>
+      </c>
+      <c r="F433" s="6" t="inlineStr">
+        <is>
+          <t>400 direct + ~1,200 indirect</t>
+        </is>
+      </c>
+      <c r="G433" s="6" t="inlineStr">
+        <is>
+          <t>$1.2B</t>
+        </is>
+      </c>
+      <c r="H433" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I433" s="6" t="inlineStr">
+        <is>
+          <t>Still paused with no confirmed reopening date; SC Ports has stated reopening depends on future cargo demand/cost competitiveness and describes it as a "short-term pause," not permanent. The earlier ambiguous "reopening with major weekly Asia service" headline is now confirmed to be recycled coverage of the Sept. 2024 post-ILA-dispute reopening, not a 2026 development — treat as noise going forward.</t>
+        </is>
+      </c>
+      <c r="J433" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K433" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/2026/06/25/sc-ports-temporarily-halts-leatherman-operations-in-face-of-high-costs-waning-demand/</t>
+        </is>
+      </c>
+      <c r="L433" s="6" t="inlineStr">
+        <is>
+          <t>Med-High (status confirmed; recycled-headline ambiguity resolved)</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B434" s="6" t="inlineStr">
+        <is>
+          <t>Cherokee Co. / Blacksburg</t>
+        </is>
+      </c>
+      <c r="C434" s="6" t="inlineStr">
+        <is>
+          <t>Cherokee</t>
+        </is>
+      </c>
+      <c r="D434" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E434" s="6" t="inlineStr">
+        <is>
+          <t>USA Rare Earth — rare-earth magnet plant</t>
+        </is>
+      </c>
+      <c r="F434" s="6" t="inlineStr">
+        <is>
+          <t>~490</t>
+        </is>
+      </c>
+      <c r="G434" s="6" t="inlineStr">
+        <is>
+          <t>$1.2B</t>
+        </is>
+      </c>
+      <c r="H434" s="6" t="inlineStr">
+        <is>
+          <t>$24.50-$63/hr (stated; unchanged)</t>
+        </is>
+      </c>
+      <c r="I434" s="6" t="inlineStr">
+        <is>
+          <t>No headcount increase past the ~490 figure found this cycle; groundbreaking (Sept. 9, 2026) and a $250,000 Spartanburg Community College "SPARK Center" workforce-training contribution remain the latest confirmed facts. Operational target April 2028 unchanged.</t>
+        </is>
+      </c>
+      <c r="J434" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K434" s="6" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/09/09/3358813/0/en/usa-rare-earth-breaks-ground-on-advanced-rare-earth-metal-and-magnet-manufacturing-facility-in-blacksburg-south-carolina.html</t>
+        </is>
+      </c>
+      <c r="L434" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B435" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg (former Kohler plant)</t>
+        </is>
+      </c>
+      <c r="C435" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D435" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E435" s="6" t="inlineStr">
+        <is>
+          <t>NorthMark/Valara "Project Moc-1" — AI/HPC data center (moratorium resolved; grandfathered)</t>
+        </is>
+      </c>
+      <c r="F435" s="6" t="inlineStr">
+        <is>
+          <t>27 FT confirmed on incentive filings (company's own ~150-at-full-operation claim not independently corroborated)</t>
+        </is>
+      </c>
+      <c r="G435" s="6" t="inlineStr">
+        <is>
+          <t>$2.8-3.0B</t>
+        </is>
+      </c>
+      <c r="H435" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I435" s="6" t="inlineStr">
+        <is>
+          <t>Major resolution this cycle: Spartanburg County Council passed a 1-year data-center moratorium 5-1 on Sept. 21, 2026 (a same-night reconsideration attempt was later called an 'illegal meeting' by the council's own press attorney; an amended final version passed Sept. 25). The moratorium explicitly exempts already-approved projects and facilities &lt;=65MW in industrial parks — Project Moc-1 is grandfathered and unaffected. Separately, the SC Public Service Commission ruled unanimously (Aug. 27, 2026) that Valara's 457MW on-site gas plant is NOT subject to the Utility Siting Act, dismissing SELC/residents' petition — a second developer-favorable ruling. SC DES approved a Synthetic Minor Air Construction Permit (Sept. 18, 2026) covering 11 combustion turbines (up from the prior count), prompting new county pollution-monitoring questions (Sept. 22). Judge Cole's ruling on SELC's Sept. 17 injunction/major-vs-minor motion remains pending, under advisement. S.867 (statewide siting bill) remains stalled with no floor action since the General Assembly adjourned its regular session May 14, 2026.</t>
+        </is>
+      </c>
+      <c r="J435" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="K435" s="6" t="inlineStr">
+        <is>
+          <t>https://www.foxcarolina.com/2026/09/22/spartanburg-county-council-passes-data-center-moratorium-with-several-amendments/</t>
+        </is>
+      </c>
+      <c r="L435" s="6" t="inlineStr">
+        <is>
+          <t>Med-High (county/state regulatory risk now resolved in developer's favor; court injunction ruling still open)</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B436" s="6" t="inlineStr">
+        <is>
+          <t>Wake County (statewide)</t>
+        </is>
+      </c>
+      <c r="C436" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D436" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E436" s="6" t="inlineStr">
+        <is>
+          <t>WakeMed / Atrium Health — merger approved by county, moves to federal review</t>
+        </is>
+      </c>
+      <c r="F436" s="6" t="inlineStr">
+        <is>
+          <t>3,300 (statewide, 5 yr)</t>
+        </is>
+      </c>
+      <c r="G436" s="6" t="inlineStr">
+        <is>
+          <t>$2.0B (Wake Co. portion)</t>
+        </is>
+      </c>
+      <c r="H436" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I436" s="6" t="inlineStr">
+        <is>
+          <t>Resolved this cycle: the Wake County Board of Commissioners voted 5-2 on Sept. 21, 2026 to approve the merger's Articles of Incorporation/Transfer Agreement amendments (for: Mial, Stallings, Jackson, Evans, Thomas; against: Adamson, Waters). The deal is not final — it now moves to FTC and DOJ regulatory review. No new jobs/capex figures disclosed beyond the previously tracked totals.</t>
+        </is>
+      </c>
+      <c r="J436" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="K436" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/wake-commissioners-schedule-vote-pave-way-wakemed-atrium-merger-september-2026/</t>
+        </is>
+      </c>
+      <c r="L436" s="6" t="inlineStr">
+        <is>
+          <t>High (vote outcome); Medium (federal-review outcome/timeline unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B437" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="C437" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="D437" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E437" s="6" t="inlineStr">
+        <is>
+          <t>Boom Supersonic — Overture assembly (AT RISK — deadline ~3 months out)</t>
+        </is>
+      </c>
+      <c r="F437" s="6" t="inlineStr">
+        <is>
+          <t>&lt;=500 currently; must hit 500 by 12/31/26 or lease may terminate</t>
+        </is>
+      </c>
+      <c r="G437" s="6" t="inlineStr">
+        <is>
+          <t>~$50M (hangar)</t>
+        </is>
+      </c>
+      <c r="H437" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I437" s="6" t="inlineStr">
+        <is>
+          <t>No headcount evidence found despite a second dedicated search pass this cycle. The hangar is confirmed still idle per in-window reporting (March 2026, Hoodline); the last concrete headcount data point found anywhere remains a pre-window (Aug. 2025) figure of ~260 employees (halved from ~520 in fall 2024) amid an ~$8B funding gap. The Dec. 31, 2026 500-employee lease-termination deadline is now roughly 3 months out with no sign of a hiring ramp. Escalating risk, unresolved.</t>
+        </is>
+      </c>
+      <c r="J437" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K437" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/greensboro-s-50-million-supersonic-ghost-hangar-puts-state-on-the-clock/</t>
+        </is>
+      </c>
+      <c r="L437" s="6" t="inlineStr">
+        <is>
+          <t>Med-High (risk escalating; deadline imminent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B438" s="6" t="inlineStr">
+        <is>
+          <t>Rowan County</t>
+        </is>
+      </c>
+      <c r="C438" s="6" t="inlineStr">
+        <is>
+          <t>Rowan</t>
+        </is>
+      </c>
+      <c r="D438" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E438" s="6" t="inlineStr">
+        <is>
+          <t>American Eagle Outfitters</t>
+        </is>
+      </c>
+      <c r="F438" s="6" t="inlineStr">
+        <is>
+          <t>200+ (state figure; county vote cited 258)</t>
+        </is>
+      </c>
+      <c r="G438" s="6" t="inlineStr">
+        <is>
+          <t>$41M</t>
+        </is>
+      </c>
+      <c r="H438" s="6" t="inlineStr">
+        <is>
+          <t>$57,351 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I438" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle beyond a minor new detail: a $150,000 One NC Fund grant tied to the project. 472,890 sq ft facility at 1415 Peeler Road (Innovation Logistics Center, Salisbury); Q1 2027 ops start still targeted.</t>
+        </is>
+      </c>
+      <c r="J438" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K438" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2026/07/17/governor-stein-announces-american-eagle-outfitters-inc-selects-rowan-county-41-million-southeast</t>
+        </is>
+      </c>
+      <c r="L438" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B439" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte (CLT airport)</t>
+        </is>
+      </c>
+      <c r="C439" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D439" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E439" s="6" t="inlineStr">
+        <is>
+          <t>Averitt — logistics campus (zoning still not confirmed approved)</t>
+        </is>
+      </c>
+      <c r="F439" s="6" t="inlineStr">
+        <is>
+          <t>211-230 (range across sources; treated as unchanged)</t>
+        </is>
+      </c>
+      <c r="G439" s="6" t="inlineStr">
+        <is>
+          <t>$200M</t>
+        </is>
+      </c>
+      <c r="H439" s="6" t="inlineStr">
+        <is>
+          <t>$81,769 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I439" s="6" t="inlineStr">
+        <is>
+          <t>City of Charlotte's zoning process (Rezoning Petition 2025-139, 53.24 acres; public hearing 3/23/26, Zoning Committee work session 4/7/26) still has no confirmed final Council approval as of Sept. 28, 2026 despite a dedicated recheck. NCDOT's Shopton Road bridge closure (through summer 2027) remains a live access/build-out complication.</t>
+        </is>
+      </c>
+      <c r="J439" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K439" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/04/averitt-s-230-job-truck-campus-poised-to-rev-up-clt-s-cargo-corridor/</t>
+        </is>
+      </c>
+      <c r="L439" s="6" t="inlineStr">
+        <is>
+          <t>High (jobs/wage); Med (zoning/construction timing still unresolved)</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B440" s="6" t="inlineStr">
+        <is>
+          <t>Wake Co. (aggregate)</t>
+        </is>
+      </c>
+      <c r="C440" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D440" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E440" s="6" t="inlineStr">
+        <is>
+          <t>County jobs pipeline (EDGE 7, 52 projects)</t>
+        </is>
+      </c>
+      <c r="F440" s="6" t="inlineStr">
+        <is>
+          <t>~11,000 (pipeline)</t>
+        </is>
+      </c>
+      <c r="G440" s="6" t="inlineStr">
+        <is>
+          <t>$11B</t>
+        </is>
+      </c>
+      <c r="H440" s="6" t="inlineStr">
+        <is>
+          <t>Mixed (office-skewed)</t>
+        </is>
+      </c>
+      <c r="I440" s="6" t="inlineStr">
+        <is>
+          <t>Discrepancy flagged last cycle resolved: the previously-cited ~$5.6B/~10,800-job figure belongs to the prior 5-year cycle (EDGE6, completed-program results), not EDGE7. EDGE7's current active pipeline remains 52 projects / $11B+ / ~11,000 jobs (Wake Co. Econ Dev director Michael Haley, Feb. 4, 2026). The underlying "New and Expanding" PDF at e1.nmcdn.io remains inaccessible (egress-blocked) for line-item reconciliation.</t>
+        </is>
+      </c>
+      <c r="J440" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K440" s="6" t="inlineStr">
+        <is>
+          <t>https://nchospitalityalliance.com/wake-county-pursues-11-billion-jobs-pipeline/</t>
+        </is>
+      </c>
+      <c r="L440" s="6" t="inlineStr">
+        <is>
+          <t>Med (pipeline scope now clarified; underlying PDF still unverified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B441" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / SouthPark</t>
+        </is>
+      </c>
+      <c r="C441" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D441" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E441" s="6" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase — SouthPark consolidated office</t>
+        </is>
+      </c>
+      <c r="F441" s="6" t="inlineStr">
+        <is>
+          <t>400 new + ~600 relocated = 1,000 total</t>
+        </is>
+      </c>
+      <c r="G441" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H441" s="6" t="inlineStr">
+        <is>
+          <t>~$105k Estimated/Inferred — basis not independently confirmed</t>
+        </is>
+      </c>
+      <c r="I441" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle. One Piedmont Town Center (4725 Piedmont Row Dr., ~145,000 sf, 5 floors) consolidation reconfirmed; move-in still targeted early 2028. Wage still not disclosed by the company.</t>
+        </is>
+      </c>
+      <c r="J441" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K441" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wfae.org/business/2026-04-21/jpmorgan-chase-adding-400-jobs-consolidate-in-southpark-offices</t>
+        </is>
+      </c>
+      <c r="L441" s="6" t="inlineStr">
+        <is>
+          <t>High (jobs/lease/timing); Low (wage basis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B442" s="6" t="inlineStr">
+        <is>
+          <t>Garner</t>
+        </is>
+      </c>
+      <c r="C442" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D442" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E442" s="6" t="inlineStr">
+        <is>
+          <t>Gregory Poole Equipment Co. — HQ relocation</t>
+        </is>
+      </c>
+      <c r="F442" s="6" t="inlineStr">
+        <is>
+          <t>500+ (5 yr)</t>
+        </is>
+      </c>
+      <c r="G442" s="6" t="inlineStr">
+        <is>
+          <t>$347M</t>
+        </is>
+      </c>
+      <c r="H442" s="6" t="inlineStr">
+        <is>
+          <t>~$75,381 companywide avg (Estimated/Inferred, sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I442" s="6" t="inlineStr">
+        <is>
+          <t>No groundbreaking confirmed this cycle; project remains at "construction expected within 24 months" per Oct. 2025 reporting on the 130-acre site purchased Feb. 2025.</t>
+        </is>
+      </c>
+      <c r="J442" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K442" s="6" t="inlineStr">
+        <is>
+          <t>https://www.garnernc.gov/Home/Components/News/News/2344/17</t>
+        </is>
+      </c>
+      <c r="L442" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B443" s="6" t="inlineStr">
+        <is>
+          <t>Benson</t>
+        </is>
+      </c>
+      <c r="C443" s="6" t="inlineStr">
+        <is>
+          <t>Johnston</t>
+        </is>
+      </c>
+      <c r="D443" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E443" s="6" t="inlineStr">
+        <is>
+          <t>Vulcan Elements — magnet factory (transmission line fast-tracked)</t>
+        </is>
+      </c>
+      <c r="F443" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (proj.)</t>
+        </is>
+      </c>
+      <c r="G443" s="6" t="inlineStr">
+        <is>
+          <t>$918.4M</t>
+        </is>
+      </c>
+      <c r="H443" s="6" t="inlineStr">
+        <is>
+          <t>$81,932 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I443" s="6" t="inlineStr">
+        <is>
+          <t>No factory-groundbreaking event found this cycle beyond the already-tracked NC Utilities Commission fast-tracked (late Aug. 2026) 230kV transmission-line approval; company's own guidance still targets starting operations Q1 2027 after doubling the planned facility to 1M+ sq ft.</t>
+        </is>
+      </c>
+      <c r="J443" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K443" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/nccapitol/north-carolina-fast-tracks-power-line-for-rare-earth-magnet-factory-august-2026/</t>
+        </is>
+      </c>
+      <c r="L443" s="6" t="inlineStr">
+        <is>
+          <t>Medium-High (infrastructure clearance confirmed; factory groundbreaking date still unconfirmed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B444" s="6" t="inlineStr">
+        <is>
+          <t>Multi-site NC incl. Wilmington</t>
+        </is>
+      </c>
+      <c r="C444" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover +</t>
+        </is>
+      </c>
+      <c r="D444" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E444" s="6" t="inlineStr">
+        <is>
+          <t>Amazon-Corning — fiber-optics partnership</t>
+        </is>
+      </c>
+      <c r="F444" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (multi-site, unallocated)</t>
+        </is>
+      </c>
+      <c r="G444" s="6" t="inlineStr">
+        <is>
+          <t>Multi-billion (undisclosed)</t>
+        </is>
+      </c>
+      <c r="H444" s="6" t="inlineStr">
+        <is>
+          <t>Avg salary &gt;$65,000 (sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I444" s="6" t="inlineStr">
+        <is>
+          <t>Not covered by any regional research pass this cycle; carried forward unchanged from the prior report. Wilmington-specific job allocation remains undisclosed.</t>
+        </is>
+      </c>
+      <c r="J444" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K444" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wilmingtonbiz.com/technology/2026/06/08/amazon_corning_strike_multibillion_dollar_deal_to_add_1000_nc_jobs/27560</t>
+        </is>
+      </c>
+      <c r="L444" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B445" s="6" t="inlineStr">
+        <is>
+          <t>Arden</t>
+        </is>
+      </c>
+      <c r="C445" s="6" t="inlineStr">
+        <is>
+          <t>Buncombe</t>
+        </is>
+      </c>
+      <c r="D445" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E445" s="6" t="inlineStr">
+        <is>
+          <t>Pratt &amp; Whitney (RTX) — casting foundry expansion</t>
+        </is>
+      </c>
+      <c r="F445" s="6" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="G445" s="6" t="inlineStr">
+        <is>
+          <t>$285M</t>
+        </is>
+      </c>
+      <c r="H445" s="6" t="inlineStr">
+        <is>
+          <t>$62,413 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I445" s="6" t="inlineStr">
+        <is>
+          <t>Still forward-looking: first equipment arrivals remain projected for end of 2026, first parts production mid-2027, full foundry operations targeted 2028 (new detail); no confirmation found this cycle that equipment has actually arrived.</t>
+        </is>
+      </c>
+      <c r="J445" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K445" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/pratt-whitney-announces-285-million-expansion-325-more-jobs-for-buncombe-county/pratt-whitney-asheville/</t>
+        </is>
+      </c>
+      <c r="L445" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B446" s="6" t="inlineStr">
+        <is>
+          <t>Asheville / Arden</t>
+        </is>
+      </c>
+      <c r="C446" s="6" t="inlineStr">
+        <is>
+          <t>Buncombe</t>
+        </is>
+      </c>
+      <c r="D446" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E446" s="6" t="inlineStr">
+        <is>
+          <t>Eaton — Low Voltage Assembly expansion</t>
+        </is>
+      </c>
+      <c r="F446" s="6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G446" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H446" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Estimated mid-$60k-$80k)</t>
+        </is>
+      </c>
+      <c r="I446" s="6" t="inlineStr">
+        <is>
+          <t>Active hiring confirmed underway: current job postings for the LVA line at the Arden/Heywood Rd facility (Electrical Test Technician, Manufacturing Supervisor, and other technical/production roles) are consistent with the "jobs filled within 12 months of the April 2026 announcement" plan.</t>
+        </is>
+      </c>
+      <c r="J446" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K446" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ashevillechamber.org/news-events/press-releases/eaton-invests-in-workforce-growth-in-buncombe-county/</t>
+        </is>
+      </c>
+      <c r="L446" s="6" t="inlineStr">
+        <is>
+          <t>High (jobs); Low (wage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B447" s="6" t="inlineStr">
+        <is>
+          <t>Hendersonville</t>
+        </is>
+      </c>
+      <c r="C447" s="6" t="inlineStr">
+        <is>
+          <t>Henderson</t>
+        </is>
+      </c>
+      <c r="D447" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E447" s="6" t="inlineStr">
+        <is>
+          <t>BorgWarner — vertical-integration expansion</t>
+        </is>
+      </c>
+      <c r="F447" s="6" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="G447" s="6" t="inlineStr">
+        <is>
+          <t>$100M</t>
+        </is>
+      </c>
+      <c r="H447" s="6" t="inlineStr">
+        <is>
+          <t>$67,047 avg (stated; below $100k)</t>
+        </is>
+      </c>
+      <c r="I447" s="6" t="inlineStr">
+        <is>
+          <t>Not covered by any regional research pass this cycle (Henderson Co. falls outside all five assigned regions); carried forward unchanged from the prior report.</t>
+        </is>
+      </c>
+      <c r="J447" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="K447" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2026/05/26/governor-stein-announces-100-million-expansion-borgwarner-hendersonville</t>
+        </is>
+      </c>
+      <c r="L447" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B448" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro</t>
+        </is>
+      </c>
+      <c r="C448" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="D448" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E448" s="6" t="inlineStr">
+        <is>
+          <t>Lumentum — AI/data-center optics (hiring underway)</t>
+        </is>
+      </c>
+      <c r="F448" s="6" t="inlineStr">
+        <is>
+          <t>~400</t>
+        </is>
+      </c>
+      <c r="G448" s="6" t="inlineStr">
+        <is>
+          <t>Hundreds of millions</t>
+        </is>
+      </c>
+      <c r="H448" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I448" s="6" t="inlineStr">
+        <is>
+          <t>Facility (ex-Qorvo) confirmed operational; hiring is underway for fab/process engineers, manufacturing technicians, ops, supply chain, and quality-engineering roles, but the production ramp remains targeted for mid-2028. No new headcount figure disclosed.</t>
+        </is>
+      </c>
+      <c r="J448" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K448" s="6" t="inlineStr">
+        <is>
+          <t>https://myfox8.com/news/north-carolina/greensboro/lumentum-holdings-opens-new-manufacturing-facility-in-greensboro/amp/</t>
+        </is>
+      </c>
+      <c r="L448" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B449" s="6" t="inlineStr">
+        <is>
+          <t>Kernersville</t>
+        </is>
+      </c>
+      <c r="C449" s="6" t="inlineStr">
+        <is>
+          <t>Forsyth</t>
+        </is>
+      </c>
+      <c r="D449" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E449" s="6" t="inlineStr">
+        <is>
+          <t>John Deere — excavator plant (relocating from Japan)</t>
+        </is>
+      </c>
+      <c r="F449" s="6" t="inlineStr">
+        <is>
+          <t>150+</t>
+        </is>
+      </c>
+      <c r="G449" s="6" t="inlineStr">
+        <is>
+          <t>$70M</t>
+        </is>
+      </c>
+      <c r="H449" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Inferred skilled-mfg)</t>
+        </is>
+      </c>
+      <c r="I449" s="6" t="inlineStr">
+        <is>
+          <t>Construction confirmed continuing on the west campus (small-excavator assembly); company messaging still targets opening "in the next year." No new milestone beyond what was already tracked.</t>
+        </is>
+      </c>
+      <c r="J449" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K449" s="6" t="inlineStr">
+        <is>
+          <t>https://www.deere.com/en-us/our-company/locations/factories/kernersville</t>
+        </is>
+      </c>
+      <c r="L449" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B450" s="6" t="inlineStr">
+        <is>
+          <t>Rowan / Kannapolis</t>
+        </is>
+      </c>
+      <c r="C450" s="6" t="inlineStr">
+        <is>
+          <t>Rowan</t>
+        </is>
+      </c>
+      <c r="D450" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E450" s="6" t="inlineStr">
+        <is>
+          <t>Google — 730k sq ft warehouse lease (operator now named: DHL)</t>
+        </is>
+      </c>
+      <c r="F450" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G450" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H450" s="6" t="inlineStr">
+        <is>
+          <t>$55k-$150k range (job-board postings)</t>
+        </is>
+      </c>
+      <c r="I450" s="6" t="inlineStr">
+        <is>
+          <t>New detail: the Overlook 85 Industrial Park facility (1894 Old Beatty Ford Road) is confirmed for warehousing/logistics (explicitly "not a data center"), with DHL now named as the third-party operator actively hiring on-site; 88-month lease with two 5-year renewal options. Google itself still discloses no jobs/wage figures.</t>
+        </is>
+      </c>
+      <c r="J450" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K450" s="6" t="inlineStr">
+        <is>
+          <t>https://www.salisburypost.com/2026/05/02/not-a-data-center-google-leases-rowan-county-side-kannapolis-industrial-site/</t>
+        </is>
+      </c>
+      <c r="L450" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B451" s="6" t="inlineStr">
+        <is>
+          <t>RTP</t>
+        </is>
+      </c>
+      <c r="C451" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D451" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E451" s="6" t="inlineStr">
+        <is>
+          <t>Apple — RTP campus extension</t>
+        </is>
+      </c>
+      <c r="F451" s="6" t="inlineStr">
+        <is>
+          <t>3,000 originally projected; only ~600-990 added to date</t>
+        </is>
+      </c>
+      <c r="G451" s="6" t="inlineStr">
+        <is>
+          <t>$552M-$1B+ (paused)</t>
+        </is>
+      </c>
+      <c r="H451" s="6" t="inlineStr">
+        <is>
+          <t>$187k avg (stated, original 2021 award)</t>
+        </is>
+      </c>
+      <c r="I451" s="6" t="inlineStr">
+        <is>
+          <t>No new Apple-specific building or hiring milestone found dated after the July 2026 RTP 3.0 framework approval already on record. ~$845.8M in state incentives remain at stake.</t>
+        </is>
+      </c>
+      <c r="J451" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K451" s="6" t="inlineStr">
+        <is>
+          <t>https://www.rtp.org/2026/06/research-triangle-park-approves-3-0/</t>
+        </is>
+      </c>
+      <c r="L451" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B452" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Raleigh / Rural Hall</t>
+        </is>
+      </c>
+      <c r="C452" s="6" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="D452" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E452" s="6" t="inlineStr">
+        <is>
+          <t>Siemens Energy — $421M NC expansion (Charlotte-specific)</t>
+        </is>
+      </c>
+      <c r="F452" s="6" t="inlineStr">
+        <is>
+          <t>500 (statewide)</t>
+        </is>
+      </c>
+      <c r="G452" s="6" t="inlineStr">
+        <is>
+          <t>$421M</t>
+        </is>
+      </c>
+      <c r="H452" s="6" t="inlineStr">
+        <is>
+          <t>$82,052 avg for the Charlotte-specific share (sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I452" s="6" t="inlineStr">
+        <is>
+          <t>No in-window groundbreaking or hiring-start milestone found this cycle. Original announcement remains pre-window (Feb. 2026).</t>
+        </is>
+      </c>
+      <c r="J452" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K452" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/02/siemens-energy-announces-421-million-expansion-in-charlotte-boosting-local-economy-with-500-new-jobs/</t>
+        </is>
+      </c>
+      <c r="L452" s="6" t="inlineStr">
+        <is>
+          <t>Med (totals uncertain; Charlotte wage confirmed sub-$100k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B453" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh / Wendell / Knightdale</t>
+        </is>
+      </c>
+      <c r="C453" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D453" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E453" s="6" t="inlineStr">
+        <is>
+          <t>Siemens AG — power devices for AI/data centers</t>
+        </is>
+      </c>
+      <c r="F453" s="6" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="G453" s="6" t="inlineStr">
+        <is>
+          <t>part of $165M</t>
+        </is>
+      </c>
+      <c r="H453" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I453" s="6" t="inlineStr">
+        <is>
+          <t>New breakdown detail confirmed (consistent with the existing 350-job total, no change): 100 jobs at a new 131,000 sq ft Knightdale power-devices facility (by end of 2026) + 50 jobs at a new 101,000 sq ft Wendell facility + 200 jobs from an existing Wendell campus expansion by 2028. No update dated after the March 2026 announcement found.</t>
+        </is>
+      </c>
+      <c r="J453" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K453" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/business/siemens-350-jobs-nc-sc-165m-investment-ai-data-centers-raleigh-wendell-march-2026/</t>
+        </is>
+      </c>
+      <c r="L453" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B454" s="6" t="inlineStr">
+        <is>
+          <t>Hamlet</t>
+        </is>
+      </c>
+      <c r="C454" s="6" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="D454" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E454" s="6" t="inlineStr">
+        <is>
+          <t>AWS/Amazon — AI/cloud campus "Project Blue Marlin" (air permits approved)</t>
+        </is>
+      </c>
+      <c r="F454" s="6" t="inlineStr">
+        <is>
+          <t>500 permanent (confirmed)</t>
+        </is>
+      </c>
+      <c r="G454" s="6" t="inlineStr">
+        <is>
+          <t>$10B</t>
+        </is>
+      </c>
+      <c r="H454" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I454" s="6" t="inlineStr">
+        <is>
+          <t>Material regulatory milestone: NC Division of Air Quality granted both Amazon's (~588 backup diesel generators) and Duke Energy's (57 generators) air-quality permits on Aug. 29, 2026, following a July 30, 2026 joint public hearing (200+ attendees, 36 testified) — clears a key hurdle toward construction. Project scope: 21 buildings, 1,600 MW backup diesel generation. 500-permanent-job and $10B figures unchanged.</t>
+        </is>
+      </c>
+      <c r="J454" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="K454" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wunc.org/2026-08-29/amazons-richmond-county-data-center-gets-green-light-on-air-quality-permits</t>
+        </is>
+      </c>
+      <c r="L454" s="6" t="inlineStr">
+        <is>
+          <t>High (permits/scheduling confirmed); Low (post-event outcome)</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B455" s="6" t="inlineStr">
+        <is>
+          <t>Orangeburg / I-26</t>
+        </is>
+      </c>
+      <c r="C455" s="6" t="inlineStr">
+        <is>
+          <t>Orangeburg</t>
+        </is>
+      </c>
+      <c r="D455" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E455" s="6" t="inlineStr">
+        <is>
+          <t>Ferrara Candy — new mfg + corporate site (groundbreaking confirmed)</t>
+        </is>
+      </c>
+      <c r="F455" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (10 yr)</t>
+        </is>
+      </c>
+      <c r="G455" s="6" t="inlineStr">
+        <is>
+          <t>$675M</t>
+        </is>
+      </c>
+      <c r="H455" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; confectionery = workforce-tier</t>
+        </is>
+      </c>
+      <c r="I455" s="6" t="inlineStr">
+        <is>
+          <t>Material milestone: groundbreaking held May 18-19, 2026 at the Hwy 21 &amp; Rowesville Rd site (750,000 sq ft); first production lines expected online Q1 2029.</t>
+        </is>
+      </c>
+      <c r="J455" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K455" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wistv.com/2026/05/19/ferrara-candy-company-breaks-ground-orangeburg/</t>
+        </is>
+      </c>
+      <c r="L455" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B456" s="6" t="inlineStr">
+        <is>
+          <t>Columbia / BullStreet</t>
+        </is>
+      </c>
+      <c r="C456" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="D456" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E456" s="6" t="inlineStr">
+        <is>
+          <t>AMAROK — new HQ (perimeter security)</t>
+        </is>
+      </c>
+      <c r="F456" s="6" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="G456" s="6" t="inlineStr">
+        <is>
+          <t>$69M</t>
+        </is>
+      </c>
+      <c r="H456" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; HQ/professional (portion likely $100k+)</t>
+        </is>
+      </c>
+      <c r="I456" s="6" t="inlineStr">
+        <is>
+          <t>No groundbreaking confirmation found this cycle; all available coverage still describes the project as "construction expected to begin in 2026" with design plans still being finalized. Online by end of 2028 unchanged.</t>
+        </is>
+      </c>
+      <c r="J456" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K456" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.sc.gov/news/2026-03/amarok-expands-richland-county-operations-new-headquarters</t>
+        </is>
+      </c>
+      <c r="L456" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B457" s="6" t="inlineStr">
+        <is>
+          <t>North Charleston</t>
+        </is>
+      </c>
+      <c r="C457" s="6" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="D457" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E457" s="6" t="inlineStr">
+        <is>
+          <t>Boeing 787 — production-rate ramp</t>
+        </is>
+      </c>
+      <c r="F457" s="6" t="inlineStr">
+        <is>
+          <t>1,000+ new jobs over 5 yrs (unchanged); campus total ~9,059</t>
+        </is>
+      </c>
+      <c r="G457" s="6" t="inlineStr">
+        <is>
+          <t>$1B+ (existing)</t>
+        </is>
+      </c>
+      <c r="H457" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mixed (production ~$70-85k; eng. above $100k)</t>
+        </is>
+      </c>
+      <c r="I457" s="6" t="inlineStr">
+        <is>
+          <t>No newer production-rate or headcount figure found this cycle beyond the already-tracked Aug. 27, 2026 apprenticeship-doubling announcement (500-&gt;1,000+ apprentices, made jointly with Acting US Labor Secretary Keith Sonderling).</t>
+        </is>
+      </c>
+      <c r="J457" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K457" s="6" t="inlineStr">
+        <is>
+          <t>https://www.live5news.com/2026/08/27/boeing-double-apprenticeship-program-north-charleston-plant/</t>
+        </is>
+      </c>
+      <c r="L457" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B458" s="6" t="inlineStr">
+        <is>
+          <t>Goose Creek</t>
+        </is>
+      </c>
+      <c r="C458" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley</t>
+        </is>
+      </c>
+      <c r="D458" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E458" s="6" t="inlineStr">
+        <is>
+          <t>HII (Newport News Shipbuilding) — no site-specific new figure</t>
+        </is>
+      </c>
+      <c r="F458" s="6" t="inlineStr">
+        <is>
+          <t>~475 employees (unchanged)</t>
+        </is>
+      </c>
+      <c r="G458" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H458" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I458" s="6" t="inlineStr">
+        <is>
+          <t>No Goose Creek-specific new expansion figure found this cycle beyond the Jan. 22, 2026 one-year-anniversary milestone (itself pre-window), which noted hopes for headcount to "rise by the hundreds" without a confirmed new number.</t>
+        </is>
+      </c>
+      <c r="J458" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K458" s="6" t="inlineStr">
+        <is>
+          <t>https://www.hii.com/news/hii-closes-on-asset-acquisition-to-expand-shipbuilding-capacity</t>
+        </is>
+      </c>
+      <c r="L458" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B459" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="C459" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D459" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E459" s="6" t="inlineStr">
+        <is>
+          <t>Siemens Smart Infrastructure</t>
+        </is>
+      </c>
+      <c r="F459" s="6" t="inlineStr">
+        <is>
+          <t>~150</t>
+        </is>
+      </c>
+      <c r="G459" s="6" t="inlineStr">
+        <is>
+          <t>$165M</t>
+        </is>
+      </c>
+      <c r="H459" s="6" t="inlineStr">
+        <is>
+          <t>Avg $78,811/yr ($37.89/hr); 90th pct ~$100k (Estimated/Inferred)</t>
+        </is>
+      </c>
+      <c r="I459" s="6" t="inlineStr">
+        <is>
+          <t>No material update found this cycle beyond the March 2026 announcement (&gt;$165M Carolinas-wide investment in electrical products for data centers).</t>
+        </is>
+      </c>
+      <c r="J459" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K459" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wspa.com/news/local-news/siemens-to-expand-production-in-spartanburg-co-add-150-jobs/</t>
+        </is>
+      </c>
+      <c r="L459" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B460" s="6" t="inlineStr">
+        <is>
+          <t>Woodruff / Spartanburg Co.</t>
+        </is>
+      </c>
+      <c r="C460" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D460" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E460" s="6" t="inlineStr">
+        <is>
+          <t>AIRSYS Cooling Technologies — global HQ (capex discrepancy flagged)</t>
+        </is>
+      </c>
+      <c r="F460" s="6" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G460" s="6" t="inlineStr">
+        <is>
+          <t>$40M (originally tracked); several 2026 secondary sources now cite ~$60M — reconciliation needed</t>
+        </is>
+      </c>
+      <c r="H460" s="6" t="inlineStr">
+        <is>
+          <t>Eng. roles $69-93k; assembly $34-46k (Estimated/Inferred)</t>
+        </is>
+      </c>
+      <c r="I460" s="6" t="inlineStr">
+        <is>
+          <t>HQ grand opening confirmed in-window (~May 2026); corporate/HQ teams operating on-site, manufacturing production start still targeted Q1 2027. New capex discrepancy: multiple 2026 sources (Post and Courier, Spartan Weekly, HereSpartanburg) now describe the investment as "$60 million" vs. the originally tracked $40M — may reflect a scope increase or inconsistent reporting; flagged for verification against the original SC Commerce release.</t>
+        </is>
+      </c>
+      <c r="J460" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K460" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/spartanburg/business/airsys-data-center-water-woodruff-sc/article_86465e32-7d21-4bba-9a9b-3e6ea0e2d691.html</t>
+        </is>
+      </c>
+      <c r="L460" s="6" t="inlineStr">
+        <is>
+          <t>Medium (capex figure needs reconciliation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B461" s="6" t="inlineStr">
+        <is>
+          <t>Gray Court</t>
+        </is>
+      </c>
+      <c r="C461" s="6" t="inlineStr">
+        <is>
+          <t>Laurens</t>
+        </is>
+      </c>
+      <c r="D461" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E461" s="6" t="inlineStr">
+        <is>
+          <t>Aptiv Services US — Connexial Center</t>
+        </is>
+      </c>
+      <c r="F461" s="6" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="G461" s="6" t="inlineStr">
+        <is>
+          <t>$120.8M</t>
+        </is>
+      </c>
+      <c r="H461" s="6" t="inlineStr">
+        <is>
+          <t>~$49-76k technician range (Estimated/Inferred)</t>
+        </is>
+      </c>
+      <c r="I461" s="6" t="inlineStr">
+        <is>
+          <t>No Aptiv-specific update found this cycle ("Project Oracle" details reconfirmed unchanged). Shamrock Technologies' HQ relocation into the same park remains a park-level momentum signal only.</t>
+        </is>
+      </c>
+      <c r="J461" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K461" s="6" t="inlineStr">
+        <is>
+          <t>https://growlaurenscounty.com/news/article/momentum-continues-at-the-connexial-center-with-aptivs-investment</t>
+        </is>
+      </c>
+      <c r="L461" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B462" s="6" t="inlineStr">
+        <is>
+          <t>Easley (Anderson/Pickens border)</t>
+        </is>
+      </c>
+      <c r="C462" s="6" t="inlineStr">
+        <is>
+          <t>Anderson</t>
+        </is>
+      </c>
+      <c r="D462" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E462" s="6" t="inlineStr">
+        <is>
+          <t>Signature Foods USA</t>
+        </is>
+      </c>
+      <c r="F462" s="6" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="G462" s="6" t="inlineStr">
+        <is>
+          <t>$11.5M</t>
+        </is>
+      </c>
+      <c r="H462" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred sub-$50k (food mfg.)</t>
+        </is>
+      </c>
+      <c r="I462" s="6" t="inlineStr">
+        <is>
+          <t>Operations confirmed online and actively hiring toward the 202-job target; no headcount change found this cycle.</t>
+        </is>
+      </c>
+      <c r="J462" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K462" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/greenville/business/easley-anderson-county-signature-foods-investment/article_1d618a58-af96-435a-a05c-7cc6f9253a83.html</t>
+        </is>
+      </c>
+      <c r="L462" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B463" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="C463" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D463" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E463" s="6" t="inlineStr">
+        <is>
+          <t>GNQ Insilico — AI/quantum techbio HQ (SPAC deadline missed; second extension sought)</t>
+        </is>
+      </c>
+      <c r="F463" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G463" s="6" t="inlineStr">
+        <is>
+          <t>$500M (valuation, not capex)</t>
+        </is>
+      </c>
+      <c r="H463" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I463" s="6" t="inlineStr">
+        <is>
+          <t>Correction/clarification: the Sept. 28, 2026 deadline tracked last cycle was itself already the result of a prior extension (shareholders voted to push the original March 28, 2026 deadline). A SEC Form DEF 14A proxy (filed ~mid-Sept. 2026) shows IB Acquisition Corp. is now seeking ANOTHER 6-month extension, to March 28, 2027 — confirming the merger has NOT closed. IBAC separately entered a $140M financing package ($50M equity facility + up to $90M convertible notes) on Sept. 15, 2026 to support the deal. Jobs remain undisclosed at every stage.</t>
+        </is>
+      </c>
+      <c r="J463" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K463" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/0001998781/000149315226041539/formdef14a.htm</t>
+        </is>
+      </c>
+      <c r="L463" s="6" t="inlineStr">
+        <is>
+          <t>Med (deal status now clarified; still not closed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B464" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="C464" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D464" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E464" s="6" t="inlineStr">
+        <is>
+          <t>GE Vernova — gas turbine mfg (strong company-wide demand; no new local jobs figure)</t>
+        </is>
+      </c>
+      <c r="F464" s="6" t="inlineStr">
+        <is>
+          <t>650 total planned; ~200 hired past yr</t>
+        </is>
+      </c>
+      <c r="G464" s="6" t="inlineStr">
+        <is>
+          <t>$160M (Greenville)</t>
+        </is>
+      </c>
+      <c r="H464" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mixed (bulk likely sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I464" s="6" t="inlineStr">
+        <is>
+          <t>Company-wide gas-turbine order backlog reconfirmed at 116 GW at Q2 2026 end, with guidance toward &gt;=125 GW under contract by year-end 2026 (reported July 22, 2026) — a strong demand signal, but no new Greenville-specific headcount figure found this cycle.</t>
+        </is>
+      </c>
+      <c r="J464" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K464" s="6" t="inlineStr">
+        <is>
+          <t>https://www.utilitydive.com/news/ge-vernova-gas-turbine-backlog-climbs-to-116-gw/826039/</t>
+        </is>
+      </c>
+      <c r="L464" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B465" s="6" t="inlineStr">
+        <is>
+          <t>Laurens Co. (Laurens)</t>
+        </is>
+      </c>
+      <c r="C465" s="6" t="inlineStr">
+        <is>
+          <t>Laurens</t>
+        </is>
+      </c>
+      <c r="D465" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E465" s="6" t="inlineStr">
+        <is>
+          <t>Suniva Inc. — solar-cell manufacturing plant (capex reconciled)</t>
+        </is>
+      </c>
+      <c r="F465" s="6" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="G465" s="6" t="inlineStr">
+        <is>
+          <t>~$600M facility-specific (reconciled this cycle; distinct from the separate $835M corporate capital raise)</t>
+        </is>
+      </c>
+      <c r="H465" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred sub-$100k blended</t>
+        </is>
+      </c>
+      <c r="I465" s="6" t="inlineStr">
+        <is>
+          <t>Capex discrepancy flagged last cycle is now reconciled: per SEC/pv-magazine coverage (Sept. 8-9, 2026), the facility-specific investment is ~$600M — up from the original ~$350M SC Governor's-office figure, which is now superseded — distinct from the separately reported $835M corporate capital raise (funding 4.5 GW of new domestic capacity company-wide). Building shell complete; opening still targeted late 2027.</t>
+        </is>
+      </c>
+      <c r="J465" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K465" s="6" t="inlineStr">
+        <is>
+          <t>https://pv-magazine-usa.com/2026/09/09/suniva-raises-835-million-to-drive-4-5-gw-in-new-domestic-cell-capacity/</t>
+        </is>
+      </c>
+      <c r="L465" s="6" t="inlineStr">
+        <is>
+          <t>High (capex now reconciled)</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B466" s="6" t="inlineStr">
+        <is>
+          <t>Piedmont</t>
+        </is>
+      </c>
+      <c r="C466" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D466" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E466" s="6" t="inlineStr">
+        <is>
+          <t>Isuzu North America — truck assembly plant</t>
+        </is>
+      </c>
+      <c r="F466" s="6" t="inlineStr">
+        <is>
+          <t>700+</t>
+        </is>
+      </c>
+      <c r="G466" s="6" t="inlineStr">
+        <is>
+          <t>$280M</t>
+        </is>
+      </c>
+      <c r="H466" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred: assembly $35-56k, engineers $79-108k — blended sub-$100k</t>
+        </is>
+      </c>
+      <c r="I466" s="6" t="inlineStr">
+        <is>
+          <t>No new hiring event found beyond the already-tracked July 8, 2026 direct-hire event; company's stated goal remains 150 employees by end of 2026, 2027 launch still targeted.</t>
+        </is>
+      </c>
+      <c r="J466" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K466" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ccjdigital.com/business/article/15767928/isuzu-building-280m-truck-plant-in-south-carolina-creating-700-jobs</t>
+        </is>
+      </c>
+      <c r="L466" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B467" s="6" t="inlineStr">
+        <is>
+          <t>Ridgeville / Camp Hall</t>
+        </is>
+      </c>
+      <c r="C467" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley</t>
+        </is>
+      </c>
+      <c r="D467" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E467" s="6" t="inlineStr">
+        <is>
+          <t>Redwood Materials — battery-materials recycling campus</t>
+        </is>
+      </c>
+      <c r="F467" s="6" t="inlineStr">
+        <is>
+          <t>1,500 (over the next decade)</t>
+        </is>
+      </c>
+      <c r="G467" s="6" t="inlineStr">
+        <is>
+          <t>$3.5B</t>
+        </is>
+      </c>
+      <c r="H467" s="6" t="inlineStr">
+        <is>
+          <t>$27-75/hr stated (~$56k-156k) — upper tier clears $100k</t>
+        </is>
+      </c>
+      <c r="I467" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone/PR found this cycle. Operations confirmed started Nov. 2025 (pre-window) at ~20,000 metric tons/yr initial capacity; current job postings (ZipRecruiter) show steady, ordinary hiring consistent with an established ramp rather than a new event.</t>
+        </is>
+      </c>
+      <c r="J467" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K467" s="6" t="inlineStr">
+        <is>
+          <t>https://www.redwoodmaterials.com/news/redwood-begins-critical-materials-recovery-in-south-carolina/</t>
+        </is>
+      </c>
+      <c r="L467" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B468" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="C468" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D468" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E468" s="6" t="inlineStr">
+        <is>
+          <t>PSA Airlines — Charlotte headquarters</t>
+        </is>
+      </c>
+      <c r="F468" s="6" t="inlineStr">
+        <is>
+          <t>~400 (450+ total team members at HQ)</t>
+        </is>
+      </c>
+      <c r="G468" s="6" t="inlineStr">
+        <is>
+          <t>Not itemized</t>
+        </is>
+      </c>
+      <c r="H468" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Estimated/Inferred mixed corporate/admin/ops, likely sub-$100k blended)</t>
+        </is>
+      </c>
+      <c r="I468" s="6" t="inlineStr">
+        <is>
+          <t>The "80% of ~250 net-new positions filled" figure is reconfirmed with no fresher update; the math implies ~50 new-hire slots remaining. The previously-flagged "still seeking 170 more employees" figure could not be found in any current source and is now treated as an unsupported legacy carryover — dropped from tracking.</t>
+        </is>
+      </c>
+      <c r="J468" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K468" s="6" t="inlineStr">
+        <is>
+          <t>https://psaairlines.com/psa-airlines-officially-opens-headquarters-in-charlotte-to-over-450-team-members/</t>
+        </is>
+      </c>
+      <c r="L468" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B469" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Steele Creek</t>
+        </is>
+      </c>
+      <c r="C469" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D469" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E469" s="6" t="inlineStr">
+        <is>
+          <t>Maersk — North American HQ (hiring ramp delayed one year)</t>
+        </is>
+      </c>
+      <c r="F469" s="6" t="inlineStr">
+        <is>
+          <t>520 (confirmed, stated)</t>
+        </is>
+      </c>
+      <c r="G469" s="6" t="inlineStr">
+        <is>
+          <t>$16M</t>
+        </is>
+      </c>
+      <c r="H469" s="6" t="inlineStr">
+        <is>
+          <t>$100,962 avg (stated) — clears $100k bar</t>
+        </is>
+      </c>
+      <c r="I469" s="6" t="inlineStr">
+        <is>
+          <t>The NC Economic Investment Committee's approval (Feb. 24, 2026, already tracked) is now understood to reflect a full one-year push of the hiring window, from 2026-2028 to 2027-2029, due to renovation delays at the Arrowpoint Boulevard space. Investment and wage pledges unchanged; no construction-start news found.</t>
+        </is>
+      </c>
+      <c r="J469" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K469" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/maersk-delays-charlotte-headquarters-plan-hiring-520-workers-by-1-year/</t>
+        </is>
+      </c>
+      <c r="L469" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); milestone timing at window edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B470" s="6" t="inlineStr">
+        <is>
+          <t>Salisbury / Granite Industrial Park</t>
+        </is>
+      </c>
+      <c r="C470" s="6" t="inlineStr">
+        <is>
+          <t>Rowan</t>
+        </is>
+      </c>
+      <c r="D470" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E470" s="6" t="inlineStr">
+        <is>
+          <t>Jabil Inc. — advanced manufacturing (AI/data-center hardware)</t>
+        </is>
+      </c>
+      <c r="F470" s="6" t="inlineStr">
+        <is>
+          <t>1,181 (stated, over 5 yr)</t>
+        </is>
+      </c>
+      <c r="G470" s="6" t="inlineStr">
+        <is>
+          <t>~$264M near-term / ~$500M multi-year</t>
+        </is>
+      </c>
+      <c r="H470" s="6" t="inlineStr">
+        <is>
+          <t>$62,034 avg (stated) — sub-$100k</t>
+        </is>
+      </c>
+      <c r="I470" s="6" t="inlineStr">
+        <is>
+          <t>No confirmation found that operations have started; active "Facilities Manager" and similar postings suggest the site remains in pre-operational/construction-readiness phase. The "mid-2026" operational target has effectively lapsed unconfirmed — flagged as at risk of further slippage.</t>
+        </is>
+      </c>
+      <c r="J470" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K470" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/fortune-500-company-eyes-rowan-county-for-264-million-investment-creating-1181-jobs/</t>
+        </is>
+      </c>
+      <c r="L470" s="6" t="inlineStr">
+        <is>
+          <t>Medium (facts High; in-window operational milestone unconfirmed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B471" s="6" t="inlineStr">
+        <is>
+          <t>Morrisville / RTP-adjacent</t>
+        </is>
+      </c>
+      <c r="C471" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D471" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E471" s="6" t="inlineStr">
+        <is>
+          <t>Forge Nano — battery-manufacturing expansion ("America's Battery Gigafactory")</t>
+        </is>
+      </c>
+      <c r="F471" s="6" t="inlineStr">
+        <is>
+          <t>250+ (projected, incremental to an existing 200-job 2023 commitment)</t>
+        </is>
+      </c>
+      <c r="G471" s="6" t="inlineStr">
+        <is>
+          <t>~$300M (incl. $100M DOE non-dilutive funding)</t>
+        </is>
+      </c>
+      <c r="H471" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed for the 2026 expansion</t>
+        </is>
+      </c>
+      <c r="I471" s="6" t="inlineStr">
+        <is>
+          <t>New detail: Samsung SDI made a $20M strategic investment in Forge Nano in July 2026 alongside a conditional cell-procurement agreement beginning 2028, on top of the already-tracked Sept. 17, 2026 Voltaiq (AI battery-software) partnership. Aug. 19, 2026 groundbreaking stands; production still targeted 2028.</t>
+        </is>
+      </c>
+      <c r="J471" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="K471" s="6" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/09/17/3363983/</t>
+        </is>
+      </c>
+      <c r="L471" s="6" t="inlineStr">
+        <is>
+          <t>High (partnerships/dates corroborated); Low (wage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B472" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington / US-421 corridor</t>
+        </is>
+      </c>
+      <c r="C472" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover</t>
+        </is>
+      </c>
+      <c r="D472" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E472" s="6" t="inlineStr">
+        <is>
+          <t>Protocase / 45Drives / ProtoSpace Mfg — precision manufacturing campus</t>
+        </is>
+      </c>
+      <c r="F472" s="6" t="inlineStr">
+        <is>
+          <t>~100 confirmed; company target 500+ total</t>
+        </is>
+      </c>
+      <c r="G472" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H472" s="6" t="inlineStr">
+        <is>
+          <t>$34,840-$41,409 stated for production/assembly roles (sub-$100k); corporate/engineering wage not disclosed</t>
+        </is>
+      </c>
+      <c r="I472" s="6" t="inlineStr">
+        <is>
+          <t>No confirmed updated headcount found this cycle. A search-indexed article title ("45Drives Shifts All Growth to Wilmington: 500-Job Update") could not be fetched/verified and its summary only reiterated the standing 500+ public target — not treated as a confirmed new figure.</t>
+        </is>
+      </c>
+      <c r="J472" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K472" s="6" t="inlineStr">
+        <is>
+          <t>https://www.newmediawire.com/news/the-protocase-companies-and-advanced-glazings-announce-wilmington-nc-career-fair-to-support-rapid-u-s-expansion-7086465</t>
+        </is>
+      </c>
+      <c r="L472" s="6" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B473" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington / US-421 corridor (Wilmington Trade Center)</t>
+        </is>
+      </c>
+      <c r="C473" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover</t>
+        </is>
+      </c>
+      <c r="D473" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E473" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington Trade Center — multi-tenant industrial park expansion</t>
+        </is>
+      </c>
+      <c r="F473" s="6" t="inlineStr">
+        <is>
+          <t>1,500+ (aggregate, long-run park build-out; not a single employer's committed headcount)</t>
+        </is>
+      </c>
+      <c r="G473" s="6" t="inlineStr">
+        <is>
+          <t>$300-400M added tax base (park build-out); ~$3.3M county incentive</t>
+        </is>
+      </c>
+      <c r="H473" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I473" s="6" t="inlineStr">
+        <is>
+          <t>No new leasing/construction milestone found this cycle beyond the already-tracked Jan. 29, 2026 leases (Glass Warehouse, American Tire Distributors) and March 2026 Phase 2 (125-acre) kickoff.</t>
+        </is>
+      </c>
+      <c r="J473" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K473" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wilmingtonbiz.com/real_estate_-_commercial/2026/01/29/wilmington_trade_center_inks_new_leases_as_park_build-out_continues/27187</t>
+        </is>
+      </c>
+      <c r="L473" s="6" t="inlineStr">
+        <is>
+          <t>Medium (aggregate park estimate, not a single-employer commitment)</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B474" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="C474" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D474" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E474" s="6" t="inlineStr">
+        <is>
+          <t>EnerSys — lithium-cell manufacturing facility (scope confirmed via SEC filing; jobs still undisclosed)</t>
+        </is>
+      </c>
+      <c r="F474" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed for the revised project (the pre-restructuring ~500-job 2024 figure must NOT be carried forward)</t>
+        </is>
+      </c>
+      <c r="G474" s="6" t="inlineStr">
+        <is>
+          <t>~$650M gross / ~$500M net (reconciled this cycle); $150M DOE grant + up to $200M state/local incentives</t>
+        </is>
+      </c>
+      <c r="H474" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I474" s="6" t="inlineStr">
+        <is>
+          <t>A July 23, 2026 SEC 8-K confirms the project was rescoped from ~4-5 GWh to up to 1 GWh, refocused on aerospace/defense/FEOC-compliant cells, dropping the prior Verkor technology relationship — this reconciles the previously flagged capex figures. No jobs figure has been disclosed in the 8-K, the 10-Q, or Q2 FY26 earnings-call coverage (Sept. 11, 2026 conference remarks again gave no new jobs number). Construction still targeted H1 of the company's fiscal 2028.</t>
+        </is>
+      </c>
+      <c r="J474" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K474" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/0001289308/000128930826000014/</t>
+        </is>
+      </c>
+      <c r="L474" s="6" t="inlineStr">
+        <is>
+          <t>Medium (restructuring/financing now SEC-confirmed; jobs figure still undisclosed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B475" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington</t>
+        </is>
+      </c>
+      <c r="C475" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover</t>
+        </is>
+      </c>
+      <c r="D475" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E475" s="6" t="inlineStr">
+        <is>
+          <t>GE Hitachi / Global Nuclear Fuel — GNF4 fuel line</t>
+        </is>
+      </c>
+      <c r="F475" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G475" s="6" t="inlineStr">
+        <is>
+          <t>Not itemized</t>
+        </is>
+      </c>
+      <c r="H475" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I475" s="6" t="inlineStr">
+        <is>
+          <t>No update found this cycle; job count for the GNF4 fuel-line program specifically remains undisclosed beyond the company's description of needing "several new positions" in engineering, supply chain, and manufacturing.</t>
+        </is>
+      </c>
+      <c r="J475" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K475" s="6" t="inlineStr">
+        <is>
+          <t>https://www.gevernova.com/news/press-releases/global-nuclear-fuel-introduces-next-generation-fuel-product</t>
+        </is>
+      </c>
+      <c r="L475" s="6" t="inlineStr">
+        <is>
+          <t>Low-Med (indirect signal only, no discrete jobs figure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B476" s="6" t="inlineStr">
+        <is>
+          <t>Burlington / Alamance-Guilford line</t>
+        </is>
+      </c>
+      <c r="C476" s="6" t="inlineStr">
+        <is>
+          <t>Alamance</t>
+        </is>
+      </c>
+      <c r="D476" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E476" s="6" t="inlineStr">
+        <is>
+          <t>Ahold Delhaize USA (Food Lion parent) — distribution center</t>
+        </is>
+      </c>
+      <c r="F476" s="6" t="inlineStr">
+        <is>
+          <t>500-505</t>
+        </is>
+      </c>
+      <c r="G476" s="6" t="inlineStr">
+        <is>
+          <t>$860M</t>
+        </is>
+      </c>
+      <c r="H476" s="6" t="inlineStr">
+        <is>
+          <t>~$60k-$67k avg (Estimated/Inferred, sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I476" s="6" t="inlineStr">
+        <is>
+          <t>Construction confirmed continuing on the $860M, 1M+ sf distribution center (Feb. 16, 2026 groundbreaking, pre-window); a search summary cited a payroll figure that may reflect only an initial/partial-phase hiring tranche rather than full deployment — not treated as a change to the tracked wage estimate. Opening still targeted 2029.</t>
+        </is>
+      </c>
+      <c r="J476" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K476" s="6" t="inlineStr">
+        <is>
+          <t>https://alamancenews.com/officials-on-hand-for-food-lion-distribution-center-groundbreaking/</t>
+        </is>
+      </c>
+      <c r="L476" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B477" s="6" t="inlineStr">
+        <is>
+          <t>Pender / New Hanover</t>
+        </is>
+      </c>
+      <c r="C477" s="6" t="inlineStr">
+        <is>
+          <t>Pender (+New Hanover)</t>
+        </is>
+      </c>
+      <c r="D477" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E477" s="6" t="inlineStr">
+        <is>
+          <t>Amazon — robotics fulfillment center (still not formally confirmed open)</t>
+        </is>
+      </c>
+      <c r="F477" s="6" t="inlineStr">
+        <is>
+          <t>1,000+</t>
+        </is>
+      </c>
+      <c r="G477" s="6" t="inlineStr">
+        <is>
+          <t>$350M</t>
+        </is>
+      </c>
+      <c r="H477" s="6" t="inlineStr">
+        <is>
+          <t>~$22/hr avg (Estimated/Inferred ~$45,760/yr, sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I477" s="6" t="inlineStr">
+        <is>
+          <t>Building shell confirmed complete with landscaping wrapping up and robotics/interior outfitting underway; target language has shifted from "mid-to-late September" (last cycle) to "Fall 2026" more broadly. No ribbon-cutting/grand-opening article found despite a dedicated search — status remains "occupancy imminent, not yet confirmed open." A smaller, separate Pender Commerce Park delivery station (100 FT jobs) is also under construction with no firm completion date.</t>
+        </is>
+      </c>
+      <c r="J477" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K477" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wilmingtonbiz.com/more_news/2026/08/10/amazon_begins_hiring_as_local_facilities_near_completion/27737</t>
+        </is>
+      </c>
+      <c r="L477" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B478" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Ballantyne</t>
+        </is>
+      </c>
+      <c r="C478" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D478" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E478" s="6" t="inlineStr">
+        <is>
+          <t>TD Bank — Ballantyne office expansion</t>
+        </is>
+      </c>
+      <c r="F478" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (an Estimated/Inferred ~430 net-new-seat capacity figure can be calculated from 540 capacity minus ~111 prior seats, but this is capacity headroom, not a confirmed hiring commitment)</t>
+        </is>
+      </c>
+      <c r="G478" s="6" t="inlineStr">
+        <is>
+          <t>Not itemized</t>
+        </is>
+      </c>
+      <c r="H478" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I478" s="6" t="inlineStr">
+        <is>
+          <t>Grand-opening ribbon-cutting reconfirmed as having occurred Sept. 2, 2026 at the Harris Building (91,464 sf, capacity up to 540, houses finance/audit/compliance/regulatory/legal), after ~2 years of construction. No update beyond what was already tracked; TD has still never disclosed a jobs or wage figure.</t>
+        </is>
+      </c>
+      <c r="J478" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K478" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/09/02/td-bank-expansion-ballantyne</t>
+        </is>
+      </c>
+      <c r="L478" s="6" t="inlineStr">
+        <is>
+          <t>Medium (occupancy/capacity confirmed; jobs/wage undisclosed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B479" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / South End</t>
+        </is>
+      </c>
+      <c r="C479" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D479" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E479" s="6" t="inlineStr">
+        <is>
+          <t>Pacific Life Insurance — Queensbridge Collective office (NEW to Watch)</t>
+        </is>
+      </c>
+      <c r="F479" s="6" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="G479" s="6" t="inlineStr">
+        <is>
+          <t>$12.3M</t>
+        </is>
+      </c>
+      <c r="H479" s="6" t="inlineStr">
+        <is>
+          <t>$176,250-$177,584 avg stated (clears $100k easily)</t>
+        </is>
+      </c>
+      <c r="I479" s="6" t="inlineStr">
+        <is>
+          <t>NEW to Watch on wage strength alone: 11-year, 68,000 sq ft lease across 3 floors, full occupancy targeted 2028. Base announcement is dated Oct. 28, 2025 — before the current coverage window — and no in-window milestone (lease execution, hiring start, occupancy) was found this cycle; job count (301) is also below the 500+ Ranked threshold regardless. Flagged: needs a genuinely in-window milestone to remain listed next cycle.</t>
+        </is>
+      </c>
+      <c r="J479" s="6" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="K479" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/pacific-life-adding-301-jobs-in-mecklenburg-average-pay-of-176k/</t>
+        </is>
+      </c>
+      <c r="L479" s="6" t="inlineStr">
+        <is>
+          <t>High (wage/facts); Low (in-window currency)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -47261,7 +52245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H173"/>
+  <dimension ref="A1:H200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -54540,6 +59524,1140 @@
         </is>
       </c>
     </row>
+    <row r="174">
+      <c r="A174" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B174" s="6" t="inlineStr">
+        <is>
+          <t>RXO — Ballantyne HQ expansion</t>
+        </is>
+      </c>
+      <c r="C174" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="D174" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E174" s="6" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="G174" s="6" t="inlineStr">
+        <is>
+          <t>Sub-500 jobs, sub-$100k wage ($89,769), and pre-window; recycled old news.</t>
+        </is>
+      </c>
+      <c r="H174" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B175" s="6" t="inlineStr">
+        <is>
+          <t>HSP US — first US mfg plant</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D175" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E175" s="6" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F175" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G175" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H175" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B176" s="6" t="inlineStr">
+        <is>
+          <t>JGA Space &amp; Defense</t>
+        </is>
+      </c>
+      <c r="C176" s="6" t="inlineStr">
+        <is>
+          <t>Huntersville</t>
+        </is>
+      </c>
+      <c r="D176" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E176" s="6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F176" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G176" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H176" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B177" s="6" t="inlineStr">
+        <is>
+          <t>Odyssey Logistics — global HQ relocation</t>
+        </is>
+      </c>
+      <c r="C177" s="6" t="inlineStr">
+        <is>
+          <t>SW Charlotte</t>
+        </is>
+      </c>
+      <c r="D177" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E177" s="6" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F177" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G177" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H177" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B178" s="6" t="inlineStr">
+        <is>
+          <t>Fit Precast / "Project Willow"</t>
+        </is>
+      </c>
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>Gastonia</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="inlineStr">
+        <is>
+          <t>Gaston</t>
+        </is>
+      </c>
+      <c r="E178" s="6" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G178" s="6" t="inlineStr">
+        <is>
+          <t>Wage ($104,000 avg) clears $100k but job count (125) is below even the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H178" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B179" s="6" t="inlineStr">
+        <is>
+          <t>Kroger fulfillment center / Red Bull-Rauch-Ball "Grounds at Concord" beverage hub</t>
+        </is>
+      </c>
+      <c r="C179" s="6" t="inlineStr">
+        <is>
+          <t>Concord</t>
+        </is>
+      </c>
+      <c r="D179" s="6" t="inlineStr">
+        <is>
+          <t>Cabarrus</t>
+        </is>
+      </c>
+      <c r="E179" s="6" t="inlineStr">
+        <is>
+          <t>~700 / 323 (RRB tranche)</t>
+        </is>
+      </c>
+      <c r="F179" s="6" t="inlineStr">
+        <is>
+          <t>2021-era</t>
+        </is>
+      </c>
+      <c r="G179" s="6" t="inlineStr">
+        <is>
+          <t>Old (2021-era) announcements; a referenced Sept. 9 groundbreaking could not be confirmed as 2026 vs. an earlier year — excluded as recycled/unconfirmed-date old news. RRB tranche wage ($50,387) is sub-$100k regardless.</t>
+        </is>
+      </c>
+      <c r="H179" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B180" s="6" t="inlineStr">
+        <is>
+          <t>Bank of America / Wells Fargo / Truist — AI-driven headcount pressure</t>
+        </is>
+      </c>
+      <c r="C180" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E180" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="F180" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="G180" s="6" t="inlineStr">
+        <is>
+          <t>Negative signal (commentary on AI-driven headcount reduction at the region's largest private employers) — no specific facility closure/layoff number found; noted but not logged as a discrete event.</t>
+        </is>
+      </c>
+      <c r="H180" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B181" s="6" t="inlineStr">
+        <is>
+          <t>Crystal Window &amp; Door Systems</t>
+        </is>
+      </c>
+      <c r="C181" s="6" t="inlineStr">
+        <is>
+          <t>Selma</t>
+        </is>
+      </c>
+      <c r="D181" s="6" t="inlineStr">
+        <is>
+          <t>Johnston (NC)</t>
+        </is>
+      </c>
+      <c r="E181" s="6" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="F181" s="6" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="G181" s="6" t="inlineStr">
+        <is>
+          <t>Average wage $56,061 (well under $100k) and the announcement is recycled 2024 news with no in-window update found.</t>
+        </is>
+      </c>
+      <c r="H181" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B182" s="6" t="inlineStr">
+        <is>
+          <t>Fujifilm Diosynth Biotechnologies expansion</t>
+        </is>
+      </c>
+      <c r="C182" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs</t>
+        </is>
+      </c>
+      <c r="D182" s="6" t="inlineStr">
+        <is>
+          <t>Wake (NC)</t>
+        </is>
+      </c>
+      <c r="E182" s="6" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="F182" s="6" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="G182" s="6" t="inlineStr">
+        <is>
+          <t>Would otherwise qualify (~$109k stated wage) but the announcement and targeted opening ("by end of 2025") both predate the window; no in-window groundbreaking/opening/hiring-ramp milestone found this cycle. Recommend a targeted recheck next cycle.</t>
+        </is>
+      </c>
+      <c r="H182" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
+        <is>
+          <t>Veetee Foods</t>
+        </is>
+      </c>
+      <c r="C183" s="6" t="inlineStr">
+        <is>
+          <t>Selma</t>
+        </is>
+      </c>
+      <c r="D183" s="6" t="inlineStr">
+        <is>
+          <t>Johnston (NC)</t>
+        </is>
+      </c>
+      <c r="E183" s="6" t="inlineStr">
+        <is>
+          <t>~200</t>
+        </is>
+      </c>
+      <c r="F183" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G183" s="6" t="inlineStr">
+        <is>
+          <t>At the very edge of the Watch job floor; wage not disclosed and food-mfg roles are typically sub-$100k — excluded pending wage confirmation.</t>
+        </is>
+      </c>
+      <c r="H183" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B184" s="6" t="inlineStr">
+        <is>
+          <t>Wake County incentive-policy overhaul</t>
+        </is>
+      </c>
+      <c r="C184" s="6" t="inlineStr">
+        <is>
+          <t>Wake Co.</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E184" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F184" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G184" s="6" t="inlineStr">
+        <is>
+          <t>Informational policy discussion (adjusted wage thresholds, new incentive tiers), not a company-specific deal.</t>
+        </is>
+      </c>
+      <c r="H184" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B185" s="6" t="inlineStr">
+        <is>
+          <t>Aspida Financial Services — HQ expansion (rechecked; remains removed)</t>
+        </is>
+      </c>
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="D185" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E185" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (removed from Ranked 2026-09-21)</t>
+        </is>
+      </c>
+      <c r="F185" s="6" t="inlineStr">
+        <is>
+          <t>2025-11/12</t>
+        </is>
+      </c>
+      <c r="G185" s="6" t="inlineStr">
+        <is>
+          <t>Rechecked this cycle: still no dated confirmation that the Imperial Tower renovation has completed or that move-in has occurred; all sources continue to use forward-looking "expected Q4 2026" language seen for 3+ consecutive cycles. Remains excluded/removed pending a hard, dated milestone.</t>
+        </is>
+      </c>
+      <c r="H185" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/imperial-tower-roars-back-as-10-million-durham-revival/</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
+        <is>
+          <t>Wells Fargo — West End Center closure</t>
+        </is>
+      </c>
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>Winston-Salem</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr">
+        <is>
+          <t>Forsyth (NC)</t>
+        </is>
+      </c>
+      <c r="E186" s="6" t="inlineStr">
+        <is>
+          <t>194 (layoffs)</t>
+        </is>
+      </c>
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G186" s="6" t="inlineStr">
+        <is>
+          <t>Negative signal: office closure completed, part of Wells Fargo's nationwide facility-reduction plan.</t>
+        </is>
+      </c>
+      <c r="H186" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/wells-fargo-closing-winston-salem-office-eliminating-194-jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B187" s="6" t="inlineStr">
+        <is>
+          <t>FedEx — Greensboro shipping center closure</t>
+        </is>
+      </c>
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="inlineStr">
+        <is>
+          <t>Guilford (NC)</t>
+        </is>
+      </c>
+      <c r="E187" s="6" t="inlineStr">
+        <is>
+          <t>164 (layoffs)</t>
+        </is>
+      </c>
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G187" s="6" t="inlineStr">
+        <is>
+          <t>Negative signal: closure effective in-window, part of FedEx's "Network 2.0" restructuring.</t>
+        </is>
+      </c>
+      <c r="H187" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/fedex-closing-greensboro-facility-some-of-164-workers-will-be-offered-other-jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
+        <is>
+          <t>Alamance Foods</t>
+        </is>
+      </c>
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>Burlington</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
+        <is>
+          <t>Alamance (NC)</t>
+        </is>
+      </c>
+      <c r="E188" s="6" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G188" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch floor; wage not disclosed, likely food-mfg-tier.</t>
+        </is>
+      </c>
+      <c r="H188" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B189" s="6" t="inlineStr">
+        <is>
+          <t>Hoffman &amp; Hoffman</t>
+        </is>
+      </c>
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro</t>
+        </is>
+      </c>
+      <c r="D189" s="6" t="inlineStr">
+        <is>
+          <t>Guilford (NC)</t>
+        </is>
+      </c>
+      <c r="E189" s="6" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G189" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H189" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B190" s="6" t="inlineStr">
+        <is>
+          <t>Southeastern Container</t>
+        </is>
+      </c>
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>Buncombe</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E190" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G190" s="6" t="inlineStr">
+        <is>
+          <t>Far below the job threshold ($31M modernization investment).</t>
+        </is>
+      </c>
+      <c r="H190" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B191" s="6" t="inlineStr">
+        <is>
+          <t>Fortified Solar</t>
+        </is>
+      </c>
+      <c r="C191" s="6" t="inlineStr">
+        <is>
+          <t>Greenville Co.</t>
+        </is>
+      </c>
+      <c r="D191" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E191" s="6" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="F191" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G191" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H191" s="6" t="inlineStr">
+        <is>
+          <t>https://www.foxcarolina.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B192" s="6" t="inlineStr">
+        <is>
+          <t>United Composite Materials LLC</t>
+        </is>
+      </c>
+      <c r="C192" s="6" t="inlineStr">
+        <is>
+          <t>Greer / Greenville Co.</t>
+        </is>
+      </c>
+      <c r="D192" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E192" s="6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G192" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H192" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B193" s="6" t="inlineStr">
+        <is>
+          <t>ZF Chassis Systems</t>
+        </is>
+      </c>
+      <c r="C193" s="6" t="inlineStr">
+        <is>
+          <t>Duncan / Spartanburg Co.</t>
+        </is>
+      </c>
+      <c r="D193" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E193" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G193" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H193" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B194" s="6" t="inlineStr">
+        <is>
+          <t>BMW Spartanburg press-shop expansion / Magna International Greenville expansion</t>
+        </is>
+      </c>
+      <c r="C194" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg &amp; Greenville Co.</t>
+        </is>
+      </c>
+      <c r="D194" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E194" s="6" t="inlineStr">
+        <is>
+          <t>200 / 200</t>
+        </is>
+      </c>
+      <c r="F194" s="6" t="inlineStr">
+        <is>
+          <t>2022 / 2024-12</t>
+        </is>
+      </c>
+      <c r="G194" s="6" t="inlineStr">
+        <is>
+          <t>Both recycled old news (2022 and Dec. 2024 respectively) mis-surfaced by search under 2026 dating; not in-window.</t>
+        </is>
+      </c>
+      <c r="H194" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B195" s="6" t="inlineStr">
+        <is>
+          <t>Univar Solutions USA — Greer facility layoff</t>
+        </is>
+      </c>
+      <c r="C195" s="6" t="inlineStr">
+        <is>
+          <t>Greer / Spartanburg Co.</t>
+        </is>
+      </c>
+      <c r="D195" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E195" s="6" t="inlineStr">
+        <is>
+          <t>99 (layoffs)</t>
+        </is>
+      </c>
+      <c r="F195" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="G195" s="6" t="inlineStr">
+        <is>
+          <t>Negative signal (SC DEW WARN report): permanent layoff tied to loss of a BMW onsite waste-management contract.</t>
+        </is>
+      </c>
+      <c r="H195" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B196" s="6" t="inlineStr">
+        <is>
+          <t>Saddle Creek Logistics Services — Duncan closure</t>
+        </is>
+      </c>
+      <c r="C196" s="6" t="inlineStr">
+        <is>
+          <t>Duncan / Spartanburg Co.</t>
+        </is>
+      </c>
+      <c r="D196" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E196" s="6" t="inlineStr">
+        <is>
+          <t>130 (layoffs)</t>
+        </is>
+      </c>
+      <c r="F196" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G196" s="6" t="inlineStr">
+        <is>
+          <t>Negative signal (SC DEW WARN report, filed 2026-01-02): permanent closure/layoff.</t>
+        </is>
+      </c>
+      <c r="H196" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B197" s="6" t="inlineStr">
+        <is>
+          <t>Sub-200-job items (SC Midlands/Lowcountry)</t>
+        </is>
+      </c>
+      <c r="C197" s="6" t="inlineStr">
+        <is>
+          <t>Charleston/Lexington/Berkeley/Dorchester</t>
+        </is>
+      </c>
+      <c r="D197" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E197" s="6" t="inlineStr">
+        <is>
+          <t>Each &lt;=170</t>
+        </is>
+      </c>
+      <c r="F197" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G197" s="6" t="inlineStr">
+        <is>
+          <t>IEB Americas (30j), Red Metals (45j), Prysmian Lexington (~135j), WiJo Pouches (170j), ALLTAPE Adhesive (130j), Techo-Bloc (46j), Century Aluminum Mt. Holly expansion (150j, hiring began Sept. 2026), Eastover Chips/AVANTech/Stobich (each &lt;70j) — all below the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H197" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B198" s="6" t="inlineStr">
+        <is>
+          <t>The Nuclear Company — Columbia engineering/construction office</t>
+        </is>
+      </c>
+      <c r="C198" s="6" t="inlineStr">
+        <is>
+          <t>Richland Co.</t>
+        </is>
+      </c>
+      <c r="D198" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E198" s="6" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="F198" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G198" s="6" t="inlineStr">
+        <is>
+          <t>Likely high-wage but headcount currently too small for Watch; worth a future look if headcount grows.</t>
+        </is>
+      </c>
+      <c r="H198" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B199" s="6" t="inlineStr">
+        <is>
+          <t>TD Bank "200 jobs in Lexington" (recycled)</t>
+        </is>
+      </c>
+      <c r="C199" s="6" t="inlineStr">
+        <is>
+          <t>Lexington Co.</t>
+        </is>
+      </c>
+      <c r="D199" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E199" s="6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F199" s="6" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="G199" s="6" t="inlineStr">
+        <is>
+          <t>Figure traces to a 2011 announcement (part of a historic 1,600-job statewide pledge), not an in-window 2026 event.</t>
+        </is>
+      </c>
+      <c r="H199" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B200" s="6" t="inlineStr">
+        <is>
+          <t>SC State Fair seasonal hiring</t>
+        </is>
+      </c>
+      <c r="C200" s="6" t="inlineStr">
+        <is>
+          <t>Columbia</t>
+        </is>
+      </c>
+      <c r="D200" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E200" s="6" t="inlineStr">
+        <is>
+          <t>~500 (seasonal)</t>
+        </is>
+      </c>
+      <c r="F200" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G200" s="6" t="inlineStr">
+        <is>
+          <t>Seasonal/temporary hiring, not a corporate expansion and not $100k-tier.</t>
+        </is>
+      </c>
+      <c r="H200" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -54551,7 +60669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E116"/>
+  <dimension ref="A1:E125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -57693,6 +63811,249 @@
         </is>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>Fox Carolina — Spartanburg moratorium final vote</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>https://www.foxcarolina.com/2026/09/22/spartanburg-county-council-passes-data-center-moratorium-with-several-amendments/</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg Co. SC</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>NorthMark/Valara moratorium 5-1 vote outcome and grandfathering</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>SC Daily Gazette — SC PSC Valara ruling</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/2026/08/27/spartanburg-data-center-not-subject-to-public-power-plant-rules-sc-regulators-rule/</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg Co. SC</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>SC Public Service Commission Aug. 27, 2026 utility-siting-jurisdiction ruling</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>WRAL — WakeMed/Atrium vote outcome</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/wake-commissioners-schedule-vote-pave-way-wakemed-atrium-merger-september-2026/</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>Wake Co. NC</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>Wake County Board of Commissioners 5-2 merger-approval vote (Sept. 21, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>SEC EDGAR — IB Acquisition Corp. / EnerSys filings</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>primary_filing</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>GNQ Insilico/IBAC second SPAC extension proxy; EnerSys 8-K project-restructuring confirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>WIS-TV — Shives lawsuit follow-up</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wistv.com/2026/08/25/blythewood-residents-respond-scout-motors-development/</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>Richland Co. SC</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors Shives-family blasting-damage lawsuit detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>WUNC — AWS Hamlet air-permit approval</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wunc.org/2026-08-29/amazons-richmond-county-data-center-gets-green-light-on-air-quality-permits</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>Richmond Co. NC</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>NC DAQ final air-quality permit approval for AWS/Amazon Hamlet</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>WIS-TV — Ferrara Candy groundbreaking</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wistv.com/2026/05/19/ferrara-candy-company-breaks-ground-orangeburg/</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>Orangeburg Co. SC</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>Ferrara Candy Orangeburg groundbreaking confirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>pv magazine USA — Suniva capex reconciliation</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>trade_journal</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>https://pv-magazine-usa.com/2026/09/09/suniva-raises-835-million-to-drive-4-5-gw-in-new-domestic-cell-capacity/</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>Laurens Co. SC</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>Suniva facility-specific capex reconciled to ~$600M</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>Axios Charlotte — TD Bank / Pacific Life</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg Co. NC</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>TD Bank Ballantyne grand opening; Pacific Life South End lease</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -57704,7 +64065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D105"/>
+  <dimension ref="A1:D115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -59740,6 +66101,206 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; tenth consecutive cycle without a new lease milestone — October 2026 move-in target reconfirmed but not yet realized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma (Rock Hill)</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; fourth consecutive cycle with no fresher dated milestone despite a dedicated recheck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie (Durham)</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new groundbreaking or hiring milestone found this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV plant (Blythewood)</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>Held flat; the Shives lawsuit gained reporting detail and an unconfirmed report suggests a longer Terra-pickup delay (Scout disputes), but neither changes job/wage/capex facts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>Genentech (Holly Springs)</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>JetZero (Greensboro)</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; NC3 construction, the JDIG hiring-delay amendment, and the EXIM LOI remain the latest confirmed facts — no new dated progress found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; active job postings confirm ongoing hiring but no discrete headcount/occupancy milestone found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — Global HQ (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; franchise-dealer litigation footprint widened to ~7 states (risk factor, not scored) but no permit/construction progress found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>Citigroup (Charlotte / Ballantyne)</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no headcount-progress update found dated after April 2026 despite a dedicated recheck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>Novartis (Durham/Morrisville)</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/Carolinas_Job_Growth_Running_Database.xlsx
+++ b/reports/Carolinas_Job_Growth_Running_Database.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Week of 2026-09-28  ·  Window 2026-03-28 to 2026-09-28  ·  NC + SC</t>
+          <t>Week of 2026-10-05  ·  Window 2026-04-05 to 2026-10-05  ·  NC + SC</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28  (Week 11)</t>
+          <t>2026-10-05  (Week 12)</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-03-28 to 2026-09-28  (trailing 6 months)</t>
+          <t>2026-04-05 to 2026-10-05  (trailing 6 months)</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>114</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Charlotte / Uptown (Mecklenburg, NC) — SMBC Group, score 94 (unchanged) — tenth consecutive cycle without a new lease milestone; October 2026 move-in target reconfirmed but not yet realized.</t>
+          <t>Charlotte / Uptown (Mecklenburg, NC) — SMBC Group, score 94 (unchanged) — eleventh consecutive cycle without a confirmed physical move-in; October 2026 move-in target reconfirmed but not yet realized.</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>No Ranked-tier score changed this cycle — the first cycle with zero Ranked-tier score movement since early in the report's run. Scout Motors (Blythewood) and Scout Motors HQ (Charlotte) both picked up new risk-factor detail (a fuller account of the Shives-family blasting-damage lawsuit plus an unconfirmed report of a longer Terra-pickup delay; a franchise-dealer lawsuit footprint now spanning ~7 states) without changing their scores. The most consequential news of the cycle was procedural/regulatory rather than score-moving: the WakeMed/Atrium Health merger was approved 5-2 by Wake County commissioners (moving to FTC/DOJ review) and the Spartanburg data-center moratorium passed 5-1 while explicitly grandfathering the NorthMark/Valara project, alongside a second developer-favorable SC PSC ruling.</t>
+          <t>Capital Group (Charlotte), raised 81-&gt;86 — the East Coast operations hub officially opened Sept. 29, 2026 (Gov. Stein attending) and the company raised its stated Charlotte job target from 600 to up to 1,000, a 67% increase, while reconfirming its very high $194,141 average wage. This is the first Ranked-tier score movement in three cycles.</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>A fourth consecutive quiet cycle for brand-new Ranked-tier finds and, for the first time in the report's run, zero Ranked-tier score changes — but an unusually consequential cycle for Watch-tier resolution. Two of the report's longest-running open threads resolved this cycle, both favorably for the tracked projects: the Wake County Board of Commissioners approved the WakeMed/Atrium Health merger 5-2 (now moving to FTC/DOJ review), and Spartanburg County Council passed its data-center moratorium 5-1 while explicitly grandfathering the NorthMark/Valara 'Project Moc-1' data center — compounded by a second developer-favorable ruling (the SC Public Service Commission's Aug. 27 finding that Valara's on-site gas plant is not subject to utility-siting review). Elsewhere, GNQ Insilico's SPAC deal did NOT close by its Sept. 28 deadline as previously flagged — IB Acquisition Corp. is seeking a second extension to March 2027, confirming the Greenville deal remains unresolved. Boom Supersonic (Greensboro) remains the region's most urgent unresolved risk: no headcount evidence was found despite a second dedicated search, with its Dec. 31, 2026 500-employee lease-termination deadline now roughly 3 months out. Amazon's Pender/New Hanover fulfillment center still has not been confirmed open despite a completed building shell. Ferrara Candy (Orangeburg, SC) broke ground in-window (May 2026) and AWS/Amazon's Hamlet, NC data center cleared a key air-quality-permit hurdle (Aug. 29, 2026) — both incremental de-risking events for carryover Watch items outside the five core regions.</t>
+          <t>The quiet multi-cycle stretch for brand-new Ranked-tier finds continues — no new 500+ job/$100k+ wage company announcement was found in-window across all five regional research passes — but Capital Group's officially-opened hub and raised job target broke the recent zero-movement streak. Elsewhere, two large negative/troubled signals surfaced this cycle: Apple told NC officials it wants to delay its RTP campus extension by up to 4 additional years (on top of an already-stalled ramp), and VinFast's Chatham County EV megasite — originally pledging up to 7,500 jobs — had its $400M county incentive agreement terminated (7/31/26) after the State of NC sued to regain site control (5/21/26); VinFast says it will resume construction before year-end with production now targeted 2028. On the positive side, Daimler Truck Financial Services opened a new 276-job, $133,940-avg-wage North American HQ in Ballantyne the same week as Capital Group; GNQ Insilico's SPAC stockholders formally approved a second extension (to 3/28/27), Suniva completed its $835M capital raise to quadruple its Laurens, SC capacity, and Amazon began active hiring at its Pender/New Hanover robotics fulfillment center ahead of a reaffirmed holiday-season 2026 opening. Pacific Life Insurance was removed from Watch after a second consecutive cycle with no in-window milestone.</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Trailing 6 months now runs 2026-03-28 to 2026-09-28 — the window advanced one week. Citigroup's April 23, 2026 anchor milestone and Scout Motors HQ's March 28, 2026 filing date both remain comfortably inside the new window; no Ranked entry's sole milestone aged out this cycle.</t>
+          <t>Trailing 6 months now runs 2026-04-05 to 2026-10-05 — the window advanced one week. No Ranked entry's sole milestone aged out this cycle; all ten entries' anchor dates remain comfortably inside the new window.</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Two long-flagged data gaps were resolved this cycle: the Wake County EDGE6-vs-EDGE7 pipeline-figure discrepancy (EDGE7's current pipeline remains 52 projects/$11B+/~11,000 jobs; the ~$5.6B/~10,800-job figure belongs to the completed prior cycle) and Suniva's capex discrepancy (facility-specific investment reconciled to ~$600M via SEC/pv-magazine coverage, distinct from the separate $835M corporate capital raise). EnerSys's restructured Greenville project scope was also confirmed via a primary SEC 8-K (rescoped to up to 1 GWh, ~$650M gross/~$500M net) though its jobs figure remains undisclosed. AIRSYS's capex now shows a new discrepancy ($40M originally tracked vs. $60M in several 2026 secondary sources) flagged for reconciliation next cycle.</t>
+          <t>Octapharma's job-count split shows an unresolved discrepancy this cycle: the originally tracked '1,200 new + 300 relocated' (1,500 total) vs. a 2026-07 secondary source's '564 HQ / 688 mfg' (1,252 total) — the original figure is held pending reconciliation against the primary SC Commerce release. AIRSYS's long-flagged $40M-vs-$60M capex discrepancy was resolved this cycle: $40M is confirmed correct, with the $60M figure traced to a conflation with Spartanburg County's (not AIRSYS's) full-year 2025 investment total.</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>All 10 Ranked entries repeated this cycle with no score changes — a fourth consecutive quiet cycle for brand-new Ranked-tier finds and the first cycle with zero Ranked-tier score movement. Aspida Financial Services was rechecked and remains excluded/removed (still no dated confirmation of its expected Q4 2026 move-in). Watch tier: 1 new item added (Pacific Life Insurance, Charlotte/South End — high wage but pre-window base announcement), 0 items removed, all 46 carried-forward items rechecked with updates ranging from major (WakeMed/Atrium merger approved; Spartanburg moratorium resolved in the developer's favor) to minor (source/detail corrections). New Excluded/Noise entries include two new negative signals (Wells Fargo Winston-Salem office closure, 194 jobs; FedEx Greensboro facility closure, 164 jobs) and roughly two dozen sub-threshold or recycled items.</t>
+          <t>9 of 10 Ranked entries repeated at their existing score; Capital Group (Charlotte) was raised 81-&gt;86 on an officially-opened hub and a raised job target (600-&gt;1,000). Watch tier: 4 new items added (Daimler Truck Financial Services, Charlotte/Ballantyne — 276 jobs, $133,940 avg wage; VinFast Chatham County EV megasite, flagged AT RISK after its incentive deal was terminated; Adeptus USA, Anderson Co., SC — 217 jobs; Morinaga America Foods, Mebane, NC — 204 jobs/ribbon-cutting), 1 item removed (Pacific Life Insurance — no in-window milestone for a second consecutive cycle), and the remaining 46 carried-forward items were rechecked with updates ranging from major (GNQ Insilico extension formally approved; Suniva's $835M capital raise completed; Apple's RTP delay of up to 4 years; AWS/Amazon Hamlet community air-quality pushback) to minor (source/detail reconciliations). New Excluded/Noise entries include several negative signals (RTI International, Pendo, Wells Fargo Raleigh, and FedEx Durham/Raleigh layoffs; two NC incentive-grant terminations at Xerox and PennyMac in Cary) and roughly three dozen sub-threshold or recycled items.</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S105"/>
+  <dimension ref="A1:S115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10282,6 +10282,916 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Uptown</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group — 2nd US HQ / bank operations</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>Office / HQ banking</t>
+        </is>
+      </c>
+      <c r="J106" s="6" t="inlineStr">
+        <is>
+          <t>$165,316 avg (stated; vs county $90,706)</t>
+        </is>
+      </c>
+      <c r="K106" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L106" s="6" t="inlineStr">
+        <is>
+          <t>$50.5M</t>
+        </is>
+      </c>
+      <c r="M106" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $70.0M / 12 yr; $23.3M IDF-Utility Account</t>
+        </is>
+      </c>
+      <c r="N106" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle; move-in still pending</t>
+        </is>
+      </c>
+      <c r="O106" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="P106" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bankingdive.com/news/smbc-revs-up-recruiting-charlotte-banking-talent-tech-cyber-data-jobs/830268/</t>
+        </is>
+      </c>
+      <c r="Q106" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R106" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="S106" s="6" t="inlineStr">
+        <is>
+          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C107" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill / York Co.</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus</t>
+        </is>
+      </c>
+      <c r="H107" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>Office/HQ + biopharma mfg</t>
+        </is>
+      </c>
+      <c r="J107" s="6" t="inlineStr">
+        <is>
+          <t>$141,502 avg HQ / $102,752 avg mfg (both stated)</t>
+        </is>
+      </c>
+      <c r="K107" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L107" s="6" t="inlineStr">
+        <is>
+          <t>$1.5B</t>
+        </is>
+      </c>
+      <c r="M107" s="6" t="inlineStr">
+        <is>
+          <t>Fee-in-lieu-of-tax; $65M SC Coordinating Council Closing Fund grant to York Co.</t>
+        </is>
+      </c>
+      <c r="N107" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone (unchanged)</t>
+        </is>
+      </c>
+      <c r="O107" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="P107" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/york-county/news/octapharma-how-company-chose-rock-hill/article_b1518265-129d-4134-9ff9-f2d686950bd6.html</t>
+        </is>
+      </c>
+      <c r="Q107" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R107" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S107" s="6" t="inlineStr">
+        <is>
+          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C108" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>Durham / RTP</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie — biopharma manufacturing campus</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="n">
+        <v>734</v>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / R&amp;D / lab</t>
+        </is>
+      </c>
+      <c r="J108" s="6" t="inlineStr">
+        <is>
+          <t>$118,041 avg (stated; vs county $102,817)</t>
+        </is>
+      </c>
+      <c r="K108" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L108" s="6" t="inlineStr">
+        <is>
+          <t>$1.4B</t>
+        </is>
+      </c>
+      <c r="M108" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $19.3M / 12 yr; $6.4M IDF-Utility; Durham Co. performance-based award not-to-exceed $15,450,000 ("Project Glass"); Durham City Council companion incentive item (taken up 2026-09-17) brings combined city+county local incentive to ~$24.8M</t>
+        </is>
+      </c>
+      <c r="N108" s="6" t="inlineStr">
+        <is>
+          <t>No new physical-groundbreaking milestone this cycle</t>
+        </is>
+      </c>
+      <c r="O108" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="P108" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/abbvie-pledges-1-3-billion-investment-734-jobs-in-durham/</t>
+        </is>
+      </c>
+      <c r="Q108" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R108" s="6" t="inlineStr">
+        <is>
+          <t>Suburban-urban</t>
+        </is>
+      </c>
+      <c r="S108" s="6" t="inlineStr">
+        <is>
+          <t>High-end MF + move-up for-sale around Durham/RTP; spillover Wake/Orange. Construction-phase rental near-term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C109" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group — East Coast ops hub (officially opened; job target raised to 1,000)</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>Office — finance/tech</t>
+        </is>
+      </c>
+      <c r="J109" s="6" t="inlineStr">
+        <is>
+          <t>$194,141 avg (stated; NC Commerce JDIG figure)</t>
+        </is>
+      </c>
+      <c r="K109" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L109" s="6" t="inlineStr">
+        <is>
+          <t>$60M</t>
+        </is>
+      </c>
+      <c r="M109" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $17.2M / 12 yr; $5.7M IDF-Utility; $19.4M state grant/12yr + $2.2M training funds + $1M local</t>
+        </is>
+      </c>
+      <c r="N109" s="6" t="inlineStr">
+        <is>
+          <t>Facility grand opening (ribbon-cutting); stated job target raised from 600 to up to 1,000</t>
+        </is>
+      </c>
+      <c r="O109" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="P109" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/capital-group-raises-charlotte-job-target-to-1000/</t>
+        </is>
+      </c>
+      <c r="Q109" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R109" s="6" t="inlineStr">
+        <is>
+          <t>Urban-suburban</t>
+        </is>
+      </c>
+      <c r="S109" s="6" t="inlineStr">
+        <is>
+          <t>High-skill eng/data workforce -&gt; walkable South End/Uptown &amp; inner-suburban Class-A and for-sale TH; the raised 1,000-job target and very high ($194k) average wage strengthen this as one of the region's top premium-housing demand drivers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C110" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>Blythewood / N. Columbia</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV assembly plant + Supplier Park</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>Auto mfg + salaried eng.</t>
+        </is>
+      </c>
+      <c r="J110" s="6" t="inlineStr">
+        <is>
+          <t>$30-$37.50/hr line (stated); salaried higher</t>
+        </is>
+      </c>
+      <c r="K110" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mix supports above-median HH income</t>
+        </is>
+      </c>
+      <c r="L110" s="6" t="inlineStr">
+        <is>
+          <t>$2.3B+ (site $2.0B + $25M training center + $300M Supplier Park)</t>
+        </is>
+      </c>
+      <c r="M110" s="6" t="inlineStr">
+        <is>
+          <t>State/local package (2023); $25M readySC; $150M cost-overrun payment cleared by Aug. 17 veto (still not confirmed disbursed); Legislative Audit Council/Inspector General joint review's scope now better documented (site-selection prudence, due-diligence adequacy, pre-permit construction risk, recoverability) — still due ~mid-Dec. 2026</t>
+        </is>
+      </c>
+      <c r="N110" s="6" t="inlineStr">
+        <is>
+          <t>No new headcount, lawsuit-ruling, or production-timeline change found this cycle</t>
+        </is>
+      </c>
+      <c r="O110" s="6" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="P110" s="6" t="inlineStr">
+        <is>
+          <t>https://blog.scoutmotors.com/september-2026-scout-motors-production-center-update/</t>
+        </is>
+      </c>
+      <c r="Q110" s="6" t="inlineStr">
+        <is>
+          <t>Medium (facts); Low (headcount/timeline)</t>
+        </is>
+      </c>
+      <c r="R110" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S110" s="6" t="inlineStr">
+        <is>
+          <t>Bifurcated: salaried/professional -&gt; higher-income for-sale &amp; Class-A; hourly base + supplier-park jobs -&gt; workforce/missing-middle rental in N. Richland/Fairfield.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C111" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs / SW Wake</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>Genentech — biomanufacturing expansion (unchanged)</t>
+        </is>
+      </c>
+      <c r="H111" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="J111" s="6" t="inlineStr">
+        <is>
+          <t>~$119,833 avg (stated, 2025 tranche)</t>
+        </is>
+      </c>
+      <c r="K111" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L111" s="6" t="inlineStr">
+        <is>
+          <t>~$2.0B</t>
+        </is>
+      </c>
+      <c r="M111" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
+        </is>
+      </c>
+      <c r="N111" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="O111" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="P111" s="6" t="inlineStr">
+        <is>
+          <t>https://www.biospace.com/press-releases/genentech-marks-topping-out-milestone-for-new-holly-springs-north-carolina-manufacturing-facility</t>
+        </is>
+      </c>
+      <c r="Q111" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R111" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S111" s="6" t="inlineStr">
+        <is>
+          <t>Strong higher-income for-sale + Class-A rental demand in fast-growing SW Wake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C112" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>JetZero — aerospace plant ($100M lender loan secured)</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace mfg + eng.</t>
+        </is>
+      </c>
+      <c r="J112" s="6" t="inlineStr">
+        <is>
+          <t>$89,340 avg (stated, 2025)</t>
+        </is>
+      </c>
+      <c r="K112" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated (2025)</t>
+        </is>
+      </c>
+      <c r="L112" s="6" t="inlineStr">
+        <is>
+          <t>$4.7B</t>
+        </is>
+      </c>
+      <c r="M112" s="6" t="inlineStr">
+        <is>
+          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr; $133.9M NC FY26-27 budget funding; new $100M lender loan (Sept. 2026, separate from state/federal incentives)</t>
+        </is>
+      </c>
+      <c r="N112" s="6" t="inlineStr">
+        <is>
+          <t>$100M loan secured from a lender group to fund technology-maturation acceleration</t>
+        </is>
+      </c>
+      <c r="O112" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P112" s="6" t="inlineStr">
+        <is>
+          <t>https://www.flightglobal.com/aerospace/2026/09/jetzero-secures-100m-loan-to-fund-development-push/</t>
+        </is>
+      </c>
+      <c r="Q112" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Medium (hiring-ramp timeline)</t>
+        </is>
+      </c>
+      <c r="R112" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S112" s="6" t="inlineStr">
+        <is>
+          <t>Same long-run scale; mass hiring is confirmed pushed to 2028, not yet underway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C113" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Plaza Midwood</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — Global HQ (litigation footprint unchanged this cycle)</t>
+        </is>
+      </c>
+      <c r="H113" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>Corporate HQ / professional</t>
+        </is>
+      </c>
+      <c r="J113" s="6" t="inlineStr">
+        <is>
+          <t>$153,978 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K113" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L113" s="6" t="inlineStr">
+        <is>
+          <t>$206.9M</t>
+        </is>
+      </c>
+      <c r="M113" s="6" t="inlineStr">
+        <is>
+          <t>Original 2025-11-12 HQ incentive/relocation commitment</t>
+        </is>
+      </c>
+      <c r="N113" s="6" t="inlineStr">
+        <is>
+          <t>No permit/construction progress found; litigation footprint reconfirmed, not expanded</t>
+        </is>
+      </c>
+      <c r="O113" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="P113" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/scout-motors-hq-move-turbocharges-second-office-building-in-plaza-midwood/</t>
+        </is>
+      </c>
+      <c r="Q113" s="6" t="inlineStr">
+        <is>
+          <t>Med (facts High; milestone stage early)</t>
+        </is>
+      </c>
+      <c r="R113" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="S113" s="6" t="inlineStr">
+        <is>
+          <t>Supports Plaza Midwood/NoDa/Elizabeth close-in rental and townhome demand from a young, high-wage corporate workforce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C114" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Ballantyne</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>Citigroup — Charlotte office (hiring ramp proceeding)</t>
+        </is>
+      </c>
+      <c r="H114" s="6" t="n">
+        <v>510</v>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>Office / financial services</t>
+        </is>
+      </c>
+      <c r="J114" s="6" t="inlineStr">
+        <is>
+          <t>$131,832 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K114" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L114" s="6" t="inlineStr">
+        <is>
+          <t>$16.1M</t>
+        </is>
+      </c>
+      <c r="M114" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $8.9M / 10 yr</t>
+        </is>
+      </c>
+      <c r="N114" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="O114" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="P114" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wfae.org/business/2026-04-23/charlottes-banking-jobs-hot-streak-continues</t>
+        </is>
+      </c>
+      <c r="Q114" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R114" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S114" s="6" t="inlineStr">
+        <is>
+          <t>$131,832 stated wage clears the $100k bar; supports Class-A rental and for-sale townhome demand in south Mecklenburg's Ballantyne/Blakeney/Rea Farms corridor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C115" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>Durham / Morrisville</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>Durham &amp; Wake</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>Novartis — API mfg building (unchanged)</t>
+        </is>
+      </c>
+      <c r="H115" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="J115" s="6" t="inlineStr">
+        <is>
+          <t>$111,161 avg (stated)</t>
+        </is>
+      </c>
+      <c r="K115" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="L115" s="6" t="inlineStr">
+        <is>
+          <t>~$991M (incl. $220M API building)</t>
+        </is>
+      </c>
+      <c r="M115" s="6" t="inlineStr">
+        <is>
+          <t>Part of original $771M package incentives; $7.6M NC cash-incentive component newly confirmed</t>
+        </is>
+      </c>
+      <c r="N115" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="O115" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="P115" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
+        </is>
+      </c>
+      <c r="Q115" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R115" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="S115" s="6" t="inlineStr">
+        <is>
+          <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10293,7 +11203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X105"/>
+  <dimension ref="A1:X115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22508,6 +23418,1166 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Uptown</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group — 2nd US HQ / bank operations</t>
+        </is>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>Banking / financial services</t>
+        </is>
+      </c>
+      <c r="J106" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle; move-in still pending</t>
+        </is>
+      </c>
+      <c r="K106" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L106" s="6" t="inlineStr">
+        <is>
+          <t>Projected (6 yr)</t>
+        </is>
+      </c>
+      <c r="M106" s="6" t="inlineStr">
+        <is>
+          <t>$165,316 avg (stated; vs county $90,706)</t>
+        </is>
+      </c>
+      <c r="N106" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O106" s="6" t="inlineStr">
+        <is>
+          <t>$50.5M</t>
+        </is>
+      </c>
+      <c r="P106" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $70.0M / 12 yr; $23.3M IDF-Utility Account</t>
+        </is>
+      </c>
+      <c r="Q106" s="6" t="inlineStr">
+        <is>
+          <t>October 2026 move-in target into former One Wells Fargo Center (301 S. College St.) reconfirmed via sublease coverage (Axios, Bisnow); bank has not yet confirmed physical relocation as of 2026-10-05; active campus recruiting continues</t>
+        </is>
+      </c>
+      <c r="R106" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="S106" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bankingdive.com/news/smbc-revs-up-recruiting-charlotte-banking-talent-tech-cyber-data-jobs/830268/</t>
+        </is>
+      </c>
+      <c r="T106" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U106" s="6" t="inlineStr">
+        <is>
+          <t>Office / HQ banking</t>
+        </is>
+      </c>
+      <c r="V106" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="W106" s="6" t="inlineStr">
+        <is>
+          <t>Premier high-income signal; Class-A urban MF + high-end for-sale TH in Uptown/South End/Dilworth.</t>
+        </is>
+      </c>
+      <c r="X106" s="6" t="inlineStr">
+        <is>
+          <t>Eleventh consecutive cycle without a confirmed physical move-in; sublease and October 2026 move-in timing reconfirmed via independent Axios/Bisnow coverage this cycle. Score held flat at 94.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D107" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill / York Co.</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="H107" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma — "Project Palmetto Rock" HQ + manufacturing campus</t>
+        </is>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>Biopharmaceutical (plasma fractionation)</t>
+        </is>
+      </c>
+      <c r="J107" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone (unchanged)</t>
+        </is>
+      </c>
+      <c r="K107" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L107" s="6" t="inlineStr">
+        <is>
+          <t>Projected (1,200 new + 300 relocated)</t>
+        </is>
+      </c>
+      <c r="M107" s="6" t="inlineStr">
+        <is>
+          <t>$141,502 avg HQ / $102,752 avg mfg (both stated)</t>
+        </is>
+      </c>
+      <c r="N107" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O107" s="6" t="inlineStr">
+        <is>
+          <t>$1.5B</t>
+        </is>
+      </c>
+      <c r="P107" s="6" t="inlineStr">
+        <is>
+          <t>Fee-in-lieu-of-tax; $65M SC Coordinating Council Closing Fund grant to York Co.</t>
+        </is>
+      </c>
+      <c r="Q107" s="6" t="inlineStr">
+        <is>
+          <t>50 acres purchased at Palmetto Research Park; construction slated to begin late 2026; full operations still projected for the 2030s</t>
+        </is>
+      </c>
+      <c r="R107" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="S107" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/york-county/news/octapharma-how-company-chose-rock-hill/article_b1518265-129d-4134-9ff9-f2d686950bd6.html</t>
+        </is>
+      </c>
+      <c r="T107" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U107" s="6" t="inlineStr">
+        <is>
+          <t>Office/HQ + biopharma mfg</t>
+        </is>
+      </c>
+      <c r="V107" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W107" s="6" t="inlineStr">
+        <is>
+          <t>Dual-tier: $141k HQ roles -&gt; luxury for-sale/Class-A in Rock Hill/Fort Mill; $102k mfg roles -&gt; premium workforce-plus rental/TH.</t>
+        </is>
+      </c>
+      <c r="X107" s="6" t="inlineStr">
+        <is>
+          <t>Fifth consecutive cycle with no fresher dated milestone found; this cycle independently reconfirmed the full local-approval chain (York County Council first/final reading, Rock Hill City Council unanimous approval 2026-07-23, SC Commerce/Gov. McMaster formal announcement 2026-07-29) — all already inside the tracked timeline, no new date. NOTE: one 2026-07 secondary source (constructionreviewonline.com) describes the job split as "564 HQ / 688 mfg" (1,252 total) rather than the originally tracked "1,200 new + 300 relocated" (1,500 total) — flagged as an unresolved figure discrepancy for next cycle; headline figure held at the originally tracked 1,500 pending reconciliation against the primary SC Commerce release. Score held flat at 91.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D108" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>Durham / RTP</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie — biopharma manufacturing campus</t>
+        </is>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>Biopharma / life sciences mfg</t>
+        </is>
+      </c>
+      <c r="J108" s="6" t="inlineStr">
+        <is>
+          <t>No new physical-groundbreaking milestone this cycle</t>
+        </is>
+      </c>
+      <c r="K108" s="6" t="n">
+        <v>734</v>
+      </c>
+      <c r="L108" s="6" t="inlineStr">
+        <is>
+          <t>Projected (+2,000 construction)</t>
+        </is>
+      </c>
+      <c r="M108" s="6" t="inlineStr">
+        <is>
+          <t>$118,041 avg (stated; vs county $102,817)</t>
+        </is>
+      </c>
+      <c r="N108" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O108" s="6" t="inlineStr">
+        <is>
+          <t>$1.4B</t>
+        </is>
+      </c>
+      <c r="P108" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $19.3M / 12 yr; $6.4M IDF-Utility; Durham Co. performance-based award not-to-exceed $15,450,000 ("Project Glass"); Durham City Council companion incentive item (taken up 2026-09-17) brings combined city+county local incentive to ~$24.8M</t>
+        </is>
+      </c>
+      <c r="Q108" s="6" t="inlineStr">
+        <is>
+          <t>Construction 2026; complete ~end-2028; hiring through ~2031</t>
+        </is>
+      </c>
+      <c r="R108" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="S108" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/abbvie-pledges-1-3-billion-investment-734-jobs-in-durham/</t>
+        </is>
+      </c>
+      <c r="T108" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U108" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / R&amp;D / lab</t>
+        </is>
+      </c>
+      <c r="V108" s="6" t="inlineStr">
+        <is>
+          <t>Suburban-urban</t>
+        </is>
+      </c>
+      <c r="W108" s="6" t="inlineStr">
+        <is>
+          <t>High-end MF + move-up for-sale around Durham/RTP; spillover Wake/Orange. Construction-phase rental near-term.</t>
+        </is>
+      </c>
+      <c r="X108" s="6" t="inlineStr">
+        <is>
+          <t>No new physical-groundbreaking or hiring milestone found this cycle beyond the already-tracked Sept. 17 Durham City Council incentive item, independently reconfirmed this cycle via ABC11 (quoting a councilmember calling it a "huge deal"); company still targets construction "in 2026." Score held flat at 87.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>Gaining Momentum</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D109" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group — East Coast ops hub (officially opened; job target raised to 1,000)</t>
+        </is>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>Investment mgmt / finance + tech</t>
+        </is>
+      </c>
+      <c r="J109" s="6" t="inlineStr">
+        <is>
+          <t>Facility grand opening (ribbon-cutting); stated job target raised from 600 to up to 1,000</t>
+        </is>
+      </c>
+      <c r="K109" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L109" s="6" t="inlineStr">
+        <is>
+          <t>Projected (raised from 600; ~30 onsite currently, ~70 open reqs, growing toward 500-700+ near-term)</t>
+        </is>
+      </c>
+      <c r="M109" s="6" t="inlineStr">
+        <is>
+          <t>$194,141 avg (stated; NC Commerce JDIG figure)</t>
+        </is>
+      </c>
+      <c r="N109" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O109" s="6" t="inlineStr">
+        <is>
+          <t>$60M</t>
+        </is>
+      </c>
+      <c r="P109" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $17.2M / 12 yr; $5.7M IDF-Utility; $19.4M state grant/12yr + $2.2M training funds + $1M local</t>
+        </is>
+      </c>
+      <c r="Q109" s="6" t="inlineStr">
+        <is>
+          <t>Ribbon-cutting/grand opening held 2026-09-29 (Gov. Stein in attendance) at One Independence Center (200,000 SF, top 8 floors); same-day grand opening paired with Daimler Truck Financial Services (combined 876 new jobs touted by the state)</t>
+        </is>
+      </c>
+      <c r="R109" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="S109" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/capital-group-raises-charlotte-job-target-to-1000/</t>
+        </is>
+      </c>
+      <c r="T109" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U109" s="6" t="inlineStr">
+        <is>
+          <t>Office — finance/tech</t>
+        </is>
+      </c>
+      <c r="V109" s="6" t="inlineStr">
+        <is>
+          <t>Urban-suburban</t>
+        </is>
+      </c>
+      <c r="W109" s="6" t="inlineStr">
+        <is>
+          <t>High-skill eng/data workforce -&gt; walkable South End/Uptown &amp; inner-suburban Class-A and for-sale TH; the raised 1,000-job target and very high ($194k) average wage strengthen this as one of the region's top premium-housing demand drivers.</t>
+        </is>
+      </c>
+      <c r="X109" s="6" t="inlineStr">
+        <is>
+          <t>Material upgrade this cycle: the hub officially opened Sept. 29, 2026 (de-risking capital investment from leased/in-development to physically operating), and the company raised its stated Charlotte job target from 600 to up to 1,000 — a 67% increase — per Gov. Stein's office and Business NC. Current onsite headcount is still small (~30) with ~70 open requisitions, so the full 1,000-job ramp remains a multi-year build; score raised 81-&gt;86 to reflect the job-count increase and improved capital certainty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D110" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>Blythewood / N. Columbia</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV assembly plant + Supplier Park</t>
+        </is>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>Automotive / EV manufacturing</t>
+        </is>
+      </c>
+      <c r="J110" s="6" t="inlineStr">
+        <is>
+          <t>No new headcount, lawsuit-ruling, or production-timeline change found this cycle</t>
+        </is>
+      </c>
+      <c r="K110" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L110" s="6" t="inlineStr">
+        <is>
+          <t>Projected (4,000-5,000 assembly + ~1,000 supplier-park; 600+ hired as of Apr 2026, no fresher figure disclosed)</t>
+        </is>
+      </c>
+      <c r="M110" s="6" t="inlineStr">
+        <is>
+          <t>$30-$37.50/hr line (stated); salaried higher</t>
+        </is>
+      </c>
+      <c r="N110" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mix supports above-median HH income</t>
+        </is>
+      </c>
+      <c r="O110" s="6" t="inlineStr">
+        <is>
+          <t>$2.3B+ (site $2.0B + $25M training center + $300M Supplier Park)</t>
+        </is>
+      </c>
+      <c r="P110" s="6" t="inlineStr">
+        <is>
+          <t>State/local package (2023); $25M readySC; $150M cost-overrun payment cleared by Aug. 17 veto (still not confirmed disbursed); Legislative Audit Council/Inspector General joint review's scope now better documented (site-selection prudence, due-diligence adequacy, pre-permit construction risk, recoverability) — still due ~mid-Dec. 2026</t>
+        </is>
+      </c>
+      <c r="Q110" s="6" t="inlineStr">
+        <is>
+          <t>Body Shop/Paint Shop/Final Assembly/Supplier Park construction progress continues per Scout's own Sept. 2026 Production Center Update; one trade report suggests pre-series/prototype production could begin "this autumn" (2026) in Blythewood; customer deliveries still targeted 2028 per Scout's own guidance</t>
+        </is>
+      </c>
+      <c r="R110" s="6" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="S110" s="6" t="inlineStr">
+        <is>
+          <t>https://blog.scoutmotors.com/september-2026-scout-motors-production-center-update/</t>
+        </is>
+      </c>
+      <c r="T110" s="6" t="inlineStr">
+        <is>
+          <t>Medium (facts); Low (headcount/timeline)</t>
+        </is>
+      </c>
+      <c r="U110" s="6" t="inlineStr">
+        <is>
+          <t>Auto mfg + salaried eng.</t>
+        </is>
+      </c>
+      <c r="V110" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W110" s="6" t="inlineStr">
+        <is>
+          <t>Bifurcated: salaried/professional -&gt; higher-income for-sale &amp; Class-A; hourly base + supplier-park jobs -&gt; workforce/missing-middle rental in N. Richland/Fairfield.</t>
+        </is>
+      </c>
+      <c r="X110" s="6" t="inlineStr">
+        <is>
+          <t>The Shives family lawsuit (filed 8/7/26) remains pending with no ruling; most recent coverage (WIS-TV, 8/25/26) covers broader Blythewood-resident reaction, not a case development. The AutoForecast Solutions-reported Terra/Traveler delay remains disputed by Scout with no resolution. No new headcount figure. Score held flat at 85.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D111" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>Holly Springs / SW Wake</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H111" s="6" t="inlineStr">
+        <is>
+          <t>Genentech — biomanufacturing expansion (unchanged)</t>
+        </is>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="J111" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="K111" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="L111" s="6" t="inlineStr">
+        <is>
+          <t>Projected (site total)</t>
+        </is>
+      </c>
+      <c r="M111" s="6" t="inlineStr">
+        <is>
+          <t>~$119,833 avg (stated, 2025 tranche)</t>
+        </is>
+      </c>
+      <c r="N111" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O111" s="6" t="inlineStr">
+        <is>
+          <t>~$2.0B</t>
+        </is>
+      </c>
+      <c r="P111" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $9.85M / 12 yr (original 420-job award)</t>
+        </is>
+      </c>
+      <c r="Q111" s="6" t="inlineStr">
+        <is>
+          <t>Topping-out ceremony (Aug. 18, 2026) reconfirmed; facility will ultimately support 2,000+ on-site jobs (500 permanent mfg + ~1,500 construction); operational target 2029 unchanged</t>
+        </is>
+      </c>
+      <c r="R111" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="S111" s="6" t="inlineStr">
+        <is>
+          <t>https://www.biospace.com/press-releases/genentech-marks-topping-out-milestone-for-new-holly-springs-north-carolina-manufacturing-facility</t>
+        </is>
+      </c>
+      <c r="T111" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U111" s="6" t="inlineStr">
+        <is>
+          <t>Adv. biomanufacturing</t>
+        </is>
+      </c>
+      <c r="V111" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W111" s="6" t="inlineStr">
+        <is>
+          <t>Strong higher-income for-sale + Class-A rental demand in fast-growing SW Wake.</t>
+        </is>
+      </c>
+      <c r="X111" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone found this cycle beyond the already-tracked Aug. 18 topping-out ceremony, independently reconfirmed via REBusinessOnline and ContractPharma this cycle. Score held flat at 82.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D112" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="inlineStr">
+        <is>
+          <t>JetZero — aerospace plant ($100M lender loan secured)</t>
+        </is>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace / advanced manufacturing</t>
+        </is>
+      </c>
+      <c r="J112" s="6" t="inlineStr">
+        <is>
+          <t>$100M loan secured from a lender group to fund technology-maturation acceleration</t>
+        </is>
+      </c>
+      <c r="K112" s="6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="L112" s="6" t="inlineStr">
+        <is>
+          <t>Projected</t>
+        </is>
+      </c>
+      <c r="M112" s="6" t="inlineStr">
+        <is>
+          <t>$89,340 avg (stated, 2025)</t>
+        </is>
+      </c>
+      <c r="N112" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated (2025)</t>
+        </is>
+      </c>
+      <c r="O112" s="6" t="inlineStr">
+        <is>
+          <t>$4.7B</t>
+        </is>
+      </c>
+      <c r="P112" s="6" t="inlineStr">
+        <is>
+          <t>Transformative JDIG up to $1.018B / 37 yr; Guilford grant $75.9M / 20 yr; $133.9M NC FY26-27 budget funding; new $100M lender loan (Sept. 2026, separate from state/federal incentives)</t>
+        </is>
+      </c>
+      <c r="Q112" s="6" t="inlineStr">
+        <is>
+          <t>NC3 construction, the JDIG hiring-delay amendment, and the $3B EXIM Bank financing LOI remain the latest confirmed structural facts; new: a $100M loan (announced 2026-09-01) will help fund the Jet1 demonstrator program, now targeting a test flight "toward the end of 2027"; current job postings remain early build-out/engineering roles, not yet the bulk hiring ramp</t>
+        </is>
+      </c>
+      <c r="R112" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="S112" s="6" t="inlineStr">
+        <is>
+          <t>https://www.flightglobal.com/aerospace/2026/09/jetzero-secures-100m-loan-to-fund-development-push/</t>
+        </is>
+      </c>
+      <c r="T112" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); Medium (hiring-ramp timeline)</t>
+        </is>
+      </c>
+      <c r="U112" s="6" t="inlineStr">
+        <is>
+          <t>Aerospace mfg + eng.</t>
+        </is>
+      </c>
+      <c r="V112" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W112" s="6" t="inlineStr">
+        <is>
+          <t>Same long-run scale; mass hiring is confirmed pushed to 2028, not yet underway.</t>
+        </is>
+      </c>
+      <c r="X112" s="6" t="inlineStr">
+        <is>
+          <t>New in-window fact: JetZero secured a $100M loan from a group of lenders (announced 9/1/26) to accelerate technology maturation, funding build-out of the Greensboro factory and the Jet1 demonstrator program (now targeting a test flight toward the end of 2027). An incremental positive financing signal layered on the already-tracked EXIM $3B LOI, but it does not change the hiring-ramp timeline (mass hiring still confirmed pushed to 2028) or the stated $89,340 average wage. Score held flat at 82.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D113" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Plaza Midwood</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H113" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — Global HQ (litigation footprint unchanged this cycle)</t>
+        </is>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>Automotive (EV) — corporate HQ</t>
+        </is>
+      </c>
+      <c r="J113" s="6" t="inlineStr">
+        <is>
+          <t>No permit/construction progress found; litigation footprint reconfirmed, not expanded</t>
+        </is>
+      </c>
+      <c r="K113" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L113" s="6" t="inlineStr">
+        <is>
+          <t>Projected (365 relocating + 835 new local hires)</t>
+        </is>
+      </c>
+      <c r="M113" s="6" t="inlineStr">
+        <is>
+          <t>$153,978 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N113" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O113" s="6" t="inlineStr">
+        <is>
+          <t>$206.9M</t>
+        </is>
+      </c>
+      <c r="P113" s="6" t="inlineStr">
+        <is>
+          <t>Original 2025-11-12 HQ incentive/relocation commitment</t>
+        </is>
+      </c>
+      <c r="Q113" s="6" t="inlineStr">
+        <is>
+          <t>2nd office building preliminary land-development plan (filed 2026-03-28) still awaiting staff review/approvals; construction start still targeted H1 2027; initial Commonwealth-development office build-out continuing</t>
+        </is>
+      </c>
+      <c r="R113" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="S113" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/scout-motors-hq-move-turbocharges-second-office-building-in-plaza-midwood/</t>
+        </is>
+      </c>
+      <c r="T113" s="6" t="inlineStr">
+        <is>
+          <t>Med (facts High; milestone stage early)</t>
+        </is>
+      </c>
+      <c r="U113" s="6" t="inlineStr">
+        <is>
+          <t>Corporate HQ / professional</t>
+        </is>
+      </c>
+      <c r="V113" s="6" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="W113" s="6" t="inlineStr">
+        <is>
+          <t>Supports Plaza Midwood/NoDa/Elizabeth close-in rental and townhome demand from a young, high-wage corporate workforce.</t>
+        </is>
+      </c>
+      <c r="X113" s="6" t="inlineStr">
+        <is>
+          <t>No fresher permit/construction-progress milestone found this cycle. The dealer-litigation footprint (direct-to-consumer sales-model challenges) is reconfirmed at roughly 6-7 states (CA, FL, CO, NY, CT, WA per Kiss 95.1/CBT News reporting), with a Virginia federal class action also noted (filed 2026-03-04) — no material change from the prior cycle's tracked footprint. Company continues stating it is proceeding with the Charlotte HQ regardless. Score held flat at 79.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D114" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Ballantyne</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H114" s="6" t="inlineStr">
+        <is>
+          <t>Citigroup — Charlotte office (hiring ramp proceeding)</t>
+        </is>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>Banking / financial services</t>
+        </is>
+      </c>
+      <c r="J114" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="K114" s="6" t="n">
+        <v>510</v>
+      </c>
+      <c r="L114" s="6" t="inlineStr">
+        <is>
+          <t>Confirmed (stated); facility ultimately to house 785 employees incl. ~275 relocated</t>
+        </is>
+      </c>
+      <c r="M114" s="6" t="inlineStr">
+        <is>
+          <t>$131,832 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N114" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O114" s="6" t="inlineStr">
+        <is>
+          <t>$16.1M</t>
+        </is>
+      </c>
+      <c r="P114" s="6" t="inlineStr">
+        <is>
+          <t>JDIG up to $8.9M / 10 yr</t>
+        </is>
+      </c>
+      <c r="Q114" s="6" t="inlineStr">
+        <is>
+          <t>No headcount-progress update found dated after the 2026-04-23 hiring-progress article despite a dedicated recheck; active job postings (finance, risk, compliance, wealth-management roles) confirm hiring is ongoing</t>
+        </is>
+      </c>
+      <c r="R114" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="S114" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wfae.org/business/2026-04-23/charlottes-banking-jobs-hot-streak-continues</t>
+        </is>
+      </c>
+      <c r="T114" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U114" s="6" t="inlineStr">
+        <is>
+          <t>Office / financial services</t>
+        </is>
+      </c>
+      <c r="V114" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W114" s="6" t="inlineStr">
+        <is>
+          <t>$131,832 stated wage clears the $100k bar; supports Class-A rental and for-sale townhome demand in south Mecklenburg's Ballantyne/Blakeney/Rea Farms corridor.</t>
+        </is>
+      </c>
+      <c r="X114" s="6" t="inlineStr">
+        <is>
+          <t>No fresher milestone found this cycle. One secondary source (job-aggregator wage data) cites a slightly higher $133,435 average wage vs. the originally tracked $131,832 — within normal variant-methodology range, not treated as a material change. Score held flat at 78.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D115" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>Durham / Morrisville</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>Durham &amp; Wake</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="H115" s="6" t="inlineStr">
+        <is>
+          <t>Novartis — API mfg building (unchanged)</t>
+        </is>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="J115" s="6" t="inlineStr">
+        <is>
+          <t>No new milestone this cycle</t>
+        </is>
+      </c>
+      <c r="K115" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="L115" s="6" t="inlineStr">
+        <is>
+          <t>Projected (part of pre-window deal)</t>
+        </is>
+      </c>
+      <c r="M115" s="6" t="inlineStr">
+        <is>
+          <t>$111,161 avg (stated)</t>
+        </is>
+      </c>
+      <c r="N115" s="6" t="inlineStr">
+        <is>
+          <t>N/A — stated</t>
+        </is>
+      </c>
+      <c r="O115" s="6" t="inlineStr">
+        <is>
+          <t>~$991M (incl. $220M API building)</t>
+        </is>
+      </c>
+      <c r="P115" s="6" t="inlineStr">
+        <is>
+          <t>Part of original $771M package incentives; $7.6M NC cash-incentive component newly confirmed</t>
+        </is>
+      </c>
+      <c r="Q115" s="6" t="inlineStr">
+        <is>
+          <t>Broader $771M "flagship manufacturing hub" (Morrisville API plant + two new Durham facilities) had its overall groundbreaking in Dec. 2025 (pre-window); Morrisville-specific construction still "scheduled to begin this year" (2026), with facilities opening 2027-2028 and ~700 direct NC jobs created by 2030</t>
+        </is>
+      </c>
+      <c r="R115" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="S115" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/novartis-pharmaceuticals-expands-nc-presence-morrisville-plant-april-2026/</t>
+        </is>
+      </c>
+      <c r="T115" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U115" s="6" t="inlineStr">
+        <is>
+          <t>Adv. mfg / API production</t>
+        </is>
+      </c>
+      <c r="V115" s="6" t="inlineStr">
+        <is>
+          <t>Suburban</t>
+        </is>
+      </c>
+      <c r="W115" s="6" t="inlineStr">
+        <is>
+          <t>Reinforces sustained high-wage biomanufacturing hiring in Wake/Durham corridor.</t>
+        </is>
+      </c>
+      <c r="X115" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window milestone found since the April 30, 2026 announcement despite a dedicated recheck; this cycle added confirmation that the broader hub's overall groundbreaking occurred Dec. 2025 (pre-window) and that the state cash-incentive component is specifically $7.6M. Score held flat at 77.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22519,7 +24589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L479"/>
+  <dimension ref="A1:L529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -52234,6 +54304,3106 @@
         </is>
       </c>
     </row>
+    <row r="480">
+      <c r="A480" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B480" s="6" t="inlineStr">
+        <is>
+          <t>Cherokee Co. / Blacksburg</t>
+        </is>
+      </c>
+      <c r="C480" s="6" t="inlineStr">
+        <is>
+          <t>Cherokee</t>
+        </is>
+      </c>
+      <c r="D480" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E480" s="6" t="inlineStr">
+        <is>
+          <t>USA Rare Earth — rare-earth magnet plant</t>
+        </is>
+      </c>
+      <c r="F480" s="6" t="inlineStr">
+        <is>
+          <t>~490</t>
+        </is>
+      </c>
+      <c r="G480" s="6" t="inlineStr">
+        <is>
+          <t>$1.2B</t>
+        </is>
+      </c>
+      <c r="H480" s="6" t="inlineStr">
+        <is>
+          <t>$24.50-$63/hr (stated; unchanged)</t>
+        </is>
+      </c>
+      <c r="I480" s="6" t="inlineStr">
+        <is>
+          <t>Groundbreaking confirmed held 2026-09-09 at a 124-acre site in Bailey Industrial Park (~800,000 sq ft facility). New in-window detail: operations now targeted to begin April 2028 (a later date than some prior estimates), and the company pledged $250,000 to Spartanburg Community College's new "SPARK Center" in Cherokee County for workforce training. Jobs (~490) and capex ($1.2B) confirmed unchanged.</t>
+        </is>
+      </c>
+      <c r="J480" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K480" s="6" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/09/09/3358813/0/en/usa-rare-earth-breaks-ground-on-advanced-rare-earth-metal-and-magnet-manufacturing-facility-in-blacksburg-south-carolina.html</t>
+        </is>
+      </c>
+      <c r="L480" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B481" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg (former Kohler plant)</t>
+        </is>
+      </c>
+      <c r="C481" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D481" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E481" s="6" t="inlineStr">
+        <is>
+          <t>NorthMark/Valara "Project Moc-1" — AI/HPC data center (moratorium resolved; grandfathered)</t>
+        </is>
+      </c>
+      <c r="F481" s="6" t="inlineStr">
+        <is>
+          <t>27 FT confirmed on incentive filings (company's own ~150-at-full-operation claim not independently corroborated)</t>
+        </is>
+      </c>
+      <c r="G481" s="6" t="inlineStr">
+        <is>
+          <t>$2.8-3.0B</t>
+        </is>
+      </c>
+      <c r="H481" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I481" s="6" t="inlineStr">
+        <is>
+          <t>Partial update: Judge Derham Cole Jr. heard oral arguments on 2026-09-17 on SELC's injunction motion and the county/Valara motions to dismiss, and said he would review filings and issue an order "in a few days or a few weeks" -- no ruling has been issued as of this cycle's search. The underlying dispute (whether the $2.8-3.0B HPC campus + 460MW gas plant was improperly split into two "minor development" permits to avoid planning-commission review) remains unresolved. The county moratorium (passed 5-1, amended/finalized 9/25/26) still explicitly grandfathers this project; the SC PSC's Aug. 27 ruling that the gas plant isn't subject to utility-siting review also stands.</t>
+        </is>
+      </c>
+      <c r="J481" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="K481" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/spartanburg/news/selc-argues-injunction-spartanburg-data-center-valara/article_caa79357-f85b-4c93-9fb3-483b64e164c7.html</t>
+        </is>
+      </c>
+      <c r="L481" s="6" t="inlineStr">
+        <is>
+          <t>Med-High (county/state regulatory risk resolved favorably for the developer; court injunction ruling still open)</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B482" s="6" t="inlineStr">
+        <is>
+          <t>Wake County (statewide)</t>
+        </is>
+      </c>
+      <c r="C482" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D482" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E482" s="6" t="inlineStr">
+        <is>
+          <t>WakeMed / Atrium Health — merger approved by county, moves to federal review</t>
+        </is>
+      </c>
+      <c r="F482" s="6" t="inlineStr">
+        <is>
+          <t>3,300 (statewide, 5 yr)</t>
+        </is>
+      </c>
+      <c r="G482" s="6" t="inlineStr">
+        <is>
+          <t>$2.0B (Wake Co. portion)</t>
+        </is>
+      </c>
+      <c r="H482" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I482" s="6" t="inlineStr">
+        <is>
+          <t>No new development beyond the 9/21/26 approval already tracked. The merger (Wake County Board of Commissioners approved 5-2) is now pending both FTC and NC Attorney General review; revised deal terms include a 5-year cap on WakeMed price increases (&lt;=1.5x Medicare cost growth), a new $150M Wake County Whole Health Program, and a charity-care minimum raised from 4.8% to 8% of adjusted revenue. No federal/AG ruling or timeline found yet.</t>
+        </is>
+      </c>
+      <c r="J482" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="K482" s="6" t="inlineStr">
+        <is>
+          <t>https://www.northcarolinahealthnews.org/2026/09/23/whats-next-for-the-atrium-wakemed-deal/</t>
+        </is>
+      </c>
+      <c r="L482" s="6" t="inlineStr">
+        <is>
+          <t>High (vote outcome); Medium (federal/AG-review outcome and timeline unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B483" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro / PTI Airport</t>
+        </is>
+      </c>
+      <c r="C483" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="D483" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E483" s="6" t="inlineStr">
+        <is>
+          <t>Boom Supersonic — Overture assembly (AT RISK — deadline ~3 months out)</t>
+        </is>
+      </c>
+      <c r="F483" s="6" t="inlineStr">
+        <is>
+          <t>&lt;=500 currently; must hit 500 by 12/31/26 or lease may terminate</t>
+        </is>
+      </c>
+      <c r="G483" s="6" t="inlineStr">
+        <is>
+          <t>~$50M (hangar)</t>
+        </is>
+      </c>
+      <c r="H483" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I483" s="6" t="inlineStr">
+        <is>
+          <t>Escalating risk, unresolved: as of August 2026, Boom Supersonic has approximately 360 employees company-wide (North America, Asia, Europe combined) -- a global, not Greensboro-site-specific, figure, and still well short of the 500-employee Greensboro threshold with less than 3 months left in 2026. The ~179,000 sq ft hangar remains largely idle per reporting; CEO stated in August 2026 that production "will start in two years," implicitly confirming no near-term hiring ramp. No positive catalyst found this cycle.</t>
+        </is>
+      </c>
+      <c r="J483" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K483" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/greensboro-s-50-million-supersonic-ghost-hangar-puts-state-on-the-clock/</t>
+        </is>
+      </c>
+      <c r="L483" s="6" t="inlineStr">
+        <is>
+          <t>Med-High (risk escalating; deadline imminent, now &lt;3 months out)</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B484" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte (CLT airport)</t>
+        </is>
+      </c>
+      <c r="C484" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D484" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E484" s="6" t="inlineStr">
+        <is>
+          <t>Averitt — logistics campus (zoning still not confirmed approved)</t>
+        </is>
+      </c>
+      <c r="F484" s="6" t="inlineStr">
+        <is>
+          <t>211-230 (range across sources; treated as unchanged)</t>
+        </is>
+      </c>
+      <c r="G484" s="6" t="inlineStr">
+        <is>
+          <t>$200M</t>
+        </is>
+      </c>
+      <c r="H484" s="6" t="inlineStr">
+        <is>
+          <t>$81,769 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I484" s="6" t="inlineStr">
+        <is>
+          <t>Zoning status clarified but still not finalized: Rezoning Petition 2025-139 (2124 Shopton Rd, ~53.24 acres to ML-2(CD)) had its public hearing 2026-03-23 and a Zoning Committee work session 2026-04-07; full City Council final approval still not confirmed as of this cycle despite a dedicated recheck. NCDOT's Shopton Road bridge closure (through summer 2027) remains a live access/build-out complication. Jobs (211-230, range across sources) and capex ($200M) unchanged.</t>
+        </is>
+      </c>
+      <c r="J484" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K484" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/04/averitt-s-230-job-truck-campus-poised-to-rev-up-clt-s-cargo-corridor/</t>
+        </is>
+      </c>
+      <c r="L484" s="6" t="inlineStr">
+        <is>
+          <t>High (jobs/wage); Med (zoning/construction timing still unresolved)</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B485" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / SouthPark</t>
+        </is>
+      </c>
+      <c r="C485" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D485" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E485" s="6" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase — SouthPark consolidated office</t>
+        </is>
+      </c>
+      <c r="F485" s="6" t="inlineStr">
+        <is>
+          <t>400 new + ~600 relocated = 1,000 total</t>
+        </is>
+      </c>
+      <c r="G485" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H485" s="6" t="inlineStr">
+        <is>
+          <t>~$105k Estimated/Inferred — basis not independently confirmed</t>
+        </is>
+      </c>
+      <c r="I485" s="6" t="inlineStr">
+        <is>
+          <t>No update to the 400-new/1,000-total job figures. New timeline detail: the consolidated SouthPark office (One Piedmont Town Center, 145,000 sq ft) will not open until early 2028 -- a longer horizon than previously assumed. Wage still not disclosed by the company.</t>
+        </is>
+      </c>
+      <c r="J485" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K485" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/04/21/jpmorgan-southpark-charlotte-400-jobs</t>
+        </is>
+      </c>
+      <c r="L485" s="6" t="inlineStr">
+        <is>
+          <t>High (jobs/lease/timing); Low (wage basis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B486" s="6" t="inlineStr">
+        <is>
+          <t>Benson</t>
+        </is>
+      </c>
+      <c r="C486" s="6" t="inlineStr">
+        <is>
+          <t>Johnston</t>
+        </is>
+      </c>
+      <c r="D486" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E486" s="6" t="inlineStr">
+        <is>
+          <t>Vulcan Elements — magnet factory (transmission line fast-tracked)</t>
+        </is>
+      </c>
+      <c r="F486" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (proj.)</t>
+        </is>
+      </c>
+      <c r="G486" s="6" t="inlineStr">
+        <is>
+          <t>$918.4M</t>
+        </is>
+      </c>
+      <c r="H486" s="6" t="inlineStr">
+        <is>
+          <t>$81,932 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I486" s="6" t="inlineStr">
+        <is>
+          <t>No factory-groundbreaking event found this cycle. New detail on the already-tracked NC Utilities Commission fast-tracked 230kV transmission line (1.31-mile, Hwy 301 to the Morgan Road site, approved under Defense Production Act urgency, late Aug. 2026): the line is expected to be complete by "end of March" (2027). Company's own guidance still targets starting operations Q1 2027 after doubling the planned facility to 1M+ sq ft.</t>
+        </is>
+      </c>
+      <c r="J486" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K486" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/nccapitol/north-carolina-fast-tracks-power-line-for-rare-earth-magnet-factory-august-2026/</t>
+        </is>
+      </c>
+      <c r="L486" s="6" t="inlineStr">
+        <is>
+          <t>Medium-High (infrastructure clearance confirmed; factory groundbreaking date still unconfirmed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B487" s="6" t="inlineStr">
+        <is>
+          <t>Multi-site NC incl. Wilmington</t>
+        </is>
+      </c>
+      <c r="C487" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover +</t>
+        </is>
+      </c>
+      <c r="D487" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E487" s="6" t="inlineStr">
+        <is>
+          <t>Amazon-Corning — fiber-optics partnership</t>
+        </is>
+      </c>
+      <c r="F487" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (multi-site, unallocated)</t>
+        </is>
+      </c>
+      <c r="G487" s="6" t="inlineStr">
+        <is>
+          <t>Multi-billion (undisclosed)</t>
+        </is>
+      </c>
+      <c r="H487" s="6" t="inlineStr">
+        <is>
+          <t>Avg salary &gt;$65,000 (sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I487" s="6" t="inlineStr">
+        <is>
+          <t>Site clarification found this cycle: Corning's named NC plants under this agreement are Hickory, Newton, Wilmington, Winston-Salem, and Concord -- none in the NC Triangle region; the related workforce-training partnership is with Catawba Valley Community College (Hickory area). 1,000-job, multi-site, unallocated figure and sub-$100k wage estimate unchanged. Wilmington-specific job allocation remains undisclosed.</t>
+        </is>
+      </c>
+      <c r="J487" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K487" s="6" t="inlineStr">
+        <is>
+          <t>https://www.corning.com/worldwide/en/about-us/news-events/news-releases/2026/06/amazon-announces-agreement-with-corning-to-boost-us-fiber-optics-manufacturing-creating-1000-advanced-manufacturing-jobs-in-north-carolina.html</t>
+        </is>
+      </c>
+      <c r="L487" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B488" s="6" t="inlineStr">
+        <is>
+          <t>Arden</t>
+        </is>
+      </c>
+      <c r="C488" s="6" t="inlineStr">
+        <is>
+          <t>Buncombe</t>
+        </is>
+      </c>
+      <c r="D488" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E488" s="6" t="inlineStr">
+        <is>
+          <t>Pratt &amp; Whitney (RTX) — casting foundry expansion</t>
+        </is>
+      </c>
+      <c r="F488" s="6" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="G488" s="6" t="inlineStr">
+        <is>
+          <t>$285M</t>
+        </is>
+      </c>
+      <c r="H488" s="6" t="inlineStr">
+        <is>
+          <t>$62,413 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I488" s="6" t="inlineStr">
+        <is>
+          <t>Still forward-looking: no confirmation found this cycle that equipment has arrived (first equipment arrivals remain projected for end of 2026, first parts production mid-2027, full foundry operations targeted 2028). Adjacent signal (not scored): Buncombe County locked in a $29.2M "Western NC Futures Factory" workforce-training/research facility near the P&amp;W site (Biltmore Park West, 70,000 sq ft), funded by a federal disaster-recovery grant + local match, to retrain ~800 workers/year -- reinforces the broader Arden/Buncombe manufacturing cluster.</t>
+        </is>
+      </c>
+      <c r="J488" s="6" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K488" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/09/buncombe-county-locks-in-29-2m-factory-to-retrain-800-workers-a-year/</t>
+        </is>
+      </c>
+      <c r="L488" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B489" s="6" t="inlineStr">
+        <is>
+          <t>Asheville / Arden</t>
+        </is>
+      </c>
+      <c r="C489" s="6" t="inlineStr">
+        <is>
+          <t>Buncombe</t>
+        </is>
+      </c>
+      <c r="D489" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E489" s="6" t="inlineStr">
+        <is>
+          <t>Eaton — Low Voltage Assembly expansion</t>
+        </is>
+      </c>
+      <c r="F489" s="6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G489" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H489" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Estimated mid-$60k-$80k)</t>
+        </is>
+      </c>
+      <c r="I489" s="6" t="inlineStr">
+        <is>
+          <t>Active hiring confirmed underway, including a WNC Career Expo held 2026-04-16; current job postings for the LVA line at the Arden/Heywood Rd facility (Electrical Test Technician, Manufacturing Supervisor, and other technical/production roles) remain consistent with the plan to fill jobs within 12 months of the April 2026 announcement. One source cites a much larger "over 725 local jobs" figure for Eaton's broader Buncombe footprint -- likely cumulative across multiple prior+current expansions, not a new standalone announcement; treated cautiously, not adopted as the tracked figure.</t>
+        </is>
+      </c>
+      <c r="J489" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K489" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ashevillechamber.org/news-events/press-releases/eaton-invests-in-workforce-growth-in-buncombe-county/</t>
+        </is>
+      </c>
+      <c r="L489" s="6" t="inlineStr">
+        <is>
+          <t>High (jobs); Low (wage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B490" s="6" t="inlineStr">
+        <is>
+          <t>Greensboro</t>
+        </is>
+      </c>
+      <c r="C490" s="6" t="inlineStr">
+        <is>
+          <t>Guilford</t>
+        </is>
+      </c>
+      <c r="D490" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E490" s="6" t="inlineStr">
+        <is>
+          <t>Lumentum — AI/data-center optics (hiring underway)</t>
+        </is>
+      </c>
+      <c r="F490" s="6" t="inlineStr">
+        <is>
+          <t>~400</t>
+        </is>
+      </c>
+      <c r="G490" s="6" t="inlineStr">
+        <is>
+          <t>Hundreds of millions</t>
+        </is>
+      </c>
+      <c r="H490" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I490" s="6" t="inlineStr">
+        <is>
+          <t>Deal confirmed closed 2026-03-17 for $38.0 million cash (per SEC 10-Q); company plans to invest "hundreds of millions of dollars" over several years. Jobs figure consistently reported as "more than 400" (not confirmed higher). Production ramp for the ex-Qorvo facility (indium-phosphide optical devices for AI data centers) is expected mid-2028 -- meaning current hiring is front-loaded engineering/technician roles, not yet full-scale manufacturing headcount.</t>
+        </is>
+      </c>
+      <c r="J490" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="K490" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/0001633978/000162828026030777/lite-20260328.htm</t>
+        </is>
+      </c>
+      <c r="L490" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B491" s="6" t="inlineStr">
+        <is>
+          <t>Hendersonville</t>
+        </is>
+      </c>
+      <c r="C491" s="6" t="inlineStr">
+        <is>
+          <t>Henderson</t>
+        </is>
+      </c>
+      <c r="D491" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E491" s="6" t="inlineStr">
+        <is>
+          <t>BorgWarner — vertical-integration expansion</t>
+        </is>
+      </c>
+      <c r="F491" s="6" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="G491" s="6" t="inlineStr">
+        <is>
+          <t>$100M</t>
+        </is>
+      </c>
+      <c r="H491" s="6" t="inlineStr">
+        <is>
+          <t>$67,047 avg (stated; below $100k)</t>
+        </is>
+      </c>
+      <c r="I491" s="6" t="inlineStr">
+        <is>
+          <t>Formal state announcement date confirmed in-window-adjacent at 2026-05-26 (Gov. Stein, NC Commerce): $100M/378 jobs, average salary $67,047 (24% above Henderson Co. average of $54,118, but still below the $100k threshold). Turbine-generator production start still targeted 2027 (initial 2 GW capacity, expected &gt;$300M first-year sales). State incentive confirmed at $3.68M over 12 years. No further update this cycle.</t>
+        </is>
+      </c>
+      <c r="J491" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="K491" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2026/05/26/governor-stein-announces-100-million-expansion-borgwarner-hendersonville</t>
+        </is>
+      </c>
+      <c r="L491" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B492" s="6" t="inlineStr">
+        <is>
+          <t>Rowan / Kannapolis</t>
+        </is>
+      </c>
+      <c r="C492" s="6" t="inlineStr">
+        <is>
+          <t>Rowan</t>
+        </is>
+      </c>
+      <c r="D492" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E492" s="6" t="inlineStr">
+        <is>
+          <t>Google — 730k sq ft warehouse lease (operator now named: DHL)</t>
+        </is>
+      </c>
+      <c r="F492" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G492" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H492" s="6" t="inlineStr">
+        <is>
+          <t>$55k-$150k range (job-board postings)</t>
+        </is>
+      </c>
+      <c r="I492" s="6" t="inlineStr">
+        <is>
+          <t>New in-window detail: Google's 88-month lease for the ~730,000 sq ft Overlook 85 Industrial Park facility (1894 Old Beatty Ford Road, Rowan Co.) was formally announced by the City of Kannapolis 2026-04-28/29; explicitly warehousing/logistics use ("not a data center"), with two 5-year renewal options. DHL's role as the third-party operator (per the previously-cited Salisbury Post reporting) could not be independently re-confirmed this cycle -- treated as reconfirmed-but-unverified pending a fresher source. Google itself still discloses no jobs/wage figures.</t>
+        </is>
+      </c>
+      <c r="J492" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="K492" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wbtv.com/2026/04/29/google-leases-massive-facility-near-rowan-cabarrus-county-line/</t>
+        </is>
+      </c>
+      <c r="L492" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B493" s="6" t="inlineStr">
+        <is>
+          <t>RTP</t>
+        </is>
+      </c>
+      <c r="C493" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D493" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E493" s="6" t="inlineStr">
+        <is>
+          <t>Apple — RTP campus extension</t>
+        </is>
+      </c>
+      <c r="F493" s="6" t="inlineStr">
+        <is>
+          <t>3,000 originally projected; only ~600-990 added to date</t>
+        </is>
+      </c>
+      <c r="G493" s="6" t="inlineStr">
+        <is>
+          <t>$552M-$1B+ (paused)</t>
+        </is>
+      </c>
+      <c r="H493" s="6" t="inlineStr">
+        <is>
+          <t>$187k avg (stated, original 2021 award)</t>
+        </is>
+      </c>
+      <c r="I493" s="6" t="inlineStr">
+        <is>
+          <t>Material negative-signal update: Apple has told state officials it wants to delay the RTP campus-extension project by up to 4 additional years beyond the original 2026 construction start, while saying it remains "deeply committed" to the $1B+ expansion. Jobs added to date remain in the ~600-990 range (vs. the original 3,000-job, $187k-avg-salary target); Apple's amended 2021 EIC grant calls for 990 jobs by end of 2026, scaling to 2,700 by 2031. This further weakens the near-term housing-demand signal from this project.</t>
+        </is>
+      </c>
+      <c r="J493" s="6" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="K493" s="6" t="inlineStr">
+        <is>
+          <t>https://www.carolinajournal.com/apple-delays-construction-on-552-million-rtp-campus/</t>
+        </is>
+      </c>
+      <c r="L493" s="6" t="inlineStr">
+        <is>
+          <t>Med (delay confirmed; new construction-start date not yet fixed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B494" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Raleigh / Rural Hall</t>
+        </is>
+      </c>
+      <c r="C494" s="6" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="D494" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E494" s="6" t="inlineStr">
+        <is>
+          <t>Siemens Energy — $421M NC expansion (Charlotte-specific)</t>
+        </is>
+      </c>
+      <c r="F494" s="6" t="inlineStr">
+        <is>
+          <t>500 (statewide)</t>
+        </is>
+      </c>
+      <c r="G494" s="6" t="inlineStr">
+        <is>
+          <t>$421M</t>
+        </is>
+      </c>
+      <c r="H494" s="6" t="inlineStr">
+        <is>
+          <t>$82,052 avg for the Charlotte-specific share (sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I494" s="6" t="inlineStr">
+        <is>
+          <t>Clarification found this cycle: the $421M/500-job figure is STATEWIDE across three sites (Charlotte, Raleigh, Rural Hall) -- not Mecklenburg-only; the Charlotte-specific share (Westinghouse Blvd plant resuming gas-turbine manufacturing after a 6-year pause) remains at an estimated sub-$100k average wage. First Charlotte-made turbines expected to ship 2028-2029. No in-window groundbreaking or hiring-start milestone found.</t>
+        </is>
+      </c>
+      <c r="J494" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K494" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/siemens-energys-421-million-n-c-expansion-adding-500-jobs/</t>
+        </is>
+      </c>
+      <c r="L494" s="6" t="inlineStr">
+        <is>
+          <t>Med (totals statewide, not site-specific; Charlotte wage confirmed sub-$100k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B495" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh / Wendell / Knightdale</t>
+        </is>
+      </c>
+      <c r="C495" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D495" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E495" s="6" t="inlineStr">
+        <is>
+          <t>Siemens AG — power devices for AI/data centers</t>
+        </is>
+      </c>
+      <c r="F495" s="6" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="G495" s="6" t="inlineStr">
+        <is>
+          <t>part of $165M</t>
+        </is>
+      </c>
+      <c r="H495" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I495" s="6" t="inlineStr">
+        <is>
+          <t>Wage recheck confirms sub-$100k at both NC sites: average pay in Knightdale ~$72,617/yr (Sept. 2026 data) and in Wendell ~$66,331/yr (June 2026 data) -- both well under the $100k qualifying threshold, consistent with Watch-tier (not Ranked) status. Breakdown unchanged: 100 jobs at a new 131,000 sq ft Knightdale facility (by end of 2026) + 50 jobs at a new 101,000 sq ft Wendell facility + 200 jobs from an existing Wendell campus expansion by 2028.</t>
+        </is>
+      </c>
+      <c r="J495" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K495" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/business/siemens-350-jobs-nc-sc-165m-investment-ai-data-centers-raleigh-wendell-march-2026/</t>
+        </is>
+      </c>
+      <c r="L495" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B496" s="6" t="inlineStr">
+        <is>
+          <t>Hamlet</t>
+        </is>
+      </c>
+      <c r="C496" s="6" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="D496" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E496" s="6" t="inlineStr">
+        <is>
+          <t>AWS/Amazon — AI/cloud campus "Project Blue Marlin" (air permits approved)</t>
+        </is>
+      </c>
+      <c r="F496" s="6" t="inlineStr">
+        <is>
+          <t>500 permanent (confirmed)</t>
+        </is>
+      </c>
+      <c r="G496" s="6" t="inlineStr">
+        <is>
+          <t>$10B</t>
+        </is>
+      </c>
+      <c r="H496" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I496" s="6" t="inlineStr">
+        <is>
+          <t>Construction confirmed actively underway (up to 20 buildings planned, each potentially 200,000+ sq ft; first building targeted operational 2027, additional phases through 2029). New this cycle: a 2026-09-16 WUNC investigative piece raised community health/air-pollution concerns over temporary diesel/gas generators powering the site before grid interconnection, alongside growing local opposition/scrutiny. 500-permanent-job and $10B figures unchanged; this is reputational/regulatory friction rather than a jobs or timeline change.</t>
+        </is>
+      </c>
+      <c r="J496" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K496" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wunc.org/environment/2026-09-16/richmond-county-amazon-data-center-air-pollution</t>
+        </is>
+      </c>
+      <c r="L496" s="6" t="inlineStr">
+        <is>
+          <t>High (permits/construction confirmed); Low-Med (community-opposition outcome)</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B497" s="6" t="inlineStr">
+        <is>
+          <t>Woodruff / Spartanburg Co.</t>
+        </is>
+      </c>
+      <c r="C497" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D497" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E497" s="6" t="inlineStr">
+        <is>
+          <t>AIRSYS Cooling Technologies — global HQ (capex discrepancy flagged)</t>
+        </is>
+      </c>
+      <c r="F497" s="6" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G497" s="6" t="inlineStr">
+        <is>
+          <t>$40M (originally tracked); several 2026 secondary sources now cite ~$60M — reconciliation needed</t>
+        </is>
+      </c>
+      <c r="H497" s="6" t="inlineStr">
+        <is>
+          <t>Eng. roles $69-93k; assembly $34-46k (Estimated/Inferred)</t>
+        </is>
+      </c>
+      <c r="I497" s="6" t="inlineStr">
+        <is>
+          <t>Capex discrepancy largely resolved this cycle: the $40M figure is confirmed correct and consistent across AIRSYS's own site and multiple local outlets (grand opening of the 264,000 sq ft global HQ/3D-printing campus at 6228 Hwy 101, Woodruff, held 2026-05-13; corporate teams already on-site, manufacturing start targeted Q1 2027). The previously-flagged "$60M" figure appears to be a conflation with Spartanburg County's full-year 2025 total of $3.5B in new investment (a OneSpartanburg county-wide figure across 20 projects), not AIRSYS's own project capex -- no independent source for a standalone $60M AIRSYS figure was found. 215 jobs unchanged.</t>
+        </is>
+      </c>
+      <c r="J497" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K497" s="6" t="inlineStr">
+        <is>
+          <t>https://www.spartanweeklyonline.com/news/local-news/airsys-opens-global-headquarters-campus-in-woodruff-bringing-215-jobs</t>
+        </is>
+      </c>
+      <c r="L497" s="6" t="inlineStr">
+        <is>
+          <t>High (capex discrepancy now resolved)</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B498" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="C498" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D498" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E498" s="6" t="inlineStr">
+        <is>
+          <t>GNQ Insilico — AI/quantum techbio HQ (SPAC deadline missed; second extension sought)</t>
+        </is>
+      </c>
+      <c r="F498" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G498" s="6" t="inlineStr">
+        <is>
+          <t>$500M (valuation, not capex)</t>
+        </is>
+      </c>
+      <c r="H498" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I498" s="6" t="inlineStr">
+        <is>
+          <t>Status update: IB Acquisition Corp.'s stockholders VOTED TO APPROVE a second extension of the business-combination deadline, moving it from 2026-09-28 to 2027-03-28 (confirmed passed, not merely sought as tracked last cycle). 117,386 shares were redeemed for ~$1.29M from trust in the same vote. Deal background reconfirmed: $500M business-combination agreement signed 2026-03-16; GNQ (Canadian TechBio/AI+quantum drug-discovery co.) is relocating HQ/labs to Greenville, with initial labs at Clemson's CUBEInC (Prisma Patewood campus) and full HQ in the City of Greenville to follow. Jobs remain undisclosed at every stage.</t>
+        </is>
+      </c>
+      <c r="J498" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K498" s="6" t="inlineStr">
+        <is>
+          <t>https://www.investing.com/news/sec-filings/ib-acquisition-stockholders-approve-extension-of-business-combination-deadline-93CH-4582632</t>
+        </is>
+      </c>
+      <c r="L498" s="6" t="inlineStr">
+        <is>
+          <t>Med-High (deal status and extension vote now confirmed; jobs still undisclosed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B499" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="C499" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D499" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E499" s="6" t="inlineStr">
+        <is>
+          <t>GE Vernova — gas turbine mfg (strong company-wide demand; no new local jobs figure)</t>
+        </is>
+      </c>
+      <c r="F499" s="6" t="inlineStr">
+        <is>
+          <t>650 total planned; ~200 hired past yr</t>
+        </is>
+      </c>
+      <c r="G499" s="6" t="inlineStr">
+        <is>
+          <t>$160M (Greenville)</t>
+        </is>
+      </c>
+      <c r="H499" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mixed (bulk likely sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I499" s="6" t="inlineStr">
+        <is>
+          <t>No new dated corporate confirmation of hires-to-date found this cycle (the 650-total/~200-hired-past-year figures remain the latest official statement). New wage-band context from job postings (Sept. 2026): Manufacturing Engineer $76-114k, Product Definition Engineer $80-120k, Customer Application Engineer (turbines) $98-164k, turbine technicians ~$70-90k -- a mixed band that straddles, but does not uniformly clear, the $100k threshold. ~69 open GE gas-turbine postings in Greenville as of Sept. 2026 consistent with continued hiring.</t>
+        </is>
+      </c>
+      <c r="J499" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K499" s="6" t="inlineStr">
+        <is>
+          <t>https://www.gevernova.com/news/press-releases/ge-vernova-announces-more-160-million-investment-greenville-facility</t>
+        </is>
+      </c>
+      <c r="L499" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B500" s="6" t="inlineStr">
+        <is>
+          <t>Laurens Co. (Laurens)</t>
+        </is>
+      </c>
+      <c r="C500" s="6" t="inlineStr">
+        <is>
+          <t>Laurens</t>
+        </is>
+      </c>
+      <c r="D500" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E500" s="6" t="inlineStr">
+        <is>
+          <t>Suniva Inc. — solar-cell manufacturing plant (capex reconciled)</t>
+        </is>
+      </c>
+      <c r="F500" s="6" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="G500" s="6" t="inlineStr">
+        <is>
+          <t>~$600M facility-specific (reconciled this cycle; distinct from the separate $835M corporate capital raise)</t>
+        </is>
+      </c>
+      <c r="H500" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred sub-$100k blended</t>
+        </is>
+      </c>
+      <c r="I500" s="6" t="inlineStr">
+        <is>
+          <t>Capital raise confirmed COMPLETED: Suniva closed an $835M debt+equity raise on/around 2026-09-17, enabling a capacity plan now described as "more than quadrupling" the Laurens facility to 4.5GW (bringing total company domestic capacity to 5.5GW alongside the existing ~1GW Georgia site). Facility-specific investment remains reconciled at ~$600M. Jobs still cited at 564 ("over 550"). Building shell confirmed complete; full completion now expected late 2027, full ramp 2028.</t>
+        </is>
+      </c>
+      <c r="J500" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="K500" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sfnet.com/home/industry-data-publications/the-secured-lender/tsl-express-daily-articles-news/tsl-express-daily-articles-news/2026/09/17/suniva-completes--835-million-capital-raise-to-build-second-major-u.s.-solar-cell-manufacturing-facility-and-more-than-quadruple-capacity-to-5.5-gw</t>
+        </is>
+      </c>
+      <c r="L500" s="6" t="inlineStr">
+        <is>
+          <t>High (capital raise and capacity plan now fully confirmed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B501" s="6" t="inlineStr">
+        <is>
+          <t>Ridgeville / Camp Hall</t>
+        </is>
+      </c>
+      <c r="C501" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley</t>
+        </is>
+      </c>
+      <c r="D501" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E501" s="6" t="inlineStr">
+        <is>
+          <t>Redwood Materials — battery-materials recycling campus</t>
+        </is>
+      </c>
+      <c r="F501" s="6" t="inlineStr">
+        <is>
+          <t>1,500 (over the next decade)</t>
+        </is>
+      </c>
+      <c r="G501" s="6" t="inlineStr">
+        <is>
+          <t>$3.5B</t>
+        </is>
+      </c>
+      <c r="H501" s="6" t="inlineStr">
+        <is>
+          <t>$27-75/hr stated (~$56k-156k) — upper tier clears $100k</t>
+        </is>
+      </c>
+      <c r="I501" s="6" t="inlineStr">
+        <is>
+          <t>Operational and actively hiring: 134 open roles as of Aug. 2026 (mechanical/chemical/automation engineers, maintenance technicians, production associates, financial analyst) at the 600-acre Camp Hall campus. Reconfirmed targets: $3.5B investment, 1,500 jobs over the decade, wages $27-$75/hr (~$56k-$156k annualized -- upper tier clears $100k, a continued strong housing-demand signal). No new headcount milestone beyond ongoing hiring activity.</t>
+        </is>
+      </c>
+      <c r="J501" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K501" s="6" t="inlineStr">
+        <is>
+          <t>https://startup.jobs/company/redwood-materials</t>
+        </is>
+      </c>
+      <c r="L501" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B502" s="6" t="inlineStr">
+        <is>
+          <t>Salisbury / Granite Industrial Park</t>
+        </is>
+      </c>
+      <c r="C502" s="6" t="inlineStr">
+        <is>
+          <t>Rowan</t>
+        </is>
+      </c>
+      <c r="D502" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E502" s="6" t="inlineStr">
+        <is>
+          <t>Jabil Inc. — advanced manufacturing (AI/data-center hardware)</t>
+        </is>
+      </c>
+      <c r="F502" s="6" t="inlineStr">
+        <is>
+          <t>1,181 (stated, over 5 yr)</t>
+        </is>
+      </c>
+      <c r="G502" s="6" t="inlineStr">
+        <is>
+          <t>~$264M near-term / ~$500M multi-year</t>
+        </is>
+      </c>
+      <c r="H502" s="6" t="inlineStr">
+        <is>
+          <t>$62,034 avg (stated) — sub-$100k</t>
+        </is>
+      </c>
+      <c r="I502" s="6" t="inlineStr">
+        <is>
+          <t>New timeline detail: the facility (2121 Heilig Road, Granite Industrial Park) is targeted to be operational "by the middle of 2026" -- an in-window ramp-up milestone -- with hiring to begin in 2026 and total investment complete by 12/31/2030. 25+ open roles were visible on Jabil's job portal as of mid-2026 (Production Manager, engineering roles), suggesting active hiring has begun. Wage ($62,034 avg) and jobs (1,181) figures unchanged, both well under the $100k threshold.</t>
+        </is>
+      </c>
+      <c r="J502" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K502" s="6" t="inlineStr">
+        <is>
+          <t>https://charlotteregion.com/news/jabil-selects-rowan-county-for-nearly-1200-new-jobs-and-500-million-multi-year-investment/</t>
+        </is>
+      </c>
+      <c r="L502" s="6" t="inlineStr">
+        <is>
+          <t>Medium (facts High; operational-start milestone not yet independently confirmed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B503" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington / US-421 corridor</t>
+        </is>
+      </c>
+      <c r="C503" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover</t>
+        </is>
+      </c>
+      <c r="D503" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E503" s="6" t="inlineStr">
+        <is>
+          <t>Protocase / 45Drives / ProtoSpace Mfg — precision manufacturing campus</t>
+        </is>
+      </c>
+      <c r="F503" s="6" t="inlineStr">
+        <is>
+          <t>~100 confirmed; company target 500+ total</t>
+        </is>
+      </c>
+      <c r="G503" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H503" s="6" t="inlineStr">
+        <is>
+          <t>$34,840-$41,409 stated for production/assembly roles (sub-$100k); corporate/engineering wage not disclosed</t>
+        </is>
+      </c>
+      <c r="I503" s="6" t="inlineStr">
+        <is>
+          <t>No confirmed updated headcount found this cycle (still ~100 confirmed against a 500+ company target). New context: the parent "Proto companies" group (Protocase, 45Drives, Protospace Mfg, Protomentum) is targeting $1B in annual revenue within 5 years, with "much of that growth" described as slated to happen in Wilmington -- a directional growth signal, but no updated headcount figure was disclosed alongside it.</t>
+        </is>
+      </c>
+      <c r="J503" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="K503" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wilmingtonbiz.com/wilmingtonbiz_magazine/2026/10/02/trends_to_watch_economic_development/27856</t>
+        </is>
+      </c>
+      <c r="L503" s="6" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B504" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington / US-421 corridor (Wilmington Trade Center)</t>
+        </is>
+      </c>
+      <c r="C504" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover</t>
+        </is>
+      </c>
+      <c r="D504" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E504" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington Trade Center — multi-tenant industrial park expansion</t>
+        </is>
+      </c>
+      <c r="F504" s="6" t="inlineStr">
+        <is>
+          <t>1,500+ (aggregate, long-run park build-out; not a single employer's committed headcount)</t>
+        </is>
+      </c>
+      <c r="G504" s="6" t="inlineStr">
+        <is>
+          <t>$300-400M added tax base (park build-out); ~$3.3M county incentive</t>
+        </is>
+      </c>
+      <c r="H504" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I504" s="6" t="inlineStr">
+        <is>
+          <t>New in-window leasing/construction activity beyond the already-tracked Jan. 2026 leases: site work has started on Building 7 (~153,000 sq ft), targeted for late-summer 2026 completion. No job-count disclosures for any tenant found this cycle -- remains an aggregate industrial-park estimate, not a single-employer commitment.</t>
+        </is>
+      </c>
+      <c r="J504" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K504" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wilmingtonbiz.com/real_estate_-_commercial/2026/03/11/industrial_projects_on_the_rise/27293</t>
+        </is>
+      </c>
+      <c r="L504" s="6" t="inlineStr">
+        <is>
+          <t>Medium (aggregate park estimate, not a single-employer commitment)</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B505" s="6" t="inlineStr">
+        <is>
+          <t>Burlington / Alamance-Guilford line</t>
+        </is>
+      </c>
+      <c r="C505" s="6" t="inlineStr">
+        <is>
+          <t>Alamance</t>
+        </is>
+      </c>
+      <c r="D505" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E505" s="6" t="inlineStr">
+        <is>
+          <t>Ahold Delhaize USA (Food Lion parent) — distribution center</t>
+        </is>
+      </c>
+      <c r="F505" s="6" t="inlineStr">
+        <is>
+          <t>500-505</t>
+        </is>
+      </c>
+      <c r="G505" s="6" t="inlineStr">
+        <is>
+          <t>$860M</t>
+        </is>
+      </c>
+      <c r="H505" s="6" t="inlineStr">
+        <is>
+          <t>~$60k-$67k avg (Estimated/Inferred, sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I505" s="6" t="inlineStr">
+        <is>
+          <t>No new jobs/wage figure found. New detail: Guilford County commissioners separately approved a $17.9M incentive package for this same project (referred to in some coverage as "Project Titan"), alongside the already-tracked Alamance-side groundbreaking (2/16/26) -- sources differ on which county's government approved incentives vs. which county the physical site sits in; flagged as a county-attribution ambiguity worth resolving against parcel records. Construction confirmed continuing on the $860M, 1M+ sq ft distribution center; opening still targeted 2029.</t>
+        </is>
+      </c>
+      <c r="J505" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K505" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wfmynews2.com/article/news/local/city-county-leaders-say-860-million-food-lion-project-will-boost-jobs-and-tax-base-burlington-guilford/83-79b9ba0f-72cc-4c87-a0e9-cd0e072d4963</t>
+        </is>
+      </c>
+      <c r="L505" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B506" s="6" t="inlineStr">
+        <is>
+          <t>Pender / New Hanover</t>
+        </is>
+      </c>
+      <c r="C506" s="6" t="inlineStr">
+        <is>
+          <t>Pender (+New Hanover)</t>
+        </is>
+      </c>
+      <c r="D506" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E506" s="6" t="inlineStr">
+        <is>
+          <t>Amazon — robotics fulfillment center (still not formally confirmed open)</t>
+        </is>
+      </c>
+      <c r="F506" s="6" t="inlineStr">
+        <is>
+          <t>1,000+</t>
+        </is>
+      </c>
+      <c r="G506" s="6" t="inlineStr">
+        <is>
+          <t>$350M</t>
+        </is>
+      </c>
+      <c r="H506" s="6" t="inlineStr">
+        <is>
+          <t>~$22/hr avg (Estimated/Inferred ~$45,760/yr, sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I506" s="6" t="inlineStr">
+        <is>
+          <t>Positive, concrete movement this cycle: Amazon began hiring in summer 2026 for the robotics fulfillment center (1,000+ jobs, 3.2M sq ft, Amazon's largest NC site) and is starting hiring soon for an adjacent 142,000 sq ft delivery station (~100 more full-time jobs). Both facilities are reported "on track to open in time for the holiday season" (i.e., Q4 2026), refining the prior cycle's vaguer "Fall 2026" target language. No formal grand-opening/ribbon-cutting article found yet.</t>
+        </is>
+      </c>
+      <c r="J506" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K506" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wilmingtonbiz.com/more_news/2026/03/18/amazon_facility_regional_projects_forecast_to_bring_hundreds_of_jobs_to_wilmington_area/27315</t>
+        </is>
+      </c>
+      <c r="L506" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B507" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="C507" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D507" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E507" s="6" t="inlineStr">
+        <is>
+          <t>EnerSys — lithium-cell manufacturing facility (scope confirmed via SEC filing; jobs still undisclosed)</t>
+        </is>
+      </c>
+      <c r="F507" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed for the revised project (the pre-restructuring ~500-job 2024 figure must NOT be carried forward)</t>
+        </is>
+      </c>
+      <c r="G507" s="6" t="inlineStr">
+        <is>
+          <t>~$650M gross / ~$500M net (reconciled this cycle); $150M DOE grant + up to $200M state/local incentives</t>
+        </is>
+      </c>
+      <c r="H507" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I507" s="6" t="inlineStr">
+        <is>
+          <t>Confirms + adds detail to the known 2026-07-23 rescoping: scope cut from ~4-5 GWh to up to 1 GWh, smaller footprint, refocused on aerospace/defense + specialized industrial applications. New detail: revised DOE grant approx $150M (subject to final documentation) plus up to $200M state/local incentives; total net investment now estimated approx $500M (down from the original scope); construction targeted to begin H1 of EnerSys fiscal year 2028; full production approx 3 years after construction starts; EnerSys is also ending its tech partnership with Verkor SAS for this project in favor of an aerospace/defense-sector technology partner. Jobs remain undisclosed.</t>
+        </is>
+      </c>
+      <c r="J507" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K507" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/0001289308/000128930826000014/exhibit991-planlithiumxion.htm</t>
+        </is>
+      </c>
+      <c r="L507" s="6" t="inlineStr">
+        <is>
+          <t>Medium (restructuring/financing now SEC-confirmed; jobs figure still undisclosed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B508" s="6" t="inlineStr">
+        <is>
+          <t>North Charleston</t>
+        </is>
+      </c>
+      <c r="C508" s="6" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="D508" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E508" s="6" t="inlineStr">
+        <is>
+          <t>SC Ports Authority — Leatherman Terminal (pause remains in effect)</t>
+        </is>
+      </c>
+      <c r="F508" s="6" t="inlineStr">
+        <is>
+          <t>400 direct + ~1,200 indirect</t>
+        </is>
+      </c>
+      <c r="G508" s="6" t="inlineStr">
+        <is>
+          <t>$1.2B</t>
+        </is>
+      </c>
+      <c r="H508" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I508" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window update found this cycle despite a recheck; prior facts reconfirmed unchanged. Still paused with no confirmed reopening date; SC Ports has stated reopening depends on future cargo demand/cost competitiveness and describes it as a "short-term pause," not permanent. The earlier ambiguous "reopening with major weekly Asia service" headline is now confirmed to be recycled coverage of the Sept. 2024 post-ILA-dispute reopening, not a 2026 development — treat as noise going forward.</t>
+        </is>
+      </c>
+      <c r="J508" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K508" s="6" t="inlineStr">
+        <is>
+          <t>https://scdailygazette.com/2026/06/25/sc-ports-temporarily-halts-leatherman-operations-in-face-of-high-costs-waning-demand/</t>
+        </is>
+      </c>
+      <c r="L508" s="6" t="inlineStr">
+        <is>
+          <t>Med-High (status confirmed; recycled-headline ambiguity resolved)</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B509" s="6" t="inlineStr">
+        <is>
+          <t>Rowan County</t>
+        </is>
+      </c>
+      <c r="C509" s="6" t="inlineStr">
+        <is>
+          <t>Rowan</t>
+        </is>
+      </c>
+      <c r="D509" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E509" s="6" t="inlineStr">
+        <is>
+          <t>American Eagle Outfitters</t>
+        </is>
+      </c>
+      <c r="F509" s="6" t="inlineStr">
+        <is>
+          <t>200+ (state figure; county vote cited 258)</t>
+        </is>
+      </c>
+      <c r="G509" s="6" t="inlineStr">
+        <is>
+          <t>$41M</t>
+        </is>
+      </c>
+      <c r="H509" s="6" t="inlineStr">
+        <is>
+          <t>$57,351 avg (stated)</t>
+        </is>
+      </c>
+      <c r="I509" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window update found this cycle despite a recheck; prior facts reconfirmed unchanged. No update found this cycle beyond a minor new detail: a $150,000 One NC Fund grant tied to the project. 472,890 sq ft facility at 1415 Peeler Road (Innovation Logistics Center, Salisbury); Q1 2027 ops start still targeted.</t>
+        </is>
+      </c>
+      <c r="J509" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K509" s="6" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nc.gov/news/press-releases/2026/07/17/governor-stein-announces-american-eagle-outfitters-inc-selects-rowan-county-41-million-southeast</t>
+        </is>
+      </c>
+      <c r="L509" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B510" s="6" t="inlineStr">
+        <is>
+          <t>Wake Co. (aggregate)</t>
+        </is>
+      </c>
+      <c r="C510" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D510" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E510" s="6" t="inlineStr">
+        <is>
+          <t>County jobs pipeline (EDGE 7, 52 projects)</t>
+        </is>
+      </c>
+      <c r="F510" s="6" t="inlineStr">
+        <is>
+          <t>~11,000 (pipeline)</t>
+        </is>
+      </c>
+      <c r="G510" s="6" t="inlineStr">
+        <is>
+          <t>$11B</t>
+        </is>
+      </c>
+      <c r="H510" s="6" t="inlineStr">
+        <is>
+          <t>Mixed (office-skewed)</t>
+        </is>
+      </c>
+      <c r="I510" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window update found this cycle despite a recheck; prior facts reconfirmed unchanged. Discrepancy flagged last cycle resolved: the previously-cited ~$5.6B/~10,800-job figure belongs to the prior 5-year cycle (EDGE6, completed-program results), not EDGE7. EDGE7's current active pipeline remains 52 projects / $11B+ / ~11,000 jobs (Wake Co. Econ Dev director Michael Haley, Feb. 4, 2026). The underlying "New and Expanding" PDF at e1.nmcdn.io remains inaccessible (egress-blocked) for line-item reconciliation.</t>
+        </is>
+      </c>
+      <c r="J510" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K510" s="6" t="inlineStr">
+        <is>
+          <t>https://nchospitalityalliance.com/wake-county-pursues-11-billion-jobs-pipeline/</t>
+        </is>
+      </c>
+      <c r="L510" s="6" t="inlineStr">
+        <is>
+          <t>Med (pipeline scope now clarified; underlying PDF still unverified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B511" s="6" t="inlineStr">
+        <is>
+          <t>Garner</t>
+        </is>
+      </c>
+      <c r="C511" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D511" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E511" s="6" t="inlineStr">
+        <is>
+          <t>Gregory Poole Equipment Co. — HQ relocation</t>
+        </is>
+      </c>
+      <c r="F511" s="6" t="inlineStr">
+        <is>
+          <t>500+ (5 yr)</t>
+        </is>
+      </c>
+      <c r="G511" s="6" t="inlineStr">
+        <is>
+          <t>$347M</t>
+        </is>
+      </c>
+      <c r="H511" s="6" t="inlineStr">
+        <is>
+          <t>~$75,381 companywide avg (Estimated/Inferred, sub-$100k)</t>
+        </is>
+      </c>
+      <c r="I511" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window update found this cycle despite a recheck; prior facts reconfirmed unchanged. No groundbreaking confirmed this cycle; project remains at "construction expected within 24 months" per Oct. 2025 reporting on the 130-acre site purchased Feb. 2025.</t>
+        </is>
+      </c>
+      <c r="J511" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K511" s="6" t="inlineStr">
+        <is>
+          <t>https://www.garnernc.gov/Home/Components/News/News/2344/17</t>
+        </is>
+      </c>
+      <c r="L511" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B512" s="6" t="inlineStr">
+        <is>
+          <t>Kernersville</t>
+        </is>
+      </c>
+      <c r="C512" s="6" t="inlineStr">
+        <is>
+          <t>Forsyth</t>
+        </is>
+      </c>
+      <c r="D512" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E512" s="6" t="inlineStr">
+        <is>
+          <t>John Deere — excavator plant (relocating from Japan)</t>
+        </is>
+      </c>
+      <c r="F512" s="6" t="inlineStr">
+        <is>
+          <t>150+</t>
+        </is>
+      </c>
+      <c r="G512" s="6" t="inlineStr">
+        <is>
+          <t>$70M</t>
+        </is>
+      </c>
+      <c r="H512" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Inferred skilled-mfg)</t>
+        </is>
+      </c>
+      <c r="I512" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window update found this cycle despite a recheck; prior facts reconfirmed unchanged. Construction confirmed continuing on the west campus (small-excavator assembly); company messaging still targets opening "in the next year." No new milestone beyond what was already tracked.</t>
+        </is>
+      </c>
+      <c r="J512" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K512" s="6" t="inlineStr">
+        <is>
+          <t>https://www.deere.com/en-us/our-company/locations/factories/kernersville</t>
+        </is>
+      </c>
+      <c r="L512" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B513" s="6" t="inlineStr">
+        <is>
+          <t>Orangeburg / I-26</t>
+        </is>
+      </c>
+      <c r="C513" s="6" t="inlineStr">
+        <is>
+          <t>Orangeburg</t>
+        </is>
+      </c>
+      <c r="D513" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E513" s="6" t="inlineStr">
+        <is>
+          <t>Ferrara Candy — new mfg + corporate site (groundbreaking confirmed)</t>
+        </is>
+      </c>
+      <c r="F513" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (10 yr)</t>
+        </is>
+      </c>
+      <c r="G513" s="6" t="inlineStr">
+        <is>
+          <t>$675M</t>
+        </is>
+      </c>
+      <c r="H513" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; confectionery = workforce-tier</t>
+        </is>
+      </c>
+      <c r="I513" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window update found this cycle despite a recheck; prior facts reconfirmed unchanged. Material milestone: groundbreaking held May 18-19, 2026 at the Hwy 21 &amp; Rowesville Rd site (750,000 sq ft); first production lines expected online Q1 2029.</t>
+        </is>
+      </c>
+      <c r="J513" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K513" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wistv.com/2026/05/19/ferrara-candy-company-breaks-ground-orangeburg/</t>
+        </is>
+      </c>
+      <c r="L513" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B514" s="6" t="inlineStr">
+        <is>
+          <t>Columbia / BullStreet</t>
+        </is>
+      </c>
+      <c r="C514" s="6" t="inlineStr">
+        <is>
+          <t>Richland</t>
+        </is>
+      </c>
+      <c r="D514" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E514" s="6" t="inlineStr">
+        <is>
+          <t>AMAROK — new HQ (perimeter security)</t>
+        </is>
+      </c>
+      <c r="F514" s="6" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="G514" s="6" t="inlineStr">
+        <is>
+          <t>$69M</t>
+        </is>
+      </c>
+      <c r="H514" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; HQ/professional (portion likely $100k+)</t>
+        </is>
+      </c>
+      <c r="I514" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window update found this cycle despite a recheck; prior facts reconfirmed unchanged. No groundbreaking confirmation found this cycle; all available coverage still describes the project as "construction expected to begin in 2026" with design plans still being finalized. Online by end of 2028 unchanged.</t>
+        </is>
+      </c>
+      <c r="J514" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K514" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.sc.gov/news/2026-03/amarok-expands-richland-county-operations-new-headquarters</t>
+        </is>
+      </c>
+      <c r="L514" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B515" s="6" t="inlineStr">
+        <is>
+          <t>North Charleston</t>
+        </is>
+      </c>
+      <c r="C515" s="6" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="D515" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E515" s="6" t="inlineStr">
+        <is>
+          <t>Boeing 787 — production-rate ramp</t>
+        </is>
+      </c>
+      <c r="F515" s="6" t="inlineStr">
+        <is>
+          <t>1,000+ new jobs over 5 yrs (unchanged); campus total ~9,059</t>
+        </is>
+      </c>
+      <c r="G515" s="6" t="inlineStr">
+        <is>
+          <t>$1B+ (existing)</t>
+        </is>
+      </c>
+      <c r="H515" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred mixed (production ~$70-85k; eng. above $100k)</t>
+        </is>
+      </c>
+      <c r="I515" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window update found this cycle despite a recheck; prior facts reconfirmed unchanged. No newer production-rate or headcount figure found this cycle beyond the already-tracked Aug. 27, 2026 apprenticeship-doubling announcement (500-&gt;1,000+ apprentices, made jointly with Acting US Labor Secretary Keith Sonderling).</t>
+        </is>
+      </c>
+      <c r="J515" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K515" s="6" t="inlineStr">
+        <is>
+          <t>https://www.live5news.com/2026/08/27/boeing-double-apprenticeship-program-north-charleston-plant/</t>
+        </is>
+      </c>
+      <c r="L515" s="6" t="inlineStr">
+        <is>
+          <t>Med-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B516" s="6" t="inlineStr">
+        <is>
+          <t>Goose Creek</t>
+        </is>
+      </c>
+      <c r="C516" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley</t>
+        </is>
+      </c>
+      <c r="D516" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E516" s="6" t="inlineStr">
+        <is>
+          <t>HII (Newport News Shipbuilding) — no site-specific new figure</t>
+        </is>
+      </c>
+      <c r="F516" s="6" t="inlineStr">
+        <is>
+          <t>~475 employees (unchanged)</t>
+        </is>
+      </c>
+      <c r="G516" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="H516" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I516" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window update found this cycle despite a recheck; prior facts reconfirmed unchanged. No Goose Creek-specific new expansion figure found this cycle beyond the Jan. 22, 2026 one-year-anniversary milestone (itself pre-window), which noted hopes for headcount to "rise by the hundreds" without a confirmed new number.</t>
+        </is>
+      </c>
+      <c r="J516" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K516" s="6" t="inlineStr">
+        <is>
+          <t>https://www.hii.com/news/hii-closes-on-asset-acquisition-to-expand-shipbuilding-capacity</t>
+        </is>
+      </c>
+      <c r="L516" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B517" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="C517" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg</t>
+        </is>
+      </c>
+      <c r="D517" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E517" s="6" t="inlineStr">
+        <is>
+          <t>Siemens Smart Infrastructure</t>
+        </is>
+      </c>
+      <c r="F517" s="6" t="inlineStr">
+        <is>
+          <t>~150</t>
+        </is>
+      </c>
+      <c r="G517" s="6" t="inlineStr">
+        <is>
+          <t>$165M</t>
+        </is>
+      </c>
+      <c r="H517" s="6" t="inlineStr">
+        <is>
+          <t>Avg $78,811/yr ($37.89/hr); 90th pct ~$100k (Estimated/Inferred)</t>
+        </is>
+      </c>
+      <c r="I517" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window update found this cycle despite a recheck; prior facts reconfirmed unchanged. No material update found this cycle beyond the March 2026 announcement (&gt;$165M Carolinas-wide investment in electrical products for data centers).</t>
+        </is>
+      </c>
+      <c r="J517" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K517" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wspa.com/news/local-news/siemens-to-expand-production-in-spartanburg-co-add-150-jobs/</t>
+        </is>
+      </c>
+      <c r="L517" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B518" s="6" t="inlineStr">
+        <is>
+          <t>Gray Court</t>
+        </is>
+      </c>
+      <c r="C518" s="6" t="inlineStr">
+        <is>
+          <t>Laurens</t>
+        </is>
+      </c>
+      <c r="D518" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E518" s="6" t="inlineStr">
+        <is>
+          <t>Aptiv Services US — Connexial Center</t>
+        </is>
+      </c>
+      <c r="F518" s="6" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="G518" s="6" t="inlineStr">
+        <is>
+          <t>$120.8M</t>
+        </is>
+      </c>
+      <c r="H518" s="6" t="inlineStr">
+        <is>
+          <t>~$49-76k technician range (Estimated/Inferred)</t>
+        </is>
+      </c>
+      <c r="I518" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window update found this cycle despite a recheck; prior facts reconfirmed unchanged. No Aptiv-specific update found this cycle ("Project Oracle" details reconfirmed unchanged). Shamrock Technologies' HQ relocation into the same park remains a park-level momentum signal only.</t>
+        </is>
+      </c>
+      <c r="J518" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K518" s="6" t="inlineStr">
+        <is>
+          <t>https://growlaurenscounty.com/news/article/momentum-continues-at-the-connexial-center-with-aptivs-investment</t>
+        </is>
+      </c>
+      <c r="L518" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B519" s="6" t="inlineStr">
+        <is>
+          <t>Easley (Anderson/Pickens border)</t>
+        </is>
+      </c>
+      <c r="C519" s="6" t="inlineStr">
+        <is>
+          <t>Anderson</t>
+        </is>
+      </c>
+      <c r="D519" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E519" s="6" t="inlineStr">
+        <is>
+          <t>Signature Foods USA</t>
+        </is>
+      </c>
+      <c r="F519" s="6" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="G519" s="6" t="inlineStr">
+        <is>
+          <t>$11.5M</t>
+        </is>
+      </c>
+      <c r="H519" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred sub-$50k (food mfg.)</t>
+        </is>
+      </c>
+      <c r="I519" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window update found this cycle despite a recheck; prior facts reconfirmed unchanged. Operations confirmed online and actively hiring toward the 202-job target; no headcount change found this cycle.</t>
+        </is>
+      </c>
+      <c r="J519" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K519" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/greenville/business/easley-anderson-county-signature-foods-investment/article_1d618a58-af96-435a-a05c-7cc6f9253a83.html</t>
+        </is>
+      </c>
+      <c r="L519" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B520" s="6" t="inlineStr">
+        <is>
+          <t>Piedmont</t>
+        </is>
+      </c>
+      <c r="C520" s="6" t="inlineStr">
+        <is>
+          <t>Greenville</t>
+        </is>
+      </c>
+      <c r="D520" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E520" s="6" t="inlineStr">
+        <is>
+          <t>Isuzu North America — truck assembly plant</t>
+        </is>
+      </c>
+      <c r="F520" s="6" t="inlineStr">
+        <is>
+          <t>700+</t>
+        </is>
+      </c>
+      <c r="G520" s="6" t="inlineStr">
+        <is>
+          <t>$280M</t>
+        </is>
+      </c>
+      <c r="H520" s="6" t="inlineStr">
+        <is>
+          <t>Estimated/Inferred: assembly $35-56k, engineers $79-108k — blended sub-$100k</t>
+        </is>
+      </c>
+      <c r="I520" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window update found this cycle despite a recheck; prior facts reconfirmed unchanged. No new hiring event found beyond the already-tracked July 8, 2026 direct-hire event; company's stated goal remains 150 employees by end of 2026, 2027 launch still targeted.</t>
+        </is>
+      </c>
+      <c r="J520" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K520" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ccjdigital.com/business/article/15767928/isuzu-building-280m-truck-plant-in-south-carolina-creating-700-jobs</t>
+        </is>
+      </c>
+      <c r="L520" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B521" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="C521" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D521" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E521" s="6" t="inlineStr">
+        <is>
+          <t>PSA Airlines — Charlotte headquarters</t>
+        </is>
+      </c>
+      <c r="F521" s="6" t="inlineStr">
+        <is>
+          <t>~400 (450+ total team members at HQ)</t>
+        </is>
+      </c>
+      <c r="G521" s="6" t="inlineStr">
+        <is>
+          <t>Not itemized</t>
+        </is>
+      </c>
+      <c r="H521" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (Estimated/Inferred mixed corporate/admin/ops, likely sub-$100k blended)</t>
+        </is>
+      </c>
+      <c r="I521" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window update found this cycle despite a recheck; prior facts reconfirmed unchanged. The "80% of ~250 net-new positions filled" figure is reconfirmed with no fresher update; the math implies ~50 new-hire slots remaining. The previously-flagged "still seeking 170 more employees" figure could not be found in any current source and is now treated as an unsupported legacy carryover — dropped from tracking.</t>
+        </is>
+      </c>
+      <c r="J521" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K521" s="6" t="inlineStr">
+        <is>
+          <t>https://psaairlines.com/psa-airlines-officially-opens-headquarters-in-charlotte-to-over-450-team-members/</t>
+        </is>
+      </c>
+      <c r="L521" s="6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B522" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Steele Creek</t>
+        </is>
+      </c>
+      <c r="C522" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D522" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E522" s="6" t="inlineStr">
+        <is>
+          <t>Maersk — North American HQ (hiring ramp delayed one year)</t>
+        </is>
+      </c>
+      <c r="F522" s="6" t="inlineStr">
+        <is>
+          <t>520 (confirmed, stated)</t>
+        </is>
+      </c>
+      <c r="G522" s="6" t="inlineStr">
+        <is>
+          <t>$16M</t>
+        </is>
+      </c>
+      <c r="H522" s="6" t="inlineStr">
+        <is>
+          <t>$100,962 avg (stated) — clears $100k bar</t>
+        </is>
+      </c>
+      <c r="I522" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window update found this cycle despite a recheck; prior facts reconfirmed unchanged. The NC Economic Investment Committee's approval (Feb. 24, 2026, already tracked) is now understood to reflect a full one-year push of the hiring window, from 2026-2028 to 2027-2029, due to renovation delays at the Arrowpoint Boulevard space. Investment and wage pledges unchanged; no construction-start news found.</t>
+        </is>
+      </c>
+      <c r="J522" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K522" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/maersk-delays-charlotte-headquarters-plan-hiring-520-workers-by-1-year/</t>
+        </is>
+      </c>
+      <c r="L522" s="6" t="inlineStr">
+        <is>
+          <t>High (facts); milestone timing at window edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B523" s="6" t="inlineStr">
+        <is>
+          <t>Morrisville / RTP-adjacent</t>
+        </is>
+      </c>
+      <c r="C523" s="6" t="inlineStr">
+        <is>
+          <t>Wake</t>
+        </is>
+      </c>
+      <c r="D523" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E523" s="6" t="inlineStr">
+        <is>
+          <t>Forge Nano — battery-manufacturing expansion ("America's Battery Gigafactory")</t>
+        </is>
+      </c>
+      <c r="F523" s="6" t="inlineStr">
+        <is>
+          <t>250+ (projected, incremental to an existing 200-job 2023 commitment)</t>
+        </is>
+      </c>
+      <c r="G523" s="6" t="inlineStr">
+        <is>
+          <t>~$300M (incl. $100M DOE non-dilutive funding)</t>
+        </is>
+      </c>
+      <c r="H523" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed for the 2026 expansion</t>
+        </is>
+      </c>
+      <c r="I523" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window update found this cycle despite a recheck; prior facts reconfirmed unchanged. New detail: Samsung SDI made a $20M strategic investment in Forge Nano in July 2026 alongside a conditional cell-procurement agreement beginning 2028, on top of the already-tracked Sept. 17, 2026 Voltaiq (AI battery-software) partnership. Aug. 19, 2026 groundbreaking stands; production still targeted 2028.</t>
+        </is>
+      </c>
+      <c r="J523" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K523" s="6" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/09/17/3363983/</t>
+        </is>
+      </c>
+      <c r="L523" s="6" t="inlineStr">
+        <is>
+          <t>High (partnerships/dates corroborated); Low (wage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B524" s="6" t="inlineStr">
+        <is>
+          <t>Wilmington</t>
+        </is>
+      </c>
+      <c r="C524" s="6" t="inlineStr">
+        <is>
+          <t>New Hanover</t>
+        </is>
+      </c>
+      <c r="D524" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E524" s="6" t="inlineStr">
+        <is>
+          <t>GE Hitachi / Global Nuclear Fuel — GNF4 fuel line</t>
+        </is>
+      </c>
+      <c r="F524" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="G524" s="6" t="inlineStr">
+        <is>
+          <t>Not itemized</t>
+        </is>
+      </c>
+      <c r="H524" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I524" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window update found this cycle despite a recheck; prior facts reconfirmed unchanged. No update found this cycle; job count for the GNF4 fuel-line program specifically remains undisclosed beyond the company's description of needing "several new positions" in engineering, supply chain, and manufacturing.</t>
+        </is>
+      </c>
+      <c r="J524" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K524" s="6" t="inlineStr">
+        <is>
+          <t>https://www.gevernova.com/news/press-releases/global-nuclear-fuel-introduces-next-generation-fuel-product</t>
+        </is>
+      </c>
+      <c r="L524" s="6" t="inlineStr">
+        <is>
+          <t>Low-Med (indirect signal only, no discrete jobs figure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B525" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Ballantyne</t>
+        </is>
+      </c>
+      <c r="C525" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D525" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E525" s="6" t="inlineStr">
+        <is>
+          <t>TD Bank — Ballantyne office expansion</t>
+        </is>
+      </c>
+      <c r="F525" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed (an Estimated/Inferred ~430 net-new-seat capacity figure can be calculated from 540 capacity minus ~111 prior seats, but this is capacity headroom, not a confirmed hiring commitment)</t>
+        </is>
+      </c>
+      <c r="G525" s="6" t="inlineStr">
+        <is>
+          <t>Not itemized</t>
+        </is>
+      </c>
+      <c r="H525" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I525" s="6" t="inlineStr">
+        <is>
+          <t>No new in-window update found this cycle despite a recheck; prior facts reconfirmed unchanged. Grand-opening ribbon-cutting reconfirmed as having occurred Sept. 2, 2026 at the Harris Building (91,464 sf, capacity up to 540, houses finance/audit/compliance/regulatory/legal), after ~2 years of construction. No update beyond what was already tracked; TD has still never disclosed a jobs or wage figure.</t>
+        </is>
+      </c>
+      <c r="J525" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K525" s="6" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/local/charlotte/2026/09/02/td-bank-expansion-ballantyne</t>
+        </is>
+      </c>
+      <c r="L525" s="6" t="inlineStr">
+        <is>
+          <t>Medium (occupancy/capacity confirmed; jobs/wage undisclosed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B526" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / Ballantyne</t>
+        </is>
+      </c>
+      <c r="C526" s="6" t="inlineStr">
+        <is>
+          <t>Mecklenburg</t>
+        </is>
+      </c>
+      <c r="D526" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E526" s="6" t="inlineStr">
+        <is>
+          <t>Daimler Truck Financial Services — North American HQ (NEW to Watch)</t>
+        </is>
+      </c>
+      <c r="F526" s="6" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G526" s="6" t="inlineStr">
+        <is>
+          <t>$7.8M</t>
+        </is>
+      </c>
+      <c r="H526" s="6" t="inlineStr">
+        <is>
+          <t>$133,940 avg (stated) — clears $100k easily</t>
+        </is>
+      </c>
+      <c r="I526" s="6" t="inlineStr">
+        <is>
+          <t>NEW to Watch: 193 newly created jobs + 83 relocated (from MI/TX) = 276 total; opened new North American HQ at the 10-story Boyle Building, 13034 Ballantyne Corporate Place, with a ribbon-cutting 2026-09-29/grand opening 2026-10-01 (same week as Capital Group's expansion). Very high average wage but job count is below the 500-job Ranked threshold.</t>
+        </is>
+      </c>
+      <c r="J526" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="K526" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/daimler-truck-financial-services-bringing-276-high-paying-jobs-to-charlotte/</t>
+        </is>
+      </c>
+      <c r="L526" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B527" s="6" t="inlineStr">
+        <is>
+          <t>Moncure</t>
+        </is>
+      </c>
+      <c r="C527" s="6" t="inlineStr">
+        <is>
+          <t>Chatham</t>
+        </is>
+      </c>
+      <c r="D527" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E527" s="6" t="inlineStr">
+        <is>
+          <t>VinFast — EV assembly megasite (AT RISK — incentive agreement terminated)</t>
+        </is>
+      </c>
+      <c r="F527" s="6" t="inlineStr">
+        <is>
+          <t>Up to 7,500 originally projected; current confirmed on-site headcount not disclosed</t>
+        </is>
+      </c>
+      <c r="G527" s="6" t="inlineStr">
+        <is>
+          <t>~$4B (original); company booked a $235.6M impairment on the postponed plant</t>
+        </is>
+      </c>
+      <c r="H527" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="I527" s="6" t="inlineStr">
+        <is>
+          <t>NEW to Watch, flagged AT RISK: the State of NC sued VinFast on 2026-05-21 to regain control of the Chatham County megasite over missed construction/job-creation deadlines tied to one of the largest incentive packages in state history; Chatham County's Board of Commissioners voted ~2026-07-31 to terminate its $400M economic-development agreement with VinFast. VinFast says it intends to resume construction on its 782,255 sq ft facility before year-end 2026, with vehicle production now targeted for 2028 (originally late 2025). This is currently a negative/troubled signal for Chatham County housing demand, not a confirmed driver — tracked for status changes given the project's scale.</t>
+        </is>
+      </c>
+      <c r="J527" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="K527" s="6" t="inlineStr">
+        <is>
+          <t>https://chathamjournal.com/2026/07/31/chatham-county-to-terminate-400m-vinfast-agreement/amp/</t>
+        </is>
+      </c>
+      <c r="L527" s="6" t="inlineStr">
+        <is>
+          <t>Low-Medium (project status highly uncertain; incentive agreement terminated, litigation ongoing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B528" s="6" t="inlineStr">
+        <is>
+          <t>Honea Path</t>
+        </is>
+      </c>
+      <c r="C528" s="6" t="inlineStr">
+        <is>
+          <t>Anderson</t>
+        </is>
+      </c>
+      <c r="D528" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E528" s="6" t="inlineStr">
+        <is>
+          <t>Adeptus USA — wood products (milwork/paneling/moulding/shiplap) manufacturing (NEW to Watch)</t>
+        </is>
+      </c>
+      <c r="F528" s="6" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="G528" s="6" t="inlineStr">
+        <is>
+          <t>$215.56M</t>
+        </is>
+      </c>
+      <c r="H528" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed; Estimated/Inferred low (SC wood-products/millwork manufacturing roles typically run ~$35k-$50k/yr per BLS wood-products production occupation data) — basis: industry/occupation comparison, sub-$100k</t>
+        </is>
+      </c>
+      <c r="I528" s="6" t="inlineStr">
+        <is>
+          <t>NEW to Watch: reusing a shuttered textile mill in rural Honea Path (~25 mi south of Greenville); $850,000 SC Closing Fund grant to Anderson County plus job-development credits and a reduced property-tax rate over 40 years. Operations expected to begin Q2 2027. 217 jobs clears the 200-job Watch floor but wage is well below $100k and the rural/workforce-tier nature limits higher-end housing-demand relevance.</t>
+        </is>
+      </c>
+      <c r="J528" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="K528" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.sc.gov/news/2026-10/adeptus-usa-selects-anderson-county-establish-first-south-carolina-operation</t>
+        </is>
+      </c>
+      <c r="L528" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B529" s="6" t="inlineStr">
+        <is>
+          <t>Mebane</t>
+        </is>
+      </c>
+      <c r="C529" s="6" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="D529" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E529" s="6" t="inlineStr">
+        <is>
+          <t>Morinaga America Foods — Hi-Chew candy factory (ribbon-cutting; NEW to Watch)</t>
+        </is>
+      </c>
+      <c r="F529" s="6" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="G529" s="6" t="inlineStr">
+        <is>
+          <t>$136M</t>
+        </is>
+      </c>
+      <c r="H529" s="6" t="inlineStr">
+        <is>
+          <t>$48,912 avg (stated) — well below $100k</t>
+        </is>
+      </c>
+      <c r="I529" s="6" t="inlineStr">
+        <is>
+          <t>NEW to Watch: original expansion announced/groundbreaking July 2024 (pre-window), but Gov. Stein held an in-window ribbon-cutting ceremony 2026-04-21 marking the facility's opening. Low wage and limited scale mean minimal housing-demand relevance (workforce-tier manufacturing); included for completeness given the in-window milestone and 200+ job count.</t>
+        </is>
+      </c>
+      <c r="J529" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="K529" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2026/04/21/governor-stein-spotlights-north-carolinas-manufacturing-workforce-morinaga-america-foods-inc-ribbon</t>
+        </is>
+      </c>
+      <c r="L529" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -52245,7 +57415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H200"/>
+  <dimension ref="A1:H248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -60655,6 +65825,2022 @@
       <c r="H200" s="6" t="inlineStr">
         <is>
           <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B201" s="6" t="inlineStr">
+        <is>
+          <t>RTI International — research-funding layoffs</t>
+        </is>
+      </c>
+      <c r="C201" s="6" t="inlineStr">
+        <is>
+          <t>Research Triangle Park</t>
+        </is>
+      </c>
+      <c r="D201" s="6" t="inlineStr">
+        <is>
+          <t>NC (Durham)</t>
+        </is>
+      </c>
+      <c r="E201" s="6" t="inlineStr">
+        <is>
+          <t>~200 (100+ in NC) (layoffs)</t>
+        </is>
+      </c>
+      <c r="F201" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G201" s="6" t="inlineStr">
+        <is>
+          <t>Negative signal: cuts tied to federal research-funding pullback; layoff, not an expansion.</t>
+        </is>
+      </c>
+      <c r="H201" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/10/rti-international-cuts-200-more-jobs-as-federal-research-money-dries-up/</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B202" s="6" t="inlineStr">
+        <is>
+          <t>Pendo — HQ layoffs</t>
+        </is>
+      </c>
+      <c r="C202" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh</t>
+        </is>
+      </c>
+      <c r="D202" s="6" t="inlineStr">
+        <is>
+          <t>NC (Wake)</t>
+        </is>
+      </c>
+      <c r="E202" s="6" t="inlineStr">
+        <is>
+          <t>~90 global (~30 at Raleigh HQ) (layoffs)</t>
+        </is>
+      </c>
+      <c r="F202" s="6" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G202" s="6" t="inlineStr">
+        <is>
+          <t>Negative signal: tech-sector layoff.</t>
+        </is>
+      </c>
+      <c r="H202" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/04/raleigh-tech-unicorn-pendo-axes-90-jobs-in-latest-layoff-shock/</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B203" s="6" t="inlineStr">
+        <is>
+          <t>Wells Fargo — Raleigh corporate office layoffs</t>
+        </is>
+      </c>
+      <c r="C203" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh</t>
+        </is>
+      </c>
+      <c r="D203" s="6" t="inlineStr">
+        <is>
+          <t>NC (Wake)</t>
+        </is>
+      </c>
+      <c r="E203" s="6" t="inlineStr">
+        <is>
+          <t>~100-112 (layoffs)</t>
+        </is>
+      </c>
+      <c r="F203" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="G203" s="6" t="inlineStr">
+        <is>
+          <t>Negative signal: corporate-office layoff, announced Feb. 2026, effective in-window.</t>
+        </is>
+      </c>
+      <c r="H203" s="6" t="inlineStr">
+        <is>
+          <t>https://spectrumlocalnews.com/nc/charlotte/news/2026/02/06/raleigh-wells-fargo-layoffs-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B204" s="6" t="inlineStr">
+        <is>
+          <t>FedEx — Durham &amp; North Raleigh shipping-center closures</t>
+        </is>
+      </c>
+      <c r="C204" s="6" t="inlineStr">
+        <is>
+          <t>Durham / Raleigh</t>
+        </is>
+      </c>
+      <c r="D204" s="6" t="inlineStr">
+        <is>
+          <t>NC (Durham/Wake)</t>
+        </is>
+      </c>
+      <c r="E204" s="6" t="inlineStr">
+        <is>
+          <t>123 + 218 (layoffs)</t>
+        </is>
+      </c>
+      <c r="F204" s="6" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="G204" s="6" t="inlineStr">
+        <is>
+          <t>Negative signal: part of FedEx's nationwide facility-reduction ('Network 2.0') restructuring.</t>
+        </is>
+      </c>
+      <c r="H204" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B205" s="6" t="inlineStr">
+        <is>
+          <t>Xerox — Cary incentive grant terminated</t>
+        </is>
+      </c>
+      <c r="C205" s="6" t="inlineStr">
+        <is>
+          <t>Cary</t>
+        </is>
+      </c>
+      <c r="D205" s="6" t="inlineStr">
+        <is>
+          <t>NC (Wake)</t>
+        </is>
+      </c>
+      <c r="E205" s="6" t="inlineStr">
+        <is>
+          <t>600 (incentive terminated; original 2019 pledge)</t>
+        </is>
+      </c>
+      <c r="F205" s="6" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="G205" s="6" t="inlineStr">
+        <is>
+          <t>Incentive terminated after Xerox said it no longer envisioned meeting hiring targets — withdrawn deal, not an expansion.</t>
+        </is>
+      </c>
+      <c r="H205" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/north-carolina-terminates-incentives-six-companies-1500-jobs-feb-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B206" s="6" t="inlineStr">
+        <is>
+          <t>PennyMac Financial Services — Cary incentive grant terminated</t>
+        </is>
+      </c>
+      <c r="C206" s="6" t="inlineStr">
+        <is>
+          <t>Cary</t>
+        </is>
+      </c>
+      <c r="D206" s="6" t="inlineStr">
+        <is>
+          <t>NC (Wake)</t>
+        </is>
+      </c>
+      <c r="E206" s="6" t="inlineStr">
+        <is>
+          <t>322 (incentive terminated; original 2021 pledge)</t>
+        </is>
+      </c>
+      <c r="F206" s="6" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="G206" s="6" t="inlineStr">
+        <is>
+          <t>Incentive terminated; company cited higher interest rates — withdrawn deal.</t>
+        </is>
+      </c>
+      <c r="H206" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wral.com/news/local/north-carolina-terminates-incentives-six-companies-1500-jobs-feb-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B207" s="6" t="inlineStr">
+        <is>
+          <t>Clorox — reported Durham jobs-deal exit</t>
+        </is>
+      </c>
+      <c r="C207" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="D207" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E207" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="F207" s="6" t="inlineStr">
+        <is>
+          <t>2026 (unconfirmed)</t>
+        </is>
+      </c>
+      <c r="G207" s="6" t="inlineStr">
+        <is>
+          <t>Reported exit from a Durham incentive deal as company shifts away from vitamins/supplements; date/job count could not be independently verified this cycle — flagged for follow-up, not logged as a confirmed event.</t>
+        </is>
+      </c>
+      <c r="H207" s="6" t="inlineStr">
+        <is>
+          <t>https://www.aol.com/clorox-exits-durham-jobs-deal-210325952.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B208" s="6" t="inlineStr">
+        <is>
+          <t>Google Cloud Hub — Durham</t>
+        </is>
+      </c>
+      <c r="C208" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="D208" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E208" s="6" t="inlineStr">
+        <is>
+          <t>1,000+</t>
+        </is>
+      </c>
+      <c r="F208" s="6" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="G208" s="6" t="inlineStr">
+        <is>
+          <t>Recycled old news — original announcement from March 2021, far outside the window.</t>
+        </is>
+      </c>
+      <c r="H208" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B209" s="6" t="inlineStr">
+        <is>
+          <t>Novo Nordisk — Clayton expansion</t>
+        </is>
+      </c>
+      <c r="C209" s="6" t="inlineStr">
+        <is>
+          <t>Clayton</t>
+        </is>
+      </c>
+      <c r="D209" s="6" t="inlineStr">
+        <is>
+          <t>NC (Johnston)</t>
+        </is>
+      </c>
+      <c r="E209" s="6" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="F209" s="6" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="G209" s="6" t="inlineStr">
+        <is>
+          <t>Recycled old news (2024 announcement); no new 2026 milestone confirmed this cycle.</t>
+        </is>
+      </c>
+      <c r="H209" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B210" s="6" t="inlineStr">
+        <is>
+          <t>LabConnect — new Raleigh HQ</t>
+        </is>
+      </c>
+      <c r="C210" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh</t>
+        </is>
+      </c>
+      <c r="D210" s="6" t="inlineStr">
+        <is>
+          <t>NC (Wake)</t>
+        </is>
+      </c>
+      <c r="E210" s="6" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="F210" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="G210" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window announcement and sub-500 jobs regardless.</t>
+        </is>
+      </c>
+      <c r="H210" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="inlineStr">
+        <is>
+          <t>Eli Lilly — RTP expansion</t>
+        </is>
+      </c>
+      <c r="C211" s="6" t="inlineStr">
+        <is>
+          <t>RTP</t>
+        </is>
+      </c>
+      <c r="D211" s="6" t="inlineStr">
+        <is>
+          <t>NC (Durham/Wake)</t>
+        </is>
+      </c>
+      <c r="E211" s="6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F211" s="6" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="G211" s="6" t="inlineStr">
+        <is>
+          <t>Recycled old news (pre-window) and sub-500 jobs regardless.</t>
+        </is>
+      </c>
+      <c r="H211" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
+        <is>
+          <t>BuildOps — Raleigh office</t>
+        </is>
+      </c>
+      <c r="C212" s="6" t="inlineStr">
+        <is>
+          <t>Raleigh</t>
+        </is>
+      </c>
+      <c r="D212" s="6" t="inlineStr">
+        <is>
+          <t>NC (Wake)</t>
+        </is>
+      </c>
+      <c r="E212" s="6" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="F212" s="6" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="G212" s="6" t="inlineStr">
+        <is>
+          <t>Would clear the $100k wage bar ($110,997 avg stated) but announcement pre-dates the window and job count is sub-500.</t>
+        </is>
+      </c>
+      <c r="H212" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B213" s="6" t="inlineStr">
+        <is>
+          <t>New Hill Digital Campus (Natelli Holdings) — data-center proposal withdrawn</t>
+        </is>
+      </c>
+      <c r="C213" s="6" t="inlineStr">
+        <is>
+          <t>Western Wake Co.</t>
+        </is>
+      </c>
+      <c r="D213" s="6" t="inlineStr">
+        <is>
+          <t>NC (Wake)</t>
+        </is>
+      </c>
+      <c r="E213" s="6" t="inlineStr">
+        <is>
+          <t>~100 (projected; project withdrawn)</t>
+        </is>
+      </c>
+      <c r="F213" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G213" s="6" t="inlineStr">
+        <is>
+          <t>Developer withdrew its annexation/rezoning applications after community opposition — dead project.</t>
+        </is>
+      </c>
+      <c r="H213" s="6" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/residents-rally-against-250mw-data-center-proposal-in-wake-county-north-carolina/</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B214" s="6" t="inlineStr">
+        <is>
+          <t>VinFast — Chatham County EV megasite (see Watch tier for AT-RISK tracking)</t>
+        </is>
+      </c>
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t>Moncure</t>
+        </is>
+      </c>
+      <c r="D214" s="6" t="inlineStr">
+        <is>
+          <t>NC (Chatham)</t>
+        </is>
+      </c>
+      <c r="E214" s="6" t="inlineStr">
+        <is>
+          <t>Up to 7,500 (original)</t>
+        </is>
+      </c>
+      <c r="F214" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G214" s="6" t="inlineStr">
+        <is>
+          <t>Added to Watch tier instead (not excluded) given project scale, but logged here for cross-reference: incentive agreement terminated by Chatham Co. 7/31/26 and NC sued VinFast 5/21/26 to regain site control — currently a negative/troubled signal.</t>
+        </is>
+      </c>
+      <c r="H214" s="6" t="inlineStr">
+        <is>
+          <t>https://chathamjournal.com/2026/07/31/chatham-county-to-terminate-400m-vinfast-agreement/amp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B215" s="6" t="inlineStr">
+        <is>
+          <t>Environmental Air Systems (EAS), LLC — Asheboro sub-assembly facility</t>
+        </is>
+      </c>
+      <c r="C215" s="6" t="inlineStr">
+        <is>
+          <t>Asheboro</t>
+        </is>
+      </c>
+      <c r="D215" s="6" t="inlineStr">
+        <is>
+          <t>NC (Randolph)</t>
+        </is>
+      </c>
+      <c r="E215" s="6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="F215" s="6" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="G215" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window announcement (11/25/25, ~4.5 months before window open); avg wage $55,133, also sub-$100k.</t>
+        </is>
+      </c>
+      <c r="H215" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.nc.gov/news/press-releases/2025/11/25/environmental-air-systems-expand-randolph-county-adding-300-jobs-and-20-million-investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B216" s="6" t="inlineStr">
+        <is>
+          <t>First Solar, Inc. — Cherokee Co. (Gaffney) facility</t>
+        </is>
+      </c>
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t>Gaffney</t>
+        </is>
+      </c>
+      <c r="D216" s="6" t="inlineStr">
+        <is>
+          <t>SC (Cherokee)</t>
+        </is>
+      </c>
+      <c r="E216" s="6" t="inlineStr">
+        <is>
+          <t>600+</t>
+        </is>
+      </c>
+      <c r="F216" s="6" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="G216" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window announcement; avg wage $74,000 also sub-$100k. Operations slated H2 2026 — worth a Watch-tier recheck once an operational milestone is confirmed.</t>
+        </is>
+      </c>
+      <c r="H216" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.sc.gov/news/2025-11/first-solar-inc-grows-south-carolina-footprint-new-cherokee-county-facility</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="inlineStr">
+        <is>
+          <t>Hoffman &amp; Hoffman Inc.</t>
+        </is>
+      </c>
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>Guilford Co.</t>
+        </is>
+      </c>
+      <c r="D217" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E217" s="6" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="F217" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G217" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H217" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B218" s="6" t="inlineStr">
+        <is>
+          <t>Alamance Foods, Inc.</t>
+        </is>
+      </c>
+      <c r="C218" s="6" t="inlineStr">
+        <is>
+          <t>Alamance Co.</t>
+        </is>
+      </c>
+      <c r="D218" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E218" s="6" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="F218" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G218" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H218" s="6" t="inlineStr">
+        <is>
+          <t>https://burlingtonnc.gov/2477/Alamance-Foods-Inc-approved-for-42-milli</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B219" s="6" t="inlineStr">
+        <is>
+          <t>American Woodmark — Hamlet plant expansion</t>
+        </is>
+      </c>
+      <c r="C219" s="6" t="inlineStr">
+        <is>
+          <t>Richmond Co.</t>
+        </is>
+      </c>
+      <c r="D219" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E219" s="6" t="inlineStr">
+        <is>
+          <t>~130</t>
+        </is>
+      </c>
+      <c r="F219" s="6" t="inlineStr">
+        <is>
+          <t>2022-10 (recycled)</t>
+        </is>
+      </c>
+      <c r="G219" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch floor and recycled 2022-era news resurfacing under 2026 search dating.</t>
+        </is>
+      </c>
+      <c r="H219" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B220" s="6" t="inlineStr">
+        <is>
+          <t>GMAX Industries / Excel Interior Door / Tex-Tech Industries</t>
+        </is>
+      </c>
+      <c r="C220" s="6" t="inlineStr">
+        <is>
+          <t>Forsyth Co.</t>
+        </is>
+      </c>
+      <c r="D220" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E220" s="6" t="inlineStr">
+        <is>
+          <t>36 / 37 / 49</t>
+        </is>
+      </c>
+      <c r="F220" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G220" s="6" t="inlineStr">
+        <is>
+          <t>All below the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H220" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B221" s="6" t="inlineStr">
+        <is>
+          <t>Unnamed Hamlet economic-development concept</t>
+        </is>
+      </c>
+      <c r="C221" s="6" t="inlineStr">
+        <is>
+          <t>Hamlet</t>
+        </is>
+      </c>
+      <c r="D221" s="6" t="inlineStr">
+        <is>
+          <t>NC (Richmond)</t>
+        </is>
+      </c>
+      <c r="E221" s="6" t="inlineStr">
+        <is>
+          <t>up to 1,000 (speculative)</t>
+        </is>
+      </c>
+      <c r="F221" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G221" s="6" t="inlineStr">
+        <is>
+          <t>Speculative — no confirmed company name; city manager described the concept as tentative, dependent on a land sale and buyer financing.</t>
+        </is>
+      </c>
+      <c r="H221" s="6" t="inlineStr">
+        <is>
+          <t>https://richmondobserver.com/stories/terziu-teases-potential-for-up-to-1000-jobs-with-proposed-economic-development-project-in-hamlet,84265</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B222" s="6" t="inlineStr">
+        <is>
+          <t>Toyota Battery Mfg NC — Randolph Co. expansion</t>
+        </is>
+      </c>
+      <c r="C222" s="6" t="inlineStr">
+        <is>
+          <t>Randolph Co.</t>
+        </is>
+      </c>
+      <c r="D222" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E222" s="6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="F222" s="6" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="G222" s="6" t="inlineStr">
+        <is>
+          <t>Recycled old news — original announcement from Oct. 2023; grand-opening celebration (Nov. 2025) also pre-window.</t>
+        </is>
+      </c>
+      <c r="H222" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B223" s="6" t="inlineStr">
+        <is>
+          <t>Publix distribution center</t>
+        </is>
+      </c>
+      <c r="C223" s="6" t="inlineStr">
+        <is>
+          <t>Guilford Co.</t>
+        </is>
+      </c>
+      <c r="D223" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E223" s="6" t="inlineStr">
+        <is>
+          <t>up to 1,000 (historical)</t>
+        </is>
+      </c>
+      <c r="F223" s="6" t="inlineStr">
+        <is>
+          <t>2021-era</t>
+        </is>
+      </c>
+      <c r="G223" s="6" t="inlineStr">
+        <is>
+          <t>Recycled old news — long-standing, already-built-out distribution center project.</t>
+        </is>
+      </c>
+      <c r="H223" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B224" s="6" t="inlineStr">
+        <is>
+          <t>Keurig Dr Pepper — Spartanburg Co. expansion</t>
+        </is>
+      </c>
+      <c r="C224" s="6" t="inlineStr">
+        <is>
+          <t>Moore/Tyger River</t>
+        </is>
+      </c>
+      <c r="D224" s="6" t="inlineStr">
+        <is>
+          <t>SC (Spartanburg)</t>
+        </is>
+      </c>
+      <c r="E224" s="6" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="F224" s="6" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="G224" s="6" t="inlineStr">
+        <is>
+          <t>Recycled old news; no new 2026 development found.</t>
+        </is>
+      </c>
+      <c r="H224" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B225" s="6" t="inlineStr">
+        <is>
+          <t>AFL — Duncan fiber-optic expansion</t>
+        </is>
+      </c>
+      <c r="C225" s="6" t="inlineStr">
+        <is>
+          <t>Duncan</t>
+        </is>
+      </c>
+      <c r="D225" s="6" t="inlineStr">
+        <is>
+          <t>SC (Spartanburg)</t>
+        </is>
+      </c>
+      <c r="E225" s="6" t="inlineStr">
+        <is>
+          <t>150+</t>
+        </is>
+      </c>
+      <c r="F225" s="6" t="inlineStr">
+        <is>
+          <t>2024-era</t>
+        </is>
+      </c>
+      <c r="G225" s="6" t="inlineStr">
+        <is>
+          <t>Sub-200 jobs and recycled old news.</t>
+        </is>
+      </c>
+      <c r="H225" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B226" s="6" t="inlineStr">
+        <is>
+          <t>BMW Manufacturing — Greer press shop &amp; EV expansion</t>
+        </is>
+      </c>
+      <c r="C226" s="6" t="inlineStr">
+        <is>
+          <t>Greer</t>
+        </is>
+      </c>
+      <c r="D226" s="6" t="inlineStr">
+        <is>
+          <t>SC (Spartanburg)</t>
+        </is>
+      </c>
+      <c r="E226" s="6" t="inlineStr">
+        <is>
+          <t>200 / 800 (various)</t>
+        </is>
+      </c>
+      <c r="F226" s="6" t="inlineStr">
+        <is>
+          <t>2022-2024</t>
+        </is>
+      </c>
+      <c r="G226" s="6" t="inlineStr">
+        <is>
+          <t>All located announcements are recycled from 2022-2024; no new 2026-dated BMW announcement found.</t>
+        </is>
+      </c>
+      <c r="H226" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B227" s="6" t="inlineStr">
+        <is>
+          <t>Huwell US Inc.</t>
+        </is>
+      </c>
+      <c r="C227" s="6" t="inlineStr">
+        <is>
+          <t>Cherokee Co.</t>
+        </is>
+      </c>
+      <c r="D227" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E227" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F227" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G227" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H227" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B228" s="6" t="inlineStr">
+        <is>
+          <t>UFP Packaging</t>
+        </is>
+      </c>
+      <c r="C228" s="6" t="inlineStr">
+        <is>
+          <t>Cherokee Co.</t>
+        </is>
+      </c>
+      <c r="D228" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E228" s="6" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="F228" s="6" t="inlineStr">
+        <is>
+          <t>2026-07 (approx.)</t>
+        </is>
+      </c>
+      <c r="G228" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H228" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B229" s="6" t="inlineStr">
+        <is>
+          <t>Tyson Steel Building Products</t>
+        </is>
+      </c>
+      <c r="C229" s="6" t="inlineStr">
+        <is>
+          <t>Pickens Co.</t>
+        </is>
+      </c>
+      <c r="D229" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E229" s="6" t="inlineStr">
+        <is>
+          <t>~20</t>
+        </is>
+      </c>
+      <c r="F229" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G229" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H229" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B230" s="6" t="inlineStr">
+        <is>
+          <t>Peabody Engineering LLC</t>
+        </is>
+      </c>
+      <c r="C230" s="6" t="inlineStr">
+        <is>
+          <t>Pickens Co.</t>
+        </is>
+      </c>
+      <c r="D230" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E230" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F230" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G230" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H230" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B231" s="6" t="inlineStr">
+        <is>
+          <t>Coastal Precast Systems</t>
+        </is>
+      </c>
+      <c r="C231" s="6" t="inlineStr">
+        <is>
+          <t>Laurens Co.</t>
+        </is>
+      </c>
+      <c r="D231" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E231" s="6" t="inlineStr">
+        <is>
+          <t>~70</t>
+        </is>
+      </c>
+      <c r="F231" s="6" t="inlineStr">
+        <is>
+          <t>2026-02 (approx.)</t>
+        </is>
+      </c>
+      <c r="G231" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H231" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B232" s="6" t="inlineStr">
+        <is>
+          <t>Shamrock Technologies, Inc. — Connexial Center HQ relocation</t>
+        </is>
+      </c>
+      <c r="C232" s="6" t="inlineStr">
+        <is>
+          <t>Laurens Co.</t>
+        </is>
+      </c>
+      <c r="D232" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E232" s="6" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F232" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G232" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H232" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B233" s="6" t="inlineStr">
+        <is>
+          <t>Milo's Tea Company — Spartanburg Co. expansion</t>
+        </is>
+      </c>
+      <c r="C233" s="6" t="inlineStr">
+        <is>
+          <t>Spartanburg Co.</t>
+        </is>
+      </c>
+      <c r="D233" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E233" s="6" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F233" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G233" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H233" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B234" s="6" t="inlineStr">
+        <is>
+          <t>Okonite Company — Orangeburg plant</t>
+        </is>
+      </c>
+      <c r="C234" s="6" t="inlineStr">
+        <is>
+          <t>Orangeburg Co.</t>
+        </is>
+      </c>
+      <c r="D234" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E234" s="6" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="F234" s="6" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="G234" s="6" t="inlineStr">
+        <is>
+          <t>Capex-heavy ($400M) but jobs well below the 200-job Watch floor; avg wage ~$33/hr (~$68,640) also sub-$100k.</t>
+        </is>
+      </c>
+      <c r="H234" s="6" t="inlineStr">
+        <is>
+          <t>https://governor.sc.gov/news/2026-09/okonite-expands-orangeburg-county-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B235" s="6" t="inlineStr">
+        <is>
+          <t>IEB Americas / Maars North America / Modus21 — Charleston Co.</t>
+        </is>
+      </c>
+      <c r="C235" s="6" t="inlineStr">
+        <is>
+          <t>Charleston Co.</t>
+        </is>
+      </c>
+      <c r="D235" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E235" s="6" t="inlineStr">
+        <is>
+          <t>30 / 10+ / 80</t>
+        </is>
+      </c>
+      <c r="F235" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G235" s="6" t="inlineStr">
+        <is>
+          <t>All below the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H235" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B236" s="6" t="inlineStr">
+        <is>
+          <t>Translucent Solar — Dorchester Co.</t>
+        </is>
+      </c>
+      <c r="C236" s="6" t="inlineStr">
+        <is>
+          <t>Dorchester Co.</t>
+        </is>
+      </c>
+      <c r="D236" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E236" s="6" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="F236" s="6" t="inlineStr">
+        <is>
+          <t>2026 (approx.)</t>
+        </is>
+      </c>
+      <c r="G236" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H236" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B237" s="6" t="inlineStr">
+        <is>
+          <t>Xerxes — Richland/Blythewood</t>
+        </is>
+      </c>
+      <c r="C237" s="6" t="inlineStr">
+        <is>
+          <t>Richland Co.</t>
+        </is>
+      </c>
+      <c r="D237" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E237" s="6" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F237" s="6" t="inlineStr">
+        <is>
+          <t>2023-05 (recycled)</t>
+        </is>
+      </c>
+      <c r="G237" s="6" t="inlineStr">
+        <is>
+          <t>Recycled old news — facility now simply operating, not a new 2026 development.</t>
+        </is>
+      </c>
+      <c r="H237" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B238" s="6" t="inlineStr">
+        <is>
+          <t>Google data centers — Berkeley/Dorchester Co. ($9B)</t>
+        </is>
+      </c>
+      <c r="C238" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley/Dorchester</t>
+        </is>
+      </c>
+      <c r="D238" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E238" s="6" t="inlineStr">
+        <is>
+          <t>200 total (jobs)</t>
+        </is>
+      </c>
+      <c r="F238" s="6" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="G238" s="6" t="inlineStr">
+        <is>
+          <t>Pre-window announcement; job count (200) also below the 500-job qualifying bar.</t>
+        </is>
+      </c>
+      <c r="H238" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B239" s="6" t="inlineStr">
+        <is>
+          <t>Prysmian / ALLTAPE / Techo-Bloc — Lexington Co.</t>
+        </is>
+      </c>
+      <c r="C239" s="6" t="inlineStr">
+        <is>
+          <t>Lexington Co.</t>
+        </is>
+      </c>
+      <c r="D239" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E239" s="6" t="inlineStr">
+        <is>
+          <t>135 / 130 / 46</t>
+        </is>
+      </c>
+      <c r="F239" s="6" t="inlineStr">
+        <is>
+          <t>2026-08 / 2026 / 2026</t>
+        </is>
+      </c>
+      <c r="G239" s="6" t="inlineStr">
+        <is>
+          <t>All below the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H239" s="6" t="inlineStr">
+        <is>
+          <t>https://www.governor.sc.gov/news/2026-08/prysmian-expands-lexington-county-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B240" s="6" t="inlineStr">
+        <is>
+          <t>AVANTech — Richland Co.</t>
+        </is>
+      </c>
+      <c r="C240" s="6" t="inlineStr">
+        <is>
+          <t>Richland Co.</t>
+        </is>
+      </c>
+      <c r="D240" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E240" s="6" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F240" s="6" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="G240" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch floor and pre-window.</t>
+        </is>
+      </c>
+      <c r="H240" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B241" s="6" t="inlineStr">
+        <is>
+          <t>Stöbich Fire Protection Systems — Dorchester Co.</t>
+        </is>
+      </c>
+      <c r="C241" s="6" t="inlineStr">
+        <is>
+          <t>Dorchester Co.</t>
+        </is>
+      </c>
+      <c r="D241" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E241" s="6" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F241" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G241" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H241" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sccommerce.com/news/stobich-expands-dorchester-county-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B242" s="6" t="inlineStr">
+        <is>
+          <t>SCHNEEBERGER / Pratt Industries — York Co.</t>
+        </is>
+      </c>
+      <c r="C242" s="6" t="inlineStr">
+        <is>
+          <t>York Co.</t>
+        </is>
+      </c>
+      <c r="D242" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E242" s="6" t="inlineStr">
+        <is>
+          <t>101 / 116</t>
+        </is>
+      </c>
+      <c r="F242" s="6" t="inlineStr">
+        <is>
+          <t>2025-07 / 2025-10</t>
+        </is>
+      </c>
+      <c r="G242" s="6" t="inlineStr">
+        <is>
+          <t>Both pre-window and below the 200-job Watch floor.</t>
+        </is>
+      </c>
+      <c r="H242" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B243" s="6" t="inlineStr">
+        <is>
+          <t>Darden Restaurants/GMRI Inc. — Rock Hill distribution</t>
+        </is>
+      </c>
+      <c r="C243" s="6" t="inlineStr">
+        <is>
+          <t>Rock Hill</t>
+        </is>
+      </c>
+      <c r="D243" s="6" t="inlineStr">
+        <is>
+          <t>SC (York)</t>
+        </is>
+      </c>
+      <c r="E243" s="6" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F243" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="G243" s="6" t="inlineStr">
+        <is>
+          <t>Below the 200-job Watch floor; wage ~$58k also sub-$100k.</t>
+        </is>
+      </c>
+      <c r="H243" s="6" t="inlineStr">
+        <is>
+          <t>https://www.postandcourier.com/york-county/business/darden-restaurants-distribution-investment-rock-hill/article_dc4e5ed4-772a-4e3d-8446-693759d904d8.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B244" s="6" t="inlineStr">
+        <is>
+          <t>Textum OPCO / Healsee Capsules — Gaston Co.</t>
+        </is>
+      </c>
+      <c r="C244" s="6" t="inlineStr">
+        <is>
+          <t>Gaston Co.</t>
+        </is>
+      </c>
+      <c r="D244" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E244" s="6" t="inlineStr">
+        <is>
+          <t>34 / 100+</t>
+        </is>
+      </c>
+      <c r="F244" s="6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G244" s="6" t="inlineStr">
+        <is>
+          <t>Both below the 200-job Watch floor and/or sub-$100k wage.</t>
+        </is>
+      </c>
+      <c r="H244" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B245" s="6" t="inlineStr">
+        <is>
+          <t>IKO Industries 'Project Phoenix' — Chester Co.</t>
+        </is>
+      </c>
+      <c r="C245" s="6" t="inlineStr">
+        <is>
+          <t>Chester Co.</t>
+        </is>
+      </c>
+      <c r="D245" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E245" s="6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F245" s="6" t="inlineStr">
+        <is>
+          <t>2025 (recycled)</t>
+        </is>
+      </c>
+      <c r="G245" s="6" t="inlineStr">
+        <is>
+          <t>Core announcement predates the window (operations expected 2025); no in-window update found.</t>
+        </is>
+      </c>
+      <c r="H245" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B246" s="6" t="inlineStr">
+        <is>
+          <t>Albemarle Corp. 'Mega-Flex' lithium plant — Chester Co.</t>
+        </is>
+      </c>
+      <c r="C246" s="6" t="inlineStr">
+        <is>
+          <t>Chester Co.</t>
+        </is>
+      </c>
+      <c r="D246" s="6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E246" s="6" t="inlineStr">
+        <is>
+          <t>300+ (paused)</t>
+        </is>
+      </c>
+      <c r="F246" s="6" t="inlineStr">
+        <is>
+          <t>2024-03 (paused)</t>
+        </is>
+      </c>
+      <c r="G246" s="6" t="inlineStr">
+        <is>
+          <t>Project remains paused pending lithium-price stabilization; no 2025/2026 restart announcement found.</t>
+        </is>
+      </c>
+      <c r="H246" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B247" s="6" t="inlineStr">
+        <is>
+          <t>Pacific Life Insurance — removed from Watch</t>
+        </is>
+      </c>
+      <c r="C247" s="6" t="inlineStr">
+        <is>
+          <t>Charlotte / South End</t>
+        </is>
+      </c>
+      <c r="D247" s="6" t="inlineStr">
+        <is>
+          <t>NC (Mecklenburg)</t>
+        </is>
+      </c>
+      <c r="E247" s="6" t="inlineStr">
+        <is>
+          <t>301 (removed from Watch 2026-10-05)</t>
+        </is>
+      </c>
+      <c r="F247" s="6" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="G247" s="6" t="inlineStr">
+        <is>
+          <t>Removed from Watch after a second consecutive cycle with no in-window milestone found; base announcement remains pre-window (Oct. 2025). Will be reconsidered if a genuinely dated in-window milestone (lease execution, hiring start, occupancy) surfaces.</t>
+        </is>
+      </c>
+      <c r="H247" s="6" t="inlineStr">
+        <is>
+          <t>https://businessnc.com/pacific-life-adding-301-jobs-in-mecklenburg-average-pay-of-176k/</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B248" s="6" t="inlineStr">
+        <is>
+          <t>Aspida Financial Services — HQ expansion (rechecked; remains removed)</t>
+        </is>
+      </c>
+      <c r="C248" s="6" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="D248" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E248" s="6" t="inlineStr">
+        <is>
+          <t>1,000 (removed from Ranked 2026-09-21)</t>
+        </is>
+      </c>
+      <c r="F248" s="6" t="inlineStr">
+        <is>
+          <t>2025-11/12</t>
+        </is>
+      </c>
+      <c r="G248" s="6" t="inlineStr">
+        <is>
+          <t>Rechecked this cycle: the Imperial Tower renovation is still described only as 'slated to wrap by summer 2026' with no dated confirmation of completion found; Aspida is now targeting Q4 2026 for HQ move-in. Remains excluded/removed pending a hard, dated completion/move-in milestone.</t>
+        </is>
+      </c>
+      <c r="H248" s="6" t="inlineStr">
+        <is>
+          <t>https://hoodline.com/2026/03/imperial-tower-roars-back-as-law-firm-joins-10-million-durham-revival/</t>
         </is>
       </c>
     </row>
@@ -64065,7 +71251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D115"/>
+  <dimension ref="A1:D125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -66301,6 +73487,206 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>SMBC Group (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; eleventh consecutive cycle without a confirmed physical move-in — October 2026 move-in target and sublease reconfirmed but not yet realized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>Octapharma (Rock Hill)</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; fifth consecutive cycle with no fresher dated milestone despite a dedicated recheck; full local-approval chain independently reconfirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>AbbVie (Durham)</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new groundbreaking or hiring milestone found this cycle beyond the already-tracked Sept. 17 council incentive item.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>Capital Group (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>Raised 81-&gt;86: the East Coast ops hub officially opened Sept. 29, 2026 and the company raised its stated Charlotte job target from 600 to up to 1,000 (+67%), materially improving capital certainty and job-count scale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — EV plant (Blythewood)</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>Held flat; the Shives lawsuit and the AutoForecast/Scout Terra-delay dispute both remain open with no ruling or resolution this cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>Genentech (Holly Springs)</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle beyond the already-tracked Aug. 18 topping-out ceremony.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>JetZero (Greensboro)</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>Held flat; a new $100M lender loan (Sept. 2026) is a modest positive financing signal but does not change the stated wage, job count, or hiring-ramp timeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>Scout Motors — Global HQ (Charlotte)</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; litigation footprint (~6-7 states) reconfirmed but not materially expanded this cycle; no permit/construction progress found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>Citigroup (Charlotte / Ballantyne)</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no headcount-progress update found dated after April 2026 despite a dedicated recheck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>Novartis (Durham/Morrisville)</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>Unchanged; no new milestone this cycle.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
